--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:BC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -696,84 +766,98 @@
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>24.69458218549128</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>184.834435261708</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.216528925619834</v>
-      </c>
-      <c r="S2" t="n">
-        <v>79.80716253443525</v>
-      </c>
-      <c r="T2" t="n">
-        <v>29811152.43342516</v>
-      </c>
-      <c r="U2" t="n">
-        <v>84.48622589531681</v>
-      </c>
-      <c r="V2" t="n">
-        <v>27.02857142857143</v>
-      </c>
-      <c r="W2" t="n">
-        <v>184.0389610389611</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.54025974025974</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>77.08441558441557</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12791168.83116883</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>79.01948051948052</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>24.19578007631368</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>184.1286518488099</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>1.814212423500961</v>
+        <v>24.8304152637486</v>
       </c>
       <c r="AE2" t="n">
-        <v>74.94865010922322</v>
+        <v>184.7519640852974</v>
       </c>
       <c r="AF2" t="n">
-        <v>18114850.84826241</v>
+        <v>2.205387205387205</v>
       </c>
       <c r="AG2" t="n">
-        <v>81.41362381579773</v>
+        <v>79.83468013468013</v>
       </c>
       <c r="AH2" t="n">
-        <v>27.850611983924</v>
+        <v>29310575.19640853</v>
       </c>
       <c r="AI2" t="n">
-        <v>181.5837078309584</v>
+        <v>84.34489337822671</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.286563755937158</v>
+        <v>26.98787878787879</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.9262939958592</v>
+        <v>183.8787878787879</v>
       </c>
       <c r="AL2" t="n">
-        <v>7130381.804895871</v>
+        <v>1.539393939393939</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.38934965290466</v>
-      </c>
-      <c r="AN2" t="inlineStr">
+        <v>77.06818181818181</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12800303.03030303</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>78.9621212121212</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>24.03719336219336</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>184.0678691678692</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.776952060285394</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>74.70817299983966</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17920840.24771525</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>81.42019400352734</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>27.909047314578</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>181.4587702472294</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.271824381926684</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>74.93484299516908</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7066695.439045183</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>76.3639634839443</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -845,84 +929,98 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>26.24242424242424</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>182.5909090909091</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>70.78787878787878</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2710606.060606061</v>
-      </c>
-      <c r="U3" t="n">
-        <v>74.42424242424242</v>
-      </c>
-      <c r="V3" t="n">
-        <v>25.78282828282828</v>
-      </c>
-      <c r="W3" t="n">
-        <v>183.2818181818182</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.65050505050505</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>82.9939393939394</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47821515.15151516</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>85.71212121212119</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>25.39583333333333</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>183.5218253968254</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="AE3" t="n">
-        <v>69.22023809523809</v>
+        <v>182.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>2214087.301587302</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>73.36607142857143</v>
+        <v>70.63636363636363</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.45782723717506</v>
+        <v>2660000</v>
       </c>
       <c r="AI3" t="n">
-        <v>183.5836841499885</v>
+        <v>74.38181818181819</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.851340004600874</v>
+        <v>25.98051948051948</v>
       </c>
       <c r="AK3" t="n">
-        <v>79.82471244536461</v>
+        <v>183.0506493506494</v>
       </c>
       <c r="AL3" t="n">
-        <v>34862064.06717276</v>
+        <v>2.719480519480519</v>
       </c>
       <c r="AM3" t="n">
-        <v>84.58364964343225</v>
-      </c>
-      <c r="AN3" t="inlineStr">
+        <v>83.32987012987012</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49383506.49350649</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>85.83766233766232</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>25.54166666666666</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>183.7595238095238</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>69.40595238095237</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2243571.428571429</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>73.41428571428571</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>23.53863501922508</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>183.8861653356995</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.908865720201124</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>80.12463028689737</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>35981939.5149364</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>84.71469239869862</v>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -990,84 +1088,98 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>24.421875</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>183.015625</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.267361111111111</v>
-      </c>
-      <c r="S4" t="n">
-        <v>83.63715277777777</v>
-      </c>
-      <c r="T4" t="n">
-        <v>60272569.44444445</v>
-      </c>
-      <c r="U4" t="n">
-        <v>86.47048611111111</v>
-      </c>
-      <c r="V4" t="n">
-        <v>26.30208333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>182.9357638888889</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.440972222222222</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>76.57638888888889</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12390842.01388889</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>79.60243055555556</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>24.61337049173736</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>179.3531874472277</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>1.778762162759841</v>
+        <v>24.33928571428572</v>
       </c>
       <c r="AE4" t="n">
-        <v>81.167044198062</v>
+        <v>183.1607142857143</v>
       </c>
       <c r="AF4" t="n">
-        <v>37184547.38952997</v>
+        <v>2.257936507936507</v>
       </c>
       <c r="AG4" t="n">
-        <v>84.52763358932089</v>
+        <v>83.58531746031746</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.26935235816815</v>
+        <v>60343253.96825397</v>
       </c>
       <c r="AI4" t="n">
-        <v>180.845497265892</v>
+        <v>86.49007936507937</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.306012189564821</v>
+        <v>26.13095238095238</v>
       </c>
       <c r="AK4" t="n">
-        <v>72.07079915698337</v>
+        <v>182.890873015873</v>
       </c>
       <c r="AL4" t="n">
-        <v>8237183.156755526</v>
+        <v>1.432539682539682</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.62661483253589</v>
-      </c>
-      <c r="AN4" t="inlineStr">
+        <v>76.48015873015872</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12462748.01587302</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>79.63492063492063</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>24.68670913341413</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>179.2607856539745</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.782871043154104</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>81.19805051207085</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>36885911.30231997</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>84.50300981636674</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>24.39053803339518</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>180.6655307098916</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.304615434690623</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>72.18617648016145</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>8229149.171630374</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>78.60334928229665</v>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -1139,84 +1251,98 @@
           <t>AovF1Mia</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>27.35227272727273</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>183.6363636363637</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.59090909090909</v>
-      </c>
-      <c r="S5" t="n">
-        <v>76.625</v>
-      </c>
-      <c r="T5" t="n">
-        <v>11089488.63636364</v>
-      </c>
-      <c r="U5" t="n">
-        <v>79.11363636363636</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25.68845598845598</v>
-      </c>
-      <c r="W5" t="n">
-        <v>182.015873015873</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.367532467532467</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>75.45324675324675</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9313535.353535352</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>80.05122655122656</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>24.87299735111436</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>186.2774220557788</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>1.358703263914262</v>
+        <v>27.2987012987013</v>
       </c>
       <c r="AE5" t="n">
-        <v>72.80910973084886</v>
+        <v>183.5844155844156</v>
       </c>
       <c r="AF5" t="n">
-        <v>7070638.434721715</v>
+        <v>1.584415584415584</v>
       </c>
       <c r="AG5" t="n">
-        <v>77.10427627572768</v>
+        <v>76.63636363636364</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.25428023182958</v>
+        <v>11137012.98701299</v>
       </c>
       <c r="AI5" t="n">
-        <v>177.9513197055138</v>
+        <v>79.14285714285714</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.42405231829574</v>
+        <v>25.90925925925926</v>
       </c>
       <c r="AK5" t="n">
-        <v>73.02006187343358</v>
+        <v>182.1851851851852</v>
       </c>
       <c r="AL5" t="n">
-        <v>8502707.158521302</v>
+        <v>1.383333333333333</v>
       </c>
       <c r="AM5" t="n">
-        <v>80.41941181077695</v>
-      </c>
-      <c r="AN5" t="inlineStr">
+        <v>75.48333333333333</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>9138518.518518519</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>79.95370370370371</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>24.6834255441307</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>186.4408633018425</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.371851349235346</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>72.74374445430347</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6932634.401586722</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>77.27155383892689</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>23.25999373433584</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>177.9137531328321</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.392794486215539</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>73.05354010025061</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8297991.854636592</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>80.37728696741854</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -1284,84 +1410,98 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>26.20568181818182</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.510227272727273</v>
-      </c>
-      <c r="S6" t="n">
-        <v>77.78977272727272</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19209886.36363636</v>
-      </c>
-      <c r="U6" t="n">
-        <v>80.83295454545454</v>
-      </c>
-      <c r="V6" t="n">
-        <v>25.43966942148761</v>
-      </c>
-      <c r="W6" t="n">
-        <v>179.7247933884298</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>72.88760330578511</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4517603.305785124</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>76.13305785123967</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>26.30639880952381</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>181.6296130952381</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>1.423809523809524</v>
+        <v>26.16363636363636</v>
       </c>
       <c r="AE6" t="n">
-        <v>74.21532738095237</v>
+        <v>185.0428571428572</v>
       </c>
       <c r="AF6" t="n">
-        <v>13207377.23214286</v>
+        <v>1.511688311688312</v>
       </c>
       <c r="AG6" t="n">
-        <v>78.5248511904762</v>
+        <v>77.81688311688312</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.89665415573344</v>
+        <v>19297012.98701298</v>
       </c>
       <c r="AI6" t="n">
-        <v>179.1119086369726</v>
+        <v>80.86623376623376</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>25.58181818181818</v>
       </c>
       <c r="AK6" t="n">
-        <v>71.01268641844089</v>
+        <v>179.8858585858586</v>
       </c>
       <c r="AL6" t="n">
-        <v>3153749.986160472</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>75.56261334573354</v>
-      </c>
-      <c r="AN6" t="inlineStr">
+        <v>72.85151515151513</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4461515.151515152</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>76.05151515151516</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>26.38588435374149</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>181.6767006802721</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.45578231292517</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>74.61751700680271</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>14065216.83673469</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>78.84982993197279</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>24.99860214617248</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>179.0143939701485</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>71.03804990595273</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3125080.210828293</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>75.40307446650156</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>Aotm1TVI</t>
         </is>
@@ -1429,84 +1569,98 @@
           <t>WdKOwxDM</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>25.18571428571429</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>184.9428571428571</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.271428571428572</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>184.9666666666667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>75.14999999999999</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8915000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>24.14285714285714</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>181.1857142857143</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.171428571428571</v>
+      </c>
+      <c r="AM7" t="n">
         <v>75</v>
       </c>
-      <c r="T7" t="n">
-        <v>8711428.571428571</v>
-      </c>
-      <c r="U7" t="n">
-        <v>78.77142857142857</v>
-      </c>
-      <c r="V7" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.1625</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>75.03749999999999</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8823750</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>79.0625</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>24.74702750665483</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>185.5041555752736</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.438065661047027</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75.36302868973677</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>10884310.85477669</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>79.63207630878438</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23.84694446714613</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>183.1413033314099</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.321878302062799</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>74.41193191105233</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>11123256.5737879</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>79.2701219554981</v>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AN7" t="n">
+        <v>8875714.285714285</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>79.10000000000001</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.71211180124224</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>185.6461525189786</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.416873706004141</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>75.14817115251897</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10341116.28709455</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>79.55626293995859</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>23.88719119226638</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>183.180123061984</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.324382655773633</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>74.30928864368714</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11108566.51911163</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>79.13479776280529</v>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -1574,84 +1728,98 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>27.92207792207792</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>183.0324675324675</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.144155844155844</v>
-      </c>
-      <c r="S8" t="n">
-        <v>79.02337662337663</v>
-      </c>
-      <c r="T8" t="n">
-        <v>18771948.05194806</v>
-      </c>
-      <c r="U8" t="n">
-        <v>80.47532467532469</v>
-      </c>
-      <c r="V8" t="n">
-        <v>26.33766233766234</v>
-      </c>
-      <c r="W8" t="n">
-        <v>182.2727272727273</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.168831168831169</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>80.05194805194806</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>26540259.74025974</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>81.77922077922078</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>27.20553130343046</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>180.9712666884936</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>1.724284259158208</v>
+        <v>28.04545454545455</v>
       </c>
       <c r="AE8" t="n">
-        <v>73.62341482047364</v>
+        <v>183.0227272727273</v>
       </c>
       <c r="AF8" t="n">
-        <v>9321292.244170396</v>
+        <v>2.137878787878788</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.50941649387028</v>
+        <v>78.96666666666668</v>
       </c>
       <c r="AH8" t="n">
-        <v>23.50816993464052</v>
+        <v>18462727.27272728</v>
       </c>
       <c r="AI8" t="n">
-        <v>183.4534897292251</v>
+        <v>80.37272727272727</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.684932306255835</v>
+        <v>26.31818181818182</v>
       </c>
       <c r="AK8" t="n">
-        <v>73.68714985994397</v>
+        <v>182.2272727272727</v>
       </c>
       <c r="AL8" t="n">
-        <v>13882030.52054155</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AM8" t="n">
-        <v>79.36519607843138</v>
-      </c>
-      <c r="AN8" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>26416666.66666667</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>81.72727272727273</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>26.70407223495458</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>181.0974301841949</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.7021411594941</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>73.16779348102878</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9405198.094389269</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>77.61812876665819</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>23.60212418300654</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>183.5383306100218</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.669458061002179</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>73.51463779956428</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>13255655.97766885</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>79.18532135076252</v>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -1719,84 +1887,98 @@
           <t>2XrRecc3</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>25.93506493506494</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>184.2597402597403</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.064935064935065</v>
-      </c>
-      <c r="S9" t="n">
-        <v>76.66233766233766</v>
-      </c>
-      <c r="T9" t="n">
-        <v>11971428.57142857</v>
-      </c>
-      <c r="U9" t="n">
-        <v>79.1948051948052</v>
-      </c>
-      <c r="V9" t="n">
-        <v>25.53409090909091</v>
-      </c>
-      <c r="W9" t="n">
-        <v>183.5454545454546</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.306818181818182</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>76.57954545454545</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>14560227.27272728</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>80.13636363636363</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>24.93975871050174</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>180.8494348616639</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>1.083674873458155</v>
+        <v>25.96969696969697</v>
       </c>
       <c r="AE9" t="n">
-        <v>73.79248611725393</v>
+        <v>184.2424242424242</v>
       </c>
       <c r="AF9" t="n">
-        <v>7413969.851098334</v>
+        <v>1.060606060606061</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.66599587203302</v>
+        <v>76.75757575757575</v>
       </c>
       <c r="AH9" t="n">
-        <v>26.62493530020704</v>
+        <v>12177272.72727273</v>
       </c>
       <c r="AI9" t="n">
-        <v>183.8685947204969</v>
+        <v>79.24242424242424</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.154427622498275</v>
+        <v>25.37662337662337</v>
       </c>
       <c r="AK9" t="n">
-        <v>73.32619478951</v>
+        <v>183.5064935064935</v>
       </c>
       <c r="AL9" t="n">
-        <v>8194615.090148378</v>
+        <v>1.311688311688312</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.50185472739821</v>
-      </c>
-      <c r="AN9" t="inlineStr">
+        <v>76.59740259740259</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>14912987.01298702</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>80.27272727272727</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>24.93897775484463</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>181.2687851163857</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.088361426441922</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>73.71160417383328</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7006344.455911019</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>77.71218036922372</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>26.69557823129252</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>184.0051020408163</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.151643990929705</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>73.31689342403628</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7812634.637188209</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>76.39342403628117</v>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -1868,84 +2050,98 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>23.35151515151515</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>182.9464646464646</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.760606060606061</v>
-      </c>
-      <c r="S10" t="n">
-        <v>78.08787878787879</v>
-      </c>
-      <c r="T10" t="n">
-        <v>20875252.52525252</v>
-      </c>
-      <c r="U10" t="n">
-        <v>83.33232323232323</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26.57999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>182.2009090909091</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.155454545454545</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>85.45636363636365</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>73403636.36363636</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>87.62272727272727</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>23.1324725968077</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>183.2198013378369</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>1.641862701041105</v>
+        <v>23.37037037037037</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.50435965877296</v>
+        <v>182.9629629629629</v>
       </c>
       <c r="AF10" t="n">
-        <v>15074880.35739161</v>
+        <v>1.740740740740741</v>
       </c>
       <c r="AG10" t="n">
-        <v>81.27796518749969</v>
+        <v>77.95061728395062</v>
       </c>
       <c r="AH10" t="n">
-        <v>24.83455273413713</v>
+        <v>20227160.49382716</v>
       </c>
       <c r="AI10" t="n">
-        <v>178.5558899646815</v>
+        <v>83.22222222222223</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.306312162546178</v>
+        <v>26.76565656565656</v>
       </c>
       <c r="AK10" t="n">
-        <v>80.69758758575895</v>
+        <v>182.1929292929293</v>
       </c>
       <c r="AL10" t="n">
-        <v>45936698.53448626</v>
+        <v>3.192929292929293</v>
       </c>
       <c r="AM10" t="n">
-        <v>85.20007560995411</v>
-      </c>
-      <c r="AN10" t="inlineStr">
+        <v>85.67878787878789</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>73944444.44444445</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>87.66161616161617</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>23.29223676619019</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>182.991007538782</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.664198104948318</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>73.58580744704943</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>15699310.74591807</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>81.25842083206241</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24.73680462523173</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>178.4747983734557</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.287436794363478</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>80.52642006883269</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>45324903.13355616</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>85.15352316449929</v>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>zuJM7XDg</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -2017,84 +2213,98 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>26.44126984126984</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>182.8444444444444</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.431746031746032</v>
-      </c>
-      <c r="S11" t="n">
-        <v>75.93333333333332</v>
-      </c>
-      <c r="T11" t="n">
-        <v>9686507.936507937</v>
-      </c>
-      <c r="U11" t="n">
-        <v>78.16825396825395</v>
-      </c>
-      <c r="V11" t="n">
-        <v>24.83055555555556</v>
-      </c>
-      <c r="W11" t="n">
-        <v>184.8805555555555</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.084722222222222</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>81.71944444444445</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>39532638.8888889</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>85.09722222222223</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>25.9965957674936</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>180.8084482596867</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>1.436927881200327</v>
+        <v>26.54222222222222</v>
       </c>
       <c r="AE11" t="n">
-        <v>73.55940988835725</v>
+        <v>182.9355555555555</v>
       </c>
       <c r="AF11" t="n">
-        <v>5927105.196145444</v>
+        <v>1.437777777777778</v>
       </c>
       <c r="AG11" t="n">
-        <v>76.38052350126654</v>
+        <v>75.77777777777779</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.29887064474913</v>
+        <v>9330666.666666668</v>
       </c>
       <c r="AI11" t="n">
-        <v>181.461406656961</v>
+        <v>77.97999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.702131016880436</v>
+        <v>24.82222222222222</v>
       </c>
       <c r="AK11" t="n">
-        <v>78.17677465723131</v>
+        <v>185.0222222222222</v>
       </c>
       <c r="AL11" t="n">
-        <v>26755605.11073947</v>
+        <v>2.080952380952381</v>
       </c>
       <c r="AM11" t="n">
-        <v>81.91576904884761</v>
-      </c>
-      <c r="AN11" t="inlineStr">
+        <v>81.75873015873016</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>39775396.82539683</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>85.15873015873015</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>25.79523407449104</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>180.6265644056666</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.432751665259405</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>73.36212121212121</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5901368.3272352</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>76.56431184914156</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>24.29394740352281</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>181.2892266555745</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.69359191044839</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>78.2360417851351</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>26775963.66397436</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>81.92414421909113</v>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
         </is>
@@ -2103,11 +2313,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2117,34 +2327,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">wembley stadium
-  london </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90000</v>
+        <v>31876</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2153,97 +2363,111 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>fa community shield</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>24.69458218549128</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>184.834435261708</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.216528925619834</v>
-      </c>
-      <c r="S12" t="n">
-        <v>79.80716253443525</v>
-      </c>
-      <c r="T12" t="n">
-        <v>29811152.43342516</v>
-      </c>
-      <c r="U12" t="n">
-        <v>84.48622589531681</v>
-      </c>
-      <c r="V12" t="n">
-        <v>26.57999999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>182.2009090909091</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.155454545454545</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>85.45636363636365</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>73403636.36363636</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>87.62272727272727</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>24.19578007631368</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>184.1286518488099</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>1.814212423500961</v>
+        <v>25.90925925925926</v>
       </c>
       <c r="AE12" t="n">
-        <v>74.94865010922322</v>
+        <v>182.1851851851852</v>
       </c>
       <c r="AF12" t="n">
-        <v>18114850.84826241</v>
+        <v>1.383333333333333</v>
       </c>
       <c r="AG12" t="n">
-        <v>81.41362381579773</v>
+        <v>75.48333333333333</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.83455273413713</v>
+        <v>9138518.518518519</v>
       </c>
       <c r="AI12" t="n">
-        <v>178.5558899646815</v>
+        <v>79.95370370370371</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.306312162546178</v>
+        <v>24.8304152637486</v>
       </c>
       <c r="AK12" t="n">
-        <v>80.69758758575895</v>
+        <v>184.7519640852974</v>
       </c>
       <c r="AL12" t="n">
-        <v>45936698.53448626</v>
+        <v>2.205387205387205</v>
       </c>
       <c r="AM12" t="n">
-        <v>85.20007560995411</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
+        <v>79.83468013468013</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29310575.19640853</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>84.34489337822671</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>23.25999373433584</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>177.9137531328321</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.392794486215539</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>73.05354010025061</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8297991.854636592</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>80.37728696741854</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>24.03719336219336</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>184.0678691678692</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.776952060285394</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>74.70817299983966</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17920840.24771525</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>81.42019400352734</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -2252,45 +2476,45 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>17949</v>
+        <v>25486</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>20242025</v>
@@ -2302,103 +2526,158 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>24.73888888888889</v>
-      </c>
-      <c r="W13" t="n">
-        <v>184.2055555555556</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>69.98333333333333</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2580555.555555556</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>74.22777777777777</v>
-      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>25.37662337662337</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>183.5064935064935</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.311688311688312</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>76.59740259740259</v>
+      </c>
       <c r="AH13" t="n">
-        <v>24.04481209150327</v>
+        <v>14912987.01298702</v>
       </c>
       <c r="AI13" t="n">
-        <v>181.8084811702459</v>
+        <v>80.27272727272727</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>28.04545454545455</v>
       </c>
       <c r="AK13" t="n">
-        <v>68.86662581699346</v>
+        <v>183.0227272727273</v>
       </c>
       <c r="AL13" t="n">
-        <v>2298258.101851852</v>
+        <v>2.137878787878788</v>
       </c>
       <c r="AM13" t="n">
-        <v>73.98942382508558</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
+        <v>78.96666666666668</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18462727.27272728</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>80.37272727272727</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>26.69557823129252</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>184.0051020408163</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.151643990929705</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>73.31689342403628</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7812634.637188209</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>76.39342403628117</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>26.70407223495458</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>181.0974301841949</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.7021411594941</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>73.16779348102878</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>9405198.094389269</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>77.61812876665819</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>hUGEt9yf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
+          <t xml:space="preserve">craven cottage
   london </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9271</v>
+        <v>26600</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>20242025</v>
@@ -2410,11 +2689,15 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -2429,61 +2712,131 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>26.98787878787879</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>183.8787878787879</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.539393939393939</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>77.06818181818181</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>12800303.03030303</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>78.9621212121212</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>26.54222222222222</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>182.9355555555555</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.437777777777778</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75.77777777777779</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9330666.666666668</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>77.97999999999999</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>27.909047314578</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>181.4587702472294</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.271824381926684</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>74.93484299516908</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7066695.439045183</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>76.3639634839443</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>25.79523407449104</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>180.6265644056666</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.432751665259405</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>73.36212121212121</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5901368.3272352</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>76.56431184914156</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10841</v>
+        <v>55097</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>20242025</v>
@@ -2495,13 +2848,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>z3dmTMMO</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2510,92 +2867,139 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>25.25454545454545</v>
-      </c>
-      <c r="W15" t="n">
-        <v>180.4590909090909</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>70.07575757575758</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2272954.545454545</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>72.93939393939394</v>
-      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>26.76565656565656</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>182.1929292929293</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.192929292929293</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>85.67878787878789</v>
+      </c>
       <c r="AH15" t="n">
-        <v>22.77799635005517</v>
+        <v>73944444.44444445</v>
       </c>
       <c r="AI15" t="n">
-        <v>179.1810139207198</v>
+        <v>87.66161616161617</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="AK15" t="n">
-        <v>66.56869535693066</v>
+        <v>182.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>1690214.222052457</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
-        <v>74.46522790934556</v>
-      </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
+        <v>70.63636363636363</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>74.38181818181819</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>24.73680462523173</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>178.4747983734557</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.287436794363478</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>80.52642006883269</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>45324903.13355616</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>85.15352316449929</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>25.54166666666666</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>183.7595238095238</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>69.40595238095237</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2243571.428571429</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>73.41428571428571</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>lhUKMQZu</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scott g 
+  eng </t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6500</v>
+        <v>32384</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>20242025</v>
@@ -2607,7 +3011,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2626,56 +3030,131 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>25.58181818181818</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>179.8858585858586</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>72.85151515151513</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4461515.151515152</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>76.05151515151516</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>184.9666666666667</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75.14999999999999</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>8915000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>24.99860214617248</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>179.0143939701485</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>71.03804990595273</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3125080.210828293</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>75.40307446650156</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>24.71211180124224</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>185.6461525189786</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.416873706004141</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>75.14817115251897</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10341116.28709455</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>79.55626293995859</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28723</v>
+        <v>62850</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>20242025</v>
@@ -2687,11 +3166,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -2706,61 +3193,131 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>24.82222222222222</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>185.0222222222222</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.080952380952381</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>81.75873015873016</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>39775396.82539683</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>85.15873015873015</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27.2987012987013</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>183.5844155844156</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.584415584415584</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11137012.98701299</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>24.29394740352281</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>181.2892266555745</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.69359191044839</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>78.2360417851351</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>26775963.66397436</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>81.92414421909113</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>24.6834255441307</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>186.4408633018425</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.371851349235346</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>72.74374445430347</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6932634.401586722</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>77.27155383892689</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>27000</v>
+        <v>42789</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>20242025</v>
@@ -2772,135 +3329,154 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>23.49861111111111</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>181.262962962963</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>68.59027777777779</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2073657.407407407</v>
-      </c>
-      <c r="U18" t="n">
-        <v>74.28055555555555</v>
-      </c>
-      <c r="V18" t="n">
-        <v>23.99965277777778</v>
-      </c>
-      <c r="W18" t="n">
-        <v>182.6833333333333</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>71.40694444444443</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4308298.611111111</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>77.10590277777777</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>25.36234559214435</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>180.7385426578925</v>
-      </c>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>26.31818181818182</v>
       </c>
       <c r="AE18" t="n">
-        <v>66.56918108551235</v>
+        <v>182.2272727272727</v>
       </c>
       <c r="AF18" t="n">
-        <v>1526923.51143009</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AG18" t="n">
-        <v>72.26419245529154</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="n">
-        <v>24.06044051891092</v>
+        <v>26416666.66666667</v>
       </c>
       <c r="AI18" t="n">
-        <v>180.9409119389383</v>
+        <v>81.72727272727273</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>24.33928571428572</v>
       </c>
       <c r="AK18" t="n">
-        <v>68.7712847459558</v>
+        <v>183.1607142857143</v>
       </c>
       <c r="AL18" t="n">
-        <v>2796514.804411597</v>
+        <v>2.257936507936507</v>
       </c>
       <c r="AM18" t="n">
-        <v>74.75720408976989</v>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
+        <v>83.58531746031746</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>60343253.96825397</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>86.49007936507937</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>23.60212418300654</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>183.5383306100218</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.669458061002179</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>73.51463779956428</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>13255655.97766885</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>79.18532135076252</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>24.68670913341413</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>179.2607856539745</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.782871043154104</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>81.19805051207085</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>36885911.30231997</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>84.50300981636674</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5000</v>
+        <v>11307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>20242025</v>
@@ -2912,11 +3488,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -2931,56 +3515,131 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
+      <c r="AD19" t="n">
+        <v>24.14285714285714</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>181.1857142857143</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.171428571428571</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8875714.285714285</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>79.10000000000001</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>26.16363636363636</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>185.0428571428572</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.511688311688312</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>77.81688311688312</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>19297012.98701298</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>80.86623376623376</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>23.88719119226638</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>183.180123061984</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.324382655773633</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>74.30928864368714</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>11108566.51911163</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>79.13479776280529</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>26.38588435374149</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>181.6767006802721</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.45578231292517</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>74.61751700680271</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14065216.83673469</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>78.84982993197279</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>zuJM7XDg</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6912</v>
+        <v>31750</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>20242025</v>
@@ -2992,11 +3651,15 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -3011,61 +3674,131 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>26.13095238095238</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>182.890873015873</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.432539682539682</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>76.48015873015872</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>12462748.01587302</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>79.63492063492063</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>23.37037037037037</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>182.9629629629629</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.740740740740741</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>77.95061728395062</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>20227160.49382716</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>83.22222222222223</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>24.39053803339518</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>180.6655307098916</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.304615434690623</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>72.18617648016145</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8229149.171630374</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>78.60334928229665</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>23.29223676619019</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>182.991007538782</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.664198104948318</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>73.58580744704943</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>15699310.74591807</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>81.25842083206241</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>x6CvOHH9</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7937</v>
+        <v>61276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>20242025</v>
@@ -3077,10 +3810,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -3088,95 +3825,142 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>183.1166666666667</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>70.71666666666667</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1868750</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>72.05</v>
-      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
+      <c r="AD21" t="n">
+        <v>25.98051948051948</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>183.0506493506494</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.719480519480519</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>83.32987012987012</v>
+      </c>
       <c r="AH21" t="n">
-        <v>26.03125216697871</v>
+        <v>49383506.49350649</v>
       </c>
       <c r="AI21" t="n">
-        <v>180.8089751924277</v>
+        <v>85.83766233766232</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>25.96969696969697</v>
       </c>
       <c r="AK21" t="n">
-        <v>67.48658683517094</v>
+        <v>184.2424242424242</v>
       </c>
       <c r="AL21" t="n">
-        <v>1462638.415765204</v>
+        <v>1.060606060606061</v>
       </c>
       <c r="AM21" t="n">
-        <v>71.40343119409195</v>
-      </c>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
+        <v>76.75757575757575</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>12177272.72727273</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>79.24242424242424</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>23.53863501922508</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>183.8861653356995</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.908865720201124</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>80.12463028689737</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>35981939.5149364</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>84.71469239869862</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>24.93897775484463</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>181.2687851163857</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.088361426441922</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>73.71160417383328</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>7006344.455911019</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>77.71218036922372</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>x6CvOHH9</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">wembley stadium
+  london </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>33280</v>
+        <v>90000</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3185,102 +3969,176 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>fa community shield</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
       <c r="P22" t="n">
-        <v>26.33333333333333</v>
+        <v>22</v>
       </c>
       <c r="Q22" t="n">
-        <v>183.0863636363636</v>
+        <v>180</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>69.85909090909091</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2035454.545454546</v>
+        <v>73</v>
       </c>
       <c r="U22" t="n">
-        <v>72.12878787878788</v>
-      </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
+        <v>6500000</v>
+      </c>
+      <c r="V22" t="n">
+        <v>83</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>169</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>77</v>
+      </c>
       <c r="AB22" t="n">
-        <v>23.81686856028961</v>
+        <v>15000000</v>
       </c>
       <c r="AC22" t="n">
-        <v>182.7815719855194</v>
+        <v>82</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>26.76565656565656</v>
       </c>
       <c r="AE22" t="n">
-        <v>64.25543024227234</v>
+        <v>182.1929292929293</v>
       </c>
       <c r="AF22" t="n">
-        <v>1364388.923698134</v>
+        <v>3.192929292929293</v>
       </c>
       <c r="AG22" t="n">
-        <v>70.32477025898079</v>
-      </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr"/>
+        <v>85.67878787878789</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>73944444.44444445</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>87.66161616161617</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>24.8304152637486</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>184.7519640852974</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.205387205387205</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>79.83468013468013</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>29310575.19640853</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>84.34489337822671</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>24.73680462523173</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>178.4747983734557</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.287436794363478</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>80.52642006883269</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>45324903.13355616</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>85.15352316449929</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>24.03719336219336</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>184.0678691678692</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.776952060285394</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>74.70817299983966</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17920840.24771525</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>81.42019400352734</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>27111</v>
+        <v>17949</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3306,93 +4164,103 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>24.71212121212121</v>
-      </c>
-      <c r="W23" t="n">
-        <v>181.9242424242424</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>69.18181818181817</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2096666.666666667</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>73.87878787878789</v>
-      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
-        <v>26.47037037037038</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>179.0731481481481</v>
-      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="n">
-        <v>1</v>
+        <v>24.62666666666667</v>
       </c>
       <c r="AK23" t="n">
-        <v>67.92037037037038</v>
+        <v>184.2866666666667</v>
       </c>
       <c r="AL23" t="n">
-        <v>1508414.351851852</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>71.0763888888889</v>
-      </c>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
+        <v>69.97999999999999</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2589166.666666667</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>74.35333333333332</v>
+      </c>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="n">
+        <v>23.95377450980392</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>181.6146218487395</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>68.57328431372549</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2240687.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>73.94286414565826</v>
+      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">brisbane road
+  london </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10105</v>
+        <v>9271</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3445,34 +4313,53 @@
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6134</v>
+        <v>10841</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3498,7 +4385,11 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -3519,17 +4410,59 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
+      <c r="AJ25" t="n">
+        <v>25.25090909090909</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>180.46</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>70.05454545454546</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2271181.818181818</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>73</v>
+      </c>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="n">
+        <v>22.66086834733894</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>178.889943977591</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>66.50061624649859</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1707802.521008403</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>74.68554621848739</v>
+      </c>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -3538,21 +4471,21 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>33597</v>
+        <v>6500</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3605,39 +4538,48 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5327</v>
+        <v>28723</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3670,82 +4612,73 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="n">
-        <v>27.4625</v>
-      </c>
-      <c r="W27" t="n">
-        <v>185.3625</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.0375</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>71.32499999999999</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2388750</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>72.825</v>
-      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="n">
-        <v>28.03419384057971</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>184.3994565217391</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.080842391304348</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>70.72327898550725</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2269769.02173913</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>72.45063405797102</v>
-      </c>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9052</v>
+        <v>27000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3771,7 +4704,11 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -3786,23 +4723,93 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AD28" t="n">
+        <v>23.27833333333333</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>181.4555555555556</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>68.54833333333333</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2086388.888888889</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>74.43666666666665</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>23.94953703703704</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>182.4611111111111</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>71.30925925925926</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>4234398.148148148</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>77.05787037037037</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>25.56422647527911</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>180.4274276600593</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>66.56537024379129</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1523308.213716109</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>72.16408976987925</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>24.21392069188122</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>181.362882585251</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>68.85962966127441</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2841603.072548795</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>74.73043878635984</v>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -3811,21 +4818,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>24121</v>
+        <v>5000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3850,71 +4857,53 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>24.10888888888889</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>182.66</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>67.50888888888889</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1695611.111111111</v>
-      </c>
-      <c r="U29" t="n">
-        <v>73.64</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="n">
-        <v>24.10917022792023</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>182.8795227920228</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>66.19565527065527</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1400157.14031339</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>72.78003917378918</v>
-      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -3923,21 +4912,21 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10669</v>
+        <v>6912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3990,34 +4979,53 @@
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7798</v>
+        <v>7937</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4064,17 +5072,59 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
+      <c r="AJ31" t="n">
+        <v>27.775</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>183.075</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1883125</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="n">
+        <v>25.87747035573123</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>180.7192193675889</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>67.48399209486166</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1440606.472332016</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>71.62406126482213</v>
+      </c>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -4083,21 +5133,21 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27137</v>
+        <v>33280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4124,92 +5174,111 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
-        <v>26.26805555555556</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>182.5819444444444</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>72.20277777777778</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3249861.111111111</v>
-      </c>
-      <c r="U32" t="n">
-        <v>74.73194444444445</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="n">
-        <v>25.37563667151263</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>183.9485827471761</v>
-      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="n">
-        <v>1</v>
+        <v>26.23636363636364</v>
       </c>
       <c r="AE32" t="n">
-        <v>68.68581210988501</v>
+        <v>183.14</v>
       </c>
       <c r="AF32" t="n">
-        <v>2330055.449665424</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>73.41813349693786</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
+        <v>69.61272727272726</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2000727.272727273</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>72.11818181818182</v>
+      </c>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="n">
+        <v>23.96913116123642</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>183.0489974937344</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>63.85096073517127</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1251822.263993317</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>69.6452798663325</v>
+      </c>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12500</v>
+        <v>27111</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4235,7 +5304,11 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -4256,45 +5329,82 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AJ33" t="n">
+        <v>24.85454545454545</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>182</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>69.23636363636362</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2081818.181818182</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>73.70909090909092</v>
+      </c>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="n">
+        <v>26.38111111111111</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>179.0461111111111</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>67.81277777777778</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1509055.555555556</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>71.21666666666667</v>
+      </c>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>21944</v>
+        <v>10105</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -4320,98 +5430,75 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="n">
-        <v>25.21666666666667</v>
-      </c>
-      <c r="W34" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>69.78333333333333</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2562500</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>73.76666666666667</v>
-      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="n">
-        <v>25.18154761904762</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>179.014880952381</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>67.8938492063492</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1700659.722222222</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>73.625</v>
-      </c>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>23408</v>
+        <v>6134</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4437,98 +5524,52 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>26.75277777777778</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>184.5333333333333</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>69.76547619047618</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1856755.952380953</v>
-      </c>
-      <c r="U35" t="n">
-        <v>71.64325396825397</v>
-      </c>
-      <c r="V35" t="n">
-        <v>22.13148148148148</v>
-      </c>
-      <c r="W35" t="n">
-        <v>182.6263888888889</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>69.42777777777778</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3138009.259259259</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>77.55740740740741</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>23.70000091804603</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>181.826948323189</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>66.86725054394228</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1690302.794532118</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>73.30192697861871</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>22.48348112128146</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>181.5315500628169</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>66.44548531655225</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1820668.333838112</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>73.84311201597343</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -4537,21 +5578,21 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12021</v>
+        <v>33597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -4578,88 +5619,79 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>181.4666666666667</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>66.85000000000001</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1078333.333333333</v>
-      </c>
-      <c r="U36" t="n">
-        <v>69.3</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="n">
-        <v>27.19016403917719</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>182.4221504007688</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>65.50509753404491</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>896852.7187359425</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>68.52780154786733</v>
-      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5108</v>
+        <v>5327</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4706,17 +5738,59 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
+      <c r="AJ37" t="n">
+        <v>27.44285714285714</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>185.4142857142857</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.042857142857143</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2377142.857142857</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>72.84285714285714</v>
+      </c>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="n">
+        <v>27.976966873706</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>184.3819875776397</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.073757763975155</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>70.78933747412009</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2305822.98136646</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>72.48395445134575</v>
+      </c>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -4725,21 +5799,21 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9877</v>
+        <v>9052</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4792,11 +5866,25 @@
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -4805,21 +5893,21 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>21088</v>
+        <v>24121</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4846,69 +5934,83 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>24.625</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>180.0625</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>69.02083333333333</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1941666.666666667</v>
-      </c>
-      <c r="U39" t="n">
-        <v>73.95833333333333</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="n">
-        <v>24.19036561993218</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>180.210887810733</v>
-      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>1</v>
+        <v>24.56666666666667</v>
       </c>
       <c r="AE39" t="n">
-        <v>67.20232994845998</v>
+        <v>182.7666666666667</v>
       </c>
       <c r="AF39" t="n">
-        <v>1572038.021747774</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="n">
-        <v>72.99934811776917</v>
-      </c>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
+        <v>67.66666666666667</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1674166.666666667</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>73.5</v>
+      </c>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
+      <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="n">
+        <v>23.75438034188034</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>182.5213675213675</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>65.9684829059829</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1425261.752136752</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>72.93568376068376</v>
+      </c>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -4917,21 +6019,21 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>16587</v>
+        <v>10669</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -4984,11 +6086,25 @@
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -4997,21 +6113,21 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11300</v>
+        <v>7798</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5064,11 +6180,25 @@
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -5077,21 +6207,21 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>22200</v>
+        <v>27137</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5118,69 +6248,83 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>SlybbadF</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>24.19393939393939</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>183.3954545454546</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>69.81818181818183</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2493939.393939394</v>
-      </c>
-      <c r="U42" t="n">
-        <v>74.10454545454546</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="n">
-        <v>23.89619277662755</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>182.3442172762825</v>
-      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="n">
-        <v>1</v>
+        <v>26.24074074074074</v>
       </c>
       <c r="AE42" t="n">
-        <v>68.31554807913504</v>
+        <v>182.6092592592593</v>
       </c>
       <c r="AF42" t="n">
-        <v>2277340.479066023</v>
+        <v>1</v>
       </c>
       <c r="AG42" t="n">
-        <v>74.16471129514608</v>
-      </c>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
+        <v>72.28703703703704</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>3291481.481481481</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>74.7925925925926</v>
+      </c>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="n">
+        <v>25.66401416145662</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>184.1604352595402</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>69.05797356948251</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2385473.092551098</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>73.27669900432049</v>
+      </c>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -5189,21 +6333,21 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>25133</v>
+        <v>12500</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5256,34 +6400,53 @@
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
+        <v>45517.65625</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>32050</v>
+        <v>21944</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>IgO7K1ZA</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5309,70 +6472,88 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>23.98686868686869</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>182.3089786756453</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>71.58686868686868</v>
-      </c>
-      <c r="T44" t="n">
-        <v>4096994.94949495</v>
-      </c>
-      <c r="U44" t="n">
-        <v>77.17519640852976</v>
-      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="n">
-        <v>23.14731254775115</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>179.8548383065927</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>69.22183485779978</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>2913259.64260723</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>76.40355491649352</v>
-      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr"/>
+      <c r="AJ44" t="n">
+        <v>25.225</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2516250</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>73.80000000000001</v>
+      </c>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="n">
+        <v>25.91517857142857</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>179.2291666666667</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>68.39732142857143</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1705825.892857143</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>72.99702380952381</v>
+      </c>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5382,21 +6563,21 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>25586</v>
+        <v>23408</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -5421,90 +6602,104 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>24.14935064935065</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>179.7064935064935</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.092207792207792</v>
-      </c>
-      <c r="S45" t="n">
-        <v>69.84155844155845</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3043311.688311689</v>
-      </c>
-      <c r="U45" t="n">
-        <v>75.03246753246754</v>
-      </c>
-      <c r="V45" t="n">
-        <v>27.11212121212121</v>
-      </c>
-      <c r="W45" t="n">
-        <v>182.8666666666667</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>67.71818181818183</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1266969.696969697</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>70.53939393939393</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>25.68600599660154</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>180.6379499625938</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="n">
-        <v>1.021757398611619</v>
+        <v>26.40388888888889</v>
       </c>
       <c r="AE45" t="n">
-        <v>70.42952543336175</v>
+        <v>184.2966666666667</v>
       </c>
       <c r="AF45" t="n">
-        <v>3078919.763557597</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="n">
-        <v>74.57694092129604</v>
+        <v>69.84666666666666</v>
       </c>
       <c r="AH45" t="n">
-        <v>25.6219806763285</v>
+        <v>1923208.333333333</v>
       </c>
       <c r="AI45" t="n">
-        <v>184.8303140096618</v>
+        <v>71.90055555555554</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.006944444444444</v>
+        <v>22.32222222222222</v>
       </c>
       <c r="AK45" t="n">
-        <v>66.38647342995169</v>
+        <v>182.2208333333333</v>
       </c>
       <c r="AL45" t="n">
-        <v>1427906.099033816</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="n">
-        <v>70.14371980676329</v>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
+        <v>69.36041666666667</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>3041388.888888889</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>77.14861111111111</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>23.98512949039265</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>181.6688387635756</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>66.89791144527987</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1655334.168755222</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>73.00902255639099</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>22.51933932898102</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>181.5326192118724</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>66.41822797482837</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1856002.500757168</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>73.95584449454839</v>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
         <is>
           <t>Y39YvFx6</t>
         </is>
@@ -5513,30 +6708,30 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17000</v>
+        <v>12021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>jizXHcsM</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -5563,205 +6758,1358 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>24.42424242424243</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>181.1666666666667</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>68.2878787878788</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2233333.333333333</v>
-      </c>
-      <c r="U46" t="n">
-        <v>73.81818181818183</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="n">
-        <v>24.5765873015873</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>181.5345669427191</v>
-      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="n">
-        <v>1</v>
+        <v>26.84</v>
       </c>
       <c r="AE46" t="n">
-        <v>66.51139579020014</v>
+        <v>181.42</v>
       </c>
       <c r="AF46" t="n">
-        <v>1416180.986887509</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="n">
-        <v>72.20861801242236</v>
-      </c>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
+        <v>66.78</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>69.3</v>
+      </c>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
+      <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="n">
+        <v>27.01910593792173</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>182.6156713900135</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>65.48793522267206</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>908723.2624831309</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>68.74245276653171</v>
+      </c>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5108</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>W4AadhN3</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>48</v>
+      </c>
+      <c r="I47" t="n">
+        <v>484</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>9877</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>EwJVdqzn</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>48</v>
+      </c>
+      <c r="I48" t="n">
+        <v>484</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>21088</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>WvZyDeKk</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" t="n">
+        <v>484</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="n">
+        <v>24.425</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>179.825</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>68.925</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1957500</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="n">
+        <v>24.29159663865546</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>180.5899074781428</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>67.26384856973092</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1573024.57346575</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>72.91500721500722</v>
+      </c>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>16587</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>6ZvdGuYf</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>48</v>
+      </c>
+      <c r="I50" t="n">
+        <v>484</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ve14a3l4</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>48</v>
+      </c>
+      <c r="I51" t="n">
+        <v>484</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vicarage road
+  watford </t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>f9KDxtkU</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>48</v>
+      </c>
+      <c r="I52" t="n">
+        <v>484</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="n">
+        <v>24.13272727272727</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>183.5745454545454</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>69.72181818181818</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2470727.272727272</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>74.12545454545455</v>
+      </c>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="n">
+        <v>23.81987577639751</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>181.8908385093168</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>68.11199102829536</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2231141.90821256</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>74.0976535541753</v>
+      </c>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dw stadium
+  wigan </t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>25133</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MgHlK2Na</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>48</v>
+      </c>
+      <c r="I53" t="n">
+        <v>484</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45517.66666666666</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>32050</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>IgO7K1ZA</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>48</v>
+      </c>
+      <c r="I54" t="n">
+        <v>484</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="n">
+        <v>23.98311688311688</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>181.8258297258297</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>71.35772005772006</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>3959628.427128427</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>77.01890331890333</v>
+      </c>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="n">
+        <v>22.98463994234671</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>179.8157444894287</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>69.08283529336161</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2904845.730971201</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>76.49504679739643</v>
+      </c>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
+      <c r="BA54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>25586</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>48</v>
+      </c>
+      <c r="I55" t="n">
+        <v>484</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="n">
+        <v>24.12878787878788</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>179.7484848484848</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.092424242424243</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>69.86060606060606</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>3053181.818181818</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>75.08333333333333</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>182.2318181818182</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>67.69090909090909</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1244772.727272727</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>70.24090909090908</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>25.55430858333672</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>180.6172908293753</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.025383631713555</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>70.42968443416014</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3033739.72415053</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>74.62547869389302</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>25.66213768115942</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>185.5788043478261</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>66.31929347826087</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1142900.815217391</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>70.20516304347825</v>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45518.65625</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home park
+  plymouth </t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>jizXHcsM</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>48</v>
+      </c>
+      <c r="I56" t="n">
+        <v>484</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>181.0227272727273</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>68.34090909090909</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2201136.363636364</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="n">
+        <v>24.2875</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>181.7586956521739</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>66.35489130434783</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>1419211.956521739</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>72.69239130434784</v>
+      </c>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B57" s="2" t="n">
         <v>45518.66666666666</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t xml:space="preserve">elland road
   leeds </t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E57" t="n">
         <v>37792</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>tUxUbLR2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>6F0lvLNC</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="H57" t="n">
         <v>48</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I57" t="n">
         <v>484</v>
       </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
         <v>20242025</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>xxxpBZl2</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>p6ahwuwJ</t>
         </is>
       </c>
-      <c r="P47" t="n">
-        <v>23.00516273849607</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>184.3420875420876</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.238383838383838</v>
-      </c>
-      <c r="S47" t="n">
-        <v>74.33221099887766</v>
-      </c>
-      <c r="T47" t="n">
-        <v>8636206.509539843</v>
-      </c>
-      <c r="U47" t="n">
-        <v>80.46318742985412</v>
-      </c>
-      <c r="V47" t="n">
-        <v>24.06666666666667</v>
-      </c>
-      <c r="W47" t="n">
-        <v>181.95</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.083333333333333</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>69.68333333333334</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2498333.333333333</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>75.71666666666667</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>24.83222776440011</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>180.4883168569572</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.054809204383508</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>73.2736175269328</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>5469143.590184612</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>77.28588348594798</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>22.26025560696614</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>179.6226061949746</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.008771929824561</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>65.94247076023392</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1891559.335036309</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>74.26931109825847</v>
-      </c>
-      <c r="AN47" t="inlineStr">
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="n">
+        <v>22.85079365079365</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>184.6476190476191</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.228571428571428</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>74.34920634920636</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>8823174.603174603</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>80.72539682539683</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>182.06</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2448000</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>75.74000000000001</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>24.64143569708585</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>180.0155910609858</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.050060813799204</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>73.19873273870952</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>5531756.044523073</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>77.3063399921372</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>22.42230672835936</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>179.6171274339695</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.010526315789474</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>66.3709649122807</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1937971.202043571</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>74.27317331791016</v>
+      </c>
+      <c r="BB57" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="BC57" t="inlineStr">
         <is>
           <t>n94TZqsm</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC57"/>
+  <dimension ref="A1:AV47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,165 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_miss_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>sum_val_player_miss_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_home</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -773,91 +738,84 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>24.8304152637486</v>
+      </c>
+      <c r="X2" t="n">
+        <v>184.7519640852974</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.205387205387205</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>79.83468013468013</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>29310575.19640853</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>84.34489337822671</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>26.98787878787879</v>
+      </c>
       <c r="AD2" t="n">
-        <v>24.8304152637486</v>
+        <v>183.8787878787879</v>
       </c>
       <c r="AE2" t="n">
-        <v>184.7519640852974</v>
+        <v>1.539393939393939</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.205387205387205</v>
+        <v>77.06818181818181</v>
       </c>
       <c r="AG2" t="n">
-        <v>79.83468013468013</v>
+        <v>12800303.03030303</v>
       </c>
       <c r="AH2" t="n">
-        <v>29310575.19640853</v>
+        <v>78.9621212121212</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.34489337822671</v>
+        <v>24.03719336219336</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.98787878787879</v>
+        <v>184.0678691678692</v>
       </c>
       <c r="AK2" t="n">
-        <v>183.8787878787879</v>
+        <v>1.776952060285394</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.539393939393939</v>
+        <v>74.70817299983966</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.06818181818181</v>
+        <v>17920840.24771525</v>
       </c>
       <c r="AN2" t="n">
-        <v>12800303.03030303</v>
+        <v>81.42019400352734</v>
       </c>
       <c r="AO2" t="n">
-        <v>78.9621212121212</v>
+        <v>27.909047314578</v>
       </c>
       <c r="AP2" t="n">
-        <v>24.03719336219336</v>
+        <v>181.4587702472294</v>
       </c>
       <c r="AQ2" t="n">
-        <v>184.0678691678692</v>
+        <v>1.271824381926684</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.776952060285394</v>
+        <v>74.93484299516908</v>
       </c>
       <c r="AS2" t="n">
-        <v>74.70817299983966</v>
+        <v>7066695.439045183</v>
       </c>
       <c r="AT2" t="n">
-        <v>17920840.24771525</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>81.42019400352734</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>27.909047314578</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>181.4587702472294</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.271824381926684</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>74.93484299516908</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7066695.439045183</v>
-      </c>
-      <c r="BA2" t="n">
         <v>76.3639634839443</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -936,91 +894,84 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="X3" t="n">
+        <v>182.3409090909091</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>70.88636363636363</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2745454.545454545</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>74.61363636363637</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>25.98051948051948</v>
+      </c>
       <c r="AD3" t="n">
-        <v>26.18181818181818</v>
+        <v>183.0506493506494</v>
       </c>
       <c r="AE3" t="n">
-        <v>182.6</v>
+        <v>2.719480519480519</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>83.32987012987012</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.63636363636363</v>
+        <v>49383506.49350649</v>
       </c>
       <c r="AH3" t="n">
-        <v>2660000</v>
+        <v>85.83766233766232</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.38181818181819</v>
+        <v>25.63541666666666</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25.98051948051948</v>
+        <v>184.0639880952381</v>
       </c>
       <c r="AK3" t="n">
-        <v>183.0506493506494</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.719480519480519</v>
+        <v>69.33035714285714</v>
       </c>
       <c r="AM3" t="n">
-        <v>83.32987012987012</v>
+        <v>2184672.619047619</v>
       </c>
       <c r="AN3" t="n">
-        <v>49383506.49350649</v>
+        <v>73.29910714285714</v>
       </c>
       <c r="AO3" t="n">
-        <v>85.83766233766232</v>
+        <v>23.53863501922508</v>
       </c>
       <c r="AP3" t="n">
-        <v>25.54166666666666</v>
+        <v>183.8861653356995</v>
       </c>
       <c r="AQ3" t="n">
-        <v>183.7595238095238</v>
+        <v>1.908865720201124</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>80.12463028689737</v>
       </c>
       <c r="AS3" t="n">
-        <v>69.40595238095237</v>
+        <v>35981939.5149364</v>
       </c>
       <c r="AT3" t="n">
-        <v>2243571.428571429</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>73.41428571428571</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>23.53863501922508</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>183.8861653356995</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.908865720201124</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>80.12463028689737</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>35981939.5149364</v>
-      </c>
-      <c r="BA3" t="n">
         <v>84.71469239869862</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -1095,91 +1046,84 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>24.33928571428572</v>
+      </c>
+      <c r="X4" t="n">
+        <v>183.1607142857143</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.257936507936507</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>83.58531746031746</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>60343253.96825397</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>86.49007936507937</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>26.13095238095238</v>
+      </c>
       <c r="AD4" t="n">
-        <v>24.33928571428572</v>
+        <v>182.890873015873</v>
       </c>
       <c r="AE4" t="n">
-        <v>183.1607142857143</v>
+        <v>1.432539682539682</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.257936507936507</v>
+        <v>76.48015873015872</v>
       </c>
       <c r="AG4" t="n">
-        <v>83.58531746031746</v>
+        <v>12462748.01587302</v>
       </c>
       <c r="AH4" t="n">
-        <v>60343253.96825397</v>
+        <v>79.63492063492063</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.49007936507937</v>
+        <v>24.68670913341413</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.13095238095238</v>
+        <v>179.2607856539745</v>
       </c>
       <c r="AK4" t="n">
-        <v>182.890873015873</v>
+        <v>1.782871043154104</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.432539682539682</v>
+        <v>81.19805051207085</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.48015873015872</v>
+        <v>36885911.30231997</v>
       </c>
       <c r="AN4" t="n">
-        <v>12462748.01587302</v>
+        <v>84.50300981636674</v>
       </c>
       <c r="AO4" t="n">
-        <v>79.63492063492063</v>
+        <v>24.39053803339518</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.68670913341413</v>
+        <v>180.6655307098916</v>
       </c>
       <c r="AQ4" t="n">
-        <v>179.2607856539745</v>
+        <v>1.304615434690623</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.782871043154104</v>
+        <v>72.18617648016145</v>
       </c>
       <c r="AS4" t="n">
-        <v>81.19805051207085</v>
+        <v>8229149.171630374</v>
       </c>
       <c r="AT4" t="n">
-        <v>36885911.30231997</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>84.50300981636674</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>24.39053803339518</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>180.6655307098916</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.304615434690623</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>72.18617648016145</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>8229149.171630374</v>
-      </c>
-      <c r="BA4" t="n">
         <v>78.60334928229665</v>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -1258,91 +1202,84 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>27.2987012987013</v>
+      </c>
+      <c r="X5" t="n">
+        <v>183.5844155844156</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.584415584415584</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>11137012.98701299</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>25.90925925925926</v>
+      </c>
       <c r="AD5" t="n">
-        <v>27.2987012987013</v>
+        <v>182.1851851851852</v>
       </c>
       <c r="AE5" t="n">
-        <v>183.5844155844156</v>
+        <v>1.383333333333333</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.584415584415584</v>
+        <v>75.48333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>76.63636363636364</v>
+        <v>9138518.518518519</v>
       </c>
       <c r="AH5" t="n">
-        <v>11137012.98701299</v>
+        <v>79.95370370370371</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.14285714285714</v>
+        <v>24.6834255441307</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.90925925925926</v>
+        <v>186.4408633018425</v>
       </c>
       <c r="AK5" t="n">
-        <v>182.1851851851852</v>
+        <v>1.371851349235346</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.383333333333333</v>
+        <v>72.74374445430347</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.48333333333333</v>
+        <v>6932634.401586722</v>
       </c>
       <c r="AN5" t="n">
-        <v>9138518.518518519</v>
+        <v>77.27155383892689</v>
       </c>
       <c r="AO5" t="n">
-        <v>79.95370370370371</v>
+        <v>23.25999373433584</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.6834255441307</v>
+        <v>177.9137531328321</v>
       </c>
       <c r="AQ5" t="n">
-        <v>186.4408633018425</v>
+        <v>1.392794486215539</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.371851349235346</v>
+        <v>73.05354010025061</v>
       </c>
       <c r="AS5" t="n">
-        <v>72.74374445430347</v>
+        <v>8297991.854636592</v>
       </c>
       <c r="AT5" t="n">
-        <v>6932634.401586722</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>77.27155383892689</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23.25999373433584</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>177.9137531328321</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.392794486215539</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>73.05354010025061</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>8297991.854636592</v>
-      </c>
-      <c r="BA5" t="n">
         <v>80.37728696741854</v>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -1417,91 +1354,84 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>26.16363636363636</v>
+      </c>
+      <c r="X6" t="n">
+        <v>185.0428571428572</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.511688311688312</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>77.81688311688312</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>19297012.98701298</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>80.86623376623376</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>25.58181818181818</v>
+      </c>
       <c r="AD6" t="n">
-        <v>26.16363636363636</v>
+        <v>179.8858585858586</v>
       </c>
       <c r="AE6" t="n">
-        <v>185.0428571428572</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.511688311688312</v>
+        <v>72.85151515151513</v>
       </c>
       <c r="AG6" t="n">
-        <v>77.81688311688312</v>
+        <v>4461515.151515152</v>
       </c>
       <c r="AH6" t="n">
-        <v>19297012.98701298</v>
+        <v>76.05151515151516</v>
       </c>
       <c r="AI6" t="n">
-        <v>80.86623376623376</v>
+        <v>26.38588435374149</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25.58181818181818</v>
+        <v>181.6767006802721</v>
       </c>
       <c r="AK6" t="n">
-        <v>179.8858585858586</v>
+        <v>1.45578231292517</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>74.61751700680271</v>
       </c>
       <c r="AM6" t="n">
-        <v>72.85151515151513</v>
+        <v>14065216.83673469</v>
       </c>
       <c r="AN6" t="n">
-        <v>4461515.151515152</v>
+        <v>78.84982993197279</v>
       </c>
       <c r="AO6" t="n">
-        <v>76.05151515151516</v>
+        <v>24.99860214617248</v>
       </c>
       <c r="AP6" t="n">
-        <v>26.38588435374149</v>
+        <v>179.0143939701485</v>
       </c>
       <c r="AQ6" t="n">
-        <v>181.6767006802721</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.45578231292517</v>
+        <v>71.03804990595273</v>
       </c>
       <c r="AS6" t="n">
-        <v>74.61751700680271</v>
+        <v>3125080.210828293</v>
       </c>
       <c r="AT6" t="n">
-        <v>14065216.83673469</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>78.84982993197279</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24.99860214617248</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>179.0143939701485</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>71.03804990595273</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3125080.210828293</v>
-      </c>
-      <c r="BA6" t="n">
         <v>75.40307446650156</v>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>Aotm1TVI</t>
         </is>
@@ -1576,91 +1506,84 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>184.9666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>75.14999999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8915000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>24.14285714285714</v>
+      </c>
       <c r="AD7" t="n">
-        <v>25.35</v>
+        <v>181.1857142857143</v>
       </c>
       <c r="AE7" t="n">
-        <v>184.9666666666667</v>
+        <v>1.171428571428571</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.283333333333333</v>
+        <v>75</v>
       </c>
       <c r="AG7" t="n">
-        <v>75.14999999999999</v>
+        <v>8875714.285714285</v>
       </c>
       <c r="AH7" t="n">
-        <v>8915000</v>
+        <v>79.10000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.75</v>
+        <v>24.71211180124224</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24.14285714285714</v>
+        <v>185.6461525189786</v>
       </c>
       <c r="AK7" t="n">
-        <v>181.1857142857143</v>
+        <v>1.416873706004141</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.171428571428571</v>
+        <v>75.14817115251897</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>10341116.28709455</v>
       </c>
       <c r="AN7" t="n">
-        <v>8875714.285714285</v>
+        <v>79.55626293995859</v>
       </c>
       <c r="AO7" t="n">
-        <v>79.10000000000001</v>
+        <v>23.88719119226638</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.71211180124224</v>
+        <v>183.180123061984</v>
       </c>
       <c r="AQ7" t="n">
-        <v>185.6461525189786</v>
+        <v>1.324382655773633</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.416873706004141</v>
+        <v>74.30928864368714</v>
       </c>
       <c r="AS7" t="n">
-        <v>75.14817115251897</v>
+        <v>11108566.51911163</v>
       </c>
       <c r="AT7" t="n">
-        <v>10341116.28709455</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>79.55626293995859</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>23.88719119226638</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>183.180123061984</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.324382655773633</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>74.30928864368714</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11108566.51911163</v>
-      </c>
-      <c r="BA7" t="n">
         <v>79.13479776280529</v>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -1735,91 +1658,84 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>28.04545454545455</v>
+      </c>
+      <c r="X8" t="n">
+        <v>183.0227272727273</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.137878787878788</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>78.96666666666668</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>18462727.27272728</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>80.37272727272727</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.31818181818182</v>
+      </c>
       <c r="AD8" t="n">
-        <v>28.04545454545455</v>
+        <v>182.2272727272727</v>
       </c>
       <c r="AE8" t="n">
-        <v>183.0227272727273</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.137878787878788</v>
+        <v>80</v>
       </c>
       <c r="AG8" t="n">
-        <v>78.96666666666668</v>
+        <v>26416666.66666667</v>
       </c>
       <c r="AH8" t="n">
-        <v>18462727.27272728</v>
+        <v>81.72727272727273</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.37272727272727</v>
+        <v>26.70407223495458</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.31818181818182</v>
+        <v>181.0974301841949</v>
       </c>
       <c r="AK8" t="n">
-        <v>182.2272727272727</v>
+        <v>1.7021411594941</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.166666666666667</v>
+        <v>73.16779348102878</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>9405198.094389269</v>
       </c>
       <c r="AN8" t="n">
-        <v>26416666.66666667</v>
+        <v>77.61812876665819</v>
       </c>
       <c r="AO8" t="n">
-        <v>81.72727272727273</v>
+        <v>23.60212418300654</v>
       </c>
       <c r="AP8" t="n">
-        <v>26.70407223495458</v>
+        <v>183.5383306100218</v>
       </c>
       <c r="AQ8" t="n">
-        <v>181.0974301841949</v>
+        <v>1.669458061002179</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.7021411594941</v>
+        <v>73.51463779956428</v>
       </c>
       <c r="AS8" t="n">
-        <v>73.16779348102878</v>
+        <v>13255655.97766885</v>
       </c>
       <c r="AT8" t="n">
-        <v>9405198.094389269</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>77.61812876665819</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>23.60212418300654</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>183.5383306100218</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.669458061002179</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>73.51463779956428</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13255655.97766885</v>
-      </c>
-      <c r="BA8" t="n">
         <v>79.18532135076252</v>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -1894,91 +1810,84 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>25.96969696969697</v>
+      </c>
+      <c r="X9" t="n">
+        <v>184.2424242424242</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.060606060606061</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>76.75757575757575</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>12177272.72727273</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>79.24242424242424</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>25.37662337662337</v>
+      </c>
       <c r="AD9" t="n">
-        <v>25.96969696969697</v>
+        <v>183.5064935064935</v>
       </c>
       <c r="AE9" t="n">
-        <v>184.2424242424242</v>
+        <v>1.311688311688312</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.060606060606061</v>
+        <v>76.59740259740259</v>
       </c>
       <c r="AG9" t="n">
-        <v>76.75757575757575</v>
+        <v>14912987.01298702</v>
       </c>
       <c r="AH9" t="n">
-        <v>12177272.72727273</v>
+        <v>80.27272727272727</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.24242424242424</v>
+        <v>24.93897775484463</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25.37662337662337</v>
+        <v>181.2687851163857</v>
       </c>
       <c r="AK9" t="n">
-        <v>183.5064935064935</v>
+        <v>1.088361426441922</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.311688311688312</v>
+        <v>73.71160417383328</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.59740259740259</v>
+        <v>7006344.455911019</v>
       </c>
       <c r="AN9" t="n">
-        <v>14912987.01298702</v>
+        <v>77.71218036922372</v>
       </c>
       <c r="AO9" t="n">
-        <v>80.27272727272727</v>
+        <v>26.69557823129252</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.93897775484463</v>
+        <v>184.0051020408163</v>
       </c>
       <c r="AQ9" t="n">
-        <v>181.2687851163857</v>
+        <v>1.151643990929705</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.088361426441922</v>
+        <v>73.31689342403628</v>
       </c>
       <c r="AS9" t="n">
-        <v>73.71160417383328</v>
+        <v>7812634.637188209</v>
       </c>
       <c r="AT9" t="n">
-        <v>7006344.455911019</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>77.71218036922372</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>26.69557823129252</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>184.0051020408163</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.151643990929705</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>73.31689342403628</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7812634.637188209</v>
-      </c>
-      <c r="BA9" t="n">
         <v>76.39342403628117</v>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -2057,91 +1966,84 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>23.37037037037037</v>
+      </c>
+      <c r="X10" t="n">
+        <v>182.9629629629629</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.740740740740741</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>77.95061728395062</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>20227160.49382716</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>83.22222222222223</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>26.76565656565656</v>
+      </c>
       <c r="AD10" t="n">
-        <v>23.37037037037037</v>
+        <v>182.1929292929293</v>
       </c>
       <c r="AE10" t="n">
-        <v>182.9629629629629</v>
+        <v>3.192929292929293</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.740740740740741</v>
+        <v>85.67878787878789</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.95061728395062</v>
+        <v>73944444.44444445</v>
       </c>
       <c r="AH10" t="n">
-        <v>20227160.49382716</v>
+        <v>87.66161616161617</v>
       </c>
       <c r="AI10" t="n">
-        <v>83.22222222222223</v>
+        <v>23.29223676619019</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26.76565656565656</v>
+        <v>182.991007538782</v>
       </c>
       <c r="AK10" t="n">
-        <v>182.1929292929293</v>
+        <v>1.664198104948318</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.192929292929293</v>
+        <v>73.58580744704943</v>
       </c>
       <c r="AM10" t="n">
-        <v>85.67878787878789</v>
+        <v>15699310.74591807</v>
       </c>
       <c r="AN10" t="n">
-        <v>73944444.44444445</v>
+        <v>81.25842083206241</v>
       </c>
       <c r="AO10" t="n">
-        <v>87.66161616161617</v>
+        <v>24.73680462523173</v>
       </c>
       <c r="AP10" t="n">
-        <v>23.29223676619019</v>
+        <v>178.4747983734557</v>
       </c>
       <c r="AQ10" t="n">
-        <v>182.991007538782</v>
+        <v>2.287436794363478</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.664198104948318</v>
+        <v>80.52642006883269</v>
       </c>
       <c r="AS10" t="n">
-        <v>73.58580744704943</v>
+        <v>45324903.13355616</v>
       </c>
       <c r="AT10" t="n">
-        <v>15699310.74591807</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>81.25842083206241</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>24.73680462523173</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>178.4747983734557</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.287436794363478</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>80.52642006883269</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>45324903.13355616</v>
-      </c>
-      <c r="BA10" t="n">
         <v>85.15352316449929</v>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>zuJM7XDg</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -2220,91 +2122,84 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>26.54222222222222</v>
+      </c>
+      <c r="X11" t="n">
+        <v>182.9355555555555</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.437777777777778</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75.77777777777779</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9330666.666666668</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>77.97999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>24.82222222222222</v>
+      </c>
       <c r="AD11" t="n">
-        <v>26.54222222222222</v>
+        <v>185.0222222222222</v>
       </c>
       <c r="AE11" t="n">
-        <v>182.9355555555555</v>
+        <v>2.080952380952381</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.437777777777778</v>
+        <v>81.75873015873016</v>
       </c>
       <c r="AG11" t="n">
-        <v>75.77777777777779</v>
+        <v>39775396.82539683</v>
       </c>
       <c r="AH11" t="n">
-        <v>9330666.666666668</v>
+        <v>85.15873015873015</v>
       </c>
       <c r="AI11" t="n">
-        <v>77.97999999999999</v>
+        <v>25.79523407449104</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24.82222222222222</v>
+        <v>180.6265644056666</v>
       </c>
       <c r="AK11" t="n">
-        <v>185.0222222222222</v>
+        <v>1.432751665259405</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.080952380952381</v>
+        <v>73.36212121212121</v>
       </c>
       <c r="AM11" t="n">
-        <v>81.75873015873016</v>
+        <v>5901368.3272352</v>
       </c>
       <c r="AN11" t="n">
-        <v>39775396.82539683</v>
+        <v>76.56431184914156</v>
       </c>
       <c r="AO11" t="n">
-        <v>85.15873015873015</v>
+        <v>24.29394740352281</v>
       </c>
       <c r="AP11" t="n">
-        <v>25.79523407449104</v>
+        <v>181.2892266555745</v>
       </c>
       <c r="AQ11" t="n">
-        <v>180.6265644056666</v>
+        <v>1.69359191044839</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.432751665259405</v>
+        <v>78.2360417851351</v>
       </c>
       <c r="AS11" t="n">
-        <v>73.36212121212121</v>
+        <v>26775963.66397436</v>
       </c>
       <c r="AT11" t="n">
-        <v>5901368.3272352</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>76.56431184914156</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>24.29394740352281</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>181.2892266555745</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.69359191044839</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>78.2360417851351</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>26775963.66397436</v>
-      </c>
-      <c r="BA11" t="n">
         <v>81.92414421909113</v>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
         </is>
@@ -2313,30 +2208,30 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45514.45833333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">wembley stadium
+  london </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31876</v>
+        <v>90000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2348,13 +2243,13 @@
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2363,12 +2258,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>fa community shield</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2376,98 +2271,105 @@
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>180</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>155</v>
+      </c>
+      <c r="U12" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>171</v>
+      </c>
+      <c r="W12" t="n">
+        <v>26.76565656565656</v>
+      </c>
+      <c r="X12" t="n">
+        <v>182.1929292929293</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.192929292929293</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>85.67878787878789</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>73944444.44444445</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>87.66161616161617</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>24.8304152637486</v>
+      </c>
       <c r="AD12" t="n">
-        <v>25.90925925925926</v>
+        <v>184.7519640852974</v>
       </c>
       <c r="AE12" t="n">
-        <v>182.1851851851852</v>
+        <v>2.205387205387205</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.383333333333333</v>
+        <v>79.83468013468013</v>
       </c>
       <c r="AG12" t="n">
-        <v>75.48333333333333</v>
+        <v>29310575.19640853</v>
       </c>
       <c r="AH12" t="n">
-        <v>9138518.518518519</v>
+        <v>84.34489337822671</v>
       </c>
       <c r="AI12" t="n">
-        <v>79.95370370370371</v>
+        <v>24.73680462523173</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24.8304152637486</v>
+        <v>178.4747983734557</v>
       </c>
       <c r="AK12" t="n">
-        <v>184.7519640852974</v>
+        <v>2.287436794363478</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.205387205387205</v>
+        <v>80.52642006883269</v>
       </c>
       <c r="AM12" t="n">
-        <v>79.83468013468013</v>
+        <v>45324903.13355616</v>
       </c>
       <c r="AN12" t="n">
-        <v>29310575.19640853</v>
+        <v>85.15352316449929</v>
       </c>
       <c r="AO12" t="n">
-        <v>84.34489337822671</v>
+        <v>24.03719336219336</v>
       </c>
       <c r="AP12" t="n">
-        <v>23.25999373433584</v>
+        <v>184.0678691678692</v>
       </c>
       <c r="AQ12" t="n">
-        <v>177.9137531328321</v>
+        <v>1.776952060285394</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.392794486215539</v>
+        <v>74.70817299983966</v>
       </c>
       <c r="AS12" t="n">
-        <v>73.05354010025061</v>
+        <v>17920840.24771525</v>
       </c>
       <c r="AT12" t="n">
-        <v>8297991.854636592</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>80.37728696741854</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>24.03719336219336</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>184.0678691678692</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.776952060285394</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>74.70817299983966</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17920840.24771525</v>
-      </c>
-      <c r="BA12" t="n">
         <v>81.42019400352734</v>
       </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -2476,45 +2378,45 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25486</v>
+        <v>17949</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>20242025</v>
@@ -2526,19 +2428,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -2552,132 +2446,92 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>24.60833333333333</v>
+      </c>
       <c r="AD13" t="n">
-        <v>25.37662337662337</v>
+        <v>184.0333333333334</v>
       </c>
       <c r="AE13" t="n">
-        <v>183.5064935064935</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.311688311688312</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AG13" t="n">
-        <v>76.59740259740259</v>
+        <v>2554583.333333333</v>
       </c>
       <c r="AH13" t="n">
-        <v>14912987.01298702</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>80.27272727272727</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>28.04545454545455</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>183.0227272727273</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.137878787878788</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>78.96666666666668</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>18462727.27272728</v>
-      </c>
+        <v>74.29166666666666</v>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>80.37272727272727</v>
+        <v>23.7672181372549</v>
       </c>
       <c r="AP13" t="n">
-        <v>26.69557823129252</v>
+        <v>181.9432773109244</v>
       </c>
       <c r="AQ13" t="n">
-        <v>184.0051020408163</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.151643990929705</v>
+        <v>68.49160539215686</v>
       </c>
       <c r="AS13" t="n">
-        <v>73.31689342403628</v>
+        <v>2282734.375</v>
       </c>
       <c r="AT13" t="n">
-        <v>7812634.637188209</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>76.39342403628117</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>26.70407223495458</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>181.0974301841949</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.7021411594941</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>73.16779348102878</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>9405198.094389269</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>77.61812876665819</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>hUGEt9yf</t>
+        <v>74.17858018207284</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
+          <t xml:space="preserve">brisbane road
   london </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26600</v>
+        <v>9271</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>20242025</v>
@@ -2689,15 +2543,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -2712,131 +2562,68 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="n">
-        <v>26.98787878787879</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>183.8787878787879</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.539393939393939</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>77.06818181818181</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>12800303.03030303</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>78.9621212121212</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>26.54222222222222</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>182.9355555555555</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.437777777777778</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>75.77777777777779</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9330666.666666668</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>77.97999999999999</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>27.909047314578</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>181.4587702472294</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.271824381926684</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>74.93484299516908</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7066695.439045183</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>76.3639634839443</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>25.79523407449104</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>180.6265644056666</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.432751665259405</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>73.36212121212121</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5901368.3272352</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>76.56431184914156</v>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>MBpIn2MH</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>55097</v>
+        <v>10841</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>20242025</v>
@@ -2848,17 +2635,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2874,132 +2657,92 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>25.38181818181818</v>
+      </c>
       <c r="AD15" t="n">
-        <v>26.76565656565656</v>
+        <v>180.6886363636364</v>
       </c>
       <c r="AE15" t="n">
-        <v>182.1929292929293</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.192929292929293</v>
+        <v>70.13636363636364</v>
       </c>
       <c r="AG15" t="n">
-        <v>85.67878787878789</v>
+        <v>2270795.454545455</v>
       </c>
       <c r="AH15" t="n">
-        <v>73944444.44444445</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>87.66161616161617</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>26.18181818181818</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>70.63636363636363</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2660000</v>
-      </c>
+        <v>73.02272727272728</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>74.38181818181819</v>
+        <v>22.36358543417367</v>
       </c>
       <c r="AP15" t="n">
-        <v>24.73680462523173</v>
+        <v>178.7749299719888</v>
       </c>
       <c r="AQ15" t="n">
-        <v>178.4747983734557</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.287436794363478</v>
+        <v>66.17577030812325</v>
       </c>
       <c r="AS15" t="n">
-        <v>80.52642006883269</v>
+        <v>1702878.151260504</v>
       </c>
       <c r="AT15" t="n">
-        <v>45324903.13355616</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>85.15352316449929</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>25.54166666666666</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>183.7595238095238</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>69.40595238095237</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2243571.428571429</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>73.41428571428571</v>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>lhUKMQZu</t>
+        <v>74.73193277310924</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scott g 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32384</v>
+        <v>6500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>20242025</v>
@@ -3011,7 +2754,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3030,131 +2773,63 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="n">
-        <v>25.58181818181818</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>179.8858585858586</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>72.85151515151513</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>4461515.151515152</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>76.05151515151516</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>184.9666666666667</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.283333333333333</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>75.14999999999999</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>8915000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>78.75</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>24.99860214617248</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>179.0143939701485</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>71.03804990595273</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3125080.210828293</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>75.40307446650156</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>24.71211180124224</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>185.6461525189786</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.416873706004141</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>75.14817115251897</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10341116.28709455</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>79.55626293995859</v>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>62850</v>
+        <v>28723</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>20242025</v>
@@ -3166,19 +2841,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -3193,131 +2860,68 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="n">
-        <v>24.82222222222222</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>185.0222222222222</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.080952380952381</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>81.75873015873016</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>39775396.82539683</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>85.15873015873015</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>27.2987012987013</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>183.5844155844156</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.584415584415584</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>76.63636363636364</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>11137012.98701299</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>79.14285714285714</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>24.29394740352281</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>181.2892266555745</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.69359191044839</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>78.2360417851351</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>26775963.66397436</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>81.92414421909113</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>24.6834255441307</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>186.4408633018425</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.371851349235346</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>72.74374445430347</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>6932634.401586722</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>77.27155383892689</v>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>42789</v>
+        <v>27000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>20242025</v>
@@ -3329,13 +2933,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -3345,138 +2949,126 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>23.19791666666666</v>
+      </c>
+      <c r="X18" t="n">
+        <v>181.3194444444445</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>68.51041666666667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2095486.111111111</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>74.52083333333333</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>23.94953703703704</v>
+      </c>
       <c r="AD18" t="n">
-        <v>26.31818181818182</v>
+        <v>182.4611111111111</v>
       </c>
       <c r="AE18" t="n">
-        <v>182.2272727272727</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.166666666666667</v>
+        <v>71.30925925925926</v>
       </c>
       <c r="AG18" t="n">
-        <v>80</v>
+        <v>4234398.148148148</v>
       </c>
       <c r="AH18" t="n">
-        <v>26416666.66666667</v>
+        <v>77.05787037037037</v>
       </c>
       <c r="AI18" t="n">
-        <v>81.72727272727273</v>
+        <v>25.55052118933698</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24.33928571428572</v>
+        <v>180.189046479836</v>
       </c>
       <c r="AK18" t="n">
-        <v>183.1607142857143</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.257936507936507</v>
+        <v>66.89718899521532</v>
       </c>
       <c r="AM18" t="n">
-        <v>83.58531746031746</v>
+        <v>1586932.886192755</v>
       </c>
       <c r="AN18" t="n">
-        <v>60343253.96825397</v>
+        <v>72.40749316473001</v>
       </c>
       <c r="AO18" t="n">
-        <v>86.49007936507937</v>
+        <v>24.21392069188122</v>
       </c>
       <c r="AP18" t="n">
-        <v>23.60212418300654</v>
+        <v>181.362882585251</v>
       </c>
       <c r="AQ18" t="n">
-        <v>183.5383306100218</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.669458061002179</v>
+        <v>68.85962966127441</v>
       </c>
       <c r="AS18" t="n">
-        <v>73.51463779956428</v>
+        <v>2841603.072548795</v>
       </c>
       <c r="AT18" t="n">
-        <v>13255655.97766885</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>79.18532135076252</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>24.68670913341413</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>179.2607856539745</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.782871043154104</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>81.19805051207085</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>36885911.30231997</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>84.50300981636674</v>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
+        <v>74.73043878635984</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11307</v>
+        <v>5000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>20242025</v>
@@ -3488,19 +3080,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -3515,131 +3099,63 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="n">
-        <v>24.14285714285714</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>181.1857142857143</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.171428571428571</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>8875714.285714285</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>79.10000000000001</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>26.16363636363636</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>185.0428571428572</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.511688311688312</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>77.81688311688312</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>19297012.98701298</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>80.86623376623376</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>23.88719119226638</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>183.180123061984</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.324382655773633</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>74.30928864368714</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>11108566.51911163</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>79.13479776280529</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>26.38588435374149</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>181.6767006802721</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.45578231292517</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>74.61751700680271</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14065216.83673469</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>78.84982993197279</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>zuJM7XDg</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31750</v>
+        <v>6912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>20242025</v>
@@ -3651,15 +3167,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -3674,131 +3186,68 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="n">
-        <v>26.13095238095238</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>182.890873015873</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.432539682539682</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>76.48015873015872</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>12462748.01587302</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>79.63492063492063</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>23.37037037037037</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>182.9629629629629</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.740740740740741</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>77.95061728395062</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>20227160.49382716</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>83.22222222222223</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>24.39053803339518</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>180.6655307098916</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.304615434690623</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>72.18617648016145</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8229149.171630374</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>78.60334928229665</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>23.29223676619019</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>182.991007538782</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.664198104948318</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>73.58580744704943</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>15699310.74591807</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>81.25842083206241</v>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>x6CvOHH9</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>61276</v>
+        <v>7937</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>20242025</v>
@@ -3810,14 +3259,10 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -3832,135 +3277,95 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>27.775</v>
+      </c>
       <c r="AD21" t="n">
-        <v>25.98051948051948</v>
+        <v>183.075</v>
       </c>
       <c r="AE21" t="n">
-        <v>183.0506493506494</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.719480519480519</v>
+        <v>70.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>83.32987012987012</v>
+        <v>1883125</v>
       </c>
       <c r="AH21" t="n">
-        <v>49383506.49350649</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>85.83766233766232</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>25.96969696969697</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>184.2424242424242</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.060606060606061</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>76.75757575757575</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>12177272.72727273</v>
-      </c>
+        <v>71.875</v>
+      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
-        <v>79.24242424242424</v>
+        <v>25.87747035573123</v>
       </c>
       <c r="AP21" t="n">
-        <v>23.53863501922508</v>
+        <v>180.7192193675889</v>
       </c>
       <c r="AQ21" t="n">
-        <v>183.8861653356995</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.908865720201124</v>
+        <v>67.48399209486166</v>
       </c>
       <c r="AS21" t="n">
-        <v>80.12463028689737</v>
+        <v>1440606.472332016</v>
       </c>
       <c r="AT21" t="n">
-        <v>35981939.5149364</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>84.71469239869862</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>24.93897775484463</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>181.2687851163857</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.088361426441922</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>73.71160417383328</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>7006344.455911019</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>77.71218036922372</v>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>x6CvOHH9</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
+        <v>71.62406126482213</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45514.45833333334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">wembley stadium
-  london </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90000</v>
+        <v>33280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3969,176 +3374,109 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>fa community shield</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>73</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V22" t="n">
-        <v>83</v>
-      </c>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="n">
-        <v>23</v>
+        <v>26.15909090909091</v>
       </c>
       <c r="X22" t="n">
-        <v>169</v>
+        <v>183.3113636363636</v>
       </c>
       <c r="Y22" t="n">
         <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>69.28863636363636</v>
       </c>
       <c r="AA22" t="n">
-        <v>77</v>
+        <v>1930454.545454545</v>
       </c>
       <c r="AB22" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>82</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>26.76565656565656</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>182.1929292929293</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.192929292929293</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>85.67878787878789</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>73944444.44444445</v>
-      </c>
+        <v>71.92045454545455</v>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>87.66161616161617</v>
+        <v>24.10615079365079</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24.8304152637486</v>
+        <v>182.5744047619048</v>
       </c>
       <c r="AK22" t="n">
-        <v>184.7519640852974</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.205387205387205</v>
+        <v>63.60317460317461</v>
       </c>
       <c r="AM22" t="n">
-        <v>79.83468013468013</v>
+        <v>1184975.198412698</v>
       </c>
       <c r="AN22" t="n">
-        <v>29310575.19640853</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>84.34489337822671</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>24.73680462523173</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>178.4747983734557</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.287436794363478</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>80.52642006883269</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>45324903.13355616</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>85.15352316449929</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>24.03719336219336</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>184.0678691678692</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.776952060285394</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>74.70817299983966</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>17920840.24771525</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>81.42019400352734</v>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
+        <v>69.25396825396825</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17949</v>
+        <v>27111</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4164,7 +3502,11 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -4178,89 +3520,82 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>25.06818181818182</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>182.1136363636363</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>69.31818181818181</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2059545.454545455</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>73.45454545454545</v>
+      </c>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="n">
-        <v>24.62666666666667</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>184.2866666666667</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>69.97999999999999</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2589166.666666667</v>
-      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="n">
-        <v>74.35333333333332</v>
-      </c>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
+        <v>26.24722222222222</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>178.7868055555555</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>67.7763888888889</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1490746.527777778</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>71.38541666666667</v>
+      </c>
       <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="n">
-        <v>23.95377450980392</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>181.6146218487395</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>68.57328431372549</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2240687.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>73.94286414565826</v>
-      </c>
-      <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9271</v>
+        <v>10105</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4320,46 +3655,34 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AU24" t="inlineStr"/>
       <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10841</v>
+        <v>6134</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4385,11 +3708,7 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -4410,59 +3729,24 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="n">
-        <v>25.25090909090909</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>180.46</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>70.05454545454546</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2271181.818181818</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>73</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr"/>
       <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="n">
-        <v>22.66086834733894</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>178.889943977591</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>66.50061624649859</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1707802.521008403</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>74.68554621848739</v>
-      </c>
-      <c r="BB25" t="inlineStr"/>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+      <c r="AV25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -4471,21 +3755,21 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6500</v>
+        <v>33597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4545,41 +3829,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AU26" t="inlineStr"/>
       <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
-      <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>28723</v>
+        <v>5327</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4619,66 +3901,82 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>27.43333333333333</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>185.2333333333333</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>71.28333333333333</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2360000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>72.80000000000001</v>
+      </c>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>28.12530193236715</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>184.286231884058</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.086050724637681</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>70.87741545893721</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2330706.52173913</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>72.4921497584541</v>
+      </c>
       <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27000</v>
+        <v>9052</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4704,11 +4002,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -4723,93 +4017,30 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="n">
-        <v>23.27833333333333</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>181.4555555555556</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>68.54833333333333</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2086388.888888889</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>74.43666666666665</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>23.94953703703704</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>182.4611111111111</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>71.30925925925926</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>4234398.148148148</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>77.05787037037037</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>25.56422647527911</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>180.4274276600593</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>66.56537024379129</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1523308.213716109</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>72.16408976987925</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>24.21392069188122</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>181.362882585251</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>68.85962966127441</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2841603.072548795</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>74.73043878635984</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="BC28" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -4818,21 +4049,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5000</v>
+        <v>24121</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4857,7 +4088,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -4866,44 +4101,65 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>24.56666666666667</v>
+      </c>
+      <c r="X29" t="n">
+        <v>182.7666666666667</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1674166.666666667</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>73.5</v>
+      </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>23.75438034188034</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>182.5213675213675</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65.9684829059829</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1425261.752136752</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>72.93568376068376</v>
+      </c>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -4912,21 +4168,21 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6912</v>
+        <v>10669</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4986,46 +4242,34 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
       <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7937</v>
+        <v>7798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -5072,59 +4316,24 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="n">
-        <v>27.775</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>183.075</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1883125</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>71.875</v>
-      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="n">
-        <v>25.87747035573123</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>180.7192193675889</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>67.48399209486166</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1440606.472332016</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>71.62406126482213</v>
-      </c>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="AV31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -5133,21 +4342,21 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33280</v>
+        <v>27137</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -5174,7 +4383,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -5185,100 +4394,88 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>26.24074074074074</v>
+      </c>
+      <c r="X32" t="n">
+        <v>182.6092592592593</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>72.28703703703704</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3291481.481481481</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>74.7925925925926</v>
+      </c>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="n">
-        <v>26.23636363636364</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>183.14</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>69.61272727272726</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2000727.272727273</v>
-      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>72.11818181818182</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
+        <v>25.66401416145662</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>184.1604352595402</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>69.05797356948251</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>2385473.092551098</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>73.27669900432049</v>
+      </c>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="n">
-        <v>23.96913116123642</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>183.0489974937344</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>63.85096073517127</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1251822.263993317</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>69.6452798663325</v>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27111</v>
+        <v>12500</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5304,11 +4501,7 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -5329,82 +4522,52 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="n">
-        <v>24.85454545454545</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>182</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>69.23636363636362</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>2081818.181818182</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>73.70909090909092</v>
-      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr"/>
       <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="n">
-        <v>26.38111111111111</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>179.0461111111111</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>67.81277777777778</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1509055.555555556</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>71.21666666666667</v>
-      </c>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
+      <c r="AV33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10105</v>
+        <v>21944</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5430,7 +4593,11 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -5444,61 +4611,87 @@
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>25.225</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2516250</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>73.80000000000001</v>
+      </c>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
+      <c r="AO34" t="n">
+        <v>25.91517857142857</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>179.2291666666667</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>68.39732142857143</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1705825.892857143</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>72.99702380952381</v>
+      </c>
       <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
-      <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6134</v>
+        <v>23408</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5524,7 +4717,11 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -5532,44 +4729,93 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="inlineStr"/>
-      <c r="BC35" t="inlineStr"/>
+      <c r="W35" t="n">
+        <v>26.40388888888889</v>
+      </c>
+      <c r="X35" t="n">
+        <v>184.2966666666667</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>69.84666666666666</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1923208.333333333</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>71.90055555555554</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>22.32222222222222</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>182.2208333333333</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>69.36041666666667</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3041388.888888889</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>77.14861111111111</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>23.98512949039265</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>181.6688387635756</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>66.89791144527987</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1655334.168755222</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>73.00902255639099</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>22.51933932898102</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>181.5326192118724</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>66.41822797482837</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1856002.500757168</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>73.95584449454839</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -5578,21 +4824,21 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>33597</v>
+        <v>12021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5626,72 +4872,88 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>26.825</v>
+      </c>
+      <c r="X36" t="n">
+        <v>181.425</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>66.67500000000001</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1058750</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>69.3</v>
+      </c>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
+      <c r="AI36" t="n">
+        <v>26.95809294871795</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>182.927483974359</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>65.62307692307692</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>932285.6570512821</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>68.84911858974358</v>
+      </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5327</v>
+        <v>5108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5738,59 +5000,24 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="n">
-        <v>27.44285714285714</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>185.4142857142857</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.042857142857143</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>71.28571428571429</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2377142.857142857</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>72.84285714285714</v>
-      </c>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr"/>
       <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="n">
-        <v>27.976966873706</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>184.3819875776397</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.073757763975155</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>70.78933747412009</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2305822.98136646</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>72.48395445134575</v>
-      </c>
-      <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="AV37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -5799,21 +5026,21 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9052</v>
+        <v>9877</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5873,18 +5100,11 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AU38" t="inlineStr"/>
       <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -5893,21 +5113,21 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24121</v>
+        <v>21088</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5934,7 +5154,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -5945,72 +5165,65 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>24.34375</v>
+      </c>
+      <c r="X39" t="n">
+        <v>179.8125</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1962500</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>74.3125</v>
+      </c>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="n">
-        <v>24.56666666666667</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>182.7666666666667</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>67.66666666666667</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1674166.666666667</v>
-      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
+        <v>24.42401960784314</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>180.5469081572023</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>67.35362023597318</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1564197.383498854</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>72.67947330447331</v>
+      </c>
       <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="n">
-        <v>23.75438034188034</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>182.5213675213675</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>65.9684829059829</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1425261.752136752</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>72.93568376068376</v>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="BC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -6019,21 +5232,21 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10669</v>
+        <v>16587</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -6093,18 +5306,11 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AU40" t="inlineStr"/>
       <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr"/>
-      <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -6113,21 +5319,21 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7798</v>
+        <v>11300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6187,18 +5393,11 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AU41" t="inlineStr"/>
       <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
-      <c r="BC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -6207,21 +5406,21 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>27137</v>
+        <v>22200</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6248,7 +5447,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>SlybbadF</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -6259,72 +5458,65 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>24.21590909090909</v>
+      </c>
+      <c r="X42" t="n">
+        <v>183.6431818181818</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>69.80227272727274</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2570909.090909091</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>74.18181818181819</v>
+      </c>
       <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="n">
-        <v>26.24074074074074</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>182.6092592592593</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>72.28703703703704</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>3291481.481481481</v>
-      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>74.7925925925926</v>
-      </c>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
+        <v>23.44151138716356</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>181.8218814699793</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>67.58443322981367</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>2006288.496376812</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>73.94151138716356</v>
+      </c>
       <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="n">
-        <v>25.66401416145662</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>184.1604352595402</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>69.05797356948251</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2385473.092551098</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>73.27669900432049</v>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
-      <c r="BB42" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="BC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -6333,21 +5525,21 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12500</v>
+        <v>25133</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6407,46 +5599,34 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AU43" t="inlineStr"/>
       <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
-      <c r="BB43" t="inlineStr"/>
-      <c r="BC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.66666666666</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21944</v>
+        <v>32050</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>IgO7K1ZA</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6472,11 +5652,7 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -6484,76 +5660,69 @@
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>23.98311688311688</v>
+      </c>
+      <c r="X44" t="n">
+        <v>181.8258297258297</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>71.35772005772006</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3959628.427128427</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>77.01890331890333</v>
+      </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
+      <c r="AI44" t="n">
+        <v>22.98463994234671</v>
+      </c>
       <c r="AJ44" t="n">
-        <v>25.225</v>
+        <v>179.8157444894287</v>
       </c>
       <c r="AK44" t="n">
-        <v>180.375</v>
+        <v>1</v>
       </c>
       <c r="AL44" t="n">
-        <v>1</v>
+        <v>69.08283529336161</v>
       </c>
       <c r="AM44" t="n">
-        <v>69.625</v>
+        <v>2904845.730971201</v>
       </c>
       <c r="AN44" t="n">
-        <v>2516250</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>73.80000000000001</v>
-      </c>
+        <v>76.49504679739643</v>
+      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="n">
-        <v>25.91517857142857</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>179.2291666666667</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>68.39732142857143</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1705825.892857143</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>72.99702380952381</v>
-      </c>
-      <c r="BB44" t="inlineStr"/>
-      <c r="BC44" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6563,21 +5732,21 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>23408</v>
+        <v>25586</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6602,12 +5771,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -6615,91 +5784,84 @@
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>24.05454545454545</v>
+      </c>
+      <c r="X45" t="n">
+        <v>179.8181818181818</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>69.67272727272727</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3016818.181818182</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>27.35</v>
+      </c>
       <c r="AD45" t="n">
-        <v>26.40388888888889</v>
+        <v>182.2318181818182</v>
       </c>
       <c r="AE45" t="n">
-        <v>184.2966666666667</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>1</v>
+        <v>67.69090909090909</v>
       </c>
       <c r="AG45" t="n">
-        <v>69.84666666666666</v>
+        <v>1244772.727272727</v>
       </c>
       <c r="AH45" t="n">
-        <v>1923208.333333333</v>
+        <v>70.24090909090908</v>
       </c>
       <c r="AI45" t="n">
-        <v>71.90055555555554</v>
+        <v>25.229876182357</v>
       </c>
       <c r="AJ45" t="n">
-        <v>22.32222222222222</v>
+        <v>180.7995725246621</v>
       </c>
       <c r="AK45" t="n">
-        <v>182.2208333333333</v>
+        <v>1.018695652173913</v>
       </c>
       <c r="AL45" t="n">
-        <v>1</v>
+        <v>70.42150367393334</v>
       </c>
       <c r="AM45" t="n">
-        <v>69.36041666666667</v>
+        <v>3104899.433686518</v>
       </c>
       <c r="AN45" t="n">
-        <v>3041388.888888889</v>
+        <v>74.86822149149515</v>
       </c>
       <c r="AO45" t="n">
-        <v>77.14861111111111</v>
+        <v>25.66213768115942</v>
       </c>
       <c r="AP45" t="n">
-        <v>23.98512949039265</v>
+        <v>185.5788043478261</v>
       </c>
       <c r="AQ45" t="n">
-        <v>181.6688387635756</v>
+        <v>1</v>
       </c>
       <c r="AR45" t="n">
-        <v>1</v>
+        <v>66.31929347826087</v>
       </c>
       <c r="AS45" t="n">
-        <v>66.89791144527987</v>
+        <v>1142900.815217391</v>
       </c>
       <c r="AT45" t="n">
-        <v>1655334.168755222</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>73.00902255639099</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>22.51933932898102</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>181.5326192118724</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>66.41822797482837</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1856002.500757168</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>73.95584449454839</v>
-      </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="BC45" t="inlineStr">
+        <v>70.20516304347825</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
         <is>
           <t>Y39YvFx6</t>
         </is>
@@ -6708,30 +5870,30 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12021</v>
+        <v>17000</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6765,95 +5927,93 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="X46" t="n">
+        <v>181.0227272727273</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>68.34090909090909</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2201136.363636364</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>73.45454545454545</v>
+      </c>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>181.42</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1069000</v>
-      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
+        <v>24.2875</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>181.7586956521739</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>66.35489130434783</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1419211.956521739</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>72.69239130434784</v>
+      </c>
       <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="n">
-        <v>27.01910593792173</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>182.6156713900135</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>65.48793522267206</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>908723.2624831309</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>68.74245276653171</v>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr"/>
-      <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr"/>
-      <c r="BA46" t="inlineStr"/>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5108</v>
+        <v>37792</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6878,8 +6038,16 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -6887,1229 +6055,84 @@
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>9877</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>EqfQ6qK4</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>EwJVdqzn</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>48</v>
-      </c>
-      <c r="I48" t="n">
-        <v>484</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr"/>
-      <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
-      <c r="BB48" t="inlineStr"/>
-      <c r="BC48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>21088</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>WvZyDeKk</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>48</v>
-      </c>
-      <c r="I49" t="n">
-        <v>484</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="n">
-        <v>24.425</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>179.825</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>68.925</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1957500</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="n">
-        <v>24.29159663865546</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>180.5899074781428</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>67.26384856973092</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1573024.57346575</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>72.91500721500722</v>
-      </c>
-      <c r="AV49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="BC49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>16587</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>jVhkb1QE</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6ZvdGuYf</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>48</v>
-      </c>
-      <c r="I50" t="n">
-        <v>484</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr"/>
-      <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr"/>
-      <c r="BB50" t="inlineStr"/>
-      <c r="BC50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>11300</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>YgrfcLuL</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>ve14a3l4</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="n">
-        <v>484</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
-      <c r="BA51" t="inlineStr"/>
-      <c r="BB51" t="inlineStr"/>
-      <c r="BC51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>22200</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>f9KDxtkU</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>48</v>
-      </c>
-      <c r="I52" t="n">
-        <v>484</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="n">
-        <v>24.13272727272727</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>183.5745454545454</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>69.72181818181818</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2470727.272727272</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>74.12545454545455</v>
-      </c>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="n">
-        <v>23.81987577639751</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>181.8908385093168</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>68.11199102829536</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2231141.90821256</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>74.0976535541753</v>
-      </c>
-      <c r="AV52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr"/>
-      <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr"/>
-      <c r="BA52" t="inlineStr"/>
-      <c r="BB52" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="BC52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>25133</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>MgHlK2Na</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>UNGEKMx6</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>48</v>
-      </c>
-      <c r="I53" t="n">
-        <v>484</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
-      <c r="BB53" t="inlineStr"/>
-      <c r="BC53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>32050</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>IgO7K1ZA</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>48</v>
-      </c>
-      <c r="I54" t="n">
-        <v>484</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="n">
-        <v>23.98311688311688</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>181.8258297258297</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>71.35772005772006</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>3959628.427128427</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>77.01890331890333</v>
-      </c>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="n">
-        <v>22.98463994234671</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>179.8157444894287</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>69.08283529336161</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2904845.730971201</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>76.49504679739643</v>
-      </c>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
-      <c r="BB54" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="BC54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>25586</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>S66R0t75</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>llcCvIcG</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>48</v>
-      </c>
-      <c r="I55" t="n">
-        <v>484</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="n">
-        <v>24.12878787878788</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>179.7484848484848</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.092424242424243</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>69.86060606060606</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>3053181.818181818</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>75.08333333333333</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>27.35</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>182.2318181818182</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>67.69090909090909</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1244772.727272727</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>70.24090909090908</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>25.55430858333672</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>180.6172908293753</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.025383631713555</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>70.42968443416014</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3033739.72415053</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>74.62547869389302</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>25.66213768115942</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>185.5788043478261</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>66.31929347826087</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1142900.815217391</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>70.20516304347825</v>
-      </c>
-      <c r="BB55" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="BC55" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>WpGM6ELj</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>jizXHcsM</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>48</v>
-      </c>
-      <c r="I56" t="n">
-        <v>484</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="n">
-        <v>24.63636363636364</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>181.0227272727273</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>68.34090909090909</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>2201136.363636364</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>73.45454545454545</v>
-      </c>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="n">
-        <v>24.2875</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>181.7586956521739</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>66.35489130434783</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1419211.956521739</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>72.69239130434784</v>
-      </c>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="BC56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45518.66666666666</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bell j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>37792</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>48</v>
-      </c>
-      <c r="I57" t="n">
-        <v>484</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="n">
+      <c r="W47" t="n">
         <v>22.85079365079365</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="X47" t="n">
         <v>184.6476190476191</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="Y47" t="n">
         <v>1.228571428571428</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="Z47" t="n">
         <v>74.34920634920636</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AA47" t="n">
         <v>8823174.603174603</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AB47" t="n">
         <v>80.72539682539683</v>
       </c>
-      <c r="AJ57" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>182.06</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>2448000</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>75.74000000000001</v>
-      </c>
-      <c r="AP57" t="n">
+      <c r="AC47" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>182.05</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>69.27500000000001</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AI47" t="n">
         <v>24.64143569708585</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AJ47" t="n">
         <v>180.0155910609858</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AK47" t="n">
         <v>1.050060813799204</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AL47" t="n">
         <v>73.19873273870952</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AM47" t="n">
         <v>5531756.044523073</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AN47" t="n">
         <v>77.3063399921372</v>
       </c>
-      <c r="AV57" t="n">
-        <v>22.42230672835936</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>179.6171274339695</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.010526315789474</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>66.3709649122807</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>1937971.202043571</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>74.27317331791016</v>
-      </c>
-      <c r="BB57" t="inlineStr">
+      <c r="AO47" t="n">
+        <v>22.54574055330634</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>179.9856950067476</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.013157894736842</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>66.46370614035088</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1916571.145411606</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>74.30575236167341</v>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="BC57" t="inlineStr">
+      <c r="AV47" t="inlineStr">
         <is>
           <t>n94TZqsm</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -781,76 +781,76 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>24.8304152637486</v>
+        <v>24.67163947163948</v>
       </c>
       <c r="AE2" t="n">
-        <v>184.7519640852974</v>
+        <v>185.0277389277389</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.205387205387205</v>
+        <v>2.211188811188811</v>
       </c>
       <c r="AG2" t="n">
-        <v>79.83468013468013</v>
+        <v>79.83682983682982</v>
       </c>
       <c r="AH2" t="n">
-        <v>29310575.19640853</v>
+        <v>29763282.82828283</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.34489337822671</v>
+        <v>84.43939393939394</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.98787878787879</v>
+        <v>26.85545454545455</v>
       </c>
       <c r="AK2" t="n">
-        <v>183.8787878787879</v>
+        <v>184.2227272727273</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.539393939393939</v>
+        <v>1.527272727272727</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.06818181818181</v>
+        <v>77.10545454545453</v>
       </c>
       <c r="AN2" t="n">
-        <v>12800303.03030303</v>
+        <v>12927636.36363636</v>
       </c>
       <c r="AO2" t="n">
-        <v>78.9621212121212</v>
+        <v>79.16454545454545</v>
       </c>
       <c r="AP2" t="n">
-        <v>24.03719336219336</v>
+        <v>24.46480536371841</v>
       </c>
       <c r="AQ2" t="n">
-        <v>184.0678691678692</v>
+        <v>184.1148421626683</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.776952060285394</v>
+        <v>1.877837862620471</v>
       </c>
       <c r="AS2" t="n">
-        <v>74.70817299983966</v>
+        <v>75.41296034882991</v>
       </c>
       <c r="AT2" t="n">
-        <v>17920840.24771525</v>
+        <v>18948707.12801691</v>
       </c>
       <c r="AU2" t="n">
-        <v>81.42019400352734</v>
+        <v>81.54998938259807</v>
       </c>
       <c r="AV2" t="n">
-        <v>27.909047314578</v>
+        <v>28.21626172208014</v>
       </c>
       <c r="AW2" t="n">
-        <v>181.4587702472294</v>
+        <v>181.2419288150043</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.271824381926684</v>
+        <v>1.308927962489344</v>
       </c>
       <c r="AY2" t="n">
-        <v>74.93484299516908</v>
+        <v>74.99781055900621</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7066695.439045183</v>
+        <v>6886981.549141395</v>
       </c>
       <c r="BA2" t="n">
-        <v>76.3639634839443</v>
+        <v>76.14754475703324</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -944,76 +944,76 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>26.18181818181818</v>
+        <v>26.38383838383838</v>
       </c>
       <c r="AE3" t="n">
-        <v>182.6</v>
+        <v>182.6767676767677</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.63636363636363</v>
+        <v>70.92929292929291</v>
       </c>
       <c r="AH3" t="n">
-        <v>2660000</v>
+        <v>2742424.242424242</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.38181818181819</v>
+        <v>74.38383838383839</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25.98051948051948</v>
+        <v>25.75619834710744</v>
       </c>
       <c r="AK3" t="n">
-        <v>183.0506493506494</v>
+        <v>183.3545454545454</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.719480519480519</v>
+        <v>2.614876033057851</v>
       </c>
       <c r="AM3" t="n">
-        <v>83.32987012987012</v>
+        <v>82.74710743801653</v>
       </c>
       <c r="AN3" t="n">
-        <v>49383506.49350649</v>
+        <v>46462231.40495867</v>
       </c>
       <c r="AO3" t="n">
-        <v>85.83766233766232</v>
+        <v>85.53305785123966</v>
       </c>
       <c r="AP3" t="n">
-        <v>25.54166666666666</v>
+        <v>25.1712962962963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>183.7595238095238</v>
+        <v>183.2784391534391</v>
       </c>
       <c r="AR3" t="n">
         <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>69.40595238095237</v>
+        <v>68.9292328042328</v>
       </c>
       <c r="AT3" t="n">
-        <v>2243571.428571429</v>
+        <v>2164021.164021164</v>
       </c>
       <c r="AU3" t="n">
-        <v>73.41428571428571</v>
+        <v>73.35515873015873</v>
       </c>
       <c r="AV3" t="n">
-        <v>23.53863501922508</v>
+        <v>23.20834551211789</v>
       </c>
       <c r="AW3" t="n">
-        <v>183.8861653356995</v>
+        <v>183.2271528769611</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.908865720201124</v>
+        <v>1.786762491557889</v>
       </c>
       <c r="AY3" t="n">
-        <v>80.12463028689737</v>
+        <v>79.20719904562615</v>
       </c>
       <c r="AZ3" t="n">
-        <v>35981939.5149364</v>
+        <v>33498280.27258334</v>
       </c>
       <c r="BA3" t="n">
-        <v>84.71469239869862</v>
+        <v>84.38545991519138</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1103,76 +1103,76 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>24.33928571428572</v>
+        <v>24.45416666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>183.1607142857143</v>
+        <v>182.8930555555555</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.257936507936507</v>
+        <v>2.236111111111111</v>
       </c>
       <c r="AG4" t="n">
-        <v>83.58531746031746</v>
+        <v>83.40416666666667</v>
       </c>
       <c r="AH4" t="n">
-        <v>60343253.96825397</v>
+        <v>58345833.33333334</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.49007936507937</v>
+        <v>86.30833333333332</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.13095238095238</v>
+        <v>26.32916666666666</v>
       </c>
       <c r="AK4" t="n">
-        <v>182.890873015873</v>
+        <v>182.9236111111111</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.432539682539682</v>
+        <v>1.452777777777778</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.48015873015872</v>
+        <v>76.4986111111111</v>
       </c>
       <c r="AN4" t="n">
-        <v>12462748.01587302</v>
+        <v>12162673.61111111</v>
       </c>
       <c r="AO4" t="n">
-        <v>79.63492063492063</v>
+        <v>79.63194444444444</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.68670913341413</v>
+        <v>24.63040227574283</v>
       </c>
       <c r="AQ4" t="n">
-        <v>179.2607856539745</v>
+        <v>179.6681381930763</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.782871043154104</v>
+        <v>1.772715612560814</v>
       </c>
       <c r="AS4" t="n">
-        <v>81.19805051207085</v>
+        <v>81.20040006433194</v>
       </c>
       <c r="AT4" t="n">
-        <v>36885911.30231997</v>
+        <v>37424843.79397692</v>
       </c>
       <c r="AU4" t="n">
-        <v>84.50300981636674</v>
+        <v>84.53740098910377</v>
       </c>
       <c r="AV4" t="n">
-        <v>24.39053803339518</v>
+        <v>23.99170791993758</v>
       </c>
       <c r="AW4" t="n">
-        <v>180.6655307098916</v>
+        <v>181.41839654232</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.304615434690623</v>
+        <v>1.253578850708037</v>
       </c>
       <c r="AY4" t="n">
-        <v>72.18617648016145</v>
+        <v>71.67427660059239</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8229149.171630374</v>
+        <v>7717944.827633822</v>
       </c>
       <c r="BA4" t="n">
-        <v>78.60334928229665</v>
+        <v>78.60448020878643</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1266,76 +1266,76 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>27.2987012987013</v>
+        <v>27.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>183.5844155844156</v>
+        <v>183.8545454545455</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.584415584415584</v>
+        <v>1.581818181818181</v>
       </c>
       <c r="AG5" t="n">
-        <v>76.63636363636364</v>
+        <v>76.67272727272727</v>
       </c>
       <c r="AH5" t="n">
-        <v>11137012.98701299</v>
+        <v>11300000</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.14285714285714</v>
+        <v>79.18181818181817</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.90925925925926</v>
+        <v>25.64769921436588</v>
       </c>
       <c r="AK5" t="n">
-        <v>182.1851851851852</v>
+        <v>182.0516273849607</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.383333333333333</v>
+        <v>1.375645342312009</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.48333333333333</v>
+        <v>75.46588103254768</v>
       </c>
       <c r="AN5" t="n">
-        <v>9138518.518518519</v>
+        <v>9438698.092031427</v>
       </c>
       <c r="AO5" t="n">
-        <v>79.95370370370371</v>
+        <v>80.13187429854096</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.6834255441307</v>
+        <v>25.25395343644704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>186.4408633018425</v>
+        <v>186.0413820890675</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.371851349235346</v>
+        <v>1.391129277798076</v>
       </c>
       <c r="AS5" t="n">
-        <v>72.74374445430347</v>
+        <v>73.15978778467908</v>
       </c>
       <c r="AT5" t="n">
-        <v>6932634.401586722</v>
+        <v>7081649.636666261</v>
       </c>
       <c r="AU5" t="n">
-        <v>77.27155383892689</v>
+        <v>77.1639765761377</v>
       </c>
       <c r="AV5" t="n">
-        <v>23.25999373433584</v>
+        <v>23.40342418546366</v>
       </c>
       <c r="AW5" t="n">
-        <v>177.9137531328321</v>
+        <v>177.98210839599</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.392794486215539</v>
+        <v>1.39187343358396</v>
       </c>
       <c r="AY5" t="n">
-        <v>73.05354010025061</v>
+        <v>73.16341791979949</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8297991.854636592</v>
+        <v>8325323.621553885</v>
       </c>
       <c r="BA5" t="n">
-        <v>80.37728696741854</v>
+        <v>80.35131892230577</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1425,76 +1425,76 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>26.16363636363636</v>
+        <v>26.40752984389348</v>
       </c>
       <c r="AE6" t="n">
-        <v>185.0428571428572</v>
+        <v>185.4415977961433</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.511688311688312</v>
+        <v>1.544903581267217</v>
       </c>
       <c r="AG6" t="n">
-        <v>77.81688311688312</v>
+        <v>78.01836547291093</v>
       </c>
       <c r="AH6" t="n">
-        <v>19297012.98701298</v>
+        <v>19569044.99540863</v>
       </c>
       <c r="AI6" t="n">
-        <v>80.86623376623376</v>
+        <v>80.84508723599632</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25.58181818181818</v>
+        <v>25.4010878010878</v>
       </c>
       <c r="AK6" t="n">
-        <v>179.8858585858586</v>
+        <v>179.6252525252525</v>
       </c>
       <c r="AL6" t="n">
         <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>72.85151515151513</v>
+        <v>72.87241647241646</v>
       </c>
       <c r="AN6" t="n">
-        <v>4461515.151515152</v>
+        <v>4502587.412587413</v>
       </c>
       <c r="AO6" t="n">
-        <v>76.05151515151516</v>
+        <v>76.17327117327117</v>
       </c>
       <c r="AP6" t="n">
-        <v>26.38588435374149</v>
+        <v>25.93938837842</v>
       </c>
       <c r="AQ6" t="n">
-        <v>181.6767006802721</v>
+        <v>181.7123021576579</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.45578231292517</v>
+        <v>1.376706363465257</v>
       </c>
       <c r="AS6" t="n">
-        <v>74.61751700680271</v>
+        <v>73.46484223944698</v>
       </c>
       <c r="AT6" t="n">
-        <v>14065216.83673469</v>
+        <v>11454052.22823948</v>
       </c>
       <c r="AU6" t="n">
-        <v>78.84982993197279</v>
+        <v>78.16608533100629</v>
       </c>
       <c r="AV6" t="n">
-        <v>24.99860214617248</v>
+        <v>24.91974415184134</v>
       </c>
       <c r="AW6" t="n">
-        <v>179.0143939701485</v>
+        <v>179.0702772078731</v>
       </c>
       <c r="AX6" t="n">
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>71.03804990595273</v>
+        <v>71.12043365841319</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3125080.210828293</v>
+        <v>3210330.255848159</v>
       </c>
       <c r="BA6" t="n">
-        <v>75.40307446650156</v>
+        <v>75.60448554003541</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1584,76 +1584,76 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>25.35</v>
+        <v>25.17090909090909</v>
       </c>
       <c r="AE7" t="n">
-        <v>184.9666666666667</v>
+        <v>185.1763636363636</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.283333333333333</v>
+        <v>1.296363636363636</v>
       </c>
       <c r="AG7" t="n">
-        <v>75.14999999999999</v>
+        <v>74.98636363636363</v>
       </c>
       <c r="AH7" t="n">
-        <v>8915000</v>
+        <v>8798454.545454545</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.75</v>
+        <v>78.77272727272728</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24.14285714285714</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AK7" t="n">
-        <v>181.1857142857143</v>
+        <v>181.4909090909091</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.171428571428571</v>
+        <v>1.163636363636364</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>74.9909090909091</v>
       </c>
       <c r="AN7" t="n">
-        <v>8875714.285714285</v>
+        <v>8609090.909090908</v>
       </c>
       <c r="AO7" t="n">
-        <v>79.10000000000001</v>
+        <v>78.98181818181818</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.71211180124224</v>
+        <v>24.67810132748751</v>
       </c>
       <c r="AQ7" t="n">
-        <v>185.6461525189786</v>
+        <v>185.0450657654366</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.416873706004141</v>
+        <v>1.437178175618073</v>
       </c>
       <c r="AS7" t="n">
-        <v>75.14817115251897</v>
+        <v>75.33199123127511</v>
       </c>
       <c r="AT7" t="n">
-        <v>10341116.28709455</v>
+        <v>10834661.85604677</v>
       </c>
       <c r="AU7" t="n">
-        <v>79.55626293995859</v>
+        <v>79.55631896236756</v>
       </c>
       <c r="AV7" t="n">
-        <v>23.88719119226638</v>
+        <v>23.77900309073078</v>
       </c>
       <c r="AW7" t="n">
-        <v>183.180123061984</v>
+        <v>183.0110664544641</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.324382655773633</v>
+        <v>1.319073547745276</v>
       </c>
       <c r="AY7" t="n">
-        <v>74.30928864368714</v>
+        <v>74.73436945309734</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11108566.51911163</v>
+        <v>11566815.05761649</v>
       </c>
       <c r="BA7" t="n">
-        <v>79.13479776280529</v>
+        <v>79.52728237079704</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -1743,76 +1743,76 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>28.04545454545455</v>
+        <v>27.74545454545455</v>
       </c>
       <c r="AE8" t="n">
-        <v>183.0227272727273</v>
+        <v>183.0772727272727</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.137878787878788</v>
+        <v>2.137272727272728</v>
       </c>
       <c r="AG8" t="n">
-        <v>78.96666666666668</v>
+        <v>79.08000000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>18462727.27272728</v>
+        <v>19071272.72727273</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.37272727272727</v>
+        <v>80.56</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.31818181818182</v>
+        <v>26.01636363636364</v>
       </c>
       <c r="AK8" t="n">
-        <v>182.2272727272727</v>
+        <v>182.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.166666666666667</v>
+        <v>2.130909090909091</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>79.64181818181819</v>
       </c>
       <c r="AN8" t="n">
-        <v>26416666.66666667</v>
+        <v>25921909.09090909</v>
       </c>
       <c r="AO8" t="n">
-        <v>81.72727272727273</v>
+        <v>81.78272727272727</v>
       </c>
       <c r="AP8" t="n">
-        <v>26.70407223495458</v>
+        <v>27.59664969017911</v>
       </c>
       <c r="AQ8" t="n">
-        <v>181.0974301841949</v>
+        <v>180.8370295390884</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.7021411594941</v>
+        <v>1.714935489347254</v>
       </c>
       <c r="AS8" t="n">
-        <v>73.16779348102878</v>
+        <v>73.76654910449028</v>
       </c>
       <c r="AT8" t="n">
-        <v>9405198.094389269</v>
+        <v>8735370.840760546</v>
       </c>
       <c r="AU8" t="n">
-        <v>77.61812876665819</v>
+        <v>77.36194868856634</v>
       </c>
       <c r="AV8" t="n">
-        <v>23.60212418300654</v>
+        <v>23.59745808468315</v>
       </c>
       <c r="AW8" t="n">
-        <v>183.5383306100218</v>
+        <v>183.2548341148054</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.669458061002179</v>
+        <v>1.71597435350952</v>
       </c>
       <c r="AY8" t="n">
-        <v>73.51463779956428</v>
+        <v>74.03274403239557</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13255655.97766885</v>
+        <v>14507861.58177039</v>
       </c>
       <c r="BA8" t="n">
-        <v>79.18532135076252</v>
+        <v>79.42498508098892</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -1902,76 +1902,76 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>25.96969696969697</v>
+        <v>26.02454545454545</v>
       </c>
       <c r="AE9" t="n">
-        <v>184.2424242424242</v>
+        <v>184.7418181818182</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.060606060606061</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AG9" t="n">
-        <v>76.75757575757575</v>
+        <v>76.45363636363636</v>
       </c>
       <c r="AH9" t="n">
-        <v>12177272.72727273</v>
+        <v>11428000</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.24242424242424</v>
+        <v>78.99636363636364</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25.37662337662337</v>
+        <v>25.70909090909091</v>
       </c>
       <c r="AK9" t="n">
-        <v>183.5064935064935</v>
+        <v>183.6272727272728</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.311688311688312</v>
+        <v>1.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.59740259740259</v>
+        <v>76.56363636363636</v>
       </c>
       <c r="AN9" t="n">
-        <v>14912987.01298702</v>
+        <v>14091818.18181818</v>
       </c>
       <c r="AO9" t="n">
-        <v>80.27272727272727</v>
+        <v>79.99090909090908</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.93897775484463</v>
+        <v>24.76496732026144</v>
       </c>
       <c r="AQ9" t="n">
-        <v>181.2687851163857</v>
+        <v>179.757034743722</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.088361426441922</v>
+        <v>1.097008943928448</v>
       </c>
       <c r="AS9" t="n">
-        <v>73.71160417383328</v>
+        <v>73.67978672170622</v>
       </c>
       <c r="AT9" t="n">
-        <v>7006344.455911019</v>
+        <v>7867469.685242519</v>
       </c>
       <c r="AU9" t="n">
-        <v>77.71218036922372</v>
+        <v>77.52444788441692</v>
       </c>
       <c r="AV9" t="n">
-        <v>26.69557823129252</v>
+        <v>26.66244824016563</v>
       </c>
       <c r="AW9" t="n">
-        <v>184.0051020408163</v>
+        <v>183.7573757763975</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.151643990929705</v>
+        <v>1.16104209799862</v>
       </c>
       <c r="AY9" t="n">
-        <v>73.31689342403628</v>
+        <v>72.87970583160799</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7812634.637188209</v>
+        <v>7252254.572118702</v>
       </c>
       <c r="BA9" t="n">
-        <v>76.39342403628117</v>
+        <v>76.25773378191857</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2065,76 +2065,76 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>23.37037037037037</v>
+        <v>23.24289044289044</v>
       </c>
       <c r="AE10" t="n">
-        <v>182.9629629629629</v>
+        <v>182.8868686868687</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.740740740740741</v>
+        <v>1.746386946386946</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.95061728395062</v>
+        <v>78.11841491841491</v>
       </c>
       <c r="AH10" t="n">
-        <v>20227160.49382716</v>
+        <v>21256332.55633255</v>
       </c>
       <c r="AI10" t="n">
-        <v>83.22222222222223</v>
+        <v>83.37280497280497</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26.76565656565656</v>
+        <v>26.38671328671328</v>
       </c>
       <c r="AK10" t="n">
-        <v>182.1929292929293</v>
+        <v>182.065034965035</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.192929292929293</v>
+        <v>3.121678321678321</v>
       </c>
       <c r="AM10" t="n">
-        <v>85.67878787878789</v>
+        <v>85.28811188811189</v>
       </c>
       <c r="AN10" t="n">
-        <v>73944444.44444445</v>
+        <v>73051048.95104894</v>
       </c>
       <c r="AO10" t="n">
-        <v>87.66161616161617</v>
+        <v>87.51888111888113</v>
       </c>
       <c r="AP10" t="n">
-        <v>23.29223676619019</v>
+        <v>23.17863676384339</v>
       </c>
       <c r="AQ10" t="n">
-        <v>182.991007538782</v>
+        <v>183.0455706069853</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.664198104948318</v>
+        <v>1.688413738487773</v>
       </c>
       <c r="AS10" t="n">
-        <v>73.58580744704943</v>
+        <v>73.53604547439519</v>
       </c>
       <c r="AT10" t="n">
-        <v>15699310.74591807</v>
+        <v>14727417.07896507</v>
       </c>
       <c r="AU10" t="n">
-        <v>81.25842083206241</v>
+        <v>81.36645894375737</v>
       </c>
       <c r="AV10" t="n">
-        <v>24.73680462523173</v>
+        <v>24.62386409413264</v>
       </c>
       <c r="AW10" t="n">
-        <v>178.4747983734557</v>
+        <v>178.2281894363097</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.287436794363478</v>
+        <v>2.240149627297965</v>
       </c>
       <c r="AY10" t="n">
-        <v>80.52642006883269</v>
+        <v>80.12656489574647</v>
       </c>
       <c r="AZ10" t="n">
-        <v>45324903.13355616</v>
+        <v>44309382.41071233</v>
       </c>
       <c r="BA10" t="n">
-        <v>85.15352316449929</v>
+        <v>84.95858003178977</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2228,76 +2228,76 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>26.54222222222222</v>
+        <v>26.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>182.9355555555555</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.437777777777778</v>
+        <v>1.376666666666666</v>
       </c>
       <c r="AG11" t="n">
-        <v>75.77777777777779</v>
+        <v>75.83222222222223</v>
       </c>
       <c r="AH11" t="n">
-        <v>9330666.666666668</v>
+        <v>9670666.666666668</v>
       </c>
       <c r="AI11" t="n">
-        <v>77.97999999999999</v>
+        <v>78.07333333333334</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24.82222222222222</v>
+        <v>24.93863636363636</v>
       </c>
       <c r="AK11" t="n">
-        <v>185.0222222222222</v>
+        <v>184.5810606060606</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.080952380952381</v>
+        <v>2.127272727272727</v>
       </c>
       <c r="AM11" t="n">
-        <v>81.75873015873016</v>
+        <v>81.80732323232324</v>
       </c>
       <c r="AN11" t="n">
-        <v>39775396.82539683</v>
+        <v>39996590.90909091</v>
       </c>
       <c r="AO11" t="n">
-        <v>85.15873015873015</v>
+        <v>85.0719696969697</v>
       </c>
       <c r="AP11" t="n">
-        <v>25.79523407449104</v>
+        <v>26.01794670757518</v>
       </c>
       <c r="AQ11" t="n">
-        <v>180.6265644056666</v>
+        <v>180.5710586369255</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.432751665259405</v>
+        <v>1.44720815819887</v>
       </c>
       <c r="AS11" t="n">
-        <v>73.36212121212121</v>
+        <v>73.5077707380339</v>
       </c>
       <c r="AT11" t="n">
-        <v>5901368.3272352</v>
+        <v>6010473.387551561</v>
       </c>
       <c r="AU11" t="n">
-        <v>76.56431184914156</v>
+        <v>76.21212069664082</v>
       </c>
       <c r="AV11" t="n">
-        <v>24.29394740352281</v>
+        <v>24.56761627370971</v>
       </c>
       <c r="AW11" t="n">
-        <v>181.2892266555745</v>
+        <v>181.8566231806627</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.69359191044839</v>
+        <v>1.791435702162553</v>
       </c>
       <c r="AY11" t="n">
-        <v>78.2360417851351</v>
+        <v>78.66044060077272</v>
       </c>
       <c r="AZ11" t="n">
-        <v>26775963.66397436</v>
+        <v>27633789.15570505</v>
       </c>
       <c r="BA11" t="n">
-        <v>81.92414421909113</v>
+        <v>82.04775332635592</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
@@ -2391,76 +2391,76 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>25.90925925925926</v>
+        <v>25.64769921436588</v>
       </c>
       <c r="AE12" t="n">
-        <v>182.1851851851852</v>
+        <v>182.0516273849607</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.383333333333333</v>
+        <v>1.375645342312009</v>
       </c>
       <c r="AG12" t="n">
-        <v>75.48333333333333</v>
+        <v>75.46588103254768</v>
       </c>
       <c r="AH12" t="n">
-        <v>9138518.518518519</v>
+        <v>9438698.092031427</v>
       </c>
       <c r="AI12" t="n">
-        <v>79.95370370370371</v>
+        <v>80.13187429854096</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24.8304152637486</v>
+        <v>24.67163947163948</v>
       </c>
       <c r="AK12" t="n">
-        <v>184.7519640852974</v>
+        <v>185.0277389277389</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.205387205387205</v>
+        <v>2.211188811188811</v>
       </c>
       <c r="AM12" t="n">
-        <v>79.83468013468013</v>
+        <v>79.83682983682982</v>
       </c>
       <c r="AN12" t="n">
-        <v>29310575.19640853</v>
+        <v>29763282.82828283</v>
       </c>
       <c r="AO12" t="n">
-        <v>84.34489337822671</v>
+        <v>84.43939393939394</v>
       </c>
       <c r="AP12" t="n">
-        <v>23.25999373433584</v>
+        <v>23.40342418546366</v>
       </c>
       <c r="AQ12" t="n">
-        <v>177.9137531328321</v>
+        <v>177.98210839599</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.392794486215539</v>
+        <v>1.39187343358396</v>
       </c>
       <c r="AS12" t="n">
-        <v>73.05354010025061</v>
+        <v>73.16341791979949</v>
       </c>
       <c r="AT12" t="n">
-        <v>8297991.854636592</v>
+        <v>8325323.621553885</v>
       </c>
       <c r="AU12" t="n">
-        <v>80.37728696741854</v>
+        <v>80.35131892230577</v>
       </c>
       <c r="AV12" t="n">
-        <v>24.03719336219336</v>
+        <v>24.46480536371841</v>
       </c>
       <c r="AW12" t="n">
-        <v>184.0678691678692</v>
+        <v>184.1148421626683</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.776952060285394</v>
+        <v>1.877837862620471</v>
       </c>
       <c r="AY12" t="n">
-        <v>74.70817299983966</v>
+        <v>75.41296034882991</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17920840.24771525</v>
+        <v>18948707.12801691</v>
       </c>
       <c r="BA12" t="n">
-        <v>81.42019400352734</v>
+        <v>81.54998938259807</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -2554,76 +2554,76 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>25.37662337662337</v>
+        <v>25.70909090909091</v>
       </c>
       <c r="AE13" t="n">
-        <v>183.5064935064935</v>
+        <v>183.6272727272728</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.311688311688312</v>
+        <v>1.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>76.59740259740259</v>
+        <v>76.56363636363636</v>
       </c>
       <c r="AH13" t="n">
-        <v>14912987.01298702</v>
+        <v>14091818.18181818</v>
       </c>
       <c r="AI13" t="n">
-        <v>80.27272727272727</v>
+        <v>79.99090909090908</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28.04545454545455</v>
+        <v>27.74545454545455</v>
       </c>
       <c r="AK13" t="n">
-        <v>183.0227272727273</v>
+        <v>183.0772727272727</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.137878787878788</v>
+        <v>2.137272727272728</v>
       </c>
       <c r="AM13" t="n">
-        <v>78.96666666666668</v>
+        <v>79.08000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>18462727.27272728</v>
+        <v>19071272.72727273</v>
       </c>
       <c r="AO13" t="n">
-        <v>80.37272727272727</v>
+        <v>80.56</v>
       </c>
       <c r="AP13" t="n">
-        <v>26.69557823129252</v>
+        <v>26.66244824016563</v>
       </c>
       <c r="AQ13" t="n">
-        <v>184.0051020408163</v>
+        <v>183.7573757763975</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.151643990929705</v>
+        <v>1.16104209799862</v>
       </c>
       <c r="AS13" t="n">
-        <v>73.31689342403628</v>
+        <v>72.87970583160799</v>
       </c>
       <c r="AT13" t="n">
-        <v>7812634.637188209</v>
+        <v>7252254.572118702</v>
       </c>
       <c r="AU13" t="n">
-        <v>76.39342403628117</v>
+        <v>76.25773378191857</v>
       </c>
       <c r="AV13" t="n">
-        <v>26.70407223495458</v>
+        <v>27.59664969017911</v>
       </c>
       <c r="AW13" t="n">
-        <v>181.0974301841949</v>
+        <v>180.8370295390884</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.7021411594941</v>
+        <v>1.714935489347254</v>
       </c>
       <c r="AY13" t="n">
-        <v>73.16779348102878</v>
+        <v>73.76654910449028</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9405198.094389269</v>
+        <v>8735370.840760546</v>
       </c>
       <c r="BA13" t="n">
-        <v>77.61812876665819</v>
+        <v>77.36194868856634</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
@@ -2713,76 +2713,76 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>26.98787878787879</v>
+        <v>26.85545454545455</v>
       </c>
       <c r="AE14" t="n">
-        <v>183.8787878787879</v>
+        <v>184.2227272727273</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.539393939393939</v>
+        <v>1.527272727272727</v>
       </c>
       <c r="AG14" t="n">
-        <v>77.06818181818181</v>
+        <v>77.10545454545453</v>
       </c>
       <c r="AH14" t="n">
-        <v>12800303.03030303</v>
+        <v>12927636.36363636</v>
       </c>
       <c r="AI14" t="n">
-        <v>78.9621212121212</v>
+        <v>79.16454545454545</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26.54222222222222</v>
+        <v>26.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>182.9355555555555</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.437777777777778</v>
+        <v>1.376666666666666</v>
       </c>
       <c r="AM14" t="n">
-        <v>75.77777777777779</v>
+        <v>75.83222222222223</v>
       </c>
       <c r="AN14" t="n">
-        <v>9330666.666666668</v>
+        <v>9670666.666666668</v>
       </c>
       <c r="AO14" t="n">
-        <v>77.97999999999999</v>
+        <v>78.07333333333334</v>
       </c>
       <c r="AP14" t="n">
-        <v>27.909047314578</v>
+        <v>28.21626172208014</v>
       </c>
       <c r="AQ14" t="n">
-        <v>181.4587702472294</v>
+        <v>181.2419288150043</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.271824381926684</v>
+        <v>1.308927962489344</v>
       </c>
       <c r="AS14" t="n">
-        <v>74.93484299516908</v>
+        <v>74.99781055900621</v>
       </c>
       <c r="AT14" t="n">
-        <v>7066695.439045183</v>
+        <v>6886981.549141395</v>
       </c>
       <c r="AU14" t="n">
-        <v>76.3639634839443</v>
+        <v>76.14754475703324</v>
       </c>
       <c r="AV14" t="n">
-        <v>25.79523407449104</v>
+        <v>26.01794670757518</v>
       </c>
       <c r="AW14" t="n">
-        <v>180.6265644056666</v>
+        <v>180.5710586369255</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.432751665259405</v>
+        <v>1.44720815819887</v>
       </c>
       <c r="AY14" t="n">
-        <v>73.36212121212121</v>
+        <v>73.5077707380339</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5901368.3272352</v>
+        <v>6010473.387551561</v>
       </c>
       <c r="BA14" t="n">
-        <v>76.56431184914156</v>
+        <v>76.21212069664082</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -2876,76 +2876,76 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
-        <v>26.76565656565656</v>
+        <v>26.38671328671328</v>
       </c>
       <c r="AE15" t="n">
-        <v>182.1929292929293</v>
+        <v>182.065034965035</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.192929292929293</v>
+        <v>3.121678321678321</v>
       </c>
       <c r="AG15" t="n">
-        <v>85.67878787878789</v>
+        <v>85.28811188811189</v>
       </c>
       <c r="AH15" t="n">
-        <v>73944444.44444445</v>
+        <v>73051048.95104894</v>
       </c>
       <c r="AI15" t="n">
-        <v>87.66161616161617</v>
+        <v>87.51888111888113</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26.18181818181818</v>
+        <v>26.38383838383838</v>
       </c>
       <c r="AK15" t="n">
-        <v>182.6</v>
+        <v>182.6767676767677</v>
       </c>
       <c r="AL15" t="n">
         <v>1</v>
       </c>
       <c r="AM15" t="n">
-        <v>70.63636363636363</v>
+        <v>70.92929292929291</v>
       </c>
       <c r="AN15" t="n">
-        <v>2660000</v>
+        <v>2742424.242424242</v>
       </c>
       <c r="AO15" t="n">
-        <v>74.38181818181819</v>
+        <v>74.38383838383839</v>
       </c>
       <c r="AP15" t="n">
-        <v>24.73680462523173</v>
+        <v>24.62386409413264</v>
       </c>
       <c r="AQ15" t="n">
-        <v>178.4747983734557</v>
+        <v>178.2281894363097</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.287436794363478</v>
+        <v>2.240149627297965</v>
       </c>
       <c r="AS15" t="n">
-        <v>80.52642006883269</v>
+        <v>80.12656489574647</v>
       </c>
       <c r="AT15" t="n">
-        <v>45324903.13355616</v>
+        <v>44309382.41071233</v>
       </c>
       <c r="AU15" t="n">
-        <v>85.15352316449929</v>
+        <v>84.95858003178977</v>
       </c>
       <c r="AV15" t="n">
-        <v>25.54166666666666</v>
+        <v>25.1712962962963</v>
       </c>
       <c r="AW15" t="n">
-        <v>183.7595238095238</v>
+        <v>183.2784391534391</v>
       </c>
       <c r="AX15" t="n">
         <v>1</v>
       </c>
       <c r="AY15" t="n">
-        <v>69.40595238095237</v>
+        <v>68.9292328042328</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2243571.428571429</v>
+        <v>2164021.164021164</v>
       </c>
       <c r="BA15" t="n">
-        <v>73.41428571428571</v>
+        <v>73.35515873015873</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
@@ -3031,76 +3031,76 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
-        <v>25.58181818181818</v>
+        <v>25.4010878010878</v>
       </c>
       <c r="AE16" t="n">
-        <v>179.8858585858586</v>
+        <v>179.6252525252525</v>
       </c>
       <c r="AF16" t="n">
         <v>1</v>
       </c>
       <c r="AG16" t="n">
-        <v>72.85151515151513</v>
+        <v>72.87241647241646</v>
       </c>
       <c r="AH16" t="n">
-        <v>4461515.151515152</v>
+        <v>4502587.412587413</v>
       </c>
       <c r="AI16" t="n">
-        <v>76.05151515151516</v>
+        <v>76.17327117327117</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25.35</v>
+        <v>25.17090909090909</v>
       </c>
       <c r="AK16" t="n">
-        <v>184.9666666666667</v>
+        <v>185.1763636363636</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.283333333333333</v>
+        <v>1.296363636363636</v>
       </c>
       <c r="AM16" t="n">
-        <v>75.14999999999999</v>
+        <v>74.98636363636363</v>
       </c>
       <c r="AN16" t="n">
-        <v>8915000</v>
+        <v>8798454.545454545</v>
       </c>
       <c r="AO16" t="n">
-        <v>78.75</v>
+        <v>78.77272727272728</v>
       </c>
       <c r="AP16" t="n">
-        <v>24.99860214617248</v>
+        <v>24.91974415184134</v>
       </c>
       <c r="AQ16" t="n">
-        <v>179.0143939701485</v>
+        <v>179.0702772078731</v>
       </c>
       <c r="AR16" t="n">
         <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>71.03804990595273</v>
+        <v>71.12043365841319</v>
       </c>
       <c r="AT16" t="n">
-        <v>3125080.210828293</v>
+        <v>3210330.255848159</v>
       </c>
       <c r="AU16" t="n">
-        <v>75.40307446650156</v>
+        <v>75.60448554003541</v>
       </c>
       <c r="AV16" t="n">
-        <v>24.71211180124224</v>
+        <v>24.67810132748751</v>
       </c>
       <c r="AW16" t="n">
-        <v>185.6461525189786</v>
+        <v>185.0450657654366</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.416873706004141</v>
+        <v>1.437178175618073</v>
       </c>
       <c r="AY16" t="n">
-        <v>75.14817115251897</v>
+        <v>75.33199123127511</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10341116.28709455</v>
+        <v>10834661.85604677</v>
       </c>
       <c r="BA16" t="n">
-        <v>79.55626293995859</v>
+        <v>79.55631896236756</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -3194,76 +3194,76 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>24.82222222222222</v>
+        <v>24.93863636363636</v>
       </c>
       <c r="AE17" t="n">
-        <v>185.0222222222222</v>
+        <v>184.5810606060606</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.080952380952381</v>
+        <v>2.127272727272727</v>
       </c>
       <c r="AG17" t="n">
-        <v>81.75873015873016</v>
+        <v>81.80732323232324</v>
       </c>
       <c r="AH17" t="n">
-        <v>39775396.82539683</v>
+        <v>39996590.90909091</v>
       </c>
       <c r="AI17" t="n">
-        <v>85.15873015873015</v>
+        <v>85.0719696969697</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27.2987012987013</v>
+        <v>27.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>183.5844155844156</v>
+        <v>183.8545454545455</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.584415584415584</v>
+        <v>1.581818181818181</v>
       </c>
       <c r="AM17" t="n">
-        <v>76.63636363636364</v>
+        <v>76.67272727272727</v>
       </c>
       <c r="AN17" t="n">
-        <v>11137012.98701299</v>
+        <v>11300000</v>
       </c>
       <c r="AO17" t="n">
-        <v>79.14285714285714</v>
+        <v>79.18181818181817</v>
       </c>
       <c r="AP17" t="n">
-        <v>24.29394740352281</v>
+        <v>24.56761627370971</v>
       </c>
       <c r="AQ17" t="n">
-        <v>181.2892266555745</v>
+        <v>181.8566231806627</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.69359191044839</v>
+        <v>1.791435702162553</v>
       </c>
       <c r="AS17" t="n">
-        <v>78.2360417851351</v>
+        <v>78.66044060077272</v>
       </c>
       <c r="AT17" t="n">
-        <v>26775963.66397436</v>
+        <v>27633789.15570505</v>
       </c>
       <c r="AU17" t="n">
-        <v>81.92414421909113</v>
+        <v>82.04775332635592</v>
       </c>
       <c r="AV17" t="n">
-        <v>24.6834255441307</v>
+        <v>25.25395343644704</v>
       </c>
       <c r="AW17" t="n">
-        <v>186.4408633018425</v>
+        <v>186.0413820890675</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.371851349235346</v>
+        <v>1.391129277798076</v>
       </c>
       <c r="AY17" t="n">
-        <v>72.74374445430347</v>
+        <v>73.15978778467908</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6932634.401586722</v>
+        <v>7081649.636666261</v>
       </c>
       <c r="BA17" t="n">
-        <v>77.27155383892689</v>
+        <v>77.1639765761377</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -3353,76 +3353,76 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>26.31818181818182</v>
+        <v>26.01636363636364</v>
       </c>
       <c r="AE18" t="n">
-        <v>182.2272727272727</v>
+        <v>182.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.166666666666667</v>
+        <v>2.130909090909091</v>
       </c>
       <c r="AG18" t="n">
-        <v>80</v>
+        <v>79.64181818181819</v>
       </c>
       <c r="AH18" t="n">
-        <v>26416666.66666667</v>
+        <v>25921909.09090909</v>
       </c>
       <c r="AI18" t="n">
-        <v>81.72727272727273</v>
+        <v>81.78272727272727</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24.33928571428572</v>
+        <v>24.45416666666667</v>
       </c>
       <c r="AK18" t="n">
-        <v>183.1607142857143</v>
+        <v>182.8930555555555</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.257936507936507</v>
+        <v>2.236111111111111</v>
       </c>
       <c r="AM18" t="n">
-        <v>83.58531746031746</v>
+        <v>83.40416666666667</v>
       </c>
       <c r="AN18" t="n">
-        <v>60343253.96825397</v>
+        <v>58345833.33333334</v>
       </c>
       <c r="AO18" t="n">
-        <v>86.49007936507937</v>
+        <v>86.30833333333332</v>
       </c>
       <c r="AP18" t="n">
-        <v>23.60212418300654</v>
+        <v>23.59745808468315</v>
       </c>
       <c r="AQ18" t="n">
-        <v>183.5383306100218</v>
+        <v>183.2548341148054</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.669458061002179</v>
+        <v>1.71597435350952</v>
       </c>
       <c r="AS18" t="n">
-        <v>73.51463779956428</v>
+        <v>74.03274403239557</v>
       </c>
       <c r="AT18" t="n">
-        <v>13255655.97766885</v>
+        <v>14507861.58177039</v>
       </c>
       <c r="AU18" t="n">
-        <v>79.18532135076252</v>
+        <v>79.42498508098892</v>
       </c>
       <c r="AV18" t="n">
-        <v>24.68670913341413</v>
+        <v>24.63040227574283</v>
       </c>
       <c r="AW18" t="n">
-        <v>179.2607856539745</v>
+        <v>179.6681381930763</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.782871043154104</v>
+        <v>1.772715612560814</v>
       </c>
       <c r="AY18" t="n">
-        <v>81.19805051207085</v>
+        <v>81.20040006433194</v>
       </c>
       <c r="AZ18" t="n">
-        <v>36885911.30231997</v>
+        <v>37424843.79397692</v>
       </c>
       <c r="BA18" t="n">
-        <v>84.50300981636674</v>
+        <v>84.53740098910377</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
@@ -3516,76 +3516,76 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
-        <v>24.14285714285714</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AE19" t="n">
-        <v>181.1857142857143</v>
+        <v>181.4909090909091</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.171428571428571</v>
+        <v>1.163636363636364</v>
       </c>
       <c r="AG19" t="n">
-        <v>75</v>
+        <v>74.9909090909091</v>
       </c>
       <c r="AH19" t="n">
-        <v>8875714.285714285</v>
+        <v>8609090.909090908</v>
       </c>
       <c r="AI19" t="n">
-        <v>79.10000000000001</v>
+        <v>78.98181818181818</v>
       </c>
       <c r="AJ19" t="n">
-        <v>26.16363636363636</v>
+        <v>26.40752984389348</v>
       </c>
       <c r="AK19" t="n">
-        <v>185.0428571428572</v>
+        <v>185.4415977961433</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.511688311688312</v>
+        <v>1.544903581267217</v>
       </c>
       <c r="AM19" t="n">
-        <v>77.81688311688312</v>
+        <v>78.01836547291093</v>
       </c>
       <c r="AN19" t="n">
-        <v>19297012.98701298</v>
+        <v>19569044.99540863</v>
       </c>
       <c r="AO19" t="n">
-        <v>80.86623376623376</v>
+        <v>80.84508723599632</v>
       </c>
       <c r="AP19" t="n">
-        <v>23.88719119226638</v>
+        <v>23.77900309073078</v>
       </c>
       <c r="AQ19" t="n">
-        <v>183.180123061984</v>
+        <v>183.0110664544641</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.324382655773633</v>
+        <v>1.319073547745276</v>
       </c>
       <c r="AS19" t="n">
-        <v>74.30928864368714</v>
+        <v>74.73436945309734</v>
       </c>
       <c r="AT19" t="n">
-        <v>11108566.51911163</v>
+        <v>11566815.05761649</v>
       </c>
       <c r="AU19" t="n">
-        <v>79.13479776280529</v>
+        <v>79.52728237079704</v>
       </c>
       <c r="AV19" t="n">
-        <v>26.38588435374149</v>
+        <v>25.93938837842</v>
       </c>
       <c r="AW19" t="n">
-        <v>181.6767006802721</v>
+        <v>181.7123021576579</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.45578231292517</v>
+        <v>1.376706363465257</v>
       </c>
       <c r="AY19" t="n">
-        <v>74.61751700680271</v>
+        <v>73.46484223944698</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14065216.83673469</v>
+        <v>11454052.22823948</v>
       </c>
       <c r="BA19" t="n">
-        <v>78.84982993197279</v>
+        <v>78.16608533100629</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
@@ -3675,76 +3675,76 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
-        <v>26.13095238095238</v>
+        <v>26.32916666666666</v>
       </c>
       <c r="AE20" t="n">
-        <v>182.890873015873</v>
+        <v>182.9236111111111</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.432539682539682</v>
+        <v>1.452777777777778</v>
       </c>
       <c r="AG20" t="n">
-        <v>76.48015873015872</v>
+        <v>76.4986111111111</v>
       </c>
       <c r="AH20" t="n">
-        <v>12462748.01587302</v>
+        <v>12162673.61111111</v>
       </c>
       <c r="AI20" t="n">
-        <v>79.63492063492063</v>
+        <v>79.63194444444444</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23.37037037037037</v>
+        <v>23.24289044289044</v>
       </c>
       <c r="AK20" t="n">
-        <v>182.9629629629629</v>
+        <v>182.8868686868687</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.740740740740741</v>
+        <v>1.746386946386946</v>
       </c>
       <c r="AM20" t="n">
-        <v>77.95061728395062</v>
+        <v>78.11841491841491</v>
       </c>
       <c r="AN20" t="n">
-        <v>20227160.49382716</v>
+        <v>21256332.55633255</v>
       </c>
       <c r="AO20" t="n">
-        <v>83.22222222222223</v>
+        <v>83.37280497280497</v>
       </c>
       <c r="AP20" t="n">
-        <v>24.39053803339518</v>
+        <v>23.99170791993758</v>
       </c>
       <c r="AQ20" t="n">
-        <v>180.6655307098916</v>
+        <v>181.41839654232</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.304615434690623</v>
+        <v>1.253578850708037</v>
       </c>
       <c r="AS20" t="n">
-        <v>72.18617648016145</v>
+        <v>71.67427660059239</v>
       </c>
       <c r="AT20" t="n">
-        <v>8229149.171630374</v>
+        <v>7717944.827633822</v>
       </c>
       <c r="AU20" t="n">
-        <v>78.60334928229665</v>
+        <v>78.60448020878643</v>
       </c>
       <c r="AV20" t="n">
-        <v>23.29223676619019</v>
+        <v>23.17863676384339</v>
       </c>
       <c r="AW20" t="n">
-        <v>182.991007538782</v>
+        <v>183.0455706069853</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.664198104948318</v>
+        <v>1.688413738487773</v>
       </c>
       <c r="AY20" t="n">
-        <v>73.58580744704943</v>
+        <v>73.53604547439519</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15699310.74591807</v>
+        <v>14727417.07896507</v>
       </c>
       <c r="BA20" t="n">
-        <v>81.25842083206241</v>
+        <v>81.36645894375737</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
@@ -3834,76 +3834,76 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
-        <v>25.98051948051948</v>
+        <v>25.75619834710744</v>
       </c>
       <c r="AE21" t="n">
-        <v>183.0506493506494</v>
+        <v>183.3545454545454</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.719480519480519</v>
+        <v>2.614876033057851</v>
       </c>
       <c r="AG21" t="n">
-        <v>83.32987012987012</v>
+        <v>82.74710743801653</v>
       </c>
       <c r="AH21" t="n">
-        <v>49383506.49350649</v>
+        <v>46462231.40495867</v>
       </c>
       <c r="AI21" t="n">
-        <v>85.83766233766232</v>
+        <v>85.53305785123966</v>
       </c>
       <c r="AJ21" t="n">
-        <v>25.96969696969697</v>
+        <v>26.02454545454545</v>
       </c>
       <c r="AK21" t="n">
-        <v>184.2424242424242</v>
+        <v>184.7418181818182</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.060606060606061</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AM21" t="n">
-        <v>76.75757575757575</v>
+        <v>76.45363636363636</v>
       </c>
       <c r="AN21" t="n">
-        <v>12177272.72727273</v>
+        <v>11428000</v>
       </c>
       <c r="AO21" t="n">
-        <v>79.24242424242424</v>
+        <v>78.99636363636364</v>
       </c>
       <c r="AP21" t="n">
-        <v>23.53863501922508</v>
+        <v>23.20834551211789</v>
       </c>
       <c r="AQ21" t="n">
-        <v>183.8861653356995</v>
+        <v>183.2271528769611</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.908865720201124</v>
+        <v>1.786762491557889</v>
       </c>
       <c r="AS21" t="n">
-        <v>80.12463028689737</v>
+        <v>79.20719904562615</v>
       </c>
       <c r="AT21" t="n">
-        <v>35981939.5149364</v>
+        <v>33498280.27258334</v>
       </c>
       <c r="AU21" t="n">
-        <v>84.71469239869862</v>
+        <v>84.38545991519138</v>
       </c>
       <c r="AV21" t="n">
-        <v>24.93897775484463</v>
+        <v>24.76496732026144</v>
       </c>
       <c r="AW21" t="n">
-        <v>181.2687851163857</v>
+        <v>179.757034743722</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.088361426441922</v>
+        <v>1.097008943928448</v>
       </c>
       <c r="AY21" t="n">
-        <v>73.71160417383328</v>
+        <v>73.67978672170622</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7006344.455911019</v>
+        <v>7867469.685242519</v>
       </c>
       <c r="BA21" t="n">
-        <v>77.71218036922372</v>
+        <v>77.52444788441692</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
@@ -4025,76 +4025,76 @@
         <v>82</v>
       </c>
       <c r="AD22" t="n">
-        <v>26.76565656565656</v>
+        <v>26.38671328671328</v>
       </c>
       <c r="AE22" t="n">
-        <v>182.1929292929293</v>
+        <v>182.065034965035</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.192929292929293</v>
+        <v>3.121678321678321</v>
       </c>
       <c r="AG22" t="n">
-        <v>85.67878787878789</v>
+        <v>85.28811188811189</v>
       </c>
       <c r="AH22" t="n">
-        <v>73944444.44444445</v>
+        <v>73051048.95104894</v>
       </c>
       <c r="AI22" t="n">
-        <v>87.66161616161617</v>
+        <v>87.51888111888113</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24.8304152637486</v>
+        <v>24.67163947163948</v>
       </c>
       <c r="AK22" t="n">
-        <v>184.7519640852974</v>
+        <v>185.0277389277389</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.205387205387205</v>
+        <v>2.211188811188811</v>
       </c>
       <c r="AM22" t="n">
-        <v>79.83468013468013</v>
+        <v>79.83682983682982</v>
       </c>
       <c r="AN22" t="n">
-        <v>29310575.19640853</v>
+        <v>29763282.82828283</v>
       </c>
       <c r="AO22" t="n">
-        <v>84.34489337822671</v>
+        <v>84.43939393939394</v>
       </c>
       <c r="AP22" t="n">
-        <v>24.73680462523173</v>
+        <v>24.62386409413264</v>
       </c>
       <c r="AQ22" t="n">
-        <v>178.4747983734557</v>
+        <v>178.2281894363097</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.287436794363478</v>
+        <v>2.240149627297965</v>
       </c>
       <c r="AS22" t="n">
-        <v>80.52642006883269</v>
+        <v>80.12656489574647</v>
       </c>
       <c r="AT22" t="n">
-        <v>45324903.13355616</v>
+        <v>44309382.41071233</v>
       </c>
       <c r="AU22" t="n">
-        <v>85.15352316449929</v>
+        <v>84.95858003178977</v>
       </c>
       <c r="AV22" t="n">
-        <v>24.03719336219336</v>
+        <v>24.46480536371841</v>
       </c>
       <c r="AW22" t="n">
-        <v>184.0678691678692</v>
+        <v>184.1148421626683</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.776952060285394</v>
+        <v>1.877837862620471</v>
       </c>
       <c r="AY22" t="n">
-        <v>74.70817299983966</v>
+        <v>75.41296034882991</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17920840.24771525</v>
+        <v>18948707.12801691</v>
       </c>
       <c r="BA22" t="n">
-        <v>81.42019400352734</v>
+        <v>81.54998938259807</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
@@ -4186,22 +4186,22 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="n">
-        <v>24.62666666666667</v>
+        <v>24.90684624017957</v>
       </c>
       <c r="AK23" t="n">
-        <v>184.2866666666667</v>
+        <v>184.3325476992144</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>69.97999999999999</v>
+        <v>69.90381593714928</v>
       </c>
       <c r="AN23" t="n">
-        <v>2589166.666666667</v>
+        <v>2453782.2671156</v>
       </c>
       <c r="AO23" t="n">
-        <v>74.35333333333332</v>
+        <v>73.80145903479236</v>
       </c>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
@@ -4210,22 +4210,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="n">
-        <v>23.95377450980392</v>
+        <v>24.34125580183764</v>
       </c>
       <c r="AW23" t="n">
-        <v>181.6146218487395</v>
+        <v>181.1732869637388</v>
       </c>
       <c r="AX23" t="n">
         <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>68.57328431372549</v>
+        <v>69.11514753244293</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2240687.5</v>
+        <v>2331285.452385463</v>
       </c>
       <c r="BA23" t="n">
-        <v>73.94286414565826</v>
+        <v>73.754784965516</v>
       </c>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr">
@@ -4411,22 +4411,22 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="n">
-        <v>25.25090909090909</v>
+        <v>25.27171717171717</v>
       </c>
       <c r="AK25" t="n">
-        <v>180.46</v>
+        <v>180.3484848484849</v>
       </c>
       <c r="AL25" t="n">
         <v>1</v>
       </c>
       <c r="AM25" t="n">
-        <v>70.05454545454546</v>
+        <v>70.13434343434344</v>
       </c>
       <c r="AN25" t="n">
-        <v>2271181.818181818</v>
+        <v>2279545.454545455</v>
       </c>
       <c r="AO25" t="n">
-        <v>73</v>
+        <v>72.85858585858585</v>
       </c>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
@@ -4435,22 +4435,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AU25" t="inlineStr"/>
       <c r="AV25" t="n">
-        <v>22.66086834733894</v>
+        <v>22.55570127040715</v>
       </c>
       <c r="AW25" t="n">
-        <v>178.889943977591</v>
+        <v>179.4922808854182</v>
       </c>
       <c r="AX25" t="n">
         <v>1</v>
       </c>
       <c r="AY25" t="n">
-        <v>66.50061624649859</v>
+        <v>66.46308085523772</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1707802.521008403</v>
+        <v>1685528.617170774</v>
       </c>
       <c r="BA25" t="n">
-        <v>74.68554621848739</v>
+        <v>74.5027445321563</v>
       </c>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr">
@@ -4724,76 +4724,76 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="n">
-        <v>23.27833333333333</v>
+        <v>23.49043209876543</v>
       </c>
       <c r="AE28" t="n">
-        <v>181.4555555555556</v>
+        <v>181.3580246913581</v>
       </c>
       <c r="AF28" t="n">
         <v>1</v>
       </c>
       <c r="AG28" t="n">
-        <v>68.54833333333333</v>
+        <v>68.49228395061729</v>
       </c>
       <c r="AH28" t="n">
-        <v>2086388.888888889</v>
+        <v>2085277.777777778</v>
       </c>
       <c r="AI28" t="n">
-        <v>74.43666666666665</v>
+        <v>74.39814814814814</v>
       </c>
       <c r="AJ28" t="n">
-        <v>23.94953703703704</v>
+        <v>24.0270202020202</v>
       </c>
       <c r="AK28" t="n">
-        <v>182.4611111111111</v>
+        <v>182.9878787878788</v>
       </c>
       <c r="AL28" t="n">
         <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>71.30925925925926</v>
+        <v>71.37777777777778</v>
       </c>
       <c r="AN28" t="n">
-        <v>4234398.148148148</v>
+        <v>4276035.353535353</v>
       </c>
       <c r="AO28" t="n">
-        <v>77.05787037037037</v>
+        <v>77.02247474747475</v>
       </c>
       <c r="AP28" t="n">
-        <v>25.56422647527911</v>
+        <v>25.45071563362495</v>
       </c>
       <c r="AQ28" t="n">
-        <v>180.4274276600593</v>
+        <v>180.7722597858843</v>
       </c>
       <c r="AR28" t="n">
         <v>1</v>
       </c>
       <c r="AS28" t="n">
-        <v>66.56537024379129</v>
+        <v>66.73589528084078</v>
       </c>
       <c r="AT28" t="n">
-        <v>1523308.213716109</v>
+        <v>1507482.153084365</v>
       </c>
       <c r="AU28" t="n">
-        <v>72.16408976987925</v>
+        <v>72.08976222730654</v>
       </c>
       <c r="AV28" t="n">
-        <v>24.21392069188122</v>
+        <v>23.99001068708007</v>
       </c>
       <c r="AW28" t="n">
-        <v>181.362882585251</v>
+        <v>180.4038447526767</v>
       </c>
       <c r="AX28" t="n">
         <v>1</v>
       </c>
       <c r="AY28" t="n">
-        <v>68.85962966127441</v>
+        <v>68.91866486548446</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2841603.072548795</v>
+        <v>2900399.877733909</v>
       </c>
       <c r="BA28" t="n">
-        <v>74.73043878635984</v>
+        <v>74.99889274343258</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
@@ -5073,22 +5073,22 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="n">
-        <v>27.775</v>
+        <v>27.89506172839506</v>
       </c>
       <c r="AK31" t="n">
-        <v>183.075</v>
+        <v>183.2382716049383</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.15</v>
+        <v>1.180246913580247</v>
       </c>
       <c r="AM31" t="n">
-        <v>70.75</v>
+        <v>70.78148148148148</v>
       </c>
       <c r="AN31" t="n">
-        <v>1883125</v>
+        <v>1844351.851851852</v>
       </c>
       <c r="AO31" t="n">
-        <v>71.875</v>
+        <v>71.97037037037038</v>
       </c>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
@@ -5097,22 +5097,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="n">
-        <v>25.87747035573123</v>
+        <v>25.76646444931207</v>
       </c>
       <c r="AW31" t="n">
-        <v>180.7192193675889</v>
+        <v>180.8710395957149</v>
       </c>
       <c r="AX31" t="n">
         <v>1</v>
       </c>
       <c r="AY31" t="n">
-        <v>67.48399209486166</v>
+        <v>67.80830153398298</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1440606.472332016</v>
+        <v>1547658.105741083</v>
       </c>
       <c r="BA31" t="n">
-        <v>71.62406126482213</v>
+        <v>71.82582312898809</v>
       </c>
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr">
@@ -5193,22 +5193,22 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="n">
-        <v>26.23636363636364</v>
+        <v>26.26262626262626</v>
       </c>
       <c r="AE32" t="n">
-        <v>183.14</v>
+        <v>182.9969696969697</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>69.61272727272726</v>
+        <v>70.11818181818181</v>
       </c>
       <c r="AH32" t="n">
-        <v>2000727.272727273</v>
+        <v>2092323.232323233</v>
       </c>
       <c r="AI32" t="n">
-        <v>72.11818181818182</v>
+        <v>72.40909090909092</v>
       </c>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
@@ -5217,22 +5217,22 @@
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="n">
-        <v>23.96913116123642</v>
+        <v>24.25657198551935</v>
       </c>
       <c r="AQ32" t="n">
-        <v>183.0489974937344</v>
+        <v>182.6230762090412</v>
       </c>
       <c r="AR32" t="n">
         <v>1</v>
       </c>
       <c r="AS32" t="n">
-        <v>63.85096073517127</v>
+        <v>65.57213868003343</v>
       </c>
       <c r="AT32" t="n">
-        <v>1251822.263993317</v>
+        <v>1558220.922677063</v>
       </c>
       <c r="AU32" t="n">
-        <v>69.6452798663325</v>
+        <v>70.97453819734521</v>
       </c>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr"/>
@@ -5330,22 +5330,22 @@
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="n">
-        <v>24.85454545454545</v>
+        <v>24.47474747474747</v>
       </c>
       <c r="AK33" t="n">
-        <v>182</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AL33" t="n">
         <v>1</v>
       </c>
       <c r="AM33" t="n">
-        <v>69.23636363636362</v>
+        <v>69.13131313131312</v>
       </c>
       <c r="AN33" t="n">
-        <v>2081818.181818182</v>
+        <v>2141616.161616162</v>
       </c>
       <c r="AO33" t="n">
-        <v>73.70909090909092</v>
+        <v>74.1919191919192</v>
       </c>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr"/>
@@ -5354,22 +5354,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AU33" t="inlineStr"/>
       <c r="AV33" t="n">
-        <v>26.38111111111111</v>
+        <v>26.44585537918872</v>
       </c>
       <c r="AW33" t="n">
-        <v>179.0461111111111</v>
+        <v>179.6592151675485</v>
       </c>
       <c r="AX33" t="n">
         <v>1</v>
       </c>
       <c r="AY33" t="n">
-        <v>67.81277777777778</v>
+        <v>67.66053791887126</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1509055.555555556</v>
+        <v>1459809.30335097</v>
       </c>
       <c r="BA33" t="n">
-        <v>71.21666666666667</v>
+        <v>70.87566137566138</v>
       </c>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr">
@@ -5739,22 +5739,22 @@
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="n">
-        <v>27.44285714285714</v>
+        <v>27.51818181818182</v>
       </c>
       <c r="AK37" t="n">
-        <v>185.4142857142857</v>
+        <v>185.3181818181818</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.042857142857143</v>
+        <v>1.027272727272727</v>
       </c>
       <c r="AM37" t="n">
-        <v>71.28571428571429</v>
+        <v>71.31818181818181</v>
       </c>
       <c r="AN37" t="n">
-        <v>2377142.857142857</v>
+        <v>2361818.181818182</v>
       </c>
       <c r="AO37" t="n">
-        <v>72.84285714285714</v>
+        <v>72.76363636363637</v>
       </c>
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr"/>
@@ -5763,22 +5763,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="n">
-        <v>27.976966873706</v>
+        <v>28.02453886693017</v>
       </c>
       <c r="AW37" t="n">
-        <v>184.3819875776397</v>
+        <v>184.4290184453228</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.073757763975155</v>
+        <v>1.08596837944664</v>
       </c>
       <c r="AY37" t="n">
-        <v>70.78933747412009</v>
+        <v>70.62779973649539</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2305822.98136646</v>
+        <v>2226939.229249012</v>
       </c>
       <c r="BA37" t="n">
-        <v>72.48395445134575</v>
+        <v>72.44779314888011</v>
       </c>
       <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="inlineStr">
@@ -5953,22 +5953,22 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>24.56666666666667</v>
+        <v>24.13055555555556</v>
       </c>
       <c r="AE39" t="n">
-        <v>182.7666666666667</v>
+        <v>182.7361111111111</v>
       </c>
       <c r="AF39" t="n">
         <v>1</v>
       </c>
       <c r="AG39" t="n">
-        <v>67.66666666666667</v>
+        <v>67.49305555555554</v>
       </c>
       <c r="AH39" t="n">
-        <v>1674166.666666667</v>
+        <v>1700729.166666667</v>
       </c>
       <c r="AI39" t="n">
-        <v>73.5</v>
+        <v>73.7861111111111</v>
       </c>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
@@ -5977,22 +5977,22 @@
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>23.75438034188034</v>
+        <v>23.75022724189391</v>
       </c>
       <c r="AQ39" t="n">
-        <v>182.5213675213675</v>
+        <v>182.5922347714015</v>
       </c>
       <c r="AR39" t="n">
         <v>1</v>
       </c>
       <c r="AS39" t="n">
-        <v>65.9684829059829</v>
+        <v>66.05305589472256</v>
       </c>
       <c r="AT39" t="n">
-        <v>1425261.752136752</v>
+        <v>1407363.358092525</v>
       </c>
       <c r="AU39" t="n">
-        <v>72.93568376068376</v>
+        <v>73.02994675078008</v>
       </c>
       <c r="AV39" t="inlineStr"/>
       <c r="AW39" t="inlineStr"/>
@@ -6267,22 +6267,22 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="n">
-        <v>26.24074074074074</v>
+        <v>26.11313131313131</v>
       </c>
       <c r="AE42" t="n">
-        <v>182.6092592592593</v>
+        <v>182.3414141414141</v>
       </c>
       <c r="AF42" t="n">
         <v>1</v>
       </c>
       <c r="AG42" t="n">
-        <v>72.28703703703704</v>
+        <v>72.06565656565657</v>
       </c>
       <c r="AH42" t="n">
-        <v>3291481.481481481</v>
+        <v>3219898.98989899</v>
       </c>
       <c r="AI42" t="n">
-        <v>74.7925925925926</v>
+        <v>74.69595959595959</v>
       </c>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
@@ -6291,22 +6291,22 @@
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="n">
-        <v>25.66401416145662</v>
+        <v>25.33131632375994</v>
       </c>
       <c r="AQ42" t="n">
-        <v>184.1604352595402</v>
+        <v>183.8965744787647</v>
       </c>
       <c r="AR42" t="n">
         <v>1</v>
       </c>
       <c r="AS42" t="n">
-        <v>69.05797356948251</v>
+        <v>68.69035579626141</v>
       </c>
       <c r="AT42" t="n">
-        <v>2385473.092551098</v>
+        <v>2330013.589061485</v>
       </c>
       <c r="AU42" t="n">
-        <v>73.27669900432049</v>
+        <v>73.54776135280669</v>
       </c>
       <c r="AV42" t="inlineStr"/>
       <c r="AW42" t="inlineStr"/>
@@ -6498,22 +6498,22 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="n">
-        <v>25.225</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="AK44" t="n">
-        <v>180.375</v>
+        <v>180.2666666666667</v>
       </c>
       <c r="AL44" t="n">
         <v>1</v>
       </c>
       <c r="AM44" t="n">
-        <v>69.625</v>
+        <v>69.95555555555556</v>
       </c>
       <c r="AN44" t="n">
-        <v>2516250</v>
+        <v>2555555.555555556</v>
       </c>
       <c r="AO44" t="n">
-        <v>73.80000000000001</v>
+        <v>73.52222222222223</v>
       </c>
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr"/>
@@ -6522,22 +6522,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AU44" t="inlineStr"/>
       <c r="AV44" t="n">
-        <v>25.91517857142857</v>
+        <v>24.95568783068783</v>
       </c>
       <c r="AW44" t="n">
-        <v>179.2291666666667</v>
+        <v>178.7414021164021</v>
       </c>
       <c r="AX44" t="n">
         <v>1</v>
       </c>
       <c r="AY44" t="n">
-        <v>68.39732142857143</v>
+        <v>67.70899470899471</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1705825.892857143</v>
+        <v>1653740.079365079</v>
       </c>
       <c r="BA44" t="n">
-        <v>72.99702380952381</v>
+        <v>73.59259259259258</v>
       </c>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr">
@@ -6623,76 +6623,76 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="n">
-        <v>26.40388888888889</v>
+        <v>26.72694444444445</v>
       </c>
       <c r="AE45" t="n">
-        <v>184.2966666666667</v>
+        <v>184.4858333333333</v>
       </c>
       <c r="AF45" t="n">
         <v>1</v>
       </c>
       <c r="AG45" t="n">
-        <v>69.84666666666666</v>
+        <v>69.68583333333333</v>
       </c>
       <c r="AH45" t="n">
-        <v>1923208.333333333</v>
+        <v>1839104.166666667</v>
       </c>
       <c r="AI45" t="n">
-        <v>71.90055555555554</v>
+        <v>71.63777777777777</v>
       </c>
       <c r="AJ45" t="n">
-        <v>22.32222222222222</v>
+        <v>21.89506172839506</v>
       </c>
       <c r="AK45" t="n">
-        <v>182.2208333333333</v>
+        <v>182.3719135802469</v>
       </c>
       <c r="AL45" t="n">
         <v>1</v>
       </c>
       <c r="AM45" t="n">
-        <v>69.36041666666667</v>
+        <v>69.24691358024691</v>
       </c>
       <c r="AN45" t="n">
-        <v>3041388.888888889</v>
+        <v>3114567.901234568</v>
       </c>
       <c r="AO45" t="n">
-        <v>77.14861111111111</v>
+        <v>77.61728395061728</v>
       </c>
       <c r="AP45" t="n">
-        <v>23.98512949039265</v>
+        <v>23.60210148296836</v>
       </c>
       <c r="AQ45" t="n">
-        <v>181.6688387635756</v>
+        <v>181.8670150867365</v>
       </c>
       <c r="AR45" t="n">
         <v>1</v>
       </c>
       <c r="AS45" t="n">
-        <v>66.89791144527987</v>
+        <v>66.59040871409293</v>
       </c>
       <c r="AT45" t="n">
-        <v>1655334.168755222</v>
+        <v>1637924.841326544</v>
       </c>
       <c r="AU45" t="n">
-        <v>73.00902255639099</v>
+        <v>73.20230126598548</v>
       </c>
       <c r="AV45" t="n">
-        <v>22.51933932898102</v>
+        <v>22.21220678740702</v>
       </c>
       <c r="AW45" t="n">
-        <v>181.5326192118724</v>
+        <v>181.6666174207953</v>
       </c>
       <c r="AX45" t="n">
         <v>1</v>
       </c>
       <c r="AY45" t="n">
-        <v>66.41822797482837</v>
+        <v>65.95240331644794</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1856002.500757168</v>
+        <v>1715239.003185522</v>
       </c>
       <c r="BA45" t="n">
-        <v>73.95584449454839</v>
+        <v>73.72859889383984</v>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
@@ -6773,22 +6773,22 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="n">
-        <v>26.84</v>
+        <v>26.72222222222222</v>
       </c>
       <c r="AE46" t="n">
-        <v>181.42</v>
+        <v>181.9888888888889</v>
       </c>
       <c r="AF46" t="n">
         <v>1</v>
       </c>
       <c r="AG46" t="n">
-        <v>66.78</v>
+        <v>66.88888888888889</v>
       </c>
       <c r="AH46" t="n">
-        <v>1069000</v>
+        <v>1103055.555555556</v>
       </c>
       <c r="AI46" t="n">
-        <v>69.3</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
@@ -6797,22 +6797,22 @@
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="n">
-        <v>27.01910593792173</v>
+        <v>27.36920026854237</v>
       </c>
       <c r="AQ46" t="n">
-        <v>182.6156713900135</v>
+        <v>182.1784994975784</v>
       </c>
       <c r="AR46" t="n">
         <v>1</v>
       </c>
       <c r="AS46" t="n">
-        <v>65.48793522267206</v>
+        <v>65.48439883703041</v>
       </c>
       <c r="AT46" t="n">
-        <v>908723.2624831309</v>
+        <v>873448.9505377664</v>
       </c>
       <c r="AU46" t="n">
-        <v>68.74245276653171</v>
+        <v>68.24484509155562</v>
       </c>
       <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>
@@ -7087,22 +7087,22 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="n">
-        <v>24.425</v>
+        <v>24.69642857142857</v>
       </c>
       <c r="AE49" t="n">
-        <v>179.825</v>
+        <v>179.9642857142857</v>
       </c>
       <c r="AF49" t="n">
         <v>1</v>
       </c>
       <c r="AG49" t="n">
-        <v>68.925</v>
+        <v>68.98214285714286</v>
       </c>
       <c r="AH49" t="n">
-        <v>1957500</v>
+        <v>1917857.142857143</v>
       </c>
       <c r="AI49" t="n">
-        <v>74.2</v>
+        <v>73.78571428571429</v>
       </c>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
@@ -7111,22 +7111,22 @@
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
       <c r="AP49" t="n">
-        <v>24.29159663865546</v>
+        <v>24.74416482878815</v>
       </c>
       <c r="AQ49" t="n">
-        <v>180.5899074781428</v>
+        <v>179.4199350128143</v>
       </c>
       <c r="AR49" t="n">
         <v>1</v>
       </c>
       <c r="AS49" t="n">
-        <v>67.26384856973092</v>
+        <v>67.58833928751369</v>
       </c>
       <c r="AT49" t="n">
-        <v>1573024.57346575</v>
+        <v>1592468.315520431</v>
       </c>
       <c r="AU49" t="n">
-        <v>72.91500721500722</v>
+        <v>72.91955477920391</v>
       </c>
       <c r="AV49" t="inlineStr"/>
       <c r="AW49" t="inlineStr"/>
@@ -7401,22 +7401,22 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="n">
-        <v>24.13272727272727</v>
+        <v>24.00707070707071</v>
       </c>
       <c r="AE52" t="n">
-        <v>183.5745454545454</v>
+        <v>183.3080808080808</v>
       </c>
       <c r="AF52" t="n">
         <v>1</v>
       </c>
       <c r="AG52" t="n">
-        <v>69.72181818181818</v>
+        <v>69.80101010101011</v>
       </c>
       <c r="AH52" t="n">
-        <v>2470727.272727272</v>
+        <v>2560404.04040404</v>
       </c>
       <c r="AI52" t="n">
-        <v>74.12545454545455</v>
+        <v>74.25858585858585</v>
       </c>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
@@ -7425,22 +7425,22 @@
       <c r="AN52" t="inlineStr"/>
       <c r="AO52" t="inlineStr"/>
       <c r="AP52" t="n">
-        <v>23.81987577639751</v>
+        <v>24.17153592515911</v>
       </c>
       <c r="AQ52" t="n">
-        <v>181.8908385093168</v>
+        <v>182.4535522582624</v>
       </c>
       <c r="AR52" t="n">
         <v>1</v>
       </c>
       <c r="AS52" t="n">
-        <v>68.11199102829536</v>
+        <v>68.52147649720114</v>
       </c>
       <c r="AT52" t="n">
-        <v>2231141.90821256</v>
+        <v>2294251.67740204</v>
       </c>
       <c r="AU52" t="n">
-        <v>74.0976535541753</v>
+        <v>74.13326432022083</v>
       </c>
       <c r="AV52" t="inlineStr"/>
       <c r="AW52" t="inlineStr"/>
@@ -7617,22 +7617,22 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="n">
-        <v>23.98311688311688</v>
+        <v>24.03818181818182</v>
       </c>
       <c r="AE54" t="n">
-        <v>181.8258297258297</v>
+        <v>182.3655808080808</v>
       </c>
       <c r="AF54" t="n">
         <v>1</v>
       </c>
       <c r="AG54" t="n">
-        <v>71.35772005772006</v>
+        <v>71.67818181818181</v>
       </c>
       <c r="AH54" t="n">
-        <v>3959628.427128427</v>
+        <v>4148545.454545455</v>
       </c>
       <c r="AI54" t="n">
-        <v>77.01890331890333</v>
+        <v>77.17017676767678</v>
       </c>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
@@ -7641,22 +7641,22 @@
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
       <c r="AP54" t="n">
-        <v>22.98463994234671</v>
+        <v>23.23972415011889</v>
       </c>
       <c r="AQ54" t="n">
-        <v>179.8157444894287</v>
+        <v>180.0264973330763</v>
       </c>
       <c r="AR54" t="n">
         <v>1</v>
       </c>
       <c r="AS54" t="n">
-        <v>69.08283529336161</v>
+        <v>69.24250851487693</v>
       </c>
       <c r="AT54" t="n">
-        <v>2904845.730971201</v>
+        <v>2863183.678346507</v>
       </c>
       <c r="AU54" t="n">
-        <v>76.49504679739643</v>
+        <v>76.43462799627272</v>
       </c>
       <c r="AV54" t="inlineStr"/>
       <c r="AW54" t="inlineStr"/>
@@ -7748,76 +7748,76 @@
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="n">
-        <v>24.12878787878788</v>
+        <v>24.2050505050505</v>
       </c>
       <c r="AE55" t="n">
-        <v>179.7484848484848</v>
+        <v>179.6383838383839</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.092424242424243</v>
+        <v>1.093939393939394</v>
       </c>
       <c r="AG55" t="n">
-        <v>69.86060606060606</v>
+        <v>70.02121212121213</v>
       </c>
       <c r="AH55" t="n">
-        <v>3053181.818181818</v>
+        <v>3147020.202020202</v>
       </c>
       <c r="AI55" t="n">
-        <v>75.08333333333333</v>
+        <v>75.11414141414143</v>
       </c>
       <c r="AJ55" t="n">
-        <v>27.35</v>
+        <v>26.5979797979798</v>
       </c>
       <c r="AK55" t="n">
-        <v>182.2318181818182</v>
+        <v>182.8343434343434</v>
       </c>
       <c r="AL55" t="n">
         <v>1</v>
       </c>
       <c r="AM55" t="n">
-        <v>67.69090909090909</v>
+        <v>67.42222222222222</v>
       </c>
       <c r="AN55" t="n">
-        <v>1244772.727272727</v>
+        <v>1263005.05050505</v>
       </c>
       <c r="AO55" t="n">
-        <v>70.24090909090908</v>
+        <v>70.77070707070706</v>
       </c>
       <c r="AP55" t="n">
-        <v>25.55430858333672</v>
+        <v>25.63840771413235</v>
       </c>
       <c r="AQ55" t="n">
-        <v>180.6172908293753</v>
+        <v>180.4452573783137</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.025383631713555</v>
+        <v>1.021552050772</v>
       </c>
       <c r="AS55" t="n">
-        <v>70.42968443416014</v>
+        <v>70.2869620472988</v>
       </c>
       <c r="AT55" t="n">
-        <v>3033739.72415053</v>
+        <v>3089030.458801878</v>
       </c>
       <c r="AU55" t="n">
-        <v>74.62547869389302</v>
+        <v>74.53751178410172</v>
       </c>
       <c r="AV55" t="n">
-        <v>25.66213768115942</v>
+        <v>25.73872785829307</v>
       </c>
       <c r="AW55" t="n">
-        <v>185.5788043478261</v>
+        <v>184.6415056360708</v>
       </c>
       <c r="AX55" t="n">
-        <v>1</v>
+        <v>1.013888888888889</v>
       </c>
       <c r="AY55" t="n">
-        <v>66.31929347826087</v>
+        <v>66.65116747181963</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1142900.815217391</v>
+        <v>1734460.547504026</v>
       </c>
       <c r="BA55" t="n">
-        <v>70.20516304347825</v>
+        <v>70.32729468599034</v>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
@@ -7898,22 +7898,22 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="n">
-        <v>24.63636363636364</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AE56" t="n">
-        <v>181.0227272727273</v>
+        <v>181.3535353535354</v>
       </c>
       <c r="AF56" t="n">
         <v>1</v>
       </c>
       <c r="AG56" t="n">
-        <v>68.34090909090909</v>
+        <v>67.95959595959596</v>
       </c>
       <c r="AH56" t="n">
-        <v>2201136.363636364</v>
+        <v>2172727.272727273</v>
       </c>
       <c r="AI56" t="n">
-        <v>73.45454545454545</v>
+        <v>74.01010101010101</v>
       </c>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
@@ -7922,22 +7922,22 @@
       <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
       <c r="AP56" t="n">
-        <v>24.2875</v>
+        <v>24.39139433551198</v>
       </c>
       <c r="AQ56" t="n">
-        <v>181.7586956521739</v>
+        <v>181.0827240558059</v>
       </c>
       <c r="AR56" t="n">
         <v>1</v>
       </c>
       <c r="AS56" t="n">
-        <v>66.35489130434783</v>
+        <v>66.0972330478085</v>
       </c>
       <c r="AT56" t="n">
-        <v>1419211.956521739</v>
+        <v>1361211.57762622</v>
       </c>
       <c r="AU56" t="n">
-        <v>72.69239130434784</v>
+        <v>72.23851845085861</v>
       </c>
       <c r="AV56" t="inlineStr"/>
       <c r="AW56" t="inlineStr"/>
@@ -8033,76 +8033,76 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="n">
-        <v>22.85079365079365</v>
+        <v>23.17887205387206</v>
       </c>
       <c r="AE57" t="n">
-        <v>184.6476190476191</v>
+        <v>184.1732323232323</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.228571428571428</v>
+        <v>1.245454545454545</v>
       </c>
       <c r="AG57" t="n">
-        <v>74.34920634920636</v>
+        <v>74.32415824915824</v>
       </c>
       <c r="AH57" t="n">
-        <v>8823174.603174603</v>
+        <v>8512154.882154882</v>
       </c>
       <c r="AI57" t="n">
-        <v>80.72539682539683</v>
+        <v>80.23905723905726</v>
       </c>
       <c r="AJ57" t="n">
-        <v>23.92</v>
+        <v>24.43333333333333</v>
       </c>
       <c r="AK57" t="n">
-        <v>182.06</v>
+        <v>181.7222222222222</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.08</v>
+        <v>1.088888888888889</v>
       </c>
       <c r="AM57" t="n">
-        <v>69.44</v>
+        <v>70.04444444444445</v>
       </c>
       <c r="AN57" t="n">
-        <v>2448000</v>
+        <v>2534444.444444444</v>
       </c>
       <c r="AO57" t="n">
-        <v>75.74000000000001</v>
+        <v>75.52222222222223</v>
       </c>
       <c r="AP57" t="n">
-        <v>24.64143569708585</v>
+        <v>24.76479582330008</v>
       </c>
       <c r="AQ57" t="n">
-        <v>180.0155910609858</v>
+        <v>180.7338363269284</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.050060813799204</v>
+        <v>1.066326201533245</v>
       </c>
       <c r="AS57" t="n">
-        <v>73.19873273870952</v>
+        <v>73.22166051362065</v>
       </c>
       <c r="AT57" t="n">
-        <v>5531756.044523073</v>
+        <v>5489823.70141039</v>
       </c>
       <c r="AU57" t="n">
-        <v>77.3063399921372</v>
+        <v>77.31830515832064</v>
       </c>
       <c r="AV57" t="n">
-        <v>22.42230672835936</v>
+        <v>22.26671361452063</v>
       </c>
       <c r="AW57" t="n">
-        <v>179.6171274339695</v>
+        <v>179.4508732657856</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.010526315789474</v>
+        <v>1.005847953216374</v>
       </c>
       <c r="AY57" t="n">
-        <v>66.3709649122807</v>
+        <v>66.05732618583495</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1937971.202043571</v>
+        <v>1948601.285085934</v>
       </c>
       <c r="BA57" t="n">
-        <v>74.27317331791016</v>
+        <v>74.2258370284686</v>
       </c>
       <c r="BB57" t="inlineStr">
         <is>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC57"/>
+  <dimension ref="A1:AO56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -766,98 +696,84 @@
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>24.79033189033189</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>184.938455988456</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.243722943722944</v>
+      </c>
+      <c r="S2" t="n">
+        <v>79.93578643578644</v>
+      </c>
+      <c r="T2" t="n">
+        <v>30165111.83261183</v>
+      </c>
+      <c r="U2" t="n">
+        <v>84.41594516594516</v>
+      </c>
+      <c r="V2" t="n">
+        <v>26.85545454545455</v>
+      </c>
+      <c r="W2" t="n">
+        <v>184.2227272727273</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.527272727272727</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>77.10545454545453</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12927636.36363636</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>79.16454545454545</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>24.31999783773852</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>184.0530677224777</v>
+      </c>
       <c r="AD2" t="n">
-        <v>24.67163947163948</v>
+        <v>1.882099443861866</v>
       </c>
       <c r="AE2" t="n">
-        <v>185.0277389277389</v>
+        <v>75.38346318105634</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.211188811188811</v>
+        <v>19021567.33315856</v>
       </c>
       <c r="AG2" t="n">
-        <v>79.83682983682982</v>
+        <v>81.55534728384107</v>
       </c>
       <c r="AH2" t="n">
-        <v>29763282.82828283</v>
+        <v>28.21626172208014</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.43939393939394</v>
+        <v>181.2419288150043</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.85545454545455</v>
+        <v>1.308927962489344</v>
       </c>
       <c r="AK2" t="n">
-        <v>184.2227272727273</v>
+        <v>74.99781055900621</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.527272727272727</v>
+        <v>6886981.549141395</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.10545454545453</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>12927636.36363636</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>79.16454545454545</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>24.46480536371841</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>184.1148421626683</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.877837862620471</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>75.41296034882991</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>18948707.12801691</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>81.54998938259807</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>28.21626172208014</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>181.2419288150043</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.308927962489344</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>74.99781055900621</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6886981.549141395</v>
-      </c>
-      <c r="BA2" t="n">
         <v>76.14754475703324</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -929,98 +845,84 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>26.38383838383838</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>182.6767676767677</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>70.92929292929291</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2742424.242424242</v>
+      </c>
+      <c r="U3" t="n">
+        <v>74.38383838383839</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.75619834710744</v>
+      </c>
+      <c r="W3" t="n">
+        <v>183.3545454545454</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.614876033057851</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>82.74710743801653</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>46462231.40495867</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>85.53305785123966</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25.1712962962963</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>183.2784391534391</v>
+      </c>
       <c r="AD3" t="n">
-        <v>26.38383838383838</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>182.6767676767677</v>
+        <v>68.9292328042328</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>2164021.164021164</v>
       </c>
       <c r="AG3" t="n">
-        <v>70.92929292929291</v>
+        <v>73.35515873015873</v>
       </c>
       <c r="AH3" t="n">
-        <v>2742424.242424242</v>
+        <v>23.20834551211789</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.38383838383839</v>
+        <v>183.2271528769611</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25.75619834710744</v>
+        <v>1.786762491557889</v>
       </c>
       <c r="AK3" t="n">
-        <v>183.3545454545454</v>
+        <v>79.20719904562615</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.614876033057851</v>
+        <v>33498280.27258334</v>
       </c>
       <c r="AM3" t="n">
-        <v>82.74710743801653</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>46462231.40495867</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>85.53305785123966</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>25.1712962962963</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>183.2784391534391</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>68.9292328042328</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2164021.164021164</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>73.35515873015873</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>23.20834551211789</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>183.2271528769611</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.786762491557889</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>79.20719904562615</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>33498280.27258334</v>
-      </c>
-      <c r="BA3" t="n">
         <v>84.38545991519138</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -1088,98 +990,84 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>24.45416666666667</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.8930555555555</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.236111111111111</v>
+      </c>
+      <c r="S4" t="n">
+        <v>83.40416666666667</v>
+      </c>
+      <c r="T4" t="n">
+        <v>58345833.33333334</v>
+      </c>
+      <c r="U4" t="n">
+        <v>86.30833333333332</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26.32916666666666</v>
+      </c>
+      <c r="W4" t="n">
+        <v>182.9236111111111</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.452777777777778</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>76.4986111111111</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>12162673.61111111</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>79.63194444444444</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>24.63040227574283</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>179.6681381930763</v>
+      </c>
       <c r="AD4" t="n">
-        <v>24.45416666666667</v>
+        <v>1.772715612560814</v>
       </c>
       <c r="AE4" t="n">
-        <v>182.8930555555555</v>
+        <v>81.20040006433194</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.236111111111111</v>
+        <v>37424843.79397692</v>
       </c>
       <c r="AG4" t="n">
-        <v>83.40416666666667</v>
+        <v>84.53740098910377</v>
       </c>
       <c r="AH4" t="n">
-        <v>58345833.33333334</v>
+        <v>23.99170791993758</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.30833333333332</v>
+        <v>181.41839654232</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.32916666666666</v>
+        <v>1.253578850708037</v>
       </c>
       <c r="AK4" t="n">
-        <v>182.9236111111111</v>
+        <v>71.67427660059239</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.452777777777778</v>
+        <v>7717944.827633822</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.4986111111111</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>12162673.61111111</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>79.63194444444444</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>24.63040227574283</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>179.6681381930763</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.772715612560814</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>81.20040006433194</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>37424843.79397692</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>84.53740098910377</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>23.99170791993758</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>181.41839654232</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.253578850708037</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>71.67427660059239</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7717944.827633822</v>
-      </c>
-      <c r="BA4" t="n">
         <v>78.60448020878643</v>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -1251,98 +1139,84 @@
           <t>AovF1Mia</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>183.8545454545455</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.581818181818181</v>
+      </c>
+      <c r="S5" t="n">
+        <v>76.67272727272727</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>79.18181818181817</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.64769921436588</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182.0516273849607</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.375645342312009</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>75.46588103254768</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9438698.092031427</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>80.13187429854096</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>25.25395343644704</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>186.0413820890675</v>
+      </c>
       <c r="AD5" t="n">
-        <v>27.2</v>
+        <v>1.391129277798076</v>
       </c>
       <c r="AE5" t="n">
-        <v>183.8545454545455</v>
+        <v>73.15978778467908</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.581818181818181</v>
+        <v>7081649.636666261</v>
       </c>
       <c r="AG5" t="n">
-        <v>76.67272727272727</v>
+        <v>77.1639765761377</v>
       </c>
       <c r="AH5" t="n">
-        <v>11300000</v>
+        <v>23.40342418546366</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.18181818181817</v>
+        <v>177.98210839599</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.64769921436588</v>
+        <v>1.39187343358396</v>
       </c>
       <c r="AK5" t="n">
-        <v>182.0516273849607</v>
+        <v>73.16341791979949</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.375645342312009</v>
+        <v>8325323.621553885</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.46588103254768</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>9438698.092031427</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>80.13187429854096</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>25.25395343644704</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>186.0413820890675</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.391129277798076</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>73.15978778467908</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7081649.636666261</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>77.1639765761377</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23.40342418546366</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>177.98210839599</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.39187343358396</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>73.16341791979949</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>8325323.621553885</v>
-      </c>
-      <c r="BA5" t="n">
         <v>80.35131892230577</v>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -1410,98 +1284,84 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>26.40752984389348</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>185.4415977961433</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.544903581267217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>78.01836547291093</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19569044.99540863</v>
+      </c>
+      <c r="U6" t="n">
+        <v>80.84508723599632</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25.4010878010878</v>
+      </c>
+      <c r="W6" t="n">
+        <v>179.6252525252525</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>72.87241647241646</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4502587.412587413</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>76.17327117327117</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>25.93938837842</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>181.7123021576579</v>
+      </c>
       <c r="AD6" t="n">
-        <v>26.40752984389348</v>
+        <v>1.376706363465257</v>
       </c>
       <c r="AE6" t="n">
-        <v>185.4415977961433</v>
+        <v>73.46484223944698</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.544903581267217</v>
+        <v>11454052.22823948</v>
       </c>
       <c r="AG6" t="n">
-        <v>78.01836547291093</v>
+        <v>78.16608533100629</v>
       </c>
       <c r="AH6" t="n">
-        <v>19569044.99540863</v>
+        <v>24.91974415184134</v>
       </c>
       <c r="AI6" t="n">
-        <v>80.84508723599632</v>
+        <v>179.0702772078731</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25.4010878010878</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>179.6252525252525</v>
+        <v>71.12043365841319</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>3210330.255848159</v>
       </c>
       <c r="AM6" t="n">
-        <v>72.87241647241646</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>4502587.412587413</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>76.17327117327117</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>25.93938837842</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>181.7123021576579</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.376706363465257</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>73.46484223944698</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11454052.22823948</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>78.16608533100629</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24.91974415184134</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>179.0702772078731</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>71.12043365841319</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3210330.255848159</v>
-      </c>
-      <c r="BA6" t="n">
         <v>75.60448554003541</v>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Aotm1TVI</t>
         </is>
@@ -1569,98 +1429,84 @@
           <t>WdKOwxDM</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>25.17090909090909</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>185.1763636363636</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.296363636363636</v>
+      </c>
+      <c r="S7" t="n">
+        <v>74.98636363636363</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8798454.545454545</v>
+      </c>
+      <c r="U7" t="n">
+        <v>78.77272727272728</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="W7" t="n">
+        <v>181.4909090909091</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.163636363636364</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>74.9909090909091</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8609090.909090908</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>78.98181818181818</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.67810132748751</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>185.0450657654366</v>
+      </c>
       <c r="AD7" t="n">
-        <v>25.17090909090909</v>
+        <v>1.437178175618073</v>
       </c>
       <c r="AE7" t="n">
-        <v>185.1763636363636</v>
+        <v>75.33199123127511</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.296363636363636</v>
+        <v>10834661.85604677</v>
       </c>
       <c r="AG7" t="n">
-        <v>74.98636363636363</v>
+        <v>79.55631896236756</v>
       </c>
       <c r="AH7" t="n">
-        <v>8798454.545454545</v>
+        <v>23.77900309073078</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.77272727272728</v>
+        <v>183.0110664544641</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24.27272727272727</v>
+        <v>1.319073547745276</v>
       </c>
       <c r="AK7" t="n">
-        <v>181.4909090909091</v>
+        <v>74.73436945309734</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.163636363636364</v>
+        <v>11566815.05761649</v>
       </c>
       <c r="AM7" t="n">
-        <v>74.9909090909091</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>8609090.909090908</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>78.98181818181818</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>24.67810132748751</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>185.0450657654366</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.437178175618073</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>75.33199123127511</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10834661.85604677</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>79.55631896236756</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>23.77900309073078</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>183.0110664544641</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.319073547745276</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>74.73436945309734</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11566815.05761649</v>
-      </c>
-      <c r="BA7" t="n">
         <v>79.52728237079704</v>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -1728,98 +1574,84 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>27.74545454545455</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.0772727272727</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.137272727272728</v>
+      </c>
+      <c r="S8" t="n">
+        <v>79.08000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>19071272.72727273</v>
+      </c>
+      <c r="U8" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26.01636363636364</v>
+      </c>
+      <c r="W8" t="n">
+        <v>182.62</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.130909090909091</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>79.64181818181819</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>25921909.09090909</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>81.78272727272727</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>27.59664969017911</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>180.8370295390884</v>
+      </c>
       <c r="AD8" t="n">
-        <v>27.74545454545455</v>
+        <v>1.714935489347254</v>
       </c>
       <c r="AE8" t="n">
-        <v>183.0772727272727</v>
+        <v>73.76654910449028</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.137272727272728</v>
+        <v>8735370.840760546</v>
       </c>
       <c r="AG8" t="n">
-        <v>79.08000000000001</v>
+        <v>77.36194868856634</v>
       </c>
       <c r="AH8" t="n">
-        <v>19071272.72727273</v>
+        <v>23.59745808468315</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.56</v>
+        <v>183.2548341148054</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.01636363636364</v>
+        <v>1.71597435350952</v>
       </c>
       <c r="AK8" t="n">
-        <v>182.62</v>
+        <v>74.03274403239557</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.130909090909091</v>
+        <v>14507861.58177039</v>
       </c>
       <c r="AM8" t="n">
-        <v>79.64181818181819</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>25921909.09090909</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>81.78272727272727</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>27.59664969017911</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>180.8370295390884</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.714935489347254</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>73.76654910449028</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8735370.840760546</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>77.36194868856634</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>23.59745808468315</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>183.2548341148054</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.71597435350952</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>74.03274403239557</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14507861.58177039</v>
-      </c>
-      <c r="BA8" t="n">
         <v>79.42498508098892</v>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -1887,98 +1719,84 @@
           <t>2XrRecc3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>26.02454545454545</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>184.7418181818182</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="S9" t="n">
+        <v>76.45363636363636</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11428000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>78.99636363636364</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.70909090909091</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183.6272727272728</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>76.56363636363636</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>14091818.18181818</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>79.99090909090908</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24.76496732026144</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>179.757034743722</v>
+      </c>
       <c r="AD9" t="n">
-        <v>26.02454545454545</v>
+        <v>1.097008943928448</v>
       </c>
       <c r="AE9" t="n">
-        <v>184.7418181818182</v>
+        <v>73.67978672170622</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.045454545454545</v>
+        <v>7867469.685242519</v>
       </c>
       <c r="AG9" t="n">
-        <v>76.45363636363636</v>
+        <v>77.52444788441692</v>
       </c>
       <c r="AH9" t="n">
-        <v>11428000</v>
+        <v>26.66244824016563</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.99636363636364</v>
+        <v>183.7573757763975</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25.70909090909091</v>
+        <v>1.16104209799862</v>
       </c>
       <c r="AK9" t="n">
-        <v>183.6272727272728</v>
+        <v>72.87970583160799</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.3</v>
+        <v>7252254.572118702</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.56363636363636</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>14091818.18181818</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>79.99090909090908</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>24.76496732026144</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>179.757034743722</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.097008943928448</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>73.67978672170622</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7867469.685242519</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>77.52444788441692</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>26.66244824016563</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>183.7573757763975</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.16104209799862</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>72.87970583160799</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7252254.572118702</v>
-      </c>
-      <c r="BA9" t="n">
         <v>76.25773378191857</v>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -1995,8 +1813,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2050,98 +1868,84 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>23.24289044289044</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>182.8868686868687</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.746386946386946</v>
+      </c>
+      <c r="S10" t="n">
+        <v>78.11841491841491</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21256332.55633255</v>
+      </c>
+      <c r="U10" t="n">
+        <v>83.37280497280497</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.12532467532467</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182.0993506493507</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.074025974025974</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>84.82597402597402</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>71237175.32467532</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>87.37792207792208</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.17863676384339</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>183.0455706069853</v>
+      </c>
       <c r="AD10" t="n">
-        <v>23.24289044289044</v>
+        <v>1.688413738487773</v>
       </c>
       <c r="AE10" t="n">
-        <v>182.8868686868687</v>
+        <v>73.53604547439519</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.746386946386946</v>
+        <v>14727417.07896507</v>
       </c>
       <c r="AG10" t="n">
-        <v>78.11841491841491</v>
+        <v>81.36645894375737</v>
       </c>
       <c r="AH10" t="n">
-        <v>21256332.55633255</v>
+        <v>24.71819126201205</v>
       </c>
       <c r="AI10" t="n">
-        <v>83.37280497280497</v>
+        <v>178.3825251114939</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26.38671328671328</v>
+        <v>2.242837352332237</v>
       </c>
       <c r="AK10" t="n">
-        <v>182.065034965035</v>
+        <v>80.06990549843125</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.121678321678321</v>
+        <v>44252779.69883605</v>
       </c>
       <c r="AM10" t="n">
-        <v>85.28811188811189</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>73051048.95104894</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>87.51888111888113</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>23.17863676384339</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>183.0455706069853</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.688413738487773</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>73.53604547439519</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>14727417.07896507</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>81.36645894375737</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>24.62386409413264</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>178.2281894363097</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.240149627297965</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>80.12656489574647</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>44309382.41071233</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>84.95858003178977</v>
-      </c>
-      <c r="BB10" t="inlineStr">
+        <v>84.8861417755508</v>
+      </c>
+      <c r="AN10" t="inlineStr">
         <is>
           <t>zuJM7XDg</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -2213,98 +2017,84 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.376666666666666</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75.83222222222223</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9670666.666666668</v>
+      </c>
+      <c r="U11" t="n">
+        <v>78.07333333333334</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.93863636363636</v>
+      </c>
+      <c r="W11" t="n">
+        <v>184.5810606060606</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.127272727272727</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>81.80732323232324</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>39996590.90909091</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85.0719696969697</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>26.01794670757518</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>180.5710586369255</v>
+      </c>
       <c r="AD11" t="n">
-        <v>26.27</v>
+        <v>1.44720815819887</v>
       </c>
       <c r="AE11" t="n">
-        <v>183.1111111111111</v>
+        <v>73.5077707380339</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.376666666666666</v>
+        <v>6010473.387551561</v>
       </c>
       <c r="AG11" t="n">
-        <v>75.83222222222223</v>
+        <v>76.21212069664082</v>
       </c>
       <c r="AH11" t="n">
-        <v>9670666.666666668</v>
+        <v>24.56761627370971</v>
       </c>
       <c r="AI11" t="n">
-        <v>78.07333333333334</v>
+        <v>181.8566231806627</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24.93863636363636</v>
+        <v>1.791435702162553</v>
       </c>
       <c r="AK11" t="n">
-        <v>184.5810606060606</v>
+        <v>78.66044060077272</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.127272727272727</v>
+        <v>27633789.15570505</v>
       </c>
       <c r="AM11" t="n">
-        <v>81.80732323232324</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>39996590.90909091</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>85.0719696969697</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>26.01794670757518</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>180.5710586369255</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.44720815819887</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>73.5077707380339</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6010473.387551561</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>76.21212069664082</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>24.56761627370971</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>181.8566231806627</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.791435702162553</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>78.66044060077272</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>27633789.15570505</v>
-      </c>
-      <c r="BA11" t="n">
         <v>82.04775332635592</v>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
         </is>
@@ -2321,8 +2111,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2376,98 +2166,84 @@
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>25.64769921436588</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>182.0516273849607</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.375645342312009</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75.46588103254768</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9438698.092031427</v>
+      </c>
+      <c r="U12" t="n">
+        <v>80.13187429854096</v>
+      </c>
+      <c r="V12" t="n">
+        <v>24.79033189033189</v>
+      </c>
+      <c r="W12" t="n">
+        <v>184.938455988456</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.243722943722944</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>79.93578643578644</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30165111.83261183</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>84.41594516594516</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>23.40342418546366</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>177.98210839599</v>
+      </c>
       <c r="AD12" t="n">
-        <v>25.64769921436588</v>
+        <v>1.39187343358396</v>
       </c>
       <c r="AE12" t="n">
-        <v>182.0516273849607</v>
+        <v>73.16341791979949</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.375645342312009</v>
+        <v>8325323.621553885</v>
       </c>
       <c r="AG12" t="n">
-        <v>75.46588103254768</v>
+        <v>80.35131892230577</v>
       </c>
       <c r="AH12" t="n">
-        <v>9438698.092031427</v>
+        <v>24.31999783773852</v>
       </c>
       <c r="AI12" t="n">
-        <v>80.13187429854096</v>
+        <v>184.0530677224777</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24.67163947163948</v>
+        <v>1.882099443861866</v>
       </c>
       <c r="AK12" t="n">
-        <v>185.0277389277389</v>
+        <v>75.38346318105634</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.211188811188811</v>
+        <v>19021567.33315856</v>
       </c>
       <c r="AM12" t="n">
-        <v>79.83682983682982</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>29763282.82828283</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>84.43939393939394</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>23.40342418546366</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>177.98210839599</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.39187343358396</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>73.16341791979949</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8325323.621553885</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>80.35131892230577</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>24.46480536371841</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>184.1148421626683</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.877837862620471</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>75.41296034882991</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18948707.12801691</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>81.54998938259807</v>
-      </c>
-      <c r="BB12" t="inlineStr">
+        <v>81.55534728384107</v>
+      </c>
+      <c r="AN12" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -2539,98 +2315,84 @@
           <t>6uz2cJBL</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>25.70909090909091</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>183.6272727272728</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>76.56363636363636</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14091818.18181818</v>
+      </c>
+      <c r="U13" t="n">
+        <v>79.99090909090908</v>
+      </c>
+      <c r="V13" t="n">
+        <v>27.74545454545455</v>
+      </c>
+      <c r="W13" t="n">
+        <v>183.0772727272727</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.137272727272728</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>79.08000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19071272.72727273</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>26.66244824016563</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>183.7573757763975</v>
+      </c>
       <c r="AD13" t="n">
-        <v>25.70909090909091</v>
+        <v>1.16104209799862</v>
       </c>
       <c r="AE13" t="n">
-        <v>183.6272727272728</v>
+        <v>72.87970583160799</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.3</v>
+        <v>7252254.572118702</v>
       </c>
       <c r="AG13" t="n">
-        <v>76.56363636363636</v>
+        <v>76.25773378191857</v>
       </c>
       <c r="AH13" t="n">
-        <v>14091818.18181818</v>
+        <v>27.59664969017911</v>
       </c>
       <c r="AI13" t="n">
-        <v>79.99090909090908</v>
+        <v>180.8370295390884</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27.74545454545455</v>
+        <v>1.714935489347254</v>
       </c>
       <c r="AK13" t="n">
-        <v>183.0772727272727</v>
+        <v>73.76654910449028</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.137272727272728</v>
+        <v>8735370.840760546</v>
       </c>
       <c r="AM13" t="n">
-        <v>79.08000000000001</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>19071272.72727273</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80.56</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>26.66244824016563</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>183.7573757763975</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.16104209799862</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>72.87970583160799</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7252254.572118702</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>76.25773378191857</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>27.59664969017911</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>180.8370295390884</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.714935489347254</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>73.76654910449028</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>8735370.840760546</v>
-      </c>
-      <c r="BA13" t="n">
         <v>77.36194868856634</v>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>CznGurCt</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>hUGEt9yf</t>
         </is>
@@ -2698,98 +2460,84 @@
           <t>UsushcZr</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>26.85545454545455</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>184.2227272727273</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.527272727272727</v>
+      </c>
+      <c r="S14" t="n">
+        <v>77.10545454545453</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12927636.36363636</v>
+      </c>
+      <c r="U14" t="n">
+        <v>79.16454545454545</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="W14" t="n">
+        <v>183.1111111111111</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.376666666666666</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>75.83222222222223</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9670666.666666668</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>78.07333333333334</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>28.21626172208014</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.2419288150043</v>
+      </c>
       <c r="AD14" t="n">
-        <v>26.85545454545455</v>
+        <v>1.308927962489344</v>
       </c>
       <c r="AE14" t="n">
-        <v>184.2227272727273</v>
+        <v>74.99781055900621</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.527272727272727</v>
+        <v>6886981.549141395</v>
       </c>
       <c r="AG14" t="n">
-        <v>77.10545454545453</v>
+        <v>76.14754475703324</v>
       </c>
       <c r="AH14" t="n">
-        <v>12927636.36363636</v>
+        <v>26.01794670757518</v>
       </c>
       <c r="AI14" t="n">
-        <v>79.16454545454545</v>
+        <v>180.5710586369255</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26.27</v>
+        <v>1.44720815819887</v>
       </c>
       <c r="AK14" t="n">
-        <v>183.1111111111111</v>
+        <v>73.5077707380339</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.376666666666666</v>
+        <v>6010473.387551561</v>
       </c>
       <c r="AM14" t="n">
-        <v>75.83222222222223</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9670666.666666668</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>78.07333333333334</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>28.21626172208014</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>181.2419288150043</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.308927962489344</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>74.99781055900621</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6886981.549141395</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>76.14754475703324</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>26.01794670757518</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>180.5710586369255</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.44720815819887</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>73.5077707380339</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6010473.387551561</v>
-      </c>
-      <c r="BA14" t="n">
         <v>76.21212069664082</v>
       </c>
-      <c r="BB14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>MBpIn2MH</t>
         </is>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>fcpIzd9s</t>
         </is>
@@ -2861,98 +2609,84 @@
           <t>Qo6off6p</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>26.12532467532467</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>182.0993506493507</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.074025974025974</v>
+      </c>
+      <c r="S15" t="n">
+        <v>84.82597402597402</v>
+      </c>
+      <c r="T15" t="n">
+        <v>71237175.32467532</v>
+      </c>
+      <c r="U15" t="n">
+        <v>87.37792207792208</v>
+      </c>
+      <c r="V15" t="n">
+        <v>26.38383838383838</v>
+      </c>
+      <c r="W15" t="n">
+        <v>182.6767676767677</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>70.92929292929291</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2742424.242424242</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>74.38383838383839</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24.71819126201205</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>178.3825251114939</v>
+      </c>
       <c r="AD15" t="n">
-        <v>26.38671328671328</v>
+        <v>2.242837352332237</v>
       </c>
       <c r="AE15" t="n">
-        <v>182.065034965035</v>
+        <v>80.06990549843125</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.121678321678321</v>
+        <v>44252779.69883605</v>
       </c>
       <c r="AG15" t="n">
-        <v>85.28811188811189</v>
+        <v>84.8861417755508</v>
       </c>
       <c r="AH15" t="n">
-        <v>73051048.95104894</v>
+        <v>25.1712962962963</v>
       </c>
       <c r="AI15" t="n">
-        <v>87.51888111888113</v>
+        <v>183.2784391534391</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26.38383838383838</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>182.6767676767677</v>
+        <v>68.9292328042328</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>2164021.164021164</v>
       </c>
       <c r="AM15" t="n">
-        <v>70.92929292929291</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2742424.242424242</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>74.38383838383839</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>24.62386409413264</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>178.2281894363097</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.240149627297965</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>80.12656489574647</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>44309382.41071233</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>84.95858003178977</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>25.1712962962963</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>183.2784391534391</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>68.9292328042328</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2164021.164021164</v>
-      </c>
-      <c r="BA15" t="n">
         <v>73.35515873015873</v>
       </c>
-      <c r="BB15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>lhUKMQZu</t>
         </is>
@@ -3016,98 +2750,84 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>25.4010878010878</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>179.6252525252525</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>72.87241647241646</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4502587.412587413</v>
+      </c>
+      <c r="U16" t="n">
+        <v>76.17327117327117</v>
+      </c>
+      <c r="V16" t="n">
+        <v>25.17090909090909</v>
+      </c>
+      <c r="W16" t="n">
+        <v>185.1763636363636</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.296363636363636</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>74.98636363636363</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8798454.545454545</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>78.77272727272728</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>24.91974415184134</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>179.0702772078731</v>
+      </c>
       <c r="AD16" t="n">
-        <v>25.4010878010878</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>179.6252525252525</v>
+        <v>71.12043365841319</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>3210330.255848159</v>
       </c>
       <c r="AG16" t="n">
-        <v>72.87241647241646</v>
+        <v>75.60448554003541</v>
       </c>
       <c r="AH16" t="n">
-        <v>4502587.412587413</v>
+        <v>24.67810132748751</v>
       </c>
       <c r="AI16" t="n">
-        <v>76.17327117327117</v>
+        <v>185.0450657654366</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25.17090909090909</v>
+        <v>1.437178175618073</v>
       </c>
       <c r="AK16" t="n">
-        <v>185.1763636363636</v>
+        <v>75.33199123127511</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.296363636363636</v>
+        <v>10834661.85604677</v>
       </c>
       <c r="AM16" t="n">
-        <v>74.98636363636363</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>8798454.545454545</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>78.77272727272728</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>24.91974415184134</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>179.0702772078731</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>71.12043365841319</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3210330.255848159</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>75.60448554003541</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>24.67810132748751</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>185.0450657654366</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.437178175618073</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>75.33199123127511</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10834661.85604677</v>
-      </c>
-      <c r="BA16" t="n">
         <v>79.55631896236756</v>
       </c>
-      <c r="BB16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
@@ -3179,98 +2899,84 @@
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>24.93863636363636</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>184.5810606060606</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.127272727272727</v>
+      </c>
+      <c r="S17" t="n">
+        <v>81.80732323232324</v>
+      </c>
+      <c r="T17" t="n">
+        <v>39996590.90909091</v>
+      </c>
+      <c r="U17" t="n">
+        <v>85.0719696969697</v>
+      </c>
+      <c r="V17" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>183.8545454545455</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.581818181818181</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>76.67272727272727</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>79.18181818181817</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>24.56761627370971</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>181.8566231806627</v>
+      </c>
       <c r="AD17" t="n">
-        <v>24.93863636363636</v>
+        <v>1.791435702162553</v>
       </c>
       <c r="AE17" t="n">
-        <v>184.5810606060606</v>
+        <v>78.66044060077272</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.127272727272727</v>
+        <v>27633789.15570505</v>
       </c>
       <c r="AG17" t="n">
-        <v>81.80732323232324</v>
+        <v>82.04775332635592</v>
       </c>
       <c r="AH17" t="n">
-        <v>39996590.90909091</v>
+        <v>25.25395343644704</v>
       </c>
       <c r="AI17" t="n">
-        <v>85.0719696969697</v>
+        <v>186.0413820890675</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27.2</v>
+        <v>1.391129277798076</v>
       </c>
       <c r="AK17" t="n">
-        <v>183.8545454545455</v>
+        <v>73.15978778467908</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.581818181818181</v>
+        <v>7081649.636666261</v>
       </c>
       <c r="AM17" t="n">
-        <v>76.67272727272727</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>11300000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>79.18181818181817</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>24.56761627370971</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>181.8566231806627</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.791435702162553</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>78.66044060077272</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>27633789.15570505</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>82.04775332635592</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>25.25395343644704</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>186.0413820890675</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.391129277798076</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>73.15978778467908</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>7081649.636666261</v>
-      </c>
-      <c r="BA17" t="n">
         <v>77.1639765761377</v>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>EoQjC3VB</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
@@ -3338,98 +3044,84 @@
           <t>UDg08Ohm</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>26.01636363636364</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>182.62</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.130909090909091</v>
+      </c>
+      <c r="S18" t="n">
+        <v>79.64181818181819</v>
+      </c>
+      <c r="T18" t="n">
+        <v>25921909.09090909</v>
+      </c>
+      <c r="U18" t="n">
+        <v>81.78272727272727</v>
+      </c>
+      <c r="V18" t="n">
+        <v>24.45416666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>182.8930555555555</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.236111111111111</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>83.40416666666667</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>58345833.33333334</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>86.30833333333332</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23.59745808468315</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.2548341148054</v>
+      </c>
       <c r="AD18" t="n">
-        <v>26.01636363636364</v>
+        <v>1.71597435350952</v>
       </c>
       <c r="AE18" t="n">
-        <v>182.62</v>
+        <v>74.03274403239557</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.130909090909091</v>
+        <v>14507861.58177039</v>
       </c>
       <c r="AG18" t="n">
-        <v>79.64181818181819</v>
+        <v>79.42498508098892</v>
       </c>
       <c r="AH18" t="n">
-        <v>25921909.09090909</v>
+        <v>24.63040227574283</v>
       </c>
       <c r="AI18" t="n">
-        <v>81.78272727272727</v>
+        <v>179.6681381930763</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24.45416666666667</v>
+        <v>1.772715612560814</v>
       </c>
       <c r="AK18" t="n">
-        <v>182.8930555555555</v>
+        <v>81.20040006433194</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.236111111111111</v>
+        <v>37424843.79397692</v>
       </c>
       <c r="AM18" t="n">
-        <v>83.40416666666667</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>58345833.33333334</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>86.30833333333332</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>23.59745808468315</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>183.2548341148054</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.71597435350952</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>74.03274403239557</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>14507861.58177039</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>79.42498508098892</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>24.63040227574283</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>179.6681381930763</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.772715612560814</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>81.20040006433194</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>37424843.79397692</v>
-      </c>
-      <c r="BA18" t="n">
         <v>84.53740098910377</v>
       </c>
-      <c r="BB18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>CznGurCt</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
@@ -3501,98 +3193,84 @@
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>181.4909090909091</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.163636363636364</v>
+      </c>
+      <c r="S19" t="n">
+        <v>74.9909090909091</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8609090.909090908</v>
+      </c>
+      <c r="U19" t="n">
+        <v>78.98181818181818</v>
+      </c>
+      <c r="V19" t="n">
+        <v>26.40752984389348</v>
+      </c>
+      <c r="W19" t="n">
+        <v>185.4415977961433</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.544903581267217</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>78.01836547291093</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>19569044.99540863</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80.84508723599632</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23.77900309073078</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>183.0110664544641</v>
+      </c>
       <c r="AD19" t="n">
-        <v>24.27272727272727</v>
+        <v>1.319073547745276</v>
       </c>
       <c r="AE19" t="n">
-        <v>181.4909090909091</v>
+        <v>74.73436945309734</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.163636363636364</v>
+        <v>11566815.05761649</v>
       </c>
       <c r="AG19" t="n">
-        <v>74.9909090909091</v>
+        <v>79.52728237079704</v>
       </c>
       <c r="AH19" t="n">
-        <v>8609090.909090908</v>
+        <v>25.93938837842</v>
       </c>
       <c r="AI19" t="n">
-        <v>78.98181818181818</v>
+        <v>181.7123021576579</v>
       </c>
       <c r="AJ19" t="n">
-        <v>26.40752984389348</v>
+        <v>1.376706363465257</v>
       </c>
       <c r="AK19" t="n">
-        <v>185.4415977961433</v>
+        <v>73.46484223944698</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.544903581267217</v>
+        <v>11454052.22823948</v>
       </c>
       <c r="AM19" t="n">
-        <v>78.01836547291093</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>19569044.99540863</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>80.84508723599632</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>23.77900309073078</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>183.0110664544641</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.319073547745276</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>74.73436945309734</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>11566815.05761649</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>79.52728237079704</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>25.93938837842</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>181.7123021576579</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.376706363465257</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>73.46484223944698</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>11454052.22823948</v>
-      </c>
-      <c r="BA19" t="n">
         <v>78.16608533100629</v>
       </c>
-      <c r="BB19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>zuJM7XDg</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -3660,98 +3338,84 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>26.32916666666666</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>182.9236111111111</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.452777777777778</v>
+      </c>
+      <c r="S20" t="n">
+        <v>76.4986111111111</v>
+      </c>
+      <c r="T20" t="n">
+        <v>12162673.61111111</v>
+      </c>
+      <c r="U20" t="n">
+        <v>79.63194444444444</v>
+      </c>
+      <c r="V20" t="n">
+        <v>23.24289044289044</v>
+      </c>
+      <c r="W20" t="n">
+        <v>182.8868686868687</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.746386946386946</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>78.11841491841491</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>21256332.55633255</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>83.37280497280497</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>23.99170791993758</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>181.41839654232</v>
+      </c>
       <c r="AD20" t="n">
-        <v>26.32916666666666</v>
+        <v>1.253578850708037</v>
       </c>
       <c r="AE20" t="n">
-        <v>182.9236111111111</v>
+        <v>71.67427660059239</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.452777777777778</v>
+        <v>7717944.827633822</v>
       </c>
       <c r="AG20" t="n">
-        <v>76.4986111111111</v>
+        <v>78.60448020878643</v>
       </c>
       <c r="AH20" t="n">
-        <v>12162673.61111111</v>
+        <v>23.17863676384339</v>
       </c>
       <c r="AI20" t="n">
-        <v>79.63194444444444</v>
+        <v>183.0455706069853</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23.24289044289044</v>
+        <v>1.688413738487773</v>
       </c>
       <c r="AK20" t="n">
-        <v>182.8868686868687</v>
+        <v>73.53604547439519</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.746386946386946</v>
+        <v>14727417.07896507</v>
       </c>
       <c r="AM20" t="n">
-        <v>78.11841491841491</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21256332.55633255</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>83.37280497280497</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>23.99170791993758</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>181.41839654232</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.253578850708037</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>71.67427660059239</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7717944.827633822</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>78.60448020878643</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>23.17863676384339</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>183.0455706069853</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.688413738487773</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>73.53604547439519</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14727417.07896507</v>
-      </c>
-      <c r="BA20" t="n">
         <v>81.36645894375737</v>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>x6CvOHH9</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -3819,98 +3483,84 @@
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>25.75619834710744</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>183.3545454545454</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.614876033057851</v>
+      </c>
+      <c r="S21" t="n">
+        <v>82.74710743801653</v>
+      </c>
+      <c r="T21" t="n">
+        <v>46462231.40495867</v>
+      </c>
+      <c r="U21" t="n">
+        <v>85.53305785123966</v>
+      </c>
+      <c r="V21" t="n">
+        <v>26.02454545454545</v>
+      </c>
+      <c r="W21" t="n">
+        <v>184.7418181818182</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>76.45363636363636</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11428000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>78.99636363636364</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>23.20834551211789</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>183.2271528769611</v>
+      </c>
       <c r="AD21" t="n">
-        <v>25.75619834710744</v>
+        <v>1.786762491557889</v>
       </c>
       <c r="AE21" t="n">
-        <v>183.3545454545454</v>
+        <v>79.20719904562615</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.614876033057851</v>
+        <v>33498280.27258334</v>
       </c>
       <c r="AG21" t="n">
-        <v>82.74710743801653</v>
+        <v>84.38545991519138</v>
       </c>
       <c r="AH21" t="n">
-        <v>46462231.40495867</v>
+        <v>24.76496732026144</v>
       </c>
       <c r="AI21" t="n">
-        <v>85.53305785123966</v>
+        <v>179.757034743722</v>
       </c>
       <c r="AJ21" t="n">
-        <v>26.02454545454545</v>
+        <v>1.097008943928448</v>
       </c>
       <c r="AK21" t="n">
-        <v>184.7418181818182</v>
+        <v>73.67978672170622</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.045454545454545</v>
+        <v>7867469.685242519</v>
       </c>
       <c r="AM21" t="n">
-        <v>76.45363636363636</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>11428000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>78.99636363636364</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>23.20834551211789</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>183.2271528769611</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.786762491557889</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>79.20719904562615</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>33498280.27258334</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>84.38545991519138</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>24.76496732026144</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>179.757034743722</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.097008943928448</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>73.67978672170622</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>7867469.685242519</v>
-      </c>
-      <c r="BA21" t="n">
         <v>77.52444788441692</v>
       </c>
-      <c r="BB21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>x6CvOHH9</t>
         </is>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -3919,48 +3569,48 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">ward g 
+  eng </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">wembley stadium
-  london </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90000</v>
+        <v>17949</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3969,176 +3619,93 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>fa community shield</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>73</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6500000</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>83</v>
+        <v>24.79116161616162</v>
       </c>
       <c r="W22" t="n">
-        <v>23</v>
+        <v>184.149292929293</v>
       </c>
       <c r="X22" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>69.81343434343435</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>2431216.54040404</v>
       </c>
       <c r="AA22" t="n">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>82</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>26.38671328671328</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>182.065034965035</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.121678321678321</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>85.28811188811189</v>
-      </c>
+        <v>73.77131313131312</v>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>73051048.95104894</v>
+        <v>24.50713022165388</v>
       </c>
       <c r="AI22" t="n">
-        <v>87.51888111888113</v>
+        <v>181.0492916006983</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24.67163947163948</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>185.0277389277389</v>
+        <v>69.06363277919863</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.211188811188811</v>
+        <v>2291556.907146917</v>
       </c>
       <c r="AM22" t="n">
-        <v>79.83682983682982</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>29763282.82828283</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>84.43939393939394</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>24.62386409413264</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>178.2281894363097</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.240149627297965</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>80.12656489574647</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>44309382.41071233</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>84.95858003178977</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>24.46480536371841</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>184.1148421626683</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.877837862620471</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>75.41296034882991</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18948707.12801691</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>81.54998938259807</v>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
+        <v>73.60597313563107</v>
+      </c>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">brisbane road
+  london </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17949</v>
+        <v>9271</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -4185,82 +3752,45 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="n">
-        <v>24.90684624017957</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>184.3325476992144</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>69.90381593714928</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2453782.2671156</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>73.80145903479236</v>
-      </c>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="n">
-        <v>24.34125580183764</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>181.1732869637388</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>69.11514753244293</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2331285.452385463</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>73.754784965516</v>
-      </c>
-      <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9271</v>
+        <v>10841</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -4286,80 +3816,93 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>25.21454545454545</v>
+      </c>
+      <c r="W24" t="n">
+        <v>180.4436363636364</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>70.12090909090909</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2255590.909090909</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>72.89272727272729</v>
+      </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AH24" t="n">
+        <v>22.97071937866055</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>179.6371704439352</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>66.73441982853747</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1746387.520159579</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>74.2701171377642</v>
+      </c>
       <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10841</v>
+        <v>6500</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -4385,11 +3928,7 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -4410,59 +3949,17 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="n">
-        <v>25.27171717171717</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>180.3484848484849</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>70.13434343434344</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2279545.454545455</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>72.85858585858585</v>
-      </c>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="n">
-        <v>22.55570127040715</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>179.4922808854182</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>66.46308085523772</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1685528.617170774</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>74.5027445321563</v>
-      </c>
-      <c r="BB25" t="inlineStr"/>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -4471,21 +3968,21 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6500</v>
+        <v>28723</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4538,48 +4035,39 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
-      <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>28723</v>
+        <v>27000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4605,80 +4093,121 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>23.50388888888889</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>181.4847222222222</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>68.49305555555557</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2084250</v>
+      </c>
+      <c r="U27" t="n">
+        <v>74.42083333333332</v>
+      </c>
+      <c r="V27" t="n">
+        <v>23.98310185185185</v>
+      </c>
+      <c r="W27" t="n">
+        <v>182.9055555555556</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>71.2837962962963</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4234282.407407408</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>76.97893518518519</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>25.59795176257015</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>180.6796491919113</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>66.89307498352591</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1506733.937775929</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>72.12693985072974</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>24.00400102456024</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>180.4842261110063</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>68.9824603372204</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2887756.905466609</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>74.98144115516406</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27000</v>
+        <v>5000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4704,11 +4233,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -4723,93 +4248,23 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="n">
-        <v>23.49043209876543</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>181.3580246913581</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>68.49228395061729</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2085277.777777778</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>74.39814814814814</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>24.0270202020202</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>182.9878787878788</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>71.37777777777778</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>4276035.353535353</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>77.02247474747475</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>25.45071563362495</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>180.7722597858843</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>66.73589528084078</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1507482.153084365</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>72.08976222730654</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>23.99001068708007</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>180.4038447526767</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>68.91866486548446</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2900399.877733909</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>74.99889274343258</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="BC28" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -4818,21 +4273,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5000</v>
+        <v>6912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4885,48 +4340,39 @@
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6912</v>
+        <v>7937</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4959,73 +4405,82 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>27.75555555555555</v>
+      </c>
+      <c r="W30" t="n">
+        <v>183.0144444444445</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.162222222222222</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>70.54083333333332</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1813041.666666667</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>71.98583333333333</v>
+      </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
+      <c r="AH30" t="n">
+        <v>25.74537355993642</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>181.0839356361434</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>67.62747138058469</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1514836.739611419</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>71.68768526053373</v>
+      </c>
       <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7937</v>
+        <v>33280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -5050,104 +4505,99 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>26.34636363636364</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>182.7972727272727</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S31" t="n">
+        <v>70.23636363636363</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2118090.909090909</v>
+      </c>
+      <c r="U31" t="n">
+        <v>72.45818181818183</v>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>24.31091478696742</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>182.8541019214704</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>65.88159147869673</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1584398.830409357</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>71.01041771094404</v>
+      </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="n">
-        <v>27.89506172839506</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>183.2382716049383</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.180246913580247</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>70.78148148148148</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1844351.851851852</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>71.97037037037038</v>
-      </c>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="n">
-        <v>25.76646444931207</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>180.8710395957149</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>67.80830153398298</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1547658.105741083</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>71.82582312898809</v>
-      </c>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33280</v>
+        <v>27111</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -5172,113 +4622,94 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>24.47474747474747</v>
+      </c>
+      <c r="W32" t="n">
+        <v>181.9090909090909</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>69.13131313131312</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2141616.161616162</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>74.1919191919192</v>
+      </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="n">
-        <v>26.26262626262626</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>182.9969696969697</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>70.11818181818181</v>
-      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>2092323.232323233</v>
+        <v>26.44585537918872</v>
       </c>
       <c r="AI32" t="n">
-        <v>72.40909090909092</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
+        <v>179.6592151675485</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>67.66053791887126</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1459809.30335097</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>70.87566137566138</v>
+      </c>
       <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="n">
-        <v>24.25657198551935</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>182.6230762090412</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>65.57213868003343</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1558220.922677063</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>70.97453819734521</v>
-      </c>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27111</v>
+        <v>10105</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5304,11 +4735,7 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -5329,59 +4756,17 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="n">
-        <v>24.47474747474747</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>181.9090909090909</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>69.13131313131312</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>2141616.161616162</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>74.1919191919192</v>
-      </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="n">
-        <v>26.44585537918872</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>179.6592151675485</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>67.66053791887126</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1459809.30335097</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>70.87566137566138</v>
-      </c>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -5390,21 +4775,21 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10105</v>
+        <v>6134</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5457,25 +4842,11 @@
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
-      <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5484,21 +4855,21 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6134</v>
+        <v>33597</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5537,62 +4908,69 @@
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>184</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>958333.3333333334</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>70.5</v>
+      </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="inlineStr"/>
-      <c r="BC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>33597</v>
+        <v>5327</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5625,73 +5003,82 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>27.40833333333333</v>
+      </c>
+      <c r="W36" t="n">
+        <v>185.225</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>71.28333333333332</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2358333.333333333</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>72.80833333333332</v>
+      </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
+      <c r="AH36" t="n">
+        <v>27.43916062801932</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>184.1551716701173</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.078804347826087</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>70.31357832988267</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2218741.91252588</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>72.74381038647344</v>
+      </c>
       <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5327</v>
+        <v>9052</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5738,59 +5125,17 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="n">
-        <v>27.51818181818182</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>185.3181818181818</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.027272727272727</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>71.31818181818181</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2361818.181818182</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>72.76363636363637</v>
-      </c>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="n">
-        <v>28.02453886693017</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>184.4290184453228</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.08596837944664</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>70.62779973649539</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2226939.229249012</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>72.44779314888011</v>
-      </c>
-      <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -5799,21 +5144,21 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9052</v>
+        <v>24121</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5838,53 +5183,71 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>24.13055555555556</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>182.7361111111111</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>67.49305555555554</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1700729.166666667</v>
+      </c>
+      <c r="U38" t="n">
+        <v>73.7861111111111</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>23.75022724189391</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>182.5922347714015</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>66.05305589472256</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1407363.358092525</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>73.02994675078008</v>
+      </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -5893,21 +5256,21 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24121</v>
+        <v>10669</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5932,11 +5295,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -5952,65 +5311,23 @@
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="n">
-        <v>24.13055555555556</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>182.7361111111111</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>67.49305555555554</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1700729.166666667</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>73.7861111111111</v>
-      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="n">
-        <v>23.75022724189391</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>182.5922347714015</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>66.05305589472256</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1407363.358092525</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>73.02994675078008</v>
-      </c>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="BC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -6019,21 +5336,21 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10669</v>
+        <v>7798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -6086,25 +5403,11 @@
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr"/>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr"/>
-      <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -6113,21 +5416,21 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7798</v>
+        <v>27137</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6152,53 +5455,71 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>26.13703703703703</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>182.4462962962963</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>72.06851851851852</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3207407.407407407</v>
+      </c>
+      <c r="U41" t="n">
+        <v>74.71296296296296</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>25.23319380960045</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>183.930834297842</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>68.66487742862422</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2302672.713049951</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>73.52775559904715</v>
+      </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
-      <c r="BC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -6207,21 +5528,21 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>27137</v>
+        <v>12500</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6246,11 +5567,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -6264,90 +5581,69 @@
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>183.6666666666667</v>
+      </c>
       <c r="AD42" t="n">
-        <v>26.11313131313131</v>
+        <v>1</v>
       </c>
       <c r="AE42" t="n">
-        <v>182.3414141414141</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AF42" t="n">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="AG42" t="n">
-        <v>72.06565656565657</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>3219898.98989899</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>74.69595959595959</v>
-      </c>
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="n">
-        <v>25.33131632375994</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>183.8965744787647</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>68.69035579626141</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2330013.589061485</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>73.54776135280669</v>
-      </c>
-      <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
-      <c r="BB42" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="BC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12500</v>
+        <v>21944</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6373,52 +5669,86 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
-      <c r="BB43" t="inlineStr"/>
-      <c r="BC43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>25.81111111111111</v>
+      </c>
+      <c r="W43" t="n">
+        <v>180.1177777777778</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>69.87111111111112</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2449166.666666667</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>73.33666666666666</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>24.85345238095238</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>178.7205952380952</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>67.56476190476191</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1632866.071428571</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>73.49333333333334</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -6426,27 +5756,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">eltringham g 
+          <t xml:space="preserve">davies a 
   eng </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21944</v>
+        <v>23408</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6474,110 +5804,119 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>26.7290404040404</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>184.6234848484848</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.011363636363636</v>
+      </c>
+      <c r="S44" t="n">
+        <v>69.81666666666666</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2210265.151515151</v>
+      </c>
+      <c r="U44" t="n">
+        <v>71.78434343434343</v>
+      </c>
+      <c r="V44" t="n">
+        <v>21.97222222222222</v>
+      </c>
+      <c r="W44" t="n">
+        <v>182.3013888888889</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>69.17777777777778</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3051166.666666667</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>77.47777777777777</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>23.53221346936517</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>181.8235490687503</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>66.72360388149862</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1675259.956761505</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>73.38087993877468</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>22.18384325152346</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>181.53566996443</v>
+      </c>
       <c r="AJ44" t="n">
-        <v>25.55555555555556</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="n">
-        <v>180.2666666666667</v>
+        <v>65.89287727051742</v>
       </c>
       <c r="AL44" t="n">
-        <v>1</v>
+        <v>1690857.960009827</v>
       </c>
       <c r="AM44" t="n">
-        <v>69.95555555555556</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>2555555.555555556</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>73.52222222222223</v>
-      </c>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="n">
-        <v>24.95568783068783</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>178.7414021164021</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>67.70899470899471</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1653740.079365079</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>73.59259259259258</v>
-      </c>
-      <c r="BB44" t="inlineStr"/>
-      <c r="BC44" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
+        <v>73.7128818615987</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>23408</v>
+        <v>12021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6603,112 +5942,66 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>26.72222222222222</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>181.9888888888889</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1103055.555555556</v>
+      </c>
+      <c r="U45" t="n">
+        <v>69.39999999999999</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
+      <c r="AB45" t="n">
+        <v>27.36920026854237</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>182.1784994975784</v>
+      </c>
       <c r="AD45" t="n">
-        <v>26.72694444444445</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="n">
-        <v>184.4858333333333</v>
+        <v>65.48439883703041</v>
       </c>
       <c r="AF45" t="n">
-        <v>1</v>
+        <v>873448.9505377664</v>
       </c>
       <c r="AG45" t="n">
-        <v>69.68583333333333</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1839104.166666667</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>71.63777777777777</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>21.89506172839506</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>182.3719135802469</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>69.24691358024691</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>3114567.901234568</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>77.61728395061728</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>23.60210148296836</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>181.8670150867365</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>66.59040871409293</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>1637924.841326544</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>73.20230126598548</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>22.21220678740702</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>181.6666174207953</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>65.95240331644794</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1715239.003185522</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>73.72859889383984</v>
-      </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="BC45" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+        <v>68.24484509155562</v>
+      </c>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -6717,21 +6010,21 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12021</v>
+        <v>5108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6772,65 +6065,23 @@
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="n">
-        <v>26.72222222222222</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>181.9888888888889</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>66.88888888888889</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1103055.555555556</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>69.39999999999999</v>
-      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="n">
-        <v>27.36920026854237</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>182.1784994975784</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>65.48439883703041</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>873448.9505377664</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>68.24484509155562</v>
-      </c>
-      <c r="AV46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr"/>
-      <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr"/>
-      <c r="BA46" t="inlineStr"/>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -6839,21 +6090,21 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5108</v>
+        <v>9877</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6906,25 +6157,11 @@
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -6933,21 +6170,21 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9877</v>
+        <v>21088</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -6972,53 +6209,71 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>24.69642857142857</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>179.9642857142857</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>68.98214285714286</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1917857.142857143</v>
+      </c>
+      <c r="U48" t="n">
+        <v>73.78571428571429</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
+      <c r="AB48" t="n">
+        <v>24.74117691733791</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>179.3993700829614</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>67.20807678733375</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1524650.055396959</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>72.72045644414065</v>
+      </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr"/>
-      <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
-      <c r="BB48" t="inlineStr"/>
-      <c r="BC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -7027,21 +6282,21 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>21088</v>
+        <v>16587</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -7066,11 +6321,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
@@ -7086,65 +6337,23 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="n">
-        <v>24.69642857142857</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>179.9642857142857</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>68.98214285714286</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1917857.142857143</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>73.78571428571429</v>
-      </c>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="n">
-        <v>24.74416482878815</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>179.4199350128143</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>67.58833928751369</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1592468.315520431</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>72.91955477920391</v>
-      </c>
-      <c r="AV49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="BC49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -7153,21 +6362,21 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16587</v>
+        <v>11300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -7220,25 +6429,11 @@
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr"/>
-      <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr"/>
-      <c r="BB50" t="inlineStr"/>
-      <c r="BC50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -7247,21 +6442,21 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11300</v>
+        <v>22200</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -7286,53 +6481,71 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>23.9730303030303</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>183.4217171717171</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>69.72090909090909</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2491030.303030303</v>
+      </c>
+      <c r="U51" t="n">
+        <v>74.15494949494951</v>
+      </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>24.2981323326432</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>182.3706970324362</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>68.51307884748101</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2241076.509661836</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>73.93868788819876</v>
+      </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
-      <c r="BA51" t="inlineStr"/>
-      <c r="BB51" t="inlineStr"/>
-      <c r="BC51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -7341,21 +6554,21 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>22200</v>
+        <v>25133</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -7380,11 +6593,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
@@ -7400,88 +6609,46 @@
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="n">
-        <v>24.00707070707071</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>183.3080808080808</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>69.80101010101011</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2560404.04040404</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>74.25858585858585</v>
-      </c>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
       <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="n">
-        <v>24.17153592515911</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>182.4535522582624</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>68.52147649720114</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2294251.67740204</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>74.13326432022083</v>
-      </c>
-      <c r="AV52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr"/>
-      <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr"/>
-      <c r="BA52" t="inlineStr"/>
-      <c r="BB52" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="BC52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>25133</v>
+        <v>32050</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>IgO7K1ZA</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -7508,74 +6675,93 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>24.03818181818182</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>182.3655808080808</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>71.67818181818181</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4148545.454545455</v>
+      </c>
+      <c r="U53" t="n">
+        <v>77.17017676767678</v>
+      </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
+      <c r="AB53" t="n">
+        <v>23.16944619707778</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>180.2543915149178</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>68.99621986200933</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2830621.525769552</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>76.29814666327825</v>
+      </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
-      <c r="BB53" t="inlineStr"/>
-      <c r="BC53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
+        <v>45518.65625</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>32050</v>
+        <v>25586</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>IgO7K1ZA</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -7600,109 +6786,122 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>24.14010101010101</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>179.8412121212121</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.084545454545454</v>
+      </c>
+      <c r="S54" t="n">
+        <v>69.90797979797981</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3085373.737373737</v>
+      </c>
+      <c r="U54" t="n">
+        <v>75.09161616161617</v>
+      </c>
+      <c r="V54" t="n">
+        <v>26.5979797979798</v>
+      </c>
+      <c r="W54" t="n">
+        <v>182.8343434343434</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>67.42222222222222</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1263005.05050505</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>70.77070707070706</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>25.21093057908275</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>180.2007316404823</v>
+      </c>
       <c r="AD54" t="n">
-        <v>24.03818181818182</v>
+        <v>1.019396845694799</v>
       </c>
       <c r="AE54" t="n">
-        <v>182.3655808080808</v>
+        <v>69.64008402438709</v>
       </c>
       <c r="AF54" t="n">
-        <v>1</v>
+        <v>2982127.41292169</v>
       </c>
       <c r="AG54" t="n">
-        <v>71.67818181818181</v>
+        <v>74.32012424205519</v>
       </c>
       <c r="AH54" t="n">
-        <v>4148545.454545455</v>
+        <v>25.73872785829307</v>
       </c>
       <c r="AI54" t="n">
-        <v>77.17017676767678</v>
-      </c>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="n">
-        <v>23.23972415011889</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>180.0264973330763</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>69.24250851487693</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2863183.678346507</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>76.43462799627272</v>
-      </c>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
-      <c r="BA54" t="inlineStr"/>
-      <c r="BB54" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="BC54" t="inlineStr"/>
+        <v>184.6415056360708</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.013888888888889</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>66.65116747181963</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1734460.547504026</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>70.32729468599034</v>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>25586</v>
+        <v>17000</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -7727,136 +6926,95 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>181.3535353535354</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>67.95959595959596</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2172727.272727273</v>
+      </c>
+      <c r="U55" t="n">
+        <v>74.01010101010101</v>
+      </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>24.39139433551198</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>181.0827240558059</v>
+      </c>
       <c r="AD55" t="n">
-        <v>24.2050505050505</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>179.6383838383839</v>
+        <v>66.0972330478085</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.093939393939394</v>
+        <v>1361211.57762622</v>
       </c>
       <c r="AG55" t="n">
-        <v>70.02121212121213</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>3147020.202020202</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>75.11414141414143</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>26.5979797979798</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>182.8343434343434</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>67.42222222222222</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1263005.05050505</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>70.77070707070706</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>25.63840771413235</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>180.4452573783137</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.021552050772</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>70.2869620472988</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3089030.458801878</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>74.53751178410172</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>25.73872785829307</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>184.6415056360708</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.013888888888889</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>66.65116747181963</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1734460.547504026</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>70.32729468599034</v>
-      </c>
-      <c r="BB55" t="inlineStr">
+        <v>72.23851845085861</v>
+      </c>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr">
         <is>
           <t>8tPSZqtA</t>
         </is>
       </c>
-      <c r="BC55" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17000</v>
+        <v>37792</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>jizXHcsM</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -7881,237 +7039,96 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>23.19075369075369</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>184.2111888111888</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.243667443667444</v>
+      </c>
+      <c r="S56" t="n">
+        <v>74.32486402486403</v>
+      </c>
+      <c r="T56" t="n">
+        <v>8444553.224553224</v>
+      </c>
+      <c r="U56" t="n">
+        <v>80.17793317793318</v>
+      </c>
+      <c r="V56" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="W56" t="n">
+        <v>181.79</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2563000</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>75.62</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>24.87756300849001</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>180.937742408289</v>
+      </c>
       <c r="AD56" t="n">
-        <v>24.09090909090909</v>
+        <v>1.078975665320628</v>
       </c>
       <c r="AE56" t="n">
-        <v>181.3535353535354</v>
+        <v>73.18094106582734</v>
       </c>
       <c r="AF56" t="n">
-        <v>1</v>
+        <v>5406582.824970537</v>
       </c>
       <c r="AG56" t="n">
-        <v>67.95959595959596</v>
+        <v>77.18731127040247</v>
       </c>
       <c r="AH56" t="n">
-        <v>2172727.272727273</v>
+        <v>22.30158071460703</v>
       </c>
       <c r="AI56" t="n">
-        <v>74.01010101010101</v>
-      </c>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="n">
-        <v>24.39139433551198</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>181.0827240558059</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>66.0972330478085</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>1361211.57762622</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>72.23851845085861</v>
-      </c>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="BC56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45518.66666666666</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bell j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>37792</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>48</v>
-      </c>
-      <c r="I57" t="n">
-        <v>484</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="n">
-        <v>23.17887205387206</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>184.1732323232323</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.245454545454545</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>74.32415824915824</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>8512154.882154882</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>80.23905723905726</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>24.43333333333333</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>181.7222222222222</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.088888888888889</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>70.04444444444445</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>2534444.444444444</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>75.52222222222223</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>24.76479582330008</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>180.7338363269284</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.066326201533245</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>73.22166051362065</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>5489823.70141039</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>77.31830515832064</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>22.26671361452063</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>179.4508732657856</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.005847953216374</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>66.05732618583495</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>1948601.285085934</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>74.2258370284686</v>
-      </c>
-      <c r="BB57" t="inlineStr">
+        <v>180.0365551699762</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.005263157894737</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>66.1823627980207</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1952971.92580811</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>74.26479178716019</v>
+      </c>
+      <c r="AN56" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="BC57" t="inlineStr">
-        <is>
-          <t>n94TZqsm</t>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO56"/>
+  <dimension ref="A1:AO46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.66666666666</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75635</v>
+        <v>31876</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -692,85 +692,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>24.79033189033189</v>
+        <v>25.95792929292929</v>
       </c>
       <c r="Q2" t="n">
-        <v>184.938455988456</v>
+        <v>182.1589646464647</v>
       </c>
       <c r="R2" t="n">
-        <v>2.243722943722944</v>
+        <v>1.413080808080808</v>
       </c>
       <c r="S2" t="n">
-        <v>79.93578643578644</v>
+        <v>75.50679292929291</v>
       </c>
       <c r="T2" t="n">
-        <v>30165111.83261183</v>
+        <v>9454828.282828283</v>
       </c>
       <c r="U2" t="n">
-        <v>84.41594516594516</v>
+        <v>79.98118686868688</v>
       </c>
       <c r="V2" t="n">
-        <v>26.85545454545455</v>
+        <v>24.84065656565656</v>
       </c>
       <c r="W2" t="n">
-        <v>184.2227272727273</v>
+        <v>184.7355339105339</v>
       </c>
       <c r="X2" t="n">
-        <v>1.527272727272727</v>
+        <v>2.28430735930736</v>
       </c>
       <c r="Y2" t="n">
-        <v>77.10545454545453</v>
+        <v>80.07864357864358</v>
       </c>
       <c r="Z2" t="n">
-        <v>12927636.36363636</v>
+        <v>30888326.11832612</v>
       </c>
       <c r="AA2" t="n">
-        <v>79.16454545454545</v>
+        <v>84.49224386724386</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.31999783773852</v>
+        <v>23.37540726817042</v>
       </c>
       <c r="AC2" t="n">
-        <v>184.0530677224777</v>
+        <v>178.0010509227614</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.882099443861866</v>
+        <v>1.373564593301436</v>
       </c>
       <c r="AE2" t="n">
-        <v>75.38346318105634</v>
+        <v>73.06198165869218</v>
       </c>
       <c r="AF2" t="n">
-        <v>19021567.33315856</v>
+        <v>8249211.950330371</v>
       </c>
       <c r="AG2" t="n">
-        <v>81.55534728384107</v>
+        <v>80.3366968557758</v>
       </c>
       <c r="AH2" t="n">
-        <v>28.21626172208014</v>
+        <v>24.31084032858101</v>
       </c>
       <c r="AI2" t="n">
-        <v>181.2419288150043</v>
+        <v>184.1186354880454</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.308927962489344</v>
+        <v>1.860854022616445</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.99781055900621</v>
+        <v>75.30947050706368</v>
       </c>
       <c r="AL2" t="n">
-        <v>6886981.549141395</v>
+        <v>18567343.88993511</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.14754475703324</v>
+        <v>81.49234362083742</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -782,35 +786,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.35416666666</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29673</v>
+        <v>25486</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -837,105 +841,105 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.38383838383838</v>
+        <v>25.60826446280992</v>
       </c>
       <c r="Q3" t="n">
-        <v>182.6767676767677</v>
+        <v>183.6884297520661</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>70.92929292929291</v>
+        <v>76.58512396694215</v>
       </c>
       <c r="T3" t="n">
-        <v>2742424.242424242</v>
+        <v>14098925.61983472</v>
       </c>
       <c r="U3" t="n">
-        <v>74.38383838383839</v>
+        <v>80.06446280991736</v>
       </c>
       <c r="V3" t="n">
-        <v>25.75619834710744</v>
+        <v>27.75454545454546</v>
       </c>
       <c r="W3" t="n">
-        <v>183.3545454545454</v>
+        <v>182.9813131313131</v>
       </c>
       <c r="X3" t="n">
-        <v>2.614876033057851</v>
+        <v>2.13020202020202</v>
       </c>
       <c r="Y3" t="n">
-        <v>82.74710743801653</v>
+        <v>79.06585858585859</v>
       </c>
       <c r="Z3" t="n">
-        <v>46462231.40495867</v>
+        <v>19009151.51515152</v>
       </c>
       <c r="AA3" t="n">
-        <v>85.53305785123966</v>
+        <v>80.53979797979798</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.1712962962963</v>
+        <v>26.67399600780608</v>
       </c>
       <c r="AC3" t="n">
-        <v>183.2784391534391</v>
+        <v>183.6885234330886</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>1.170325352247549</v>
       </c>
       <c r="AE3" t="n">
-        <v>68.9292328042328</v>
+        <v>73.15379955983502</v>
       </c>
       <c r="AF3" t="n">
-        <v>2164021.164021164</v>
+        <v>7489130.950729921</v>
       </c>
       <c r="AG3" t="n">
-        <v>73.35515873015873</v>
+        <v>76.42569099791639</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.20834551211789</v>
+        <v>27.44039969017911</v>
       </c>
       <c r="AI3" t="n">
-        <v>183.2271528769611</v>
+        <v>180.6861366819455</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.786762491557889</v>
+        <v>1.691721203632968</v>
       </c>
       <c r="AK3" t="n">
-        <v>79.20719904562615</v>
+        <v>73.924584818776</v>
       </c>
       <c r="AL3" t="n">
-        <v>33498280.27258334</v>
+        <v>9206085.126474831</v>
       </c>
       <c r="AM3" t="n">
-        <v>84.38545991519138</v>
+        <v>77.54409154570919</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,21 +949,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">craven cottage
   london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60704</v>
+        <v>26600</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -984,127 +988,127 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
       <c r="P4" t="n">
-        <v>24.45416666666667</v>
+        <v>26.75272727272727</v>
       </c>
       <c r="Q4" t="n">
-        <v>182.8930555555555</v>
+        <v>184.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.236111111111111</v>
+        <v>1.512727272727272</v>
       </c>
       <c r="S4" t="n">
-        <v>83.40416666666667</v>
+        <v>77.00727272727272</v>
       </c>
       <c r="T4" t="n">
-        <v>58345833.33333334</v>
+        <v>12767727.27272727</v>
       </c>
       <c r="U4" t="n">
-        <v>86.30833333333332</v>
+        <v>79.10909090909091</v>
       </c>
       <c r="V4" t="n">
-        <v>26.32916666666666</v>
+        <v>26.32666666666666</v>
       </c>
       <c r="W4" t="n">
-        <v>182.9236111111111</v>
+        <v>182.8144444444444</v>
       </c>
       <c r="X4" t="n">
-        <v>1.452777777777778</v>
+        <v>1.395555555555556</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.4986111111111</v>
+        <v>75.88777777777777</v>
       </c>
       <c r="Z4" t="n">
-        <v>12162673.61111111</v>
+        <v>9569777.77777778</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.63194444444444</v>
+        <v>78.24555555555555</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.63040227574283</v>
+        <v>28.05046085627927</v>
       </c>
       <c r="AC4" t="n">
-        <v>179.6681381930763</v>
+        <v>181.4882491613246</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.772715612560814</v>
+        <v>1.302867356428738</v>
       </c>
       <c r="AE4" t="n">
-        <v>81.20040006433194</v>
+        <v>74.82053783173349</v>
       </c>
       <c r="AF4" t="n">
-        <v>37424843.79397692</v>
+        <v>6867890.640050486</v>
       </c>
       <c r="AG4" t="n">
-        <v>84.53740098910377</v>
+        <v>76.19927635876485</v>
       </c>
       <c r="AH4" t="n">
-        <v>23.99170791993758</v>
+        <v>26.0333313229598</v>
       </c>
       <c r="AI4" t="n">
-        <v>181.41839654232</v>
+        <v>180.5984624830794</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.253578850708037</v>
+        <v>1.456823542814255</v>
       </c>
       <c r="AK4" t="n">
-        <v>71.67427660059239</v>
+        <v>73.54142458418774</v>
       </c>
       <c r="AL4" t="n">
-        <v>7717944.827633822</v>
+        <v>5998922.906782331</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.60448020878643</v>
+        <v>76.36644761971775</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39572</v>
+        <v>55097</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1131,129 +1135,129 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>27.2</v>
+        <v>26.06883116883117</v>
       </c>
       <c r="Q5" t="n">
-        <v>183.8545454545455</v>
+        <v>182.0311688311688</v>
       </c>
       <c r="R5" t="n">
-        <v>1.581818181818181</v>
+        <v>3.081818181818182</v>
       </c>
       <c r="S5" t="n">
-        <v>76.67272727272727</v>
+        <v>84.82402597402597</v>
       </c>
       <c r="T5" t="n">
-        <v>11300000</v>
+        <v>71205681.81818183</v>
       </c>
       <c r="U5" t="n">
-        <v>79.18181818181817</v>
+        <v>87.43506493506493</v>
       </c>
       <c r="V5" t="n">
-        <v>25.64769921436588</v>
+        <v>26.19191919191919</v>
       </c>
       <c r="W5" t="n">
-        <v>182.0516273849607</v>
+        <v>182.5050505050505</v>
       </c>
       <c r="X5" t="n">
-        <v>1.375645342312009</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>75.46588103254768</v>
+        <v>70.94949494949495</v>
       </c>
       <c r="Z5" t="n">
-        <v>9438698.092031427</v>
+        <v>2815151.515151515</v>
       </c>
       <c r="AA5" t="n">
-        <v>80.13187429854096</v>
+        <v>74.60606060606061</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.25395343644704</v>
+        <v>24.84064024160389</v>
       </c>
       <c r="AC5" t="n">
-        <v>186.0413820890675</v>
+        <v>178.6274230706776</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.391129277798076</v>
+        <v>2.260184291107747</v>
       </c>
       <c r="AE5" t="n">
-        <v>73.15978778467908</v>
+        <v>80.25051774332921</v>
       </c>
       <c r="AF5" t="n">
-        <v>7081649.636666261</v>
+        <v>44786325.61720341</v>
       </c>
       <c r="AG5" t="n">
-        <v>77.1639765761377</v>
+        <v>84.93818259187732</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.40342418546366</v>
+        <v>25.1765873015873</v>
       </c>
       <c r="AI5" t="n">
-        <v>177.98210839599</v>
+        <v>183.0873015873016</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.39187343358396</v>
+        <v>1.005291005291005</v>
       </c>
       <c r="AK5" t="n">
-        <v>73.16341791979949</v>
+        <v>69.06216931216932</v>
       </c>
       <c r="AL5" t="n">
-        <v>8325323.621553885</v>
+        <v>2286772.486772487</v>
       </c>
       <c r="AM5" t="n">
-        <v>80.35131892230577</v>
+        <v>73.38690476190476</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52305</v>
+        <v>32384</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1278,127 +1282,123 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>26.40752984389348</v>
+        <v>25.41212121212121</v>
       </c>
       <c r="Q6" t="n">
-        <v>185.4415977961433</v>
+        <v>179.7472582972583</v>
       </c>
       <c r="R6" t="n">
-        <v>1.544903581267217</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>78.01836547291093</v>
+        <v>72.88946608946608</v>
       </c>
       <c r="T6" t="n">
-        <v>19569044.99540863</v>
+        <v>4524624.81962482</v>
       </c>
       <c r="U6" t="n">
-        <v>80.84508723599632</v>
+        <v>76.2005772005772</v>
       </c>
       <c r="V6" t="n">
-        <v>25.4010878010878</v>
+        <v>25.11</v>
       </c>
       <c r="W6" t="n">
-        <v>179.6252525252525</v>
+        <v>185.08</v>
       </c>
       <c r="X6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>74.97999999999999</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8868000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>78.80999999999999</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.65599619294358</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>179.0003223423757</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="n">
-        <v>72.87241647241646</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4502587.412587413</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>76.17327117327117</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>25.93938837842</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>181.7123021576579</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.376706363465257</v>
-      </c>
       <c r="AE6" t="n">
-        <v>73.46484223944698</v>
+        <v>70.89429878670836</v>
       </c>
       <c r="AF6" t="n">
-        <v>11454052.22823948</v>
+        <v>3220631.341469395</v>
       </c>
       <c r="AG6" t="n">
-        <v>78.16608533100629</v>
+        <v>75.78533397548743</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.91974415184134</v>
+        <v>24.65595847034466</v>
       </c>
       <c r="AI6" t="n">
-        <v>179.0702772078731</v>
+        <v>185.0414943368652</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>1.39932103276093</v>
       </c>
       <c r="AK6" t="n">
-        <v>71.12043365841319</v>
+        <v>75.25341980270369</v>
       </c>
       <c r="AL6" t="n">
-        <v>3210330.255848159</v>
+        <v>10611518.99890391</v>
       </c>
       <c r="AM6" t="n">
-        <v>75.60448554003541</v>
+        <v>79.4291761052247</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30404</v>
+        <v>62850</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1423,127 +1423,131 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>25.17090909090909</v>
+        <v>24.93106060606061</v>
       </c>
       <c r="Q7" t="n">
-        <v>185.1763636363636</v>
+        <v>184.7376262626262</v>
       </c>
       <c r="R7" t="n">
-        <v>1.296363636363636</v>
+        <v>2.10580808080808</v>
       </c>
       <c r="S7" t="n">
-        <v>74.98636363636363</v>
+        <v>81.75808080808082</v>
       </c>
       <c r="T7" t="n">
-        <v>8798454.545454545</v>
+        <v>39735858.58585859</v>
       </c>
       <c r="U7" t="n">
-        <v>78.77272727272728</v>
+        <v>85.02904040404042</v>
       </c>
       <c r="V7" t="n">
-        <v>24.27272727272727</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="W7" t="n">
-        <v>181.4909090909091</v>
+        <v>183.7107438016529</v>
       </c>
       <c r="X7" t="n">
-        <v>1.163636363636364</v>
+        <v>1.586776859504132</v>
       </c>
       <c r="Y7" t="n">
-        <v>74.9909090909091</v>
+        <v>76.62809917355372</v>
       </c>
       <c r="Z7" t="n">
-        <v>8609090.909090908</v>
+        <v>11128305.78512397</v>
       </c>
       <c r="AA7" t="n">
-        <v>78.98181818181818</v>
+        <v>79.07438016528926</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.67810132748751</v>
+        <v>24.35057573848736</v>
       </c>
       <c r="AC7" t="n">
-        <v>185.0450657654366</v>
+        <v>181.9618966950271</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.437178175618073</v>
+        <v>1.770577772213714</v>
       </c>
       <c r="AE7" t="n">
-        <v>75.33199123127511</v>
+        <v>78.47468696047362</v>
       </c>
       <c r="AF7" t="n">
-        <v>10834661.85604677</v>
+        <v>27306688.60474086</v>
       </c>
       <c r="AG7" t="n">
-        <v>79.55631896236756</v>
+        <v>82.14751719884705</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.77900309073078</v>
+        <v>25.2238737534134</v>
       </c>
       <c r="AI7" t="n">
-        <v>183.0110664544641</v>
+        <v>186.0865711299215</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.319073547745276</v>
+        <v>1.369558084711537</v>
       </c>
       <c r="AK7" t="n">
-        <v>74.73436945309734</v>
+        <v>73.18022665740058</v>
       </c>
       <c r="AL7" t="n">
-        <v>11566815.05761649</v>
+        <v>7226324.844521775</v>
       </c>
       <c r="AM7" t="n">
-        <v>79.52728237079704</v>
+        <v>77.05816052376154</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
-  london </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>62500</v>
+        <v>42789</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1568,127 +1572,127 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
       <c r="P8" t="n">
-        <v>27.74545454545455</v>
+        <v>26.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>183.0772727272727</v>
+        <v>182.63</v>
       </c>
       <c r="R8" t="n">
-        <v>2.137272727272728</v>
+        <v>2.13</v>
       </c>
       <c r="S8" t="n">
-        <v>79.08000000000001</v>
+        <v>79.73454545454545</v>
       </c>
       <c r="T8" t="n">
-        <v>19071272.72727273</v>
+        <v>25907363.63636364</v>
       </c>
       <c r="U8" t="n">
-        <v>80.56</v>
+        <v>81.76363636363635</v>
       </c>
       <c r="V8" t="n">
-        <v>26.01636363636364</v>
+        <v>24.39015151515152</v>
       </c>
       <c r="W8" t="n">
-        <v>182.62</v>
+        <v>182.8914141414141</v>
       </c>
       <c r="X8" t="n">
-        <v>2.130909090909091</v>
+        <v>2.248737373737373</v>
       </c>
       <c r="Y8" t="n">
-        <v>79.64181818181819</v>
+        <v>83.48106060606061</v>
       </c>
       <c r="Z8" t="n">
-        <v>25921909.09090909</v>
+        <v>59070075.75757576</v>
       </c>
       <c r="AA8" t="n">
-        <v>81.78272727272727</v>
+        <v>86.39393939393939</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.59664969017911</v>
+        <v>23.44079141801648</v>
       </c>
       <c r="AC8" t="n">
-        <v>180.8370295390884</v>
+        <v>182.9650722100434</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.714935489347254</v>
+        <v>1.668831496366663</v>
       </c>
       <c r="AE8" t="n">
-        <v>73.76654910449028</v>
+        <v>73.83322022287174</v>
       </c>
       <c r="AF8" t="n">
-        <v>8735370.840760546</v>
+        <v>14046885.3912942</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.36194868856634</v>
+        <v>79.45903270003654</v>
       </c>
       <c r="AH8" t="n">
-        <v>23.59745808468315</v>
+        <v>24.62991115976621</v>
       </c>
       <c r="AI8" t="n">
-        <v>183.2548341148054</v>
+        <v>179.4312619937057</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.71597435350952</v>
+        <v>1.804741465964376</v>
       </c>
       <c r="AK8" t="n">
-        <v>74.03274403239557</v>
+        <v>81.13672733121088</v>
       </c>
       <c r="AL8" t="n">
-        <v>14507861.58177039</v>
+        <v>37488494.35816084</v>
       </c>
       <c r="AM8" t="n">
-        <v>79.42498508098892</v>
+        <v>84.53400089918524</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17250</v>
+        <v>11307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1713,127 +1717,131 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>26.02454545454545</v>
+        <v>24.16565656565656</v>
       </c>
       <c r="Q9" t="n">
-        <v>184.7418181818182</v>
+        <v>181.2868686868687</v>
       </c>
       <c r="R9" t="n">
-        <v>1.045454545454545</v>
+        <v>1.164646464646464</v>
       </c>
       <c r="S9" t="n">
-        <v>76.45363636363636</v>
+        <v>75.02525252525253</v>
       </c>
       <c r="T9" t="n">
-        <v>11428000</v>
+        <v>8701313.131313132</v>
       </c>
       <c r="U9" t="n">
-        <v>78.99636363636364</v>
+        <v>79.13939393939394</v>
       </c>
       <c r="V9" t="n">
-        <v>25.70909090909091</v>
+        <v>26.30752984389348</v>
       </c>
       <c r="W9" t="n">
-        <v>183.6272727272728</v>
+        <v>185.3779614325069</v>
       </c>
       <c r="X9" t="n">
-        <v>1.3</v>
+        <v>1.535812672176309</v>
       </c>
       <c r="Y9" t="n">
-        <v>76.56363636363636</v>
+        <v>77.98200183654728</v>
       </c>
       <c r="Z9" t="n">
-        <v>14091818.18181818</v>
+        <v>19609044.99540863</v>
       </c>
       <c r="AA9" t="n">
-        <v>79.99090909090908</v>
+        <v>80.91781450872359</v>
       </c>
       <c r="AB9" t="n">
-        <v>24.76496732026144</v>
+        <v>23.75232324883355</v>
       </c>
       <c r="AC9" t="n">
-        <v>179.757034743722</v>
+        <v>183.0073115137526</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.097008943928448</v>
+        <v>1.279547856045672</v>
       </c>
       <c r="AE9" t="n">
-        <v>73.67978672170622</v>
+        <v>74.52231411712897</v>
       </c>
       <c r="AF9" t="n">
-        <v>7867469.685242519</v>
+        <v>11116913.87184574</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.52444788441692</v>
+        <v>79.43281596763498</v>
       </c>
       <c r="AH9" t="n">
-        <v>26.66244824016563</v>
+        <v>26.12590023612751</v>
       </c>
       <c r="AI9" t="n">
-        <v>183.7573757763975</v>
+        <v>181.8205037386856</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16104209799862</v>
+        <v>1.387081857536403</v>
       </c>
       <c r="AK9" t="n">
-        <v>72.87970583160799</v>
+        <v>73.69878492719401</v>
       </c>
       <c r="AL9" t="n">
-        <v>7252254.572118702</v>
+        <v>11748839.7776466</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.25773378191857</v>
+        <v>78.0719647776466</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.52083333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">taylor a 
+  eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40341</v>
+        <v>31750</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1858,131 +1866,127 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
       <c r="P10" t="n">
-        <v>23.24289044289044</v>
+        <v>26.37962962962963</v>
       </c>
       <c r="Q10" t="n">
-        <v>182.8868686868687</v>
+        <v>182.8317901234568</v>
       </c>
       <c r="R10" t="n">
-        <v>1.746386946386946</v>
+        <v>1.447530864197531</v>
       </c>
       <c r="S10" t="n">
-        <v>78.11841491841491</v>
+        <v>76.59567901234567</v>
       </c>
       <c r="T10" t="n">
-        <v>21256332.55633255</v>
+        <v>12223804.01234568</v>
       </c>
       <c r="U10" t="n">
-        <v>83.37280497280497</v>
+        <v>79.56327160493828</v>
       </c>
       <c r="V10" t="n">
-        <v>26.12532467532467</v>
+        <v>23.15198135198135</v>
       </c>
       <c r="W10" t="n">
-        <v>182.0993506493507</v>
+        <v>182.9148407148407</v>
       </c>
       <c r="X10" t="n">
-        <v>3.074025974025974</v>
+        <v>1.739393939393939</v>
       </c>
       <c r="Y10" t="n">
-        <v>84.82597402597402</v>
+        <v>78.12540792540791</v>
       </c>
       <c r="Z10" t="n">
-        <v>71237175.32467532</v>
+        <v>21626961.92696192</v>
       </c>
       <c r="AA10" t="n">
-        <v>87.37792207792208</v>
+        <v>83.49168609168609</v>
       </c>
       <c r="AB10" t="n">
-        <v>23.17863676384339</v>
+        <v>24.26921988166007</v>
       </c>
       <c r="AC10" t="n">
-        <v>183.0455706069853</v>
+        <v>181.0604148111325</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.688413738487773</v>
+        <v>1.301425740660191</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.53604547439519</v>
+        <v>72.11881770542058</v>
       </c>
       <c r="AF10" t="n">
-        <v>14727417.07896507</v>
+        <v>8247751.265215381</v>
       </c>
       <c r="AG10" t="n">
-        <v>81.36645894375737</v>
+        <v>78.65667681600695</v>
       </c>
       <c r="AH10" t="n">
-        <v>24.71819126201205</v>
+        <v>23.16745990651268</v>
       </c>
       <c r="AI10" t="n">
-        <v>178.3825251114939</v>
+        <v>182.8115140652365</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.242837352332237</v>
+        <v>1.643706309164959</v>
       </c>
       <c r="AK10" t="n">
-        <v>80.06990549843125</v>
+        <v>73.78982588202174</v>
       </c>
       <c r="AL10" t="n">
-        <v>44252779.69883605</v>
+        <v>15528206.03360017</v>
       </c>
       <c r="AM10" t="n">
-        <v>84.8861417755508</v>
+        <v>81.37763580108806</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.66666666666</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32261</v>
+        <v>61276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2009,129 +2013,125 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>26.27</v>
+        <v>25.7297520661157</v>
       </c>
       <c r="Q11" t="n">
-        <v>183.1111111111111</v>
+        <v>183.4049586776859</v>
       </c>
       <c r="R11" t="n">
-        <v>1.376666666666666</v>
+        <v>2.647107438016529</v>
       </c>
       <c r="S11" t="n">
-        <v>75.83222222222223</v>
+        <v>82.91239669421488</v>
       </c>
       <c r="T11" t="n">
-        <v>9670666.666666668</v>
+        <v>47609173.553719</v>
       </c>
       <c r="U11" t="n">
-        <v>78.07333333333334</v>
+        <v>85.69504132231404</v>
       </c>
       <c r="V11" t="n">
-        <v>24.93863636363636</v>
+        <v>25.93818181818182</v>
       </c>
       <c r="W11" t="n">
-        <v>184.5810606060606</v>
+        <v>184.6927272727273</v>
       </c>
       <c r="X11" t="n">
-        <v>2.127272727272727</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="Y11" t="n">
-        <v>81.80732323232324</v>
+        <v>76.45090909090909</v>
       </c>
       <c r="Z11" t="n">
-        <v>39996590.90909091</v>
+        <v>11463818.18181818</v>
       </c>
       <c r="AA11" t="n">
-        <v>85.0719696969697</v>
+        <v>79.08363636363637</v>
       </c>
       <c r="AB11" t="n">
-        <v>26.01794670757518</v>
+        <v>23.33581586784911</v>
       </c>
       <c r="AC11" t="n">
-        <v>180.5710586369255</v>
+        <v>183.5767576200441</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44720815819887</v>
+        <v>1.798422570609272</v>
       </c>
       <c r="AE11" t="n">
-        <v>73.5077707380339</v>
+        <v>79.53091446064592</v>
       </c>
       <c r="AF11" t="n">
-        <v>6010473.387551561</v>
+        <v>34011501.61645686</v>
       </c>
       <c r="AG11" t="n">
-        <v>76.21212069664082</v>
+        <v>84.47004489542854</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.56761627370971</v>
+        <v>24.71417784657723</v>
       </c>
       <c r="AI11" t="n">
-        <v>181.8566231806627</v>
+        <v>179.8178242174063</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.791435702162553</v>
+        <v>1.12358789129687</v>
       </c>
       <c r="AK11" t="n">
-        <v>78.66044060077272</v>
+        <v>73.72873409012728</v>
       </c>
       <c r="AL11" t="n">
-        <v>27633789.15570505</v>
+        <v>7912673.632610939</v>
       </c>
       <c r="AM11" t="n">
-        <v>82.04775332635592</v>
+        <v>77.78260577915376</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">hooper s 
+  eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31876</v>
+        <v>60704</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2158,129 +2158,129 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>AovF1Mia</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
       <c r="P12" t="n">
-        <v>25.64769921436588</v>
+        <v>24.39015151515152</v>
       </c>
       <c r="Q12" t="n">
-        <v>182.0516273849607</v>
+        <v>182.8914141414141</v>
       </c>
       <c r="R12" t="n">
-        <v>1.375645342312009</v>
+        <v>2.248737373737373</v>
       </c>
       <c r="S12" t="n">
-        <v>75.46588103254768</v>
+        <v>83.48106060606061</v>
       </c>
       <c r="T12" t="n">
-        <v>9438698.092031427</v>
+        <v>59070075.75757576</v>
       </c>
       <c r="U12" t="n">
-        <v>80.13187429854096</v>
+        <v>86.39393939393939</v>
       </c>
       <c r="V12" t="n">
-        <v>24.79033189033189</v>
+        <v>25.95792929292929</v>
       </c>
       <c r="W12" t="n">
-        <v>184.938455988456</v>
+        <v>182.1589646464647</v>
       </c>
       <c r="X12" t="n">
-        <v>2.243722943722944</v>
+        <v>1.413080808080808</v>
       </c>
       <c r="Y12" t="n">
-        <v>79.93578643578644</v>
+        <v>75.50679292929291</v>
       </c>
       <c r="Z12" t="n">
-        <v>30165111.83261183</v>
+        <v>9454828.282828283</v>
       </c>
       <c r="AA12" t="n">
-        <v>84.41594516594516</v>
+        <v>79.98118686868688</v>
       </c>
       <c r="AB12" t="n">
-        <v>23.40342418546366</v>
+        <v>24.62991115976621</v>
       </c>
       <c r="AC12" t="n">
-        <v>177.98210839599</v>
+        <v>179.4312619937057</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39187343358396</v>
+        <v>1.804741465964376</v>
       </c>
       <c r="AE12" t="n">
-        <v>73.16341791979949</v>
+        <v>81.13672733121088</v>
       </c>
       <c r="AF12" t="n">
-        <v>8325323.621553885</v>
+        <v>37488494.35816084</v>
       </c>
       <c r="AG12" t="n">
-        <v>80.35131892230577</v>
+        <v>84.53400089918524</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.31999783773852</v>
+        <v>23.37540726817042</v>
       </c>
       <c r="AI12" t="n">
-        <v>184.0530677224777</v>
+        <v>178.0010509227614</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.882099443861866</v>
+        <v>1.373564593301436</v>
       </c>
       <c r="AK12" t="n">
-        <v>75.38346318105634</v>
+        <v>73.06198165869218</v>
       </c>
       <c r="AL12" t="n">
-        <v>19021567.33315856</v>
+        <v>8249211.950330371</v>
       </c>
       <c r="AM12" t="n">
-        <v>81.55534728384107</v>
+        <v>80.3366968557758</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
+          <t xml:space="preserve">brentford community stadium
   london </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25486</v>
+        <v>17250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2305,131 +2305,123 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>25.70909090909091</v>
+        <v>25.93818181818182</v>
       </c>
       <c r="Q13" t="n">
-        <v>183.6272727272728</v>
+        <v>184.6927272727273</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="S13" t="n">
-        <v>76.56363636363636</v>
+        <v>76.45090909090909</v>
       </c>
       <c r="T13" t="n">
-        <v>14091818.18181818</v>
+        <v>11463818.18181818</v>
       </c>
       <c r="U13" t="n">
-        <v>79.99090909090908</v>
+        <v>79.08363636363637</v>
       </c>
       <c r="V13" t="n">
-        <v>27.74545454545455</v>
+        <v>25.41212121212121</v>
       </c>
       <c r="W13" t="n">
-        <v>183.0772727272727</v>
+        <v>179.7472582972583</v>
       </c>
       <c r="X13" t="n">
-        <v>2.137272727272728</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>79.08000000000001</v>
+        <v>72.88946608946608</v>
       </c>
       <c r="Z13" t="n">
-        <v>19071272.72727273</v>
+        <v>4524624.81962482</v>
       </c>
       <c r="AA13" t="n">
-        <v>80.56</v>
+        <v>76.2005772005772</v>
       </c>
       <c r="AB13" t="n">
-        <v>26.66244824016563</v>
+        <v>24.71417784657723</v>
       </c>
       <c r="AC13" t="n">
-        <v>183.7573757763975</v>
+        <v>179.8178242174063</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.16104209799862</v>
+        <v>1.12358789129687</v>
       </c>
       <c r="AE13" t="n">
-        <v>72.87970583160799</v>
+        <v>73.72873409012728</v>
       </c>
       <c r="AF13" t="n">
-        <v>7252254.572118702</v>
+        <v>7912673.632610939</v>
       </c>
       <c r="AG13" t="n">
-        <v>76.25773378191857</v>
+        <v>77.78260577915376</v>
       </c>
       <c r="AH13" t="n">
-        <v>27.59664969017911</v>
+        <v>24.65599619294358</v>
       </c>
       <c r="AI13" t="n">
-        <v>180.8370295390884</v>
+        <v>179.0003223423757</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.714935489347254</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>73.76654910449028</v>
+        <v>70.89429878670836</v>
       </c>
       <c r="AL13" t="n">
-        <v>8735370.840760546</v>
+        <v>3220631.341469395</v>
       </c>
       <c r="AM13" t="n">
-        <v>77.36194868856634</v>
+        <v>75.78533397548743</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>hUGEt9yf</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26600</v>
+        <v>39572</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2454,127 +2446,131 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>26.85545454545455</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="Q14" t="n">
-        <v>184.2227272727273</v>
+        <v>183.7107438016529</v>
       </c>
       <c r="R14" t="n">
-        <v>1.527272727272727</v>
+        <v>1.586776859504132</v>
       </c>
       <c r="S14" t="n">
-        <v>77.10545454545453</v>
+        <v>76.62809917355372</v>
       </c>
       <c r="T14" t="n">
-        <v>12927636.36363636</v>
+        <v>11128305.78512397</v>
       </c>
       <c r="U14" t="n">
-        <v>79.16454545454545</v>
+        <v>79.07438016528926</v>
       </c>
       <c r="V14" t="n">
-        <v>26.27</v>
+        <v>24.16565656565656</v>
       </c>
       <c r="W14" t="n">
-        <v>183.1111111111111</v>
+        <v>181.2868686868687</v>
       </c>
       <c r="X14" t="n">
-        <v>1.376666666666666</v>
+        <v>1.164646464646464</v>
       </c>
       <c r="Y14" t="n">
-        <v>75.83222222222223</v>
+        <v>75.02525252525253</v>
       </c>
       <c r="Z14" t="n">
-        <v>9670666.666666668</v>
+        <v>8701313.131313132</v>
       </c>
       <c r="AA14" t="n">
-        <v>78.07333333333334</v>
+        <v>79.13939393939394</v>
       </c>
       <c r="AB14" t="n">
-        <v>28.21626172208014</v>
+        <v>25.2238737534134</v>
       </c>
       <c r="AC14" t="n">
-        <v>181.2419288150043</v>
+        <v>186.0865711299215</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.308927962489344</v>
+        <v>1.369558084711537</v>
       </c>
       <c r="AE14" t="n">
-        <v>74.99781055900621</v>
+        <v>73.18022665740058</v>
       </c>
       <c r="AF14" t="n">
-        <v>6886981.549141395</v>
+        <v>7226324.844521775</v>
       </c>
       <c r="AG14" t="n">
-        <v>76.14754475703324</v>
+        <v>77.05816052376154</v>
       </c>
       <c r="AH14" t="n">
-        <v>26.01794670757518</v>
+        <v>23.75232324883355</v>
       </c>
       <c r="AI14" t="n">
-        <v>180.5710586369255</v>
+        <v>183.0073115137526</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.44720815819887</v>
+        <v>1.279547856045672</v>
       </c>
       <c r="AK14" t="n">
-        <v>73.5077707380339</v>
+        <v>74.52231411712897</v>
       </c>
       <c r="AL14" t="n">
-        <v>6010473.387551561</v>
+        <v>11116913.87184574</v>
       </c>
       <c r="AM14" t="n">
-        <v>76.21212069664082</v>
+        <v>79.43281596763498</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>MBpIn2MH</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>55097</v>
+        <v>29673</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2601,129 +2597,125 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
           <t>Qo6off6p</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>26.12532467532467</v>
+        <v>26.19191919191919</v>
       </c>
       <c r="Q15" t="n">
-        <v>182.0993506493507</v>
+        <v>182.5050505050505</v>
       </c>
       <c r="R15" t="n">
-        <v>3.074025974025974</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>84.82597402597402</v>
+        <v>70.94949494949495</v>
       </c>
       <c r="T15" t="n">
-        <v>71237175.32467532</v>
+        <v>2815151.515151515</v>
       </c>
       <c r="U15" t="n">
-        <v>87.37792207792208</v>
+        <v>74.60606060606061</v>
       </c>
       <c r="V15" t="n">
-        <v>26.38383838383838</v>
+        <v>26.75272727272727</v>
       </c>
       <c r="W15" t="n">
-        <v>182.6767676767677</v>
+        <v>184.15</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.512727272727272</v>
       </c>
       <c r="Y15" t="n">
-        <v>70.92929292929291</v>
+        <v>77.00727272727272</v>
       </c>
       <c r="Z15" t="n">
-        <v>2742424.242424242</v>
+        <v>12767727.27272727</v>
       </c>
       <c r="AA15" t="n">
-        <v>74.38383838383839</v>
+        <v>79.10909090909091</v>
       </c>
       <c r="AB15" t="n">
-        <v>24.71819126201205</v>
+        <v>25.1765873015873</v>
       </c>
       <c r="AC15" t="n">
-        <v>178.3825251114939</v>
+        <v>183.0873015873016</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.242837352332237</v>
+        <v>1.005291005291005</v>
       </c>
       <c r="AE15" t="n">
-        <v>80.06990549843125</v>
+        <v>69.06216931216932</v>
       </c>
       <c r="AF15" t="n">
-        <v>44252779.69883605</v>
+        <v>2286772.486772487</v>
       </c>
       <c r="AG15" t="n">
-        <v>84.8861417755508</v>
+        <v>73.38690476190476</v>
       </c>
       <c r="AH15" t="n">
-        <v>25.1712962962963</v>
+        <v>28.05046085627927</v>
       </c>
       <c r="AI15" t="n">
-        <v>183.2784391534391</v>
+        <v>181.4882491613246</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>1.302867356428738</v>
       </c>
       <c r="AK15" t="n">
-        <v>68.9292328042328</v>
+        <v>74.82053783173349</v>
       </c>
       <c r="AL15" t="n">
-        <v>2164021.164021164</v>
+        <v>6867890.640050486</v>
       </c>
       <c r="AM15" t="n">
-        <v>73.35515873015873</v>
+        <v>76.19927635876485</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>lhUKMQZu</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">scott g 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32384</v>
+        <v>32261</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2748,123 +2740,127 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>25.4010878010878</v>
+        <v>26.32666666666666</v>
       </c>
       <c r="Q16" t="n">
-        <v>179.6252525252525</v>
+        <v>182.8144444444444</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>1.395555555555556</v>
       </c>
       <c r="S16" t="n">
-        <v>72.87241647241646</v>
+        <v>75.88777777777777</v>
       </c>
       <c r="T16" t="n">
-        <v>4502587.412587413</v>
+        <v>9569777.77777778</v>
       </c>
       <c r="U16" t="n">
-        <v>76.17327117327117</v>
+        <v>78.24555555555555</v>
       </c>
       <c r="V16" t="n">
-        <v>25.17090909090909</v>
+        <v>26.07</v>
       </c>
       <c r="W16" t="n">
-        <v>185.1763636363636</v>
+        <v>182.63</v>
       </c>
       <c r="X16" t="n">
-        <v>1.296363636363636</v>
+        <v>2.13</v>
       </c>
       <c r="Y16" t="n">
-        <v>74.98636363636363</v>
+        <v>79.73454545454545</v>
       </c>
       <c r="Z16" t="n">
-        <v>8798454.545454545</v>
+        <v>25907363.63636364</v>
       </c>
       <c r="AA16" t="n">
-        <v>78.77272727272728</v>
+        <v>81.76363636363635</v>
       </c>
       <c r="AB16" t="n">
-        <v>24.91974415184134</v>
+        <v>26.0333313229598</v>
       </c>
       <c r="AC16" t="n">
-        <v>179.0702772078731</v>
+        <v>180.5984624830794</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>1.456823542814255</v>
       </c>
       <c r="AE16" t="n">
-        <v>71.12043365841319</v>
+        <v>73.54142458418774</v>
       </c>
       <c r="AF16" t="n">
-        <v>3210330.255848159</v>
+        <v>5998922.906782331</v>
       </c>
       <c r="AG16" t="n">
-        <v>75.60448554003541</v>
+        <v>76.36644761971775</v>
       </c>
       <c r="AH16" t="n">
-        <v>24.67810132748751</v>
+        <v>23.44079141801648</v>
       </c>
       <c r="AI16" t="n">
-        <v>185.0450657654366</v>
+        <v>182.9650722100434</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.437178175618073</v>
+        <v>1.668831496366663</v>
       </c>
       <c r="AK16" t="n">
-        <v>75.33199123127511</v>
+        <v>73.83322022287174</v>
       </c>
       <c r="AL16" t="n">
-        <v>10834661.85604677</v>
+        <v>14046885.3912942</v>
       </c>
       <c r="AM16" t="n">
-        <v>79.55631896236756</v>
+        <v>79.45903270003654</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>62850</v>
+        <v>30404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2889,131 +2885,123 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>24.93863636363636</v>
+        <v>25.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>184.5810606060606</v>
+        <v>185.08</v>
       </c>
       <c r="R17" t="n">
-        <v>2.127272727272727</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>81.80732323232324</v>
+        <v>74.97999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>39996590.90909091</v>
+        <v>8868000</v>
       </c>
       <c r="U17" t="n">
-        <v>85.0719696969697</v>
+        <v>78.80999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>27.2</v>
+        <v>26.37962962962963</v>
       </c>
       <c r="W17" t="n">
-        <v>183.8545454545455</v>
+        <v>182.8317901234568</v>
       </c>
       <c r="X17" t="n">
-        <v>1.581818181818181</v>
+        <v>1.447530864197531</v>
       </c>
       <c r="Y17" t="n">
-        <v>76.67272727272727</v>
+        <v>76.59567901234567</v>
       </c>
       <c r="Z17" t="n">
-        <v>11300000</v>
+        <v>12223804.01234568</v>
       </c>
       <c r="AA17" t="n">
-        <v>79.18181818181817</v>
+        <v>79.56327160493828</v>
       </c>
       <c r="AB17" t="n">
-        <v>24.56761627370971</v>
+        <v>24.65595847034466</v>
       </c>
       <c r="AC17" t="n">
-        <v>181.8566231806627</v>
+        <v>185.0414943368652</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.791435702162553</v>
+        <v>1.39932103276093</v>
       </c>
       <c r="AE17" t="n">
-        <v>78.66044060077272</v>
+        <v>75.25341980270369</v>
       </c>
       <c r="AF17" t="n">
-        <v>27633789.15570505</v>
+        <v>10611518.99890391</v>
       </c>
       <c r="AG17" t="n">
-        <v>82.04775332635592</v>
+        <v>79.4291761052247</v>
       </c>
       <c r="AH17" t="n">
-        <v>25.25395343644704</v>
+        <v>24.26921988166007</v>
       </c>
       <c r="AI17" t="n">
-        <v>186.0413820890675</v>
+        <v>181.0604148111325</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.391129277798076</v>
+        <v>1.301425740660191</v>
       </c>
       <c r="AK17" t="n">
-        <v>73.15978778467908</v>
+        <v>72.11881770542058</v>
       </c>
       <c r="AL17" t="n">
-        <v>7081649.636666261</v>
+        <v>8247751.265215381</v>
       </c>
       <c r="AM17" t="n">
-        <v>77.1639765761377</v>
+        <v>78.65667681600695</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>42789</v>
+        <v>62500</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3038,127 +3026,131 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>26.01636363636364</v>
+        <v>27.75454545454546</v>
       </c>
       <c r="Q18" t="n">
-        <v>182.62</v>
+        <v>182.9813131313131</v>
       </c>
       <c r="R18" t="n">
-        <v>2.130909090909091</v>
+        <v>2.13020202020202</v>
       </c>
       <c r="S18" t="n">
-        <v>79.64181818181819</v>
+        <v>79.06585858585859</v>
       </c>
       <c r="T18" t="n">
-        <v>25921909.09090909</v>
+        <v>19009151.51515152</v>
       </c>
       <c r="U18" t="n">
-        <v>81.78272727272727</v>
+        <v>80.53979797979798</v>
       </c>
       <c r="V18" t="n">
-        <v>24.45416666666667</v>
+        <v>26.06883116883117</v>
       </c>
       <c r="W18" t="n">
-        <v>182.8930555555555</v>
+        <v>182.0311688311688</v>
       </c>
       <c r="X18" t="n">
-        <v>2.236111111111111</v>
+        <v>3.081818181818182</v>
       </c>
       <c r="Y18" t="n">
-        <v>83.40416666666667</v>
+        <v>84.82402597402597</v>
       </c>
       <c r="Z18" t="n">
-        <v>58345833.33333334</v>
+        <v>71205681.81818183</v>
       </c>
       <c r="AA18" t="n">
-        <v>86.30833333333332</v>
+        <v>87.43506493506493</v>
       </c>
       <c r="AB18" t="n">
-        <v>23.59745808468315</v>
+        <v>27.44039969017911</v>
       </c>
       <c r="AC18" t="n">
-        <v>183.2548341148054</v>
+        <v>180.6861366819455</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71597435350952</v>
+        <v>1.691721203632968</v>
       </c>
       <c r="AE18" t="n">
-        <v>74.03274403239557</v>
+        <v>73.924584818776</v>
       </c>
       <c r="AF18" t="n">
-        <v>14507861.58177039</v>
+        <v>9206085.126474831</v>
       </c>
       <c r="AG18" t="n">
-        <v>79.42498508098892</v>
+        <v>77.54409154570919</v>
       </c>
       <c r="AH18" t="n">
-        <v>24.63040227574283</v>
+        <v>24.84064024160389</v>
       </c>
       <c r="AI18" t="n">
-        <v>179.6681381930763</v>
+        <v>178.6274230706776</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.772715612560814</v>
+        <v>2.260184291107747</v>
       </c>
       <c r="AK18" t="n">
-        <v>81.20040006433194</v>
+        <v>80.25051774332921</v>
       </c>
       <c r="AL18" t="n">
-        <v>37424843.79397692</v>
+        <v>44786325.61720341</v>
       </c>
       <c r="AM18" t="n">
-        <v>84.53740098910377</v>
+        <v>84.93818259187732</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11307</v>
+        <v>40341</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3185,129 +3177,129 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>24.27272727272727</v>
+        <v>23.15198135198135</v>
       </c>
       <c r="Q19" t="n">
-        <v>181.4909090909091</v>
+        <v>182.9148407148407</v>
       </c>
       <c r="R19" t="n">
-        <v>1.163636363636364</v>
+        <v>1.739393939393939</v>
       </c>
       <c r="S19" t="n">
-        <v>74.9909090909091</v>
+        <v>78.12540792540791</v>
       </c>
       <c r="T19" t="n">
-        <v>8609090.909090908</v>
+        <v>21626961.92696192</v>
       </c>
       <c r="U19" t="n">
-        <v>78.98181818181818</v>
+        <v>83.49168609168609</v>
       </c>
       <c r="V19" t="n">
-        <v>26.40752984389348</v>
+        <v>25.60826446280992</v>
       </c>
       <c r="W19" t="n">
-        <v>185.4415977961433</v>
+        <v>183.6884297520661</v>
       </c>
       <c r="X19" t="n">
-        <v>1.544903581267217</v>
+        <v>1.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>78.01836547291093</v>
+        <v>76.58512396694215</v>
       </c>
       <c r="Z19" t="n">
-        <v>19569044.99540863</v>
+        <v>14098925.61983472</v>
       </c>
       <c r="AA19" t="n">
-        <v>80.84508723599632</v>
+        <v>80.06446280991736</v>
       </c>
       <c r="AB19" t="n">
-        <v>23.77900309073078</v>
+        <v>23.16745990651268</v>
       </c>
       <c r="AC19" t="n">
-        <v>183.0110664544641</v>
+        <v>182.8115140652365</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.319073547745276</v>
+        <v>1.643706309164959</v>
       </c>
       <c r="AE19" t="n">
-        <v>74.73436945309734</v>
+        <v>73.78982588202174</v>
       </c>
       <c r="AF19" t="n">
-        <v>11566815.05761649</v>
+        <v>15528206.03360017</v>
       </c>
       <c r="AG19" t="n">
-        <v>79.52728237079704</v>
+        <v>81.37763580108806</v>
       </c>
       <c r="AH19" t="n">
-        <v>25.93938837842</v>
+        <v>26.67399600780608</v>
       </c>
       <c r="AI19" t="n">
-        <v>181.7123021576579</v>
+        <v>183.6885234330886</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.376706363465257</v>
+        <v>1.170325352247549</v>
       </c>
       <c r="AK19" t="n">
-        <v>73.46484223944698</v>
+        <v>73.15379955983502</v>
       </c>
       <c r="AL19" t="n">
-        <v>11454052.22823948</v>
+        <v>7489130.950729921</v>
       </c>
       <c r="AM19" t="n">
-        <v>78.16608533100629</v>
+        <v>76.42569099791639</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31750</v>
+        <v>52305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3332,127 +3324,131 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>26.32916666666666</v>
+        <v>26.30752984389348</v>
       </c>
       <c r="Q20" t="n">
-        <v>182.9236111111111</v>
+        <v>185.3779614325069</v>
       </c>
       <c r="R20" t="n">
-        <v>1.452777777777778</v>
+        <v>1.535812672176309</v>
       </c>
       <c r="S20" t="n">
-        <v>76.4986111111111</v>
+        <v>77.98200183654728</v>
       </c>
       <c r="T20" t="n">
-        <v>12162673.61111111</v>
+        <v>19609044.99540863</v>
       </c>
       <c r="U20" t="n">
-        <v>79.63194444444444</v>
+        <v>80.91781450872359</v>
       </c>
       <c r="V20" t="n">
-        <v>23.24289044289044</v>
+        <v>24.93106060606061</v>
       </c>
       <c r="W20" t="n">
-        <v>182.8868686868687</v>
+        <v>184.7376262626262</v>
       </c>
       <c r="X20" t="n">
-        <v>1.746386946386946</v>
+        <v>2.10580808080808</v>
       </c>
       <c r="Y20" t="n">
-        <v>78.11841491841491</v>
+        <v>81.75808080808082</v>
       </c>
       <c r="Z20" t="n">
-        <v>21256332.55633255</v>
+        <v>39735858.58585859</v>
       </c>
       <c r="AA20" t="n">
-        <v>83.37280497280497</v>
+        <v>85.02904040404042</v>
       </c>
       <c r="AB20" t="n">
-        <v>23.99170791993758</v>
+        <v>26.12590023612751</v>
       </c>
       <c r="AC20" t="n">
-        <v>181.41839654232</v>
+        <v>181.8205037386856</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.253578850708037</v>
+        <v>1.387081857536403</v>
       </c>
       <c r="AE20" t="n">
-        <v>71.67427660059239</v>
+        <v>73.69878492719401</v>
       </c>
       <c r="AF20" t="n">
-        <v>7717944.827633822</v>
+        <v>11748839.7776466</v>
       </c>
       <c r="AG20" t="n">
-        <v>78.60448020878643</v>
+        <v>78.0719647776466</v>
       </c>
       <c r="AH20" t="n">
-        <v>23.17863676384339</v>
+        <v>24.35057573848736</v>
       </c>
       <c r="AI20" t="n">
-        <v>183.0455706069853</v>
+        <v>181.9618966950271</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.688413738487773</v>
+        <v>1.770577772213714</v>
       </c>
       <c r="AK20" t="n">
-        <v>73.53604547439519</v>
+        <v>78.47468696047362</v>
       </c>
       <c r="AL20" t="n">
-        <v>14727417.07896507</v>
+        <v>27306688.60474086</v>
       </c>
       <c r="AM20" t="n">
-        <v>81.36645894375737</v>
+        <v>82.14751719884705</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>61276</v>
+        <v>75635</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3479,120 +3475,124 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>25.75619834710744</v>
+        <v>24.84065656565656</v>
       </c>
       <c r="Q21" t="n">
-        <v>183.3545454545454</v>
+        <v>184.7355339105339</v>
       </c>
       <c r="R21" t="n">
-        <v>2.614876033057851</v>
+        <v>2.28430735930736</v>
       </c>
       <c r="S21" t="n">
-        <v>82.74710743801653</v>
+        <v>80.07864357864358</v>
       </c>
       <c r="T21" t="n">
-        <v>46462231.40495867</v>
+        <v>30888326.11832612</v>
       </c>
       <c r="U21" t="n">
-        <v>85.53305785123966</v>
+        <v>84.49224386724386</v>
       </c>
       <c r="V21" t="n">
-        <v>26.02454545454545</v>
+        <v>25.7297520661157</v>
       </c>
       <c r="W21" t="n">
-        <v>184.7418181818182</v>
+        <v>183.4049586776859</v>
       </c>
       <c r="X21" t="n">
-        <v>1.045454545454545</v>
+        <v>2.647107438016529</v>
       </c>
       <c r="Y21" t="n">
-        <v>76.45363636363636</v>
+        <v>82.91239669421488</v>
       </c>
       <c r="Z21" t="n">
-        <v>11428000</v>
+        <v>47609173.553719</v>
       </c>
       <c r="AA21" t="n">
-        <v>78.99636363636364</v>
+        <v>85.69504132231404</v>
       </c>
       <c r="AB21" t="n">
-        <v>23.20834551211789</v>
+        <v>24.31084032858101</v>
       </c>
       <c r="AC21" t="n">
-        <v>183.2271528769611</v>
+        <v>184.1186354880454</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.786762491557889</v>
+        <v>1.860854022616445</v>
       </c>
       <c r="AE21" t="n">
-        <v>79.20719904562615</v>
+        <v>75.30947050706368</v>
       </c>
       <c r="AF21" t="n">
-        <v>33498280.27258334</v>
+        <v>18567343.88993511</v>
       </c>
       <c r="AG21" t="n">
-        <v>84.38545991519138</v>
+        <v>81.49234362083742</v>
       </c>
       <c r="AH21" t="n">
-        <v>24.76496732026144</v>
+        <v>23.33581586784911</v>
       </c>
       <c r="AI21" t="n">
-        <v>179.757034743722</v>
+        <v>183.5767576200441</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.097008943928448</v>
+        <v>1.798422570609272</v>
       </c>
       <c r="AK21" t="n">
-        <v>73.67978672170622</v>
+        <v>79.53091446064592</v>
       </c>
       <c r="AL21" t="n">
-        <v>7867469.685242519</v>
+        <v>34011501.61645686</v>
       </c>
       <c r="AM21" t="n">
-        <v>77.52444788441692</v>
+        <v>84.47004489542854</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>rRQ6H30k</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45531.63541666666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">nield t 
   eng </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17949</v>
+        <v>34742</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3622,90 +3622,127 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>24.225</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>182.1954545454546</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.081818181818182</v>
+      </c>
+      <c r="S22" t="n">
+        <v>69.82954545454545</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2511250</v>
+      </c>
+      <c r="U22" t="n">
+        <v>75.59318181818183</v>
+      </c>
       <c r="V22" t="n">
-        <v>24.79116161616162</v>
+        <v>24.55509641873278</v>
       </c>
       <c r="W22" t="n">
-        <v>184.149292929293</v>
+        <v>183.7468319559229</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>69.81343434343435</v>
+        <v>69.47685950413224</v>
       </c>
       <c r="Z22" t="n">
-        <v>2431216.54040404</v>
+        <v>2394672.865013774</v>
       </c>
       <c r="AA22" t="n">
-        <v>73.77131313131312</v>
-      </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
+        <v>73.89816345270891</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>22.32362952664811</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>180.4113068390158</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.020827469743878</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>66.25589131370864</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1935880.895119672</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>74.45649520757878</v>
+      </c>
       <c r="AH22" t="n">
-        <v>24.50713022165388</v>
+        <v>24.34195632798574</v>
       </c>
       <c r="AI22" t="n">
-        <v>181.0492916006983</v>
+        <v>181.1081243103302</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>69.06363277919863</v>
+        <v>68.63159536541889</v>
       </c>
       <c r="AL22" t="n">
-        <v>2291556.907146917</v>
+        <v>2178384.098336304</v>
       </c>
       <c r="AM22" t="n">
-        <v>73.60597313563107</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
+        <v>73.58090675664205</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">oakwell
+  barnsley </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9271</v>
+        <v>23287</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3738,59 +3775,91 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>24.03818181818182</v>
+      </c>
+      <c r="W23" t="n">
+        <v>182.3655808080808</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>71.67818181818181</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4148545.454545455</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>77.17017676767678</v>
+      </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
+      <c r="AH23" t="n">
+        <v>22.98319655589839</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>180.4300356559109</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>68.71535345789931</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2803640.536887962</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>76.22422364720828</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>tMOy79y1</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45531.65625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">madley r 
   eng </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10841</v>
+        <v>6500</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3816,35 +3885,19 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
-        <v>25.21454545454545</v>
-      </c>
-      <c r="W24" t="n">
-        <v>180.4436363636364</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>70.12090909090909</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2255590.909090909</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>72.89272727272729</v>
-      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
@@ -3852,57 +3905,66 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>22.97071937866055</v>
+        <v>26.04761904761905</v>
       </c>
       <c r="AI24" t="n">
-        <v>179.6371704439352</v>
+        <v>182.4285714285714</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>66.73441982853747</v>
+        <v>65.0952380952381</v>
       </c>
       <c r="AL24" t="n">
-        <v>1746387.520159579</v>
+        <v>1007738.095238095</v>
       </c>
       <c r="AM24" t="n">
-        <v>74.2701171377642</v>
-      </c>
-      <c r="AN24" t="inlineStr"/>
+        <v>69.17857142857143</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>pA2vPxeA</t>
+          <t>phM8NElP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6500</v>
+        <v>31367</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3927,62 +3989,115 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>25.21818181818182</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>180.5190082644628</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>70.11239669421488</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2234504.132231405</v>
+      </c>
+      <c r="U25" t="n">
+        <v>72.97024793388429</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>23.71793202419434</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>180.2578742472776</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>67.11422536246629</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1733033.04597176</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>73.84019155001424</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>66.55555555555556</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1108333.333333333</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Sx94bg0H</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkinson b 
+  eng </t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>28723</v>
+        <v>31876</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -4007,67 +4122,103 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>25.95792929292929</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>182.1589646464647</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.413080808080808</v>
+      </c>
+      <c r="S26" t="n">
+        <v>75.50679292929291</v>
+      </c>
+      <c r="T26" t="n">
+        <v>9454828.282828283</v>
+      </c>
+      <c r="U26" t="n">
+        <v>79.98118686868688</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>23.37540726817042</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>178.0010509227614</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.373564593301436</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>73.06198165869218</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8249211.950330371</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>80.3366968557758</v>
+      </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>r597nj0B</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45531.65625</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">coventry building society arena
+  coventry </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>27000</v>
+        <v>32753</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4092,122 +4243,115 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>KrrdAMyI</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>23.50388888888889</v>
+        <v>23.98440170940171</v>
       </c>
       <c r="Q27" t="n">
-        <v>181.4847222222222</v>
+        <v>182.7282051282051</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>68.49305555555557</v>
+        <v>71.13119658119658</v>
       </c>
       <c r="T27" t="n">
-        <v>2084250</v>
+        <v>4084722.222222222</v>
       </c>
       <c r="U27" t="n">
-        <v>74.42083333333332</v>
-      </c>
-      <c r="V27" t="n">
-        <v>23.98310185185185</v>
-      </c>
-      <c r="W27" t="n">
-        <v>182.9055555555556</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>71.2837962962963</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4234282.407407408</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>76.97893518518519</v>
-      </c>
+        <v>76.8344017094017</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="n">
-        <v>25.59795176257015</v>
+        <v>23.99543630174435</v>
       </c>
       <c r="AC27" t="n">
-        <v>180.6796491919113</v>
+        <v>180.6219789154773</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>66.89307498352591</v>
+        <v>69.03064405494746</v>
       </c>
       <c r="AF27" t="n">
-        <v>1506733.937775929</v>
+        <v>2905864.729847895</v>
       </c>
       <c r="AG27" t="n">
-        <v>72.12693985072974</v>
+        <v>74.91476340996465</v>
       </c>
       <c r="AH27" t="n">
-        <v>24.00400102456024</v>
+        <v>25.39206349206349</v>
       </c>
       <c r="AI27" t="n">
-        <v>180.4842261110063</v>
+        <v>182.9460317460318</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>68.9824603372204</v>
+        <v>66.3111111111111</v>
       </c>
       <c r="AL27" t="n">
-        <v>2887756.905466609</v>
+        <v>1240952.380952381</v>
       </c>
       <c r="AM27" t="n">
-        <v>74.98144115516406</v>
+        <v>71.34603174603176</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>IPNnvzM7</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>IuMTL627</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5000</v>
+        <v>39572</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4232,62 +4376,103 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>183.7107438016529</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.586776859504132</v>
+      </c>
+      <c r="S28" t="n">
+        <v>76.62809917355372</v>
+      </c>
+      <c r="T28" t="n">
+        <v>11128305.78512397</v>
+      </c>
+      <c r="U28" t="n">
+        <v>79.07438016528926</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>25.2238737534134</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>186.0865711299215</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.369558084711537</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>73.18022665740058</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>7226324.844521775</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>77.05816052376154</v>
+      </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>pWQ6LC1N</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oldham s 
+  eng </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6912</v>
+        <v>5327</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4320,59 +4505,91 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>26.7375</v>
+      </c>
+      <c r="W29" t="n">
+        <v>181.825</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>66.825</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1085937.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>69.32499999999999</v>
+      </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
+      <c r="AH29" t="n">
+        <v>27.28520555954766</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>182.4113037303827</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>65.68942529205688</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>899556.7547705706</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>68.41614138785192</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>v9wEyhMe</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45531.65625</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">webb d 
+          <t xml:space="preserve">whitestone d 
   eng </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7937</v>
+        <v>9052</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4406,22 +4623,22 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>27.75555555555555</v>
+        <v>26.36652892561983</v>
       </c>
       <c r="W30" t="n">
-        <v>183.0144444444445</v>
+        <v>182.7917355371901</v>
       </c>
       <c r="X30" t="n">
-        <v>1.162222222222222</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>70.54083333333332</v>
+        <v>67.2409090909091</v>
       </c>
       <c r="Z30" t="n">
-        <v>1813041.666666667</v>
+        <v>1272117.768595041</v>
       </c>
       <c r="AA30" t="n">
-        <v>71.98583333333333</v>
+        <v>70.96239669421487</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -4430,57 +4647,66 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>25.74537355993642</v>
+        <v>25.82424962123838</v>
       </c>
       <c r="AI30" t="n">
-        <v>181.0839356361434</v>
+        <v>183.8519005322625</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>1.011363636363636</v>
       </c>
       <c r="AK30" t="n">
-        <v>67.62747138058469</v>
+        <v>66.48751216134718</v>
       </c>
       <c r="AL30" t="n">
-        <v>1514836.739611419</v>
+        <v>1617339.8208736</v>
       </c>
       <c r="AM30" t="n">
-        <v>71.68768526053373</v>
-      </c>
-      <c r="AN30" t="inlineStr"/>
+        <v>70.40536449369921</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">envirovent stadium
+  harrogate </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>33280</v>
+        <v>5000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4505,99 +4731,99 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>26.34636363636364</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>182.7972727272727</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S31" t="n">
-        <v>70.23636363636363</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2118090.909090909</v>
-      </c>
-      <c r="U31" t="n">
-        <v>72.45818181818183</v>
-      </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="n">
-        <v>24.31091478696742</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>182.8541019214704</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>65.88159147869673</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1584398.830409357</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>71.01041771094404</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>26.72731481481481</v>
+      </c>
+      <c r="W31" t="n">
+        <v>184.7613425925926</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.028935185185185</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>70.06689814814816</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2803304.398148148</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>72.0025462962963</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="n">
+        <v>23.58712705280043</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>181.7193807640015</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.004166666666667</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>67.08340159725608</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1879938.048600007</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>73.55330661054346</v>
+      </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr"/>
+          <t>zLZktkzH</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45531.65625</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">simpson s 
   eng </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27111</v>
+        <v>32261</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4622,94 +4848,103 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="n">
-        <v>24.47474747474747</v>
-      </c>
-      <c r="W32" t="n">
-        <v>181.9090909090909</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>69.13131313131312</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2141616.161616162</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>74.1919191919192</v>
-      </c>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="n">
-        <v>26.44585537918872</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>179.6592151675485</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>67.66053791887126</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1459809.30335097</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>70.87566137566138</v>
-      </c>
-      <c r="AN32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>26.32666666666666</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>182.8144444444444</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.395555555555556</v>
+      </c>
+      <c r="S32" t="n">
+        <v>75.88777777777777</v>
+      </c>
+      <c r="T32" t="n">
+        <v>9569777.77777778</v>
+      </c>
+      <c r="U32" t="n">
+        <v>78.24555555555555</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>26.0333313229598</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>180.5984624830794</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.456823542814255</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>73.54142458418774</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>5998922.906782331</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>76.36644761971775</v>
+      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>pQTmYFAh</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hicks c 
+  eng </t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">the den
+  london </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>10105</v>
+        <v>20146</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4734,62 +4969,115 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>26.08222222222222</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>179.9655555555556</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>69.77222222222221</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2339833.333333333</v>
+      </c>
+      <c r="U33" t="n">
+        <v>73.11333333333332</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>25.03875028480292</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>179.0503018910913</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>67.31574390521759</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1559501.167691957</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>73.13082706766917</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>20.42857142857143</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>179.2857142857143</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>59.71428571428572</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>675000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>71.28571428571429</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>6watkf6m</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>hzeTFV7m</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">loftus road
+  london </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6134</v>
+        <v>18439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>SlybbadF</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -4815,61 +5103,126 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>27.67283950617285</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>183.004938271605</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.158024691358025</v>
+      </c>
+      <c r="S34" t="n">
+        <v>70.48981481481481</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1817268.518518519</v>
+      </c>
+      <c r="U34" t="n">
+        <v>72.02870370370371</v>
+      </c>
+      <c r="V34" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>184.0148760330578</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.104132231404959</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>72.06446280991736</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3718822.314049587</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>75.81570247933884</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>26.00632105164558</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>181.364888198446</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>67.6336647568159</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1472097.383790943</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>71.35367520599733</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>27.5203397093103</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>181.0053319573443</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.172115964530825</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>69.76035741004782</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2042393.077661073</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>72.03922593144729</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">herczeg a 
+  eng </t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>33597</v>
+        <v>9877</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4908,24 +5261,12 @@
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>184</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>64.33333333333333</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>958333.3333333334</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>70.5</v>
-      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
@@ -4934,43 +5275,47 @@
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr"/>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>bZDu1Nqp</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45531.65625</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">webb d 
+          <t xml:space="preserve">mather s 
   eng </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5327</v>
+        <v>11300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -4996,7 +5341,11 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -5004,22 +5353,22 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>27.40833333333333</v>
+        <v>24.03492063492064</v>
       </c>
       <c r="W36" t="n">
-        <v>185.225</v>
+        <v>182.6269841269841</v>
       </c>
       <c r="X36" t="n">
-        <v>1.025</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>71.28333333333332</v>
+        <v>67.4063492063492</v>
       </c>
       <c r="Z36" t="n">
-        <v>2358333.333333333</v>
+        <v>1687261.904761905</v>
       </c>
       <c r="AA36" t="n">
-        <v>72.80833333333332</v>
+        <v>73.78412698412697</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
@@ -5028,57 +5377,66 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
-        <v>27.43916062801932</v>
+        <v>24.24312615584545</v>
       </c>
       <c r="AI36" t="n">
-        <v>184.1551716701173</v>
+        <v>182.584715974409</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.078804347826087</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>70.31357832988267</v>
+        <v>66.04637251961815</v>
       </c>
       <c r="AL36" t="n">
-        <v>2218741.91252588</v>
+        <v>1356360.851826861</v>
       </c>
       <c r="AM36" t="n">
-        <v>72.74381038647344</v>
-      </c>
-      <c r="AN36" t="inlineStr"/>
+        <v>72.45350564802318</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>C2z7zmRI</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
+        <v>45531.65625</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9052</v>
+        <v>22200</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5103,62 +5461,127 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>24.06260330578512</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>183.461914600551</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>69.51976584022037</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2348234.618916437</v>
+      </c>
+      <c r="U37" t="n">
+        <v>73.84641873278237</v>
+      </c>
+      <c r="V37" t="n">
+        <v>24.16652892561983</v>
+      </c>
+      <c r="W37" t="n">
+        <v>181.8399678604224</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>67.88119834710743</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2120757.001836548</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>73.85055096418733</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>24.04779707007968</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>182.2667952820127</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>68.31946561892214</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2170923.089591568</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>73.90335262563524</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>24.52979797979798</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>181.1985805257545</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>66.73594171528954</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1539265.206411946</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>72.38392151326934</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
+        <v>45531.66666666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24121</v>
+        <v>29409</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5185,92 +5608,125 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>24.13055555555556</v>
+        <v>24.55429292929293</v>
       </c>
       <c r="Q38" t="n">
-        <v>182.7361111111111</v>
+        <v>181.8876262626262</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>67.49305555555554</v>
+        <v>68.76641414141415</v>
       </c>
       <c r="T38" t="n">
-        <v>1700729.166666667</v>
+        <v>2050814.393939394</v>
       </c>
       <c r="U38" t="n">
-        <v>73.7861111111111</v>
-      </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
+        <v>73.95454545454547</v>
+      </c>
+      <c r="V38" t="n">
+        <v>26.75272727272727</v>
+      </c>
+      <c r="W38" t="n">
+        <v>184.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.512727272727272</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>77.00727272727272</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>12767727.27272727</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>79.10909090909091</v>
+      </c>
       <c r="AB38" t="n">
-        <v>23.75022724189391</v>
+        <v>26.27455908289242</v>
       </c>
       <c r="AC38" t="n">
-        <v>182.5922347714015</v>
+        <v>179.5666225749559</v>
       </c>
       <c r="AD38" t="n">
         <v>1</v>
       </c>
       <c r="AE38" t="n">
-        <v>66.05305589472256</v>
+        <v>67.99387125220458</v>
       </c>
       <c r="AF38" t="n">
-        <v>1407363.358092525</v>
+        <v>1593952.821869488</v>
       </c>
       <c r="AG38" t="n">
-        <v>73.02994675078008</v>
-      </c>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
+        <v>71.15343915343915</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>28.05046085627927</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>181.4882491613246</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.302867356428738</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>74.82053783173349</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>6867890.640050486</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>76.19927635876485</v>
+      </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr"/>
+          <t>UXQtpeyg</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
+        <v>45531.66666666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10669</v>
+        <v>25486</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5295,62 +5751,131 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>25.60826446280992</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>183.6884297520661</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>76.58512396694215</v>
+      </c>
+      <c r="T39" t="n">
+        <v>14098925.61983472</v>
+      </c>
+      <c r="U39" t="n">
+        <v>80.06446280991736</v>
+      </c>
+      <c r="V39" t="n">
+        <v>26.17676767676767</v>
+      </c>
+      <c r="W39" t="n">
+        <v>182.5141414141414</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>72.1020202020202</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3213535.353535354</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>74.72323232323232</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>26.67399600780608</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>183.6885234330886</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.170325352247549</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>73.15379955983502</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>7489130.950729921</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>76.42569099791639</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>25.15589127575159</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>183.5889932580371</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>68.59375187734425</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2261520.374176286</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>73.57034227494584</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>GEugARyP</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
+        <v>45532.64583333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>7798</v>
+        <v>31750</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5376,61 +5901,126 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>26.37962962962963</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>182.8317901234568</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.447530864197531</v>
+      </c>
+      <c r="S40" t="n">
+        <v>76.59567901234567</v>
+      </c>
+      <c r="T40" t="n">
+        <v>12223804.01234568</v>
+      </c>
+      <c r="U40" t="n">
+        <v>79.56327160493828</v>
+      </c>
+      <c r="V40" t="n">
+        <v>23.45371900826446</v>
+      </c>
+      <c r="W40" t="n">
+        <v>184.8190082644628</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.009090909090909</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>72.56859504132231</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>5036611.570247933</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>78.40578512396695</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>24.26921988166007</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>181.0604148111325</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.301425740660191</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>72.11881770542058</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>8247751.265215381</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>78.65667681600695</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>25.22741734061042</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>180.7773659897815</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.152707313560818</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>72.7019736022023</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>4855440.863745817</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>77.11913925349754</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
+        <v>45532.65625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">the cherry red records stadium
+  london </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>27137</v>
+        <v>9215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5455,94 +6045,103 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>26.13703703703703</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>182.4462962962963</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>26.19191919191919</v>
+      </c>
+      <c r="W41" t="n">
+        <v>182.5050505050505</v>
+      </c>
+      <c r="X41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
-        <v>72.06851851851852</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3207407.407407407</v>
-      </c>
-      <c r="U41" t="n">
-        <v>74.71296296296296</v>
-      </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="n">
-        <v>25.23319380960045</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>183.930834297842</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>68.66487742862422</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2302672.713049951</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>73.52775559904715</v>
-      </c>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
+      <c r="Y41" t="n">
+        <v>70.94949494949495</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2815151.515151515</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>74.60606060606061</v>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="n">
+        <v>25.1765873015873</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>183.0873015873016</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.005291005291005</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>69.06216931216932</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2286772.486772487</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>73.38690476190476</v>
+      </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr"/>
+          <t>dKVYSSZa</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
+        <v>45532.65625</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>12500</v>
+        <v>33280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5567,83 +6166,127 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>26.46454545454545</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>182.7309090909091</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S42" t="n">
+        <v>70.27545454545455</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2121363.636363637</v>
+      </c>
+      <c r="U42" t="n">
+        <v>72.39363636363638</v>
+      </c>
+      <c r="V42" t="n">
+        <v>25.41212121212121</v>
+      </c>
+      <c r="W42" t="n">
+        <v>179.7472582972583</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>72.88946608946608</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4524624.81962482</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>76.2005772005772</v>
+      </c>
       <c r="AB42" t="n">
-        <v>25.83333333333333</v>
+        <v>24.29067669172932</v>
       </c>
       <c r="AC42" t="n">
-        <v>183.6666666666667</v>
+        <v>182.9017209690894</v>
       </c>
       <c r="AD42" t="n">
+        <v>1.00625</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>65.75034147869674</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1530927.10421888</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>70.8270843776107</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>24.65599619294358</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>179.0003223423757</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>1</v>
       </c>
-      <c r="AE42" t="n">
-        <v>65.33333333333333</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>68.66666666666667</v>
-      </c>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
+      <c r="AK42" t="n">
+        <v>70.89429878670836</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>3220631.341469395</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>75.78533397548743</v>
+      </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr"/>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45532.65625</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">busby j 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>21944</v>
+        <v>10105</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5669,11 +6312,7 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -5681,102 +6320,90 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>25.81111111111111</v>
+        <v>25.93818181818182</v>
       </c>
       <c r="W43" t="n">
-        <v>180.1177777777778</v>
+        <v>184.6927272727273</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="Y43" t="n">
-        <v>69.87111111111112</v>
+        <v>76.45090909090909</v>
       </c>
       <c r="Z43" t="n">
-        <v>2449166.666666667</v>
+        <v>11463818.18181818</v>
       </c>
       <c r="AA43" t="n">
-        <v>73.33666666666666</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>174.2</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>71.8</v>
-      </c>
+        <v>79.08363636363637</v>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="n">
-        <v>24.85345238095238</v>
+        <v>24.71417784657723</v>
       </c>
       <c r="AI43" t="n">
-        <v>178.7205952380952</v>
+        <v>179.8178242174063</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1</v>
+        <v>1.12358789129687</v>
       </c>
       <c r="AK43" t="n">
-        <v>67.56476190476191</v>
+        <v>73.72873409012728</v>
       </c>
       <c r="AL43" t="n">
-        <v>1632866.071428571</v>
+        <v>7912673.632610939</v>
       </c>
       <c r="AM43" t="n">
-        <v>73.49333333333334</v>
+        <v>77.78260577915376</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>MiVxbVgA</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45532.65625</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">davies a 
+          <t xml:space="preserve">bourne d 
   eng </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>23408</v>
+        <v>21088</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -5801,122 +6428,103 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>26.7290404040404</v>
+        <v>24.69642857142857</v>
       </c>
       <c r="Q44" t="n">
-        <v>184.6234848484848</v>
+        <v>179.9642857142857</v>
       </c>
       <c r="R44" t="n">
-        <v>1.011363636363636</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>69.81666666666666</v>
+        <v>68.98214285714286</v>
       </c>
       <c r="T44" t="n">
-        <v>2210265.151515151</v>
+        <v>1917857.142857143</v>
       </c>
       <c r="U44" t="n">
-        <v>71.78434343434343</v>
-      </c>
-      <c r="V44" t="n">
-        <v>21.97222222222222</v>
-      </c>
-      <c r="W44" t="n">
-        <v>182.3013888888889</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>69.17777777777778</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3051166.666666667</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>77.47777777777777</v>
-      </c>
+        <v>73.78571428571429</v>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="n">
-        <v>23.53221346936517</v>
+        <v>24.77396975229792</v>
       </c>
       <c r="AC44" t="n">
-        <v>181.8235490687503</v>
+        <v>179.6118603696707</v>
       </c>
       <c r="AD44" t="n">
         <v>1</v>
       </c>
       <c r="AE44" t="n">
-        <v>66.72360388149862</v>
+        <v>67.006661396895</v>
       </c>
       <c r="AF44" t="n">
-        <v>1675259.956761505</v>
+        <v>1467352.833940929</v>
       </c>
       <c r="AG44" t="n">
-        <v>73.38087993877468</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>22.18384325152346</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>181.53566996443</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>65.89287727051742</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1690857.960009827</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>73.7128818615987</v>
-      </c>
+        <v>72.48045309289328</v>
+      </c>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>6wEAqBAE</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>pYaUUJs1</t>
+          <t>65pf39vc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
+        <v>45532.65625</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12021</v>
+        <v>62500</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -5941,90 +6549,131 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
       <c r="P45" t="n">
-        <v>26.72222222222222</v>
+        <v>27.75454545454546</v>
       </c>
       <c r="Q45" t="n">
-        <v>181.9888888888889</v>
+        <v>182.9813131313131</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>2.13020202020202</v>
       </c>
       <c r="S45" t="n">
-        <v>66.88888888888889</v>
+        <v>79.06585858585859</v>
       </c>
       <c r="T45" t="n">
-        <v>1103055.555555556</v>
+        <v>19009151.51515152</v>
       </c>
       <c r="U45" t="n">
-        <v>69.39999999999999</v>
-      </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
+        <v>80.53979797979798</v>
+      </c>
+      <c r="V45" t="n">
+        <v>24.16565656565656</v>
+      </c>
+      <c r="W45" t="n">
+        <v>181.2868686868687</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.164646464646464</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>75.02525252525253</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>8701313.131313132</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>79.13939393939394</v>
+      </c>
       <c r="AB45" t="n">
-        <v>27.36920026854237</v>
+        <v>27.44039969017911</v>
       </c>
       <c r="AC45" t="n">
-        <v>182.1784994975784</v>
+        <v>180.6861366819455</v>
       </c>
       <c r="AD45" t="n">
-        <v>1</v>
+        <v>1.691721203632968</v>
       </c>
       <c r="AE45" t="n">
-        <v>65.48439883703041</v>
+        <v>73.924584818776</v>
       </c>
       <c r="AF45" t="n">
-        <v>873448.9505377664</v>
+        <v>9206085.126474831</v>
       </c>
       <c r="AG45" t="n">
-        <v>68.24484509155562</v>
-      </c>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
+        <v>77.54409154570919</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>23.75232324883355</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>183.0073115137526</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.279547856045672</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>74.52231411712897</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>11116913.87184574</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>79.43281596763498</v>
+      </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr"/>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
+        <v>45532.66666666666</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5108</v>
+        <v>30404</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6050,1085 +6699,91 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>9877</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>EqfQ6qK4</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>EwJVdqzn</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>48</v>
-      </c>
-      <c r="I47" t="n">
-        <v>484</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>21088</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>WvZyDeKk</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>48</v>
-      </c>
-      <c r="I48" t="n">
-        <v>484</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>24.69642857142857</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>179.9642857142857</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>68.98214285714286</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1917857.142857143</v>
-      </c>
-      <c r="U48" t="n">
-        <v>73.78571428571429</v>
-      </c>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="n">
-        <v>24.74117691733791</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>179.3993700829614</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>67.20807678733375</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1524650.055396959</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>72.72045644414065</v>
-      </c>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>16587</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>jVhkb1QE</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6ZvdGuYf</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>48</v>
-      </c>
-      <c r="I49" t="n">
-        <v>484</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>11300</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>YgrfcLuL</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>ve14a3l4</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>48</v>
-      </c>
-      <c r="I50" t="n">
-        <v>484</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>22200</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>f9KDxtkU</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="n">
-        <v>484</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>23.9730303030303</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>183.4217171717171</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>69.72090909090909</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2491030.303030303</v>
-      </c>
-      <c r="U51" t="n">
-        <v>74.15494949494951</v>
-      </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="n">
-        <v>24.2981323326432</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>182.3706970324362</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>68.51307884748101</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>2241076.509661836</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>73.93868788819876</v>
-      </c>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the brick community stadium
-  wigan </t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>25133</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>MgHlK2Na</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>UNGEKMx6</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>48</v>
-      </c>
-      <c r="I52" t="n">
-        <v>484</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>32050</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>IgO7K1ZA</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>48</v>
-      </c>
-      <c r="I53" t="n">
-        <v>484</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
-        <v>24.03818181818182</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>182.3655808080808</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>71.67818181818181</v>
-      </c>
-      <c r="T53" t="n">
-        <v>4148545.454545455</v>
-      </c>
-      <c r="U53" t="n">
-        <v>77.17017676767678</v>
-      </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="n">
-        <v>23.16944619707778</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>180.2543915149178</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>68.99621986200933</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2830621.525769552</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>76.29814666327825</v>
-      </c>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>6wEAqBAE</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>25586</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>S66R0t75</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>llcCvIcG</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>48</v>
-      </c>
-      <c r="I54" t="n">
-        <v>484</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>24.14010101010101</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>179.8412121212121</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.084545454545454</v>
-      </c>
-      <c r="S54" t="n">
-        <v>69.90797979797981</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3085373.737373737</v>
-      </c>
-      <c r="U54" t="n">
-        <v>75.09161616161617</v>
-      </c>
-      <c r="V54" t="n">
-        <v>26.5979797979798</v>
-      </c>
-      <c r="W54" t="n">
-        <v>182.8343434343434</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>67.42222222222222</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1263005.05050505</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>70.77070707070706</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>25.21093057908275</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>180.2007316404823</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.019396845694799</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>69.64008402438709</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2982127.41292169</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>74.32012424205519</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>25.73872785829307</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>184.6415056360708</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.013888888888889</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>66.65116747181963</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1734460.547504026</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>70.32729468599034</v>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>IPNnvzM7</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>WpGM6ELj</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>jizXHcsM</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>48</v>
-      </c>
-      <c r="I55" t="n">
-        <v>484</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>24.09090909090909</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>181.3535353535354</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>67.95959595959596</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2172727.272727273</v>
-      </c>
-      <c r="U55" t="n">
-        <v>74.01010101010101</v>
-      </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="n">
-        <v>24.39139433551198</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>181.0827240558059</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>66.0972330478085</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1361211.57762622</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>72.23851845085861</v>
-      </c>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>45518.66666666666</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>37792</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>48</v>
-      </c>
-      <c r="I56" t="n">
-        <v>484</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>23.19075369075369</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>184.2111888111888</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.243667443667444</v>
-      </c>
-      <c r="S56" t="n">
-        <v>74.32486402486403</v>
-      </c>
-      <c r="T56" t="n">
-        <v>8444553.224553224</v>
-      </c>
-      <c r="U56" t="n">
-        <v>80.17793317793318</v>
-      </c>
-      <c r="V56" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="W56" t="n">
-        <v>181.79</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>70.09</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2563000</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>75.62</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>24.87756300849001</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>180.937742408289</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.078975665320628</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>73.18094106582734</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>5406582.824970537</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>77.18731127040247</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>22.30158071460703</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>180.0365551699762</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.005263157894737</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>66.1823627980207</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1952971.92580811</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>74.26479178716019</v>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>185.08</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>74.97999999999999</v>
+      </c>
+      <c r="T46" t="n">
+        <v>8868000</v>
+      </c>
+      <c r="U46" t="n">
+        <v>78.80999999999999</v>
+      </c>
+      <c r="V46" t="n">
+        <v>26.30752984389348</v>
+      </c>
+      <c r="W46" t="n">
+        <v>185.3779614325069</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.535812672176309</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>77.98200183654728</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>19609044.99540863</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>80.91781450872359</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>24.65595847034466</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>185.0414943368652</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.39932103276093</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>75.25341980270369</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>10611518.99890391</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>79.4291761052247</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>26.12590023612751</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>181.8205037386856</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.387081857536403</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>73.69878492719401</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>11748839.7776466</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>78.0719647776466</v>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO46"/>
+  <dimension ref="A1:AO21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">salisbury m 
   eng </t>
         </is>
       </c>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
@@ -1527,8 +1527,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">oliver m 
+  eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
@@ -3563,3227 +3563,6 @@
       <c r="AO21" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rRQ6H30k</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45531.63541666666</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nield t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">riverside stadium
-  middlesbrough </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>34742</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>hSUajdSS</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>48</v>
-      </c>
-      <c r="I22" t="n">
-        <v>484</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>24.225</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>182.1954545454546</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.081818181818182</v>
-      </c>
-      <c r="S22" t="n">
-        <v>69.82954545454545</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2511250</v>
-      </c>
-      <c r="U22" t="n">
-        <v>75.59318181818183</v>
-      </c>
-      <c r="V22" t="n">
-        <v>24.55509641873278</v>
-      </c>
-      <c r="W22" t="n">
-        <v>183.7468319559229</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>69.47685950413224</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2394672.865013774</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>73.89816345270891</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>22.32362952664811</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>180.4113068390158</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.020827469743878</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>66.25589131370864</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1935880.895119672</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>74.45649520757878</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>24.34195632798574</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>181.1081243103302</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>68.63159536541889</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2178384.098336304</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>73.58090675664205</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>pA2vPxeA</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>dUjtW2Fr</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backhouse a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oakwell
-  barnsley </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>23287</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UNGEKMx6</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>48</v>
-      </c>
-      <c r="I23" t="n">
-        <v>484</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>24.03818181818182</v>
-      </c>
-      <c r="W23" t="n">
-        <v>182.3655808080808</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>71.67818181818181</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4148545.454545455</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>77.17017676767678</v>
-      </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
-        <v>22.98319655589839</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>180.4300356559109</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>68.71535345789931</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2803640.536887962</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>76.22422364720828</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>tMOy79y1</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>MFnpCm7C</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KKJL7QXd</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Iug0YO0Q</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>48</v>
-      </c>
-      <c r="I24" t="n">
-        <v>484</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="n">
-        <v>26.04761904761905</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>182.4285714285714</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>65.0952380952381</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1007738.095238095</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>69.17857142857143</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>joDBK9gn</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>UsklUtpe</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">corlett m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ewood park
-  blackburn </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>31367</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>8EFIJthC</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>48</v>
-      </c>
-      <c r="I25" t="n">
-        <v>484</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>25.21818181818182</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>180.5190082644628</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>70.11239669421488</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2234504.132231405</v>
-      </c>
-      <c r="U25" t="n">
-        <v>72.97024793388429</v>
-      </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="n">
-        <v>23.71793202419434</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>180.2578742472776</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>67.11422536246629</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1733033.04597176</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>73.84019155001424</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>26.22222222222222</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>66.55555555555556</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1108333.333333333</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>69.33333333333333</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>thRJMAq0</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sx94bg0H</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddFjPf2b</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkinson b 
-  eng </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>31876</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>QVmLl54o</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>48</v>
-      </c>
-      <c r="I26" t="n">
-        <v>484</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>25.95792929292929</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>182.1589646464647</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.413080808080808</v>
-      </c>
-      <c r="S26" t="n">
-        <v>75.50679292929291</v>
-      </c>
-      <c r="T26" t="n">
-        <v>9454828.282828283</v>
-      </c>
-      <c r="U26" t="n">
-        <v>79.98118686868688</v>
-      </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="n">
-        <v>23.37540726817042</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>178.0010509227614</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.373564593301436</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>73.06198165869218</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>8249211.950330371</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>80.3366968557758</v>
-      </c>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>r597nj0B</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Sh9BS8ig</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coventry building society arena
-  coventry </t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>32753</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>GOvB22xg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>vgOBT43c</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>48</v>
-      </c>
-      <c r="I27" t="n">
-        <v>484</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>23.98440170940171</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>182.7282051282051</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>71.13119658119658</v>
-      </c>
-      <c r="T27" t="n">
-        <v>4084722.222222222</v>
-      </c>
-      <c r="U27" t="n">
-        <v>76.8344017094017</v>
-      </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="n">
-        <v>23.99543630174435</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>180.6219789154773</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>69.03064405494746</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2905864.729847895</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>74.91476340996465</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>25.39206349206349</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>182.9460317460318</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>66.3111111111111</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1240952.380952381</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>71.34603174603176</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>lYgfxNV9</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>dAfPwfHi</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stockbridge s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>39572</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>hlzYDy5q</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>48</v>
-      </c>
-      <c r="I28" t="n">
-        <v>484</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>27.27272727272727</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>183.7107438016529</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.586776859504132</v>
-      </c>
-      <c r="S28" t="n">
-        <v>76.62809917355372</v>
-      </c>
-      <c r="T28" t="n">
-        <v>11128305.78512397</v>
-      </c>
-      <c r="U28" t="n">
-        <v>79.07438016528926</v>
-      </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="n">
-        <v>25.2238737534134</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>186.0865711299215</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.369558084711537</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>73.18022665740058</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>7226324.844521775</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>77.05816052376154</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>pSZhI8SM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>pWQ6LC1N</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oldham s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>5327</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>tCZ3D68d</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>KMfM7P4b</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>48</v>
-      </c>
-      <c r="I29" t="n">
-        <v>484</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="n">
-        <v>26.7375</v>
-      </c>
-      <c r="W29" t="n">
-        <v>181.825</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>66.825</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1085937.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>69.32499999999999</v>
-      </c>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="n">
-        <v>27.28520555954766</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>182.4113037303827</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>65.68942529205688</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>899556.7547705706</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>68.41614138785192</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>d6KwHx8i</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>v9wEyhMe</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>jiUEFsV1</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">whitestone d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>9052</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>OEaiS3za</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>llcCvIcG</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>48</v>
-      </c>
-      <c r="I30" t="n">
-        <v>484</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="n">
-        <v>26.36652892561983</v>
-      </c>
-      <c r="W30" t="n">
-        <v>182.7917355371901</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>67.2409090909091</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1272117.768595041</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>70.96239669421487</v>
-      </c>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="n">
-        <v>25.82424962123838</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>183.8519005322625</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.011363636363636</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>66.48751216134718</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1617339.8208736</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>70.40536449369921</v>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>SGvTSGmc</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>dY0SOQjI</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">martin s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">envirovent stadium
-  harrogate </t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>CQv5qrFt</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>x8IDVcbi</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>48</v>
-      </c>
-      <c r="I31" t="n">
-        <v>484</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="n">
-        <v>26.72731481481481</v>
-      </c>
-      <c r="W31" t="n">
-        <v>184.7613425925926</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.028935185185185</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>70.06689814814816</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2803304.398148148</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>72.0025462962963</v>
-      </c>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="n">
-        <v>23.58712705280043</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>181.7193807640015</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.004166666666667</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>67.08340159725608</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1879938.048600007</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>73.55330661054346</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>zLZktkzH</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>dtwAbyJ5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>hO8aNYWA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simpson s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>32261</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>jVhkb1QE</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>48</v>
-      </c>
-      <c r="I32" t="n">
-        <v>484</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
-        <v>26.32666666666666</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>182.8144444444444</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.395555555555556</v>
-      </c>
-      <c r="S32" t="n">
-        <v>75.88777777777777</v>
-      </c>
-      <c r="T32" t="n">
-        <v>9569777.77777778</v>
-      </c>
-      <c r="U32" t="n">
-        <v>78.24555555555555</v>
-      </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="n">
-        <v>26.0333313229598</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>180.5984624830794</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.456823542814255</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>73.54142458418774</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>5998922.906782331</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>76.36644761971775</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>pQTmYFAh</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>vDA9yPiL</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hicks c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the den
-  london </t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>20146</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>KKyYcus9</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>48</v>
-      </c>
-      <c r="I33" t="n">
-        <v>484</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
-        <v>26.08222222222222</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>179.9655555555556</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>69.77222222222221</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2339833.333333333</v>
-      </c>
-      <c r="U33" t="n">
-        <v>73.11333333333332</v>
-      </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="n">
-        <v>25.03875028480292</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>179.0503018910913</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>67.31574390521759</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1559501.167691957</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>73.13082706766917</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>20.42857142857143</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>179.2857142857143</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>59.71428571428572</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>675000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>71.28571428571429</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>6watkf6m</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>hzeTFV7m</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busby j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">loftus road
-  london </t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>18439</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>lrMHUHDc</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>48</v>
-      </c>
-      <c r="I34" t="n">
-        <v>484</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>27.67283950617285</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>183.004938271605</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.158024691358025</v>
-      </c>
-      <c r="S34" t="n">
-        <v>70.48981481481481</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1817268.518518519</v>
-      </c>
-      <c r="U34" t="n">
-        <v>72.02870370370371</v>
-      </c>
-      <c r="V34" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>184.0148760330578</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.104132231404959</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>72.06446280991736</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3718822.314049587</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>75.81570247933884</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>26.00632105164558</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>181.364888198446</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>67.6336647568159</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1472097.383790943</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>71.35367520599733</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>27.5203397093103</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>181.0053319573443</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.172115964530825</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>69.76035741004782</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2042393.077661073</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>72.03922593144729</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>MBpIn2MH</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Q9rcSKE7</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">herczeg a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>9877</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>EqfQ6qK4</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Or1bBrWD</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>48</v>
-      </c>
-      <c r="I35" t="n">
-        <v>484</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>EqN1jJFK</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>bZDu1Nqp</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>zJCJQnM5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mather s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>11300</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>YgrfcLuL</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>48</v>
-      </c>
-      <c r="I36" t="n">
-        <v>484</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="n">
-        <v>24.03492063492064</v>
-      </c>
-      <c r="W36" t="n">
-        <v>182.6269841269841</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>67.4063492063492</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1687261.904761905</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>73.78412698412697</v>
-      </c>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="n">
-        <v>24.24312615584545</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>182.584715974409</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>66.04637251961815</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1356360.851826861</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>72.45350564802318</v>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>YTxm48Ng</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>C2z7zmRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>QkntzCGG</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doughty l 
-  eng </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22200</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>WpGM6ELj</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>48</v>
-      </c>
-      <c r="I37" t="n">
-        <v>484</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>24.06260330578512</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>183.461914600551</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>69.51976584022037</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2348234.618916437</v>
-      </c>
-      <c r="U37" t="n">
-        <v>73.84641873278237</v>
-      </c>
-      <c r="V37" t="n">
-        <v>24.16652892561983</v>
-      </c>
-      <c r="W37" t="n">
-        <v>181.8399678604224</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>67.88119834710743</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2120757.001836548</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>73.85055096418733</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>24.04779707007968</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>182.2667952820127</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>68.31946561892214</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2170923.089591568</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>73.90335262563524</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>24.52979797979798</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>181.1985805257545</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>66.73594171528954</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1539265.206411946</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>72.38392151326934</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>n94TZqsm</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>IPNnvzM7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Wn71woN8</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45531.66666666666</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  andrew s stadium
-  birmingham </t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>29409</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SWk4muv7</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>48</v>
-      </c>
-      <c r="I38" t="n">
-        <v>484</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>24.55429292929293</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>181.8876262626262</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>68.76641414141415</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2050814.393939394</v>
-      </c>
-      <c r="U38" t="n">
-        <v>73.95454545454547</v>
-      </c>
-      <c r="V38" t="n">
-        <v>26.75272727272727</v>
-      </c>
-      <c r="W38" t="n">
-        <v>184.15</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.512727272727272</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>77.00727272727272</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>12767727.27272727</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>79.10909090909091</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>26.27455908289242</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>179.5666225749559</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>67.99387125220458</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1593952.821869488</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>71.15343915343915</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>28.05046085627927</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>181.4882491613246</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.302867356428738</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>74.82053783173349</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>6867890.640050486</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>76.19927635876485</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>UXQtpeyg</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkqxE9x0</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45531.66666666666</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bell j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>25486</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>48</v>
-      </c>
-      <c r="I39" t="n">
-        <v>484</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>25.60826446280992</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>183.6884297520661</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>76.58512396694215</v>
-      </c>
-      <c r="T39" t="n">
-        <v>14098925.61983472</v>
-      </c>
-      <c r="U39" t="n">
-        <v>80.06446280991736</v>
-      </c>
-      <c r="V39" t="n">
-        <v>26.17676767676767</v>
-      </c>
-      <c r="W39" t="n">
-        <v>182.5141414141414</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>72.1020202020202</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3213535.353535354</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>74.72323232323232</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>26.67399600780608</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>183.6885234330886</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.170325352247549</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>73.15379955983502</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>7489130.950729921</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>76.42569099791639</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>25.15589127575159</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>183.5889932580371</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>68.59375187734425</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2261520.374176286</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>73.57034227494584</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>GEugARyP</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45532.64583333334</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">salisbury m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>48</v>
-      </c>
-      <c r="I40" t="n">
-        <v>484</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>26.37962962962963</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>182.8317901234568</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.447530864197531</v>
-      </c>
-      <c r="S40" t="n">
-        <v>76.59567901234567</v>
-      </c>
-      <c r="T40" t="n">
-        <v>12223804.01234568</v>
-      </c>
-      <c r="U40" t="n">
-        <v>79.56327160493828</v>
-      </c>
-      <c r="V40" t="n">
-        <v>23.45371900826446</v>
-      </c>
-      <c r="W40" t="n">
-        <v>184.8190082644628</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.009090909090909</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>72.56859504132231</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>5036611.570247933</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>78.40578512396695</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>24.26921988166007</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>181.0604148111325</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.301425740660191</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>72.11881770542058</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>8247751.265215381</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>78.65667681600695</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>25.22741734061042</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>180.7773659897815</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.152707313560818</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>72.7019736022023</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>4855440.863745817</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>77.11913925349754</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>U32wGjPp</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the cherry red records stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>9215</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4KREuF43</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>48</v>
-      </c>
-      <c r="I41" t="n">
-        <v>484</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="n">
-        <v>26.19191919191919</v>
-      </c>
-      <c r="W41" t="n">
-        <v>182.5050505050505</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>70.94949494949495</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2815151.515151515</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>74.60606060606061</v>
-      </c>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="n">
-        <v>25.1765873015873</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>183.0873015873016</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.005291005291005</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>69.06216931216932</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2286772.486772487</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>73.38690476190476</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>dKVYSSZa</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>hGzqjO6E</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>33280</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>48</v>
-      </c>
-      <c r="I42" t="n">
-        <v>484</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>26.46454545454545</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>182.7309090909091</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S42" t="n">
-        <v>70.27545454545455</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2121363.636363637</v>
-      </c>
-      <c r="U42" t="n">
-        <v>72.39363636363638</v>
-      </c>
-      <c r="V42" t="n">
-        <v>25.41212121212121</v>
-      </c>
-      <c r="W42" t="n">
-        <v>179.7472582972583</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>72.88946608946608</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4524624.81962482</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>76.2005772005772</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>24.29067669172932</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>182.9017209690894</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.00625</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>65.75034147869674</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1530927.10421888</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>70.8270843776107</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>24.65599619294358</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>179.0003223423757</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>70.89429878670836</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>3220631.341469395</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>75.78533397548743</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>YuNX1zGT</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>OrHrRGXo</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>10105</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>xYu73rNn</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>48</v>
-      </c>
-      <c r="I43" t="n">
-        <v>484</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="n">
-        <v>25.93818181818182</v>
-      </c>
-      <c r="W43" t="n">
-        <v>184.6927272727273</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.045454545454545</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>76.45090909090909</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>11463818.18181818</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>79.08363636363637</v>
-      </c>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="n">
-        <v>24.71417784657723</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>179.8178242174063</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.12358789129687</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>73.72873409012728</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>7912673.632610939</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>77.78260577915376</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>MiVxbVgA</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>WQF2UUMt</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bourne d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>21088</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>hl2V5JIl</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>48</v>
-      </c>
-      <c r="I44" t="n">
-        <v>484</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>24.69642857142857</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>179.9642857142857</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>68.98214285714286</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1917857.142857143</v>
-      </c>
-      <c r="U44" t="n">
-        <v>73.78571428571429</v>
-      </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="n">
-        <v>24.77396975229792</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>179.6118603696707</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>67.006661396895</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1467352.833940929</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>72.48045309289328</v>
-      </c>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>65pf39vc</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>rkazN4LU</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">london stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>62500</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>48</v>
-      </c>
-      <c r="I45" t="n">
-        <v>484</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>27.75454545454546</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>182.9813131313131</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2.13020202020202</v>
-      </c>
-      <c r="S45" t="n">
-        <v>79.06585858585859</v>
-      </c>
-      <c r="T45" t="n">
-        <v>19009151.51515152</v>
-      </c>
-      <c r="U45" t="n">
-        <v>80.53979797979798</v>
-      </c>
-      <c r="V45" t="n">
-        <v>24.16565656565656</v>
-      </c>
-      <c r="W45" t="n">
-        <v>181.2868686868687</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.164646464646464</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>75.02525252525253</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>8701313.131313132</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>79.13939393939394</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>27.44039969017911</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>180.6861366819455</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.691721203632968</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>73.924584818776</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>9206085.126474831</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>77.54409154570919</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>23.75232324883355</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>183.0073115137526</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.279547856045672</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>74.52231411712897</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>11116913.87184574</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>79.43281596763498</v>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>hxlYyYo4</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>45532.66666666666</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>48</v>
-      </c>
-      <c r="I46" t="n">
-        <v>484</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>185.08</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>74.97999999999999</v>
-      </c>
-      <c r="T46" t="n">
-        <v>8868000</v>
-      </c>
-      <c r="U46" t="n">
-        <v>78.80999999999999</v>
-      </c>
-      <c r="V46" t="n">
-        <v>26.30752984389348</v>
-      </c>
-      <c r="W46" t="n">
-        <v>185.3779614325069</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.535812672176309</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>77.98200183654728</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>19609044.99540863</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>80.91781450872359</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>24.65595847034466</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>185.0414943368652</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.39932103276093</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>75.25341980270369</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>10611518.99890391</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>79.4291761052247</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>26.12590023612751</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>181.8205037386856</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.387081857536403</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>73.69878492719401</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>11748839.7776466</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>78.0719647776466</v>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC8"/>
+  <dimension ref="A1:BC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31876</v>
+        <v>11307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -762,171 +762,171 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>194</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="U2" t="n">
-        <v>10500000</v>
+        <v>50000000</v>
       </c>
       <c r="V2" t="n">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="W2" t="n">
-        <v>24.5</v>
+        <v>24.85714285714286</v>
       </c>
       <c r="X2" t="n">
-        <v>182</v>
+        <v>186.4285714285714</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
-        <v>316</v>
+        <v>540</v>
       </c>
       <c r="AB2" t="n">
-        <v>92000000</v>
+        <v>188375000</v>
       </c>
       <c r="AC2" t="n">
-        <v>333</v>
+        <v>576</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.95792929292929</v>
+        <v>24.16565656565656</v>
       </c>
       <c r="AE2" t="n">
-        <v>182.1589646464647</v>
+        <v>181.2868686868687</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.413080808080808</v>
+        <v>1.164646464646464</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.50679292929291</v>
+        <v>75.02525252525253</v>
       </c>
       <c r="AH2" t="n">
-        <v>9454828.282828283</v>
+        <v>8701313.131313132</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.98118686868688</v>
+        <v>79.13939393939394</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24.84065656565656</v>
+        <v>26.30752984389348</v>
       </c>
       <c r="AK2" t="n">
-        <v>184.7355339105339</v>
+        <v>185.3779614325069</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.28430735930736</v>
+        <v>1.535812672176309</v>
       </c>
       <c r="AM2" t="n">
-        <v>80.07864357864358</v>
+        <v>77.98200183654728</v>
       </c>
       <c r="AN2" t="n">
-        <v>30888326.11832612</v>
+        <v>19609044.99540863</v>
       </c>
       <c r="AO2" t="n">
-        <v>84.49224386724386</v>
+        <v>80.91781450872359</v>
       </c>
       <c r="AP2" t="n">
-        <v>23.37540726817042</v>
+        <v>23.75232324883355</v>
       </c>
       <c r="AQ2" t="n">
-        <v>178.0010509227614</v>
+        <v>183.0073115137526</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.373564593301436</v>
+        <v>1.279547856045672</v>
       </c>
       <c r="AS2" t="n">
-        <v>73.06198165869218</v>
+        <v>74.52231411712897</v>
       </c>
       <c r="AT2" t="n">
-        <v>8249211.950330371</v>
+        <v>11116913.87184574</v>
       </c>
       <c r="AU2" t="n">
-        <v>80.3366968557758</v>
+        <v>79.43281596763498</v>
       </c>
       <c r="AV2" t="n">
-        <v>24.31084032858101</v>
+        <v>26.12590023612751</v>
       </c>
       <c r="AW2" t="n">
-        <v>184.1186354880454</v>
+        <v>181.8205037386856</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.860854022616445</v>
+        <v>1.387081857536403</v>
       </c>
       <c r="AY2" t="n">
-        <v>75.30947050706368</v>
+        <v>73.69878492719401</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18567343.88993511</v>
+        <v>11748839.7776466</v>
       </c>
       <c r="BA2" t="n">
-        <v>81.49234362083742</v>
+        <v>78.0719647776466</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25486</v>
+        <v>31750</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -951,23 +951,33 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>200</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>79</v>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -976,120 +986,120 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>25.60826446280992</v>
+        <v>26.37962962962963</v>
       </c>
       <c r="AE3" t="n">
-        <v>183.6884297520661</v>
+        <v>182.8317901234568</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.3</v>
+        <v>1.447530864197531</v>
       </c>
       <c r="AG3" t="n">
-        <v>76.58512396694215</v>
+        <v>76.59567901234567</v>
       </c>
       <c r="AH3" t="n">
-        <v>14098925.61983472</v>
+        <v>12223804.01234568</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.06446280991736</v>
+        <v>79.56327160493828</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27.75454545454546</v>
+        <v>23.15198135198135</v>
       </c>
       <c r="AK3" t="n">
-        <v>182.9813131313131</v>
+        <v>182.9148407148407</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.13020202020202</v>
+        <v>1.739393939393939</v>
       </c>
       <c r="AM3" t="n">
-        <v>79.06585858585859</v>
+        <v>78.12540792540791</v>
       </c>
       <c r="AN3" t="n">
-        <v>19009151.51515152</v>
+        <v>21626961.92696192</v>
       </c>
       <c r="AO3" t="n">
-        <v>80.53979797979798</v>
+        <v>83.49168609168609</v>
       </c>
       <c r="AP3" t="n">
-        <v>26.67399600780608</v>
+        <v>24.26921988166007</v>
       </c>
       <c r="AQ3" t="n">
-        <v>183.6885234330886</v>
+        <v>181.0604148111325</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.170325352247549</v>
+        <v>1.301425740660191</v>
       </c>
       <c r="AS3" t="n">
-        <v>73.15379955983502</v>
+        <v>72.11881770542058</v>
       </c>
       <c r="AT3" t="n">
-        <v>7489130.950729921</v>
+        <v>8247751.265215381</v>
       </c>
       <c r="AU3" t="n">
-        <v>76.42569099791639</v>
+        <v>78.65667681600695</v>
       </c>
       <c r="AV3" t="n">
-        <v>27.44039969017911</v>
+        <v>23.16745990651268</v>
       </c>
       <c r="AW3" t="n">
-        <v>180.6861366819455</v>
+        <v>182.8115140652365</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.691721203632968</v>
+        <v>1.643706309164959</v>
       </c>
       <c r="AY3" t="n">
-        <v>73.924584818776</v>
+        <v>73.78982588202174</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9206085.126474831</v>
+        <v>15528206.03360017</v>
       </c>
       <c r="BA3" t="n">
-        <v>77.54409154570919</v>
+        <v>81.37763580108806</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26600</v>
+        <v>61276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1114,12 +1124,12 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -1131,7 +1141,7 @@
         <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>188.5</v>
+        <v>177.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
@@ -1140,129 +1150,129 @@
         <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AB4" t="n">
-        <v>7000000</v>
+        <v>23000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="AD4" t="n">
-        <v>26.75272727272727</v>
+        <v>25.7297520661157</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.15</v>
+        <v>183.4049586776859</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.512727272727272</v>
+        <v>2.647107438016529</v>
       </c>
       <c r="AG4" t="n">
-        <v>77.00727272727272</v>
+        <v>82.91239669421488</v>
       </c>
       <c r="AH4" t="n">
-        <v>12767727.27272727</v>
+        <v>47609173.553719</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.10909090909091</v>
+        <v>85.69504132231404</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.32666666666666</v>
+        <v>25.93818181818182</v>
       </c>
       <c r="AK4" t="n">
-        <v>182.8144444444444</v>
+        <v>184.6927272727273</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.395555555555556</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.88777777777777</v>
+        <v>76.45090909090909</v>
       </c>
       <c r="AN4" t="n">
-        <v>9569777.77777778</v>
+        <v>11463818.18181818</v>
       </c>
       <c r="AO4" t="n">
-        <v>78.24555555555555</v>
+        <v>79.08363636363637</v>
       </c>
       <c r="AP4" t="n">
-        <v>28.05046085627927</v>
+        <v>23.33581586784911</v>
       </c>
       <c r="AQ4" t="n">
-        <v>181.4882491613246</v>
+        <v>183.5767576200441</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.302867356428738</v>
+        <v>1.798422570609272</v>
       </c>
       <c r="AS4" t="n">
-        <v>74.82053783173349</v>
+        <v>79.53091446064592</v>
       </c>
       <c r="AT4" t="n">
-        <v>6867890.640050486</v>
+        <v>34011501.61645686</v>
       </c>
       <c r="AU4" t="n">
-        <v>76.19927635876485</v>
+        <v>84.47004489542854</v>
       </c>
       <c r="AV4" t="n">
-        <v>26.0333313229598</v>
+        <v>24.71417784657723</v>
       </c>
       <c r="AW4" t="n">
-        <v>180.5984624830794</v>
+        <v>179.8178242174063</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.456823542814255</v>
+        <v>1.12358789129687</v>
       </c>
       <c r="AY4" t="n">
-        <v>73.54142458418774</v>
+        <v>73.72873409012728</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5998922.906782331</v>
+        <v>7912673.632610939</v>
       </c>
       <c r="BA4" t="n">
-        <v>76.36644761971775</v>
+        <v>77.78260577915376</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.35416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">salisbury m 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55097</v>
+        <v>60704</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1289,147 +1299,119 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>174</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>68</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>82</v>
-      </c>
-      <c r="W5" t="n">
-        <v>25.83333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>181.1666666666667</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>426</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>21800000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>441</v>
-      </c>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>26.06883116883117</v>
+        <v>24.29513888888889</v>
       </c>
       <c r="AE5" t="n">
-        <v>182.0311688311688</v>
+        <v>182.931712962963</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.081818181818182</v>
+        <v>2.269675925925926</v>
       </c>
       <c r="AG5" t="n">
-        <v>84.82402597402597</v>
+        <v>83.52430555555556</v>
       </c>
       <c r="AH5" t="n">
-        <v>71205681.81818183</v>
+        <v>59730902.77777778</v>
       </c>
       <c r="AI5" t="n">
-        <v>87.43506493506493</v>
+        <v>86.50694444444444</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26.19191919191919</v>
+        <v>26.14357208448117</v>
       </c>
       <c r="AK5" t="n">
-        <v>182.5050505050505</v>
+        <v>182.1142102846648</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>1.43613406795225</v>
       </c>
       <c r="AM5" t="n">
-        <v>70.94949494949495</v>
+        <v>75.52132690541781</v>
       </c>
       <c r="AN5" t="n">
-        <v>2815151.515151515</v>
+        <v>9431662.07529844</v>
       </c>
       <c r="AO5" t="n">
-        <v>74.60606060606061</v>
+        <v>79.87178604224059</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.84064024160389</v>
+        <v>24.59527570597617</v>
       </c>
       <c r="AQ5" t="n">
-        <v>178.6274230706776</v>
+        <v>179.2524663513731</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.260184291107747</v>
+        <v>1.797203486657821</v>
       </c>
       <c r="AS5" t="n">
-        <v>80.25051774332921</v>
+        <v>80.94676195837188</v>
       </c>
       <c r="AT5" t="n">
-        <v>44786325.61720341</v>
+        <v>36855524.59021886</v>
       </c>
       <c r="AU5" t="n">
-        <v>84.93818259187732</v>
+        <v>84.471643681396</v>
       </c>
       <c r="AV5" t="n">
-        <v>25.1765873015873</v>
+        <v>23.26457787461077</v>
       </c>
       <c r="AW5" t="n">
-        <v>183.0873015873016</v>
+        <v>177.9252057701071</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.005291005291005</v>
+        <v>1.357585725677831</v>
       </c>
       <c r="AY5" t="n">
-        <v>69.06216931216932</v>
+        <v>72.96969530834662</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2286772.486772487</v>
+        <v>8211209.439317991</v>
       </c>
       <c r="BA5" t="n">
-        <v>73.38690476190476</v>
+        <v>80.39197211779448</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1439,21 +1421,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32384</v>
+        <v>17250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1480,27 +1462,13 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>189</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>72</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>82</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1509,120 +1477,120 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>25.41212121212121</v>
+        <v>25.93818181818182</v>
       </c>
       <c r="AE6" t="n">
-        <v>179.7472582972583</v>
+        <v>184.6927272727273</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>76.45090909090909</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>11463818.18181818</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>79.08363636363637</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>25.4216835016835</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>179.8529966329966</v>
+      </c>
+      <c r="AL6" t="n">
         <v>1</v>
       </c>
-      <c r="AG6" t="n">
-        <v>72.88946608946608</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>4524624.81962482</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>76.2005772005772</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>185.08</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AM6" t="n">
-        <v>74.97999999999999</v>
+        <v>72.90424242424243</v>
       </c>
       <c r="AN6" t="n">
-        <v>8868000</v>
+        <v>4543723.905723905</v>
       </c>
       <c r="AO6" t="n">
-        <v>78.80999999999999</v>
+        <v>76.22424242424243</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.65599619294358</v>
+        <v>24.71417784657723</v>
       </c>
       <c r="AQ6" t="n">
-        <v>179.0003223423757</v>
+        <v>179.8178242174063</v>
       </c>
       <c r="AR6" t="n">
+        <v>1.12358789129687</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>73.72873409012728</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7912673.632610939</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>77.78260577915376</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>24.51226311341401</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>179.0040045565877</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1</v>
       </c>
-      <c r="AS6" t="n">
-        <v>70.89429878670836</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3220631.341469395</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>75.78533397548743</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24.65595847034466</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>185.0414943368652</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.39932103276093</v>
-      </c>
       <c r="AY6" t="n">
-        <v>75.25341980270369</v>
+        <v>70.70504923796484</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10611518.99890391</v>
+        <v>3192404.066852916</v>
       </c>
       <c r="BA6" t="n">
-        <v>79.4291761052247</v>
+        <v>75.83297837712159</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62850</v>
+        <v>39572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1649,323 +1617,1233 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>187</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>39500000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>85</v>
-      </c>
-      <c r="W7" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="X7" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>443</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>40625000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>479</v>
-      </c>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>24.93106060606061</v>
+        <v>27.25833333333334</v>
       </c>
       <c r="AE7" t="n">
-        <v>184.7376262626262</v>
+        <v>183.6515151515152</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.10580808080808</v>
+        <v>1.587878787878788</v>
       </c>
       <c r="AG7" t="n">
-        <v>81.75808080808082</v>
+        <v>76.60909090909092</v>
       </c>
       <c r="AH7" t="n">
-        <v>39735858.58585859</v>
+        <v>11055946.96969697</v>
       </c>
       <c r="AI7" t="n">
-        <v>85.02904040404042</v>
+        <v>79.01818181818182</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27.27272727272727</v>
+        <v>24.16565656565656</v>
       </c>
       <c r="AK7" t="n">
-        <v>183.7107438016529</v>
+        <v>181.2868686868687</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.586776859504132</v>
+        <v>1.164646464646464</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.62809917355372</v>
+        <v>75.02525252525253</v>
       </c>
       <c r="AN7" t="n">
-        <v>11128305.78512397</v>
+        <v>8701313.131313132</v>
       </c>
       <c r="AO7" t="n">
-        <v>79.07438016528926</v>
+        <v>79.13939393939394</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.35057573848736</v>
+        <v>25.23993982951784</v>
       </c>
       <c r="AQ7" t="n">
-        <v>181.9618966950271</v>
+        <v>186.0724124246503</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.770577772213714</v>
+        <v>1.359594910985576</v>
       </c>
       <c r="AS7" t="n">
-        <v>78.47468696047362</v>
+        <v>73.20687443595052</v>
       </c>
       <c r="AT7" t="n">
-        <v>27306688.60474086</v>
+        <v>7371700.551922739</v>
       </c>
       <c r="AU7" t="n">
-        <v>82.14751719884705</v>
+        <v>76.98386936900364</v>
       </c>
       <c r="AV7" t="n">
-        <v>25.2238737534134</v>
+        <v>23.75232324883355</v>
       </c>
       <c r="AW7" t="n">
-        <v>186.0865711299215</v>
+        <v>183.0073115137526</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.369558084711537</v>
+        <v>1.279547856045672</v>
       </c>
       <c r="AY7" t="n">
-        <v>73.18022665740058</v>
+        <v>74.52231411712897</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7226324.844521775</v>
+        <v>11116913.87184574</v>
       </c>
       <c r="BA7" t="n">
-        <v>77.05816052376154</v>
+        <v>79.43281596763498</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>26.02272727272727</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>182.5045454545455</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>71.08454545454545</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2949636.363636364</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>74.91545454545454</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>26.65702479338843</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>184.1363636363636</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.502479338842975</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>76.93388429752066</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12644297.52066116</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>79.0900826446281</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>25.16762422360248</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>183.026397515528</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.004761904761905</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>69.06899585921326</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2294616.977225673</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>73.35256211180123</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>27.98678259661752</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>181.4938628739315</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.302606687662489</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>74.75503439248497</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6797173.309136805</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>76.19025123524078</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>42789</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>W00wmLO0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>26.28787878787879</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>182.7131313131313</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.386868686868687</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>75.80707070707071</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>9388888.88888889</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>78.26868686868687</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>26.03057851239669</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>182.7545454545455</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.126446280991736</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>79.73388429752066</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25829834.7107438</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>81.77685950413223</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>25.98939211178164</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>180.4213295300721</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.447112311649323</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>73.56038598562522</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6091634.46071121</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>76.47858874519794</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>23.48297055317515</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>182.8124033078317</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.646989672021642</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>73.96959414200464</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13943488.88386053</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>79.54284358011979</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>25.01818181818182</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>184.9636363636364</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.309090909090909</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>74.98181818181818</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>8990000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>78.89090909090909</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26.37962962962963</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>182.8317901234568</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.447530864197531</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>76.59567901234567</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12223804.01234568</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>79.56327160493828</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24.75900530796883</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>185.2195403062411</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.377373187677401</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>75.30693666274497</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10602337.8458935</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>79.41886822963011</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24.26921988166007</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>181.0604148111325</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.301425740660191</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>72.11881770542058</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>8247751.265215381</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>78.65667681600695</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>27.68595041322314</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>183.0032139577594</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.128466483011938</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>79.08007346189164</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19129531.68044077</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>80.57153351698807</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>26.01757575757576</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>181.9957575757576</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.089696969696969</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>84.81575757575757</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71201969.6969697</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>87.45939393939393</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>27.48622194056685</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>180.699518195708</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.729847558858254</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>74.34053165343272</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9910077.387704393</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>77.78755797084675</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>24.90038703251451</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>178.8838404800008</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.256873759419862</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>80.2899569113178</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>44635658.29535475</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>84.9072160331206</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>23.15198135198135</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>182.9148407148407</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.739393939393939</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>78.12540792540791</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21626961.92696192</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>83.49168609168609</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>25.50757575757576</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>183.6477272727273</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>76.60303030303031</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>14082348.48484849</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>80.1340909090909</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>23.16745990651268</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>182.8115140652365</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.643706309164959</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>73.78982588202174</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>15528206.03360017</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>81.37763580108806</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>26.75671856271113</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>183.6311464803313</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.170020461782476</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>73.27292737429322</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7437953.371502426</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>76.41799452586781</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>48</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I13" t="n">
         <v>481</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K13" t="n">
         <v>20242025</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>190</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>161</v>
-      </c>
-      <c r="U8" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>164</v>
-      </c>
-      <c r="W8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>183</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>158</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>44000000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>165</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>182.63</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>79.73454545454545</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>25907363.63636364</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>81.76363636363635</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24.39015151515152</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>182.8914141414141</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.248737373737373</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>83.48106060606061</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>59070075.75757576</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>86.39393939393939</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>23.44079141801648</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>182.9650722100434</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.668831496366663</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>73.83322022287174</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>14046885.3912942</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>79.45903270003654</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>24.62991115976621</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>179.4312619937057</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.804741465964376</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>81.13672733121088</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>37488494.35816084</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>84.53400089918524</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>26.30752984389348</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>185.3779614325069</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.535812672176309</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>77.98200183654728</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19609044.99540863</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80.91781450872359</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>24.87199074074074</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>184.7039351851852</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.096990740740741</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>81.66712962962963</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>39644907.40740741</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>85.03587962962963</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>26.12590023612751</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>181.8205037386856</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.387081857536403</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>73.69878492719401</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11748839.7776466</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>78.0719647776466</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>24.21950924176156</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>182.1548867852564</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.761918513418127</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>78.328648232286</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>26643515.48027172</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>82.2231870619061</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>24.86794612794613</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>184.6364983164983</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.315353535353536</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>80.206734006734</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>31470771.04377104</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>84.54276094276095</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>25.7297520661157</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>183.4049586776859</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.647107438016529</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>82.91239669421488</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>47609173.553719</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>85.69504132231404</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>24.34011764000894</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>184.149615344398</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.875685976664238</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>75.43328358437053</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>18796187.63060611</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>81.49840960167049</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>23.33581586784911</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>183.5767576200441</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.798422570609272</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>79.53091446064592</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>34011501.61645686</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>84.47004489542854</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -860,22 +860,22 @@
         <v>79.08429752066117</v>
       </c>
       <c r="V3" t="n">
-        <v>25.4216835016835</v>
+        <v>25.46767676767677</v>
       </c>
       <c r="W3" t="n">
-        <v>179.8529966329966</v>
+        <v>179.945670995671</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>72.90424242424243</v>
+        <v>72.9132756132756</v>
       </c>
       <c r="Z3" t="n">
-        <v>4543723.905723905</v>
+        <v>4532561.327561328</v>
       </c>
       <c r="AA3" t="n">
-        <v>76.22424242424243</v>
+        <v>76.17676767676768</v>
       </c>
       <c r="AB3" t="n">
         <v>24.54016167870657</v>
@@ -896,22 +896,22 @@
         <v>78.03267192044281</v>
       </c>
       <c r="AH3" t="n">
-        <v>24.51226311341401</v>
+        <v>24.47431917431004</v>
       </c>
       <c r="AI3" t="n">
-        <v>179.0040045565877</v>
+        <v>179.0198185466545</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>70.70504923796484</v>
+        <v>70.62497511521077</v>
       </c>
       <c r="AL3" t="n">
-        <v>3192404.066852916</v>
+        <v>3169501.251752348</v>
       </c>
       <c r="AM3" t="n">
-        <v>75.83297837712159</v>
+        <v>75.83036503138806</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -991,76 +991,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>27.25833333333334</v>
+        <v>27.36446280991736</v>
       </c>
       <c r="Q4" t="n">
-        <v>183.6515151515152</v>
+        <v>183.5619834710744</v>
       </c>
       <c r="R4" t="n">
-        <v>1.587878787878788</v>
+        <v>1.591735537190082</v>
       </c>
       <c r="S4" t="n">
-        <v>76.60909090909092</v>
+        <v>76.59834710743803</v>
       </c>
       <c r="T4" t="n">
-        <v>11055946.96969697</v>
+        <v>10980041.32231405</v>
       </c>
       <c r="U4" t="n">
-        <v>79.01818181818182</v>
+        <v>78.97851239669421</v>
       </c>
       <c r="V4" t="n">
-        <v>24.21666666666667</v>
+        <v>24.20909090909091</v>
       </c>
       <c r="W4" t="n">
-        <v>181.1703703703704</v>
+        <v>181.1858585858586</v>
       </c>
       <c r="X4" t="n">
-        <v>1.169444444444445</v>
+        <v>1.157575757575758</v>
       </c>
       <c r="Y4" t="n">
-        <v>75.05092592592592</v>
+        <v>75.02828282828283</v>
       </c>
       <c r="Z4" t="n">
-        <v>8662314.814814815</v>
+        <v>8630707.07070707</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.11851851851851</v>
+        <v>79.12929292929293</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.23993982951784</v>
+        <v>25.02942930896895</v>
       </c>
       <c r="AC4" t="n">
-        <v>186.0724124246503</v>
+        <v>186.1749549683053</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.359594910985576</v>
+        <v>1.346830811984265</v>
       </c>
       <c r="AE4" t="n">
-        <v>73.20687443595052</v>
+        <v>73.08931756649149</v>
       </c>
       <c r="AF4" t="n">
-        <v>7371700.551922739</v>
+        <v>7371274.339471269</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.98386936900364</v>
+        <v>76.99250395810499</v>
       </c>
       <c r="AH4" t="n">
-        <v>23.59240742254186</v>
+        <v>23.58262627913658</v>
       </c>
       <c r="AI4" t="n">
-        <v>182.7613318505695</v>
+        <v>182.5623620188031</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.256252201375199</v>
+        <v>1.261366037863853</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.35841757033118</v>
+        <v>74.26372825854311</v>
       </c>
       <c r="AL4" t="n">
-        <v>10839578.45659934</v>
+        <v>10723176.49810837</v>
       </c>
       <c r="AM4" t="n">
-        <v>79.50785908144319</v>
+        <v>79.45857354339256</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1136,76 +1136,76 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>26.02272727272727</v>
+        <v>25.98484848484848</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.5045454545455</v>
+        <v>182.540404040404</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>71.08454545454545</v>
+        <v>71.04343434343433</v>
       </c>
       <c r="T5" t="n">
-        <v>2949636.363636364</v>
+        <v>2948080.808080808</v>
       </c>
       <c r="U5" t="n">
-        <v>74.91545454545454</v>
+        <v>74.93636363636364</v>
       </c>
       <c r="V5" t="n">
-        <v>26.65702479338843</v>
+        <v>26.65</v>
       </c>
       <c r="W5" t="n">
-        <v>184.1363636363636</v>
+        <v>184.0772727272727</v>
       </c>
       <c r="X5" t="n">
-        <v>1.502479338842975</v>
+        <v>1.498181818181818</v>
       </c>
       <c r="Y5" t="n">
-        <v>76.93388429752066</v>
+        <v>76.90909090909091</v>
       </c>
       <c r="Z5" t="n">
-        <v>12644297.52066116</v>
+        <v>12607818.18181818</v>
       </c>
       <c r="AA5" t="n">
-        <v>79.0900826446281</v>
+        <v>79.05363636363636</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.16762422360248</v>
+        <v>25.25106395215091</v>
       </c>
       <c r="AC5" t="n">
-        <v>183.026397515528</v>
+        <v>183.0108120542903</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.004761904761905</v>
+        <v>1.005291005291005</v>
       </c>
       <c r="AE5" t="n">
-        <v>69.06899585921326</v>
+        <v>69.2016620657925</v>
       </c>
       <c r="AF5" t="n">
-        <v>2294616.977225673</v>
+        <v>2316704.048769266</v>
       </c>
       <c r="AG5" t="n">
-        <v>73.35256211180123</v>
+        <v>73.34080975385324</v>
       </c>
       <c r="AH5" t="n">
-        <v>27.98678259661752</v>
+        <v>27.86641323723165</v>
       </c>
       <c r="AI5" t="n">
-        <v>181.4938628739315</v>
+        <v>181.4575348756103</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.302606687662489</v>
+        <v>1.299534023095404</v>
       </c>
       <c r="AK5" t="n">
-        <v>74.75503439248497</v>
+        <v>74.73529973649538</v>
       </c>
       <c r="AL5" t="n">
-        <v>6797173.309136805</v>
+        <v>6887843.021002868</v>
       </c>
       <c r="AM5" t="n">
-        <v>76.19025123524078</v>
+        <v>76.27118112066961</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1281,76 +1281,76 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>26.28787878787879</v>
+        <v>26.26666666666666</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.7131313131313</v>
+        <v>182.6644444444444</v>
       </c>
       <c r="R6" t="n">
-        <v>1.386868686868687</v>
+        <v>1.395555555555556</v>
       </c>
       <c r="S6" t="n">
-        <v>75.80707070707071</v>
+        <v>75.79777777777778</v>
       </c>
       <c r="T6" t="n">
-        <v>9388888.88888889</v>
+        <v>9408777.77777778</v>
       </c>
       <c r="U6" t="n">
-        <v>78.26868686868687</v>
+        <v>78.29555555555555</v>
       </c>
       <c r="V6" t="n">
-        <v>26.03057851239669</v>
+        <v>26.06363636363636</v>
       </c>
       <c r="W6" t="n">
-        <v>182.7545454545455</v>
+        <v>182.8</v>
       </c>
       <c r="X6" t="n">
-        <v>2.126446280991736</v>
+        <v>2.109090909090909</v>
       </c>
       <c r="Y6" t="n">
-        <v>79.73388429752066</v>
+        <v>79.62727272727273</v>
       </c>
       <c r="Z6" t="n">
-        <v>25829834.7107438</v>
+        <v>25281818.18181818</v>
       </c>
       <c r="AA6" t="n">
-        <v>81.77685950413223</v>
+        <v>81.65454545454546</v>
       </c>
       <c r="AB6" t="n">
-        <v>25.98939211178164</v>
+        <v>25.90261703724552</v>
       </c>
       <c r="AC6" t="n">
-        <v>180.4213295300721</v>
+        <v>180.4348910545079</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.447112311649323</v>
+        <v>1.420394971385683</v>
       </c>
       <c r="AE6" t="n">
-        <v>73.56038598562522</v>
+        <v>73.54499601275917</v>
       </c>
       <c r="AF6" t="n">
-        <v>6091634.46071121</v>
+        <v>6015976.478210902</v>
       </c>
       <c r="AG6" t="n">
-        <v>76.47858874519794</v>
+        <v>76.56216190543202</v>
       </c>
       <c r="AH6" t="n">
-        <v>23.48297055317515</v>
+        <v>23.50952847805789</v>
       </c>
       <c r="AI6" t="n">
-        <v>182.8124033078317</v>
+        <v>182.7762523342671</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.646989672021642</v>
+        <v>1.655166900093371</v>
       </c>
       <c r="AK6" t="n">
-        <v>73.96959414200464</v>
+        <v>74.04481442577031</v>
       </c>
       <c r="AL6" t="n">
-        <v>13943488.88386053</v>
+        <v>14170772.55485528</v>
       </c>
       <c r="AM6" t="n">
-        <v>79.54284358011979</v>
+        <v>79.59278011204484</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1422,22 +1422,22 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>25.01818181818182</v>
+        <v>24.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>184.9636363636364</v>
+        <v>184.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.309090909090909</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>74.98181818181818</v>
+        <v>74.94</v>
       </c>
       <c r="T7" t="n">
-        <v>8990000</v>
+        <v>8873000</v>
       </c>
       <c r="U7" t="n">
-        <v>78.89090909090909</v>
+        <v>78.91</v>
       </c>
       <c r="V7" t="n">
         <v>26.39166666666666</v>
@@ -1458,40 +1458,40 @@
         <v>79.56944444444444</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.75900530796883</v>
+        <v>24.87019995641277</v>
       </c>
       <c r="AC7" t="n">
-        <v>185.2195403062411</v>
+        <v>185.3826708074534</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.377373187677401</v>
+        <v>1.379816388798082</v>
       </c>
       <c r="AE7" t="n">
-        <v>75.30693666274497</v>
+        <v>75.37880679960772</v>
       </c>
       <c r="AF7" t="n">
-        <v>10602337.8458935</v>
+        <v>10626689.27754168</v>
       </c>
       <c r="AG7" t="n">
-        <v>79.41886822963011</v>
+        <v>79.42546093494606</v>
       </c>
       <c r="AH7" t="n">
-        <v>24.57031430328644</v>
+        <v>24.74842368439329</v>
       </c>
       <c r="AI7" t="n">
-        <v>180.8642037729499</v>
+        <v>180.7508485603898</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.320424575997332</v>
+        <v>1.344503577855675</v>
       </c>
       <c r="AK7" t="n">
-        <v>72.46675936722376</v>
+        <v>72.8273738551532</v>
       </c>
       <c r="AL7" t="n">
-        <v>8361909.248016059</v>
+        <v>8737865.644300347</v>
       </c>
       <c r="AM7" t="n">
-        <v>78.60195374800638</v>
+        <v>78.65667681600695</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1571,22 +1571,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>27.68595041322314</v>
+        <v>27.73636363636364</v>
       </c>
       <c r="Q8" t="n">
-        <v>183.0032139577594</v>
+        <v>183.0126262626263</v>
       </c>
       <c r="R8" t="n">
-        <v>2.128466483011938</v>
+        <v>2.132222222222222</v>
       </c>
       <c r="S8" t="n">
-        <v>79.08007346189164</v>
+        <v>79.06989898989899</v>
       </c>
       <c r="T8" t="n">
-        <v>19129531.68044077</v>
+        <v>19069757.57575758</v>
       </c>
       <c r="U8" t="n">
-        <v>80.57153351698807</v>
+        <v>80.56505050505049</v>
       </c>
       <c r="V8" t="n">
         <v>26.01757575757576</v>
@@ -1607,22 +1607,22 @@
         <v>87.45939393939393</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.48622194056685</v>
+        <v>27.25706635684577</v>
       </c>
       <c r="AC8" t="n">
-        <v>180.699518195708</v>
+        <v>180.6194700152788</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.729847558858254</v>
+        <v>1.730610092521857</v>
       </c>
       <c r="AE8" t="n">
-        <v>74.34053165343272</v>
+        <v>74.23014037433155</v>
       </c>
       <c r="AF8" t="n">
-        <v>9910077.387704393</v>
+        <v>10185529.57091928</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.78755797084675</v>
+        <v>77.81631376793142</v>
       </c>
       <c r="AH8" t="n">
         <v>24.90038703251451</v>
@@ -1720,76 +1720,76 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23.06255411255411</v>
+        <v>23.12890442890443</v>
       </c>
       <c r="Q9" t="n">
-        <v>182.9280663780664</v>
+        <v>182.9763791763791</v>
       </c>
       <c r="R9" t="n">
-        <v>1.715151515151515</v>
+        <v>1.716317016317016</v>
       </c>
       <c r="S9" t="n">
-        <v>78.12359307359306</v>
+        <v>78.11002331002331</v>
       </c>
       <c r="T9" t="n">
-        <v>21800036.07503607</v>
+        <v>21573115.77311577</v>
       </c>
       <c r="U9" t="n">
-        <v>83.54227994227995</v>
+        <v>83.49937839937841</v>
       </c>
       <c r="V9" t="n">
-        <v>25.50757575757576</v>
+        <v>25.44628099173554</v>
       </c>
       <c r="W9" t="n">
-        <v>183.6477272727273</v>
+        <v>183.6074380165289</v>
       </c>
       <c r="X9" t="n">
-        <v>1.291666666666667</v>
+        <v>1.293388429752067</v>
       </c>
       <c r="Y9" t="n">
-        <v>76.60303030303031</v>
+        <v>76.60826446280991</v>
       </c>
       <c r="Z9" t="n">
-        <v>14082348.48484849</v>
+        <v>14240247.9338843</v>
       </c>
       <c r="AA9" t="n">
-        <v>80.1340909090909</v>
+        <v>80.17933884297521</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.17781991319034</v>
+        <v>23.14204781860059</v>
       </c>
       <c r="AC9" t="n">
-        <v>182.6106916320053</v>
+        <v>182.7126129663354</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.637905858510319</v>
+        <v>1.610052463011113</v>
       </c>
       <c r="AE9" t="n">
-        <v>74.17983831902019</v>
+        <v>74.29806764026351</v>
       </c>
       <c r="AF9" t="n">
-        <v>16555209.1740573</v>
+        <v>16792835.1544793</v>
       </c>
       <c r="AG9" t="n">
-        <v>81.52923324386749</v>
+        <v>81.57543799889027</v>
       </c>
       <c r="AH9" t="n">
-        <v>26.75671856271113</v>
+        <v>26.6607384320485</v>
       </c>
       <c r="AI9" t="n">
-        <v>183.6311464803313</v>
+        <v>183.7907961603614</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.170020461782476</v>
+        <v>1.162749594671792</v>
       </c>
       <c r="AK9" t="n">
-        <v>73.27292737429322</v>
+        <v>73.40569349922896</v>
       </c>
       <c r="AL9" t="n">
-        <v>7437953.371502426</v>
+        <v>7800636.632548102</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.41799452586781</v>
+        <v>76.58099402821944</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1869,76 +1869,76 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26.30690235690236</v>
+        <v>26.19338842975207</v>
       </c>
       <c r="Q10" t="n">
-        <v>185.5381313131313</v>
+        <v>185.4355371900827</v>
       </c>
       <c r="R10" t="n">
-        <v>1.532828282828283</v>
+        <v>1.520661157024793</v>
       </c>
       <c r="S10" t="n">
-        <v>78.05850168350169</v>
+        <v>77.96280991735537</v>
       </c>
       <c r="T10" t="n">
-        <v>19835791.24579125</v>
+        <v>19746115.70247934</v>
       </c>
       <c r="U10" t="n">
-        <v>80.90799663299663</v>
+        <v>80.9198347107438</v>
       </c>
       <c r="V10" t="n">
-        <v>24.87199074074074</v>
+        <v>24.82626262626263</v>
       </c>
       <c r="W10" t="n">
-        <v>184.7039351851852</v>
+        <v>184.8020202020202</v>
       </c>
       <c r="X10" t="n">
-        <v>2.096990740740741</v>
+        <v>2.071717171717172</v>
       </c>
       <c r="Y10" t="n">
-        <v>81.66712962962963</v>
+        <v>81.6141414141414</v>
       </c>
       <c r="Z10" t="n">
-        <v>39644907.40740741</v>
+        <v>39430808.08080809</v>
       </c>
       <c r="AA10" t="n">
-        <v>85.03587962962963</v>
+        <v>85.05050505050507</v>
       </c>
       <c r="AB10" t="n">
-        <v>26.11102258487127</v>
+        <v>26.17070232399179</v>
       </c>
       <c r="AC10" t="n">
-        <v>181.7082687780056</v>
+        <v>181.7850535429483</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.394298720285563</v>
+        <v>1.392953975848713</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.91686863940153</v>
+        <v>73.92584016860333</v>
       </c>
       <c r="AF10" t="n">
-        <v>12156962.77863219</v>
+        <v>12409765.17999544</v>
       </c>
       <c r="AG10" t="n">
-        <v>78.26333613389535</v>
+        <v>78.29967247664617</v>
       </c>
       <c r="AH10" t="n">
-        <v>24.21950924176156</v>
+        <v>24.12789437944237</v>
       </c>
       <c r="AI10" t="n">
-        <v>182.1548867852564</v>
+        <v>182.0491326913541</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.761918513418127</v>
+        <v>1.744406973315642</v>
       </c>
       <c r="AK10" t="n">
-        <v>78.328648232286</v>
+        <v>78.17257493108886</v>
       </c>
       <c r="AL10" t="n">
-        <v>26643515.48027172</v>
+        <v>26236417.71401543</v>
       </c>
       <c r="AM10" t="n">
-        <v>82.2231870619061</v>
+        <v>82.17322886092235</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:BC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -645,7 +715,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
@@ -701,85 +771,113 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>24.29513888888889</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>182.931712962963</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="R2" t="n">
-        <v>2.269675925925926</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>83.52430555555556</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>59730902.77777778</v>
+        <v>241</v>
       </c>
       <c r="U2" t="n">
-        <v>86.50694444444444</v>
+        <v>87500000</v>
       </c>
       <c r="V2" t="n">
-        <v>26.14357208448117</v>
-      </c>
-      <c r="W2" t="n">
-        <v>182.1142102846648</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.43613406795225</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>75.52132690541781</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9431662.07529844</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>79.87178604224059</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>24.59527570597617</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>179.2524663513731</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>1.797203486657821</v>
+        <v>24.26136363636364</v>
       </c>
       <c r="AE2" t="n">
-        <v>80.94676195837188</v>
+        <v>182.875</v>
       </c>
       <c r="AF2" t="n">
-        <v>36855524.59021886</v>
+        <v>2.273989898989899</v>
       </c>
       <c r="AG2" t="n">
-        <v>84.471643681396</v>
+        <v>83.53156565656565</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.26457787461077</v>
+        <v>59863005.05050505</v>
       </c>
       <c r="AI2" t="n">
-        <v>177.9252057701071</v>
+        <v>86.51262626262626</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.357585725677831</v>
+        <v>25.74997704315886</v>
       </c>
       <c r="AK2" t="n">
-        <v>72.96969530834662</v>
+        <v>181.7815656565657</v>
       </c>
       <c r="AL2" t="n">
-        <v>8211209.439317991</v>
+        <v>1.40307621671258</v>
       </c>
       <c r="AM2" t="n">
-        <v>80.39197211779448</v>
-      </c>
-      <c r="AN2" t="inlineStr">
+        <v>75.09777318640955</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>9015494.719926538</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>79.93790174471992</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>24.59056814983497</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>179.2112467148669</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.810853001487676</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>80.9312269492399</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>36874476.02355427</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>84.48243481820741</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23.16136150034177</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>177.7503519689375</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.335655901116428</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>72.52437367091972</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>8162298.620604542</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>80.09489609440267</v>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
         </is>
       </c>
     </row>
@@ -794,7 +892,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
@@ -842,85 +940,127 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>25.91900826446281</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>184.6793388429752</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>1.041322314049587</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>76.43471074380165</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>11414214.87603306</v>
+        <v>233</v>
       </c>
       <c r="U3" t="n">
-        <v>79.08429752066117</v>
+        <v>46000000</v>
       </c>
       <c r="V3" t="n">
-        <v>25.46767676767677</v>
+        <v>240</v>
       </c>
       <c r="W3" t="n">
-        <v>179.945670995671</v>
+        <v>23.5</v>
       </c>
       <c r="X3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" t="n">
-        <v>72.9132756132756</v>
-      </c>
       <c r="Z3" t="n">
-        <v>4532561.327561328</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>76.17676767676768</v>
+        <v>144</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.54016167870657</v>
+        <v>7400000</v>
       </c>
       <c r="AC3" t="n">
-        <v>179.7010523188542</v>
+        <v>155</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.136595052694124</v>
+        <v>25.90090909090909</v>
       </c>
       <c r="AE3" t="n">
-        <v>73.7170309910248</v>
+        <v>184.5872727272727</v>
       </c>
       <c r="AF3" t="n">
-        <v>7946521.484191763</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AG3" t="n">
-        <v>78.03267192044281</v>
+        <v>76.49818181818182</v>
       </c>
       <c r="AH3" t="n">
-        <v>24.47431917431004</v>
+        <v>11559636.36363636</v>
       </c>
       <c r="AI3" t="n">
-        <v>179.0198185466545</v>
+        <v>79.13272727272728</v>
       </c>
       <c r="AJ3" t="n">
+        <v>25.45749805749806</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>179.9722610722611</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1</v>
       </c>
-      <c r="AK3" t="n">
-        <v>70.62497511521077</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3169501.251752348</v>
-      </c>
       <c r="AM3" t="n">
-        <v>75.83036503138806</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
+        <v>72.92198912198911</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4562758.352758354</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>76.19805749805749</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>24.42081026988147</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>180.2584685867968</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.127291490758983</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>73.73430903461862</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7935098.039215687</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>78.15122588110204</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>24.43228620727708</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>179.0104778873138</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.016483516483516</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>70.40079929103494</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3159666.086917183</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>75.93805733908036</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
@@ -935,7 +1075,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
@@ -991,85 +1131,127 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>27.36446280991736</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>183.5619834710744</v>
+        <v>190</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591735537190082</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>76.59834710743803</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>10980041.32231405</v>
+        <v>220</v>
       </c>
       <c r="U4" t="n">
-        <v>78.97851239669421</v>
+        <v>31100000</v>
       </c>
       <c r="V4" t="n">
-        <v>24.20909090909091</v>
+        <v>250</v>
       </c>
       <c r="W4" t="n">
-        <v>181.1858585858586</v>
+        <v>25</v>
       </c>
       <c r="X4" t="n">
-        <v>1.157575757575758</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="Y4" t="n">
-        <v>75.02828282828283</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>8630707.07070707</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.12929292929293</v>
+        <v>232</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.02942930896895</v>
+        <v>50000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>186.1749549683053</v>
+        <v>237</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.346830811984265</v>
+        <v>27.2147842056933</v>
       </c>
       <c r="AE4" t="n">
-        <v>73.08931756649149</v>
+        <v>183.6492194674013</v>
       </c>
       <c r="AF4" t="n">
-        <v>7371274.339471269</v>
+        <v>1.582552800734619</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.99250395810499</v>
+        <v>76.39632690541782</v>
       </c>
       <c r="AH4" t="n">
-        <v>23.58262627913658</v>
+        <v>10702883.37924702</v>
       </c>
       <c r="AI4" t="n">
-        <v>182.5623620188031</v>
+        <v>78.87658402203856</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.261366037863853</v>
+        <v>24.13535353535353</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.26372825854311</v>
+        <v>180.9333333333333</v>
       </c>
       <c r="AL4" t="n">
-        <v>10723176.49810837</v>
+        <v>1.168686868686869</v>
       </c>
       <c r="AM4" t="n">
-        <v>79.45857354339256</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
+        <v>74.8959595959596</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8575858.585858585</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>79.17676767676768</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>25.33056567260531</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>185.5897276955781</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.348724751378204</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>73.07795393012785</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7191586.839471269</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>76.81826153386255</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>23.56738563742535</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>182.3428433022256</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.234093310591126</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>74.12362130667147</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10299459.92056826</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>79.33317247387384</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1266,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">smith l 
   eng </t>
         </is>
       </c>
@@ -1136,85 +1318,113 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>25.98484848484848</v>
+        <v>25.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.540404040404</v>
+        <v>181.8</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>71.04343434343433</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2948080.808080808</v>
+        <v>349</v>
       </c>
       <c r="U5" t="n">
-        <v>74.93636363636364</v>
+        <v>10800000</v>
       </c>
       <c r="V5" t="n">
-        <v>26.65</v>
-      </c>
-      <c r="W5" t="n">
-        <v>184.0772727272727</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.498181818181818</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>76.90909090909091</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>12607818.18181818</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>79.05363636363636</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>25.25106395215091</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>183.0108120542903</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>1.005291005291005</v>
+        <v>25.88383838383838</v>
       </c>
       <c r="AE5" t="n">
-        <v>69.2016620657925</v>
+        <v>182.6994949494949</v>
       </c>
       <c r="AF5" t="n">
-        <v>2316704.048769266</v>
+        <v>1.013888888888889</v>
       </c>
       <c r="AG5" t="n">
-        <v>73.34080975385324</v>
+        <v>71.05353535353535</v>
       </c>
       <c r="AH5" t="n">
-        <v>27.86641323723165</v>
+        <v>3033055.555555556</v>
       </c>
       <c r="AI5" t="n">
-        <v>181.4575348756103</v>
+        <v>74.90479797979798</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.299534023095404</v>
+        <v>26.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>74.73529973649538</v>
+        <v>184.1472727272727</v>
       </c>
       <c r="AL5" t="n">
-        <v>6887843.021002868</v>
+        <v>1.488181818181818</v>
       </c>
       <c r="AM5" t="n">
-        <v>76.27118112066961</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
+        <v>76.5590909090909</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11867818.18181818</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>78.75363636363636</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>25.20981816090512</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>182.967882761361</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01034151034151</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>69.25006273919318</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2378825.260890478</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>73.49106227910576</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>27.49224657056499</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>181.7858682089437</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.282867356428738</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>74.67113306982871</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7114676.3543362</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>76.46118112066961</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1439,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
@@ -1281,83 +1491,125 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>26.26666666666666</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.6644444444444</v>
+        <v>188.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.395555555555556</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>75.79777777777778</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>9408777.77777778</v>
+        <v>138</v>
       </c>
       <c r="U6" t="n">
-        <v>78.29555555555555</v>
+        <v>7000000</v>
       </c>
       <c r="V6" t="n">
+        <v>148</v>
+      </c>
+      <c r="W6" t="n">
+        <v>26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>244</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26.28888888888889</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>182.2711111111111</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.402222222222222</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>75.60333333333334</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>9166305.555555556</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>78.11777777777777</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>26.06363636363636</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AK6" t="n">
         <v>182.8</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AL6" t="n">
         <v>2.109090909090909</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AM6" t="n">
         <v>79.62727272727273</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AN6" t="n">
         <v>25281818.18181818</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AO6" t="n">
         <v>81.65454545454546</v>
       </c>
-      <c r="AB6" t="n">
-        <v>25.90261703724552</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>180.4348910545079</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.420394971385683</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>73.54499601275917</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6015976.478210902</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>76.56216190543202</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AP6" t="n">
+        <v>25.63833132295981</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>180.4193066389235</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.380135231125943</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>73.30408692185009</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6002031.673016096</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>76.64333073660086</v>
+      </c>
+      <c r="AV6" t="n">
         <v>23.50952847805789</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AW6" t="n">
         <v>182.7762523342671</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AX6" t="n">
         <v>1.655166900093371</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AY6" t="n">
         <v>74.04481442577031</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AZ6" t="n">
         <v>14170772.55485528</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BA6" t="n">
         <v>79.59278011204484</v>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
@@ -1374,7 +1626,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">england d 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
@@ -1421,86 +1673,114 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>184.86</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S7" t="n">
-        <v>74.94</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8873000</v>
-      </c>
-      <c r="U7" t="n">
-        <v>78.91</v>
-      </c>
-      <c r="V7" t="n">
-        <v>26.39166666666666</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>182.7611111111111</v>
+        <v>25</v>
       </c>
       <c r="X7" t="n">
-        <v>1.452777777777778</v>
+        <v>200</v>
       </c>
       <c r="Y7" t="n">
-        <v>76.64861111111111</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>12315173.61111111</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.56944444444444</v>
+        <v>77</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.87019995641277</v>
+        <v>13500000</v>
       </c>
       <c r="AC7" t="n">
-        <v>185.3826708074534</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.379816388798082</v>
+        <v>25.07777777777778</v>
       </c>
       <c r="AE7" t="n">
-        <v>75.37880679960772</v>
+        <v>184.8666666666667</v>
       </c>
       <c r="AF7" t="n">
-        <v>10626689.27754168</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>79.42546093494606</v>
+        <v>75.03333333333333</v>
       </c>
       <c r="AH7" t="n">
-        <v>24.74842368439329</v>
+        <v>9026666.666666666</v>
       </c>
       <c r="AI7" t="n">
-        <v>180.7508485603898</v>
+        <v>78.91111111111111</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.344503577855675</v>
+        <v>26.31666666666666</v>
       </c>
       <c r="AK7" t="n">
-        <v>72.8273738551532</v>
+        <v>182.6486111111111</v>
       </c>
       <c r="AL7" t="n">
-        <v>8737865.644300347</v>
+        <v>1.427777777777778</v>
       </c>
       <c r="AM7" t="n">
-        <v>78.65667681600695</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
+        <v>76.41111111111113</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>11977673.61111111</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.69311662307944</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>185.3841589026915</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.38368543641713</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>75.34458060913153</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10655320.22992263</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>79.61028236351748</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>25.14185378370574</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>180.3711694160048</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.36131030054475</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>73.14211793460316</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>8670132.642008521</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>78.49090141493744</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1795,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allison s 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
@@ -1571,83 +1851,125 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>27.73636363636364</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
-        <v>183.0126262626263</v>
+        <v>175</v>
       </c>
       <c r="R8" t="n">
-        <v>2.132222222222222</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>79.06989898989899</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>19069757.57575758</v>
+        <v>76</v>
       </c>
       <c r="U8" t="n">
-        <v>80.56505050505049</v>
+        <v>3900000</v>
       </c>
       <c r="V8" t="n">
-        <v>26.01757575757576</v>
+        <v>76</v>
       </c>
       <c r="W8" t="n">
-        <v>181.9957575757576</v>
+        <v>19</v>
       </c>
       <c r="X8" t="n">
-        <v>3.089696969696969</v>
+        <v>174</v>
       </c>
       <c r="Y8" t="n">
-        <v>84.81575757575757</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>71201969.6969697</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>87.45939393939393</v>
+        <v>68</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.25706635684577</v>
+        <v>2900000</v>
       </c>
       <c r="AC8" t="n">
-        <v>180.6194700152788</v>
+        <v>82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.730610092521857</v>
+        <v>27.70795454545455</v>
       </c>
       <c r="AE8" t="n">
-        <v>74.23014037433155</v>
+        <v>182.8796717171717</v>
       </c>
       <c r="AF8" t="n">
-        <v>10185529.57091928</v>
+        <v>2.123131313131313</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.81631376793142</v>
+        <v>79.07330808080808</v>
       </c>
       <c r="AH8" t="n">
-        <v>24.90038703251451</v>
+        <v>19049530.3030303</v>
       </c>
       <c r="AI8" t="n">
-        <v>178.8838404800008</v>
+        <v>80.58550505050505</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.256873759419862</v>
+        <v>25.98311688311688</v>
       </c>
       <c r="AK8" t="n">
-        <v>80.2899569113178</v>
+        <v>181.9097402597403</v>
       </c>
       <c r="AL8" t="n">
-        <v>44635658.29535475</v>
+        <v>3.074675324675325</v>
       </c>
       <c r="AM8" t="n">
-        <v>84.9072160331206</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
+        <v>84.73116883116883</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>70366396.10389611</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>87.44220779220778</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>27.14383106272812</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>180.67535236822</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.79237479840421</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>75.05661096256685</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>12050860.45327222</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>78.45969612087261</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>24.98150711466891</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>179.1066358084042</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.271020204420441</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>80.39890341338672</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>45332406.99712379</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>84.95100877498216</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
@@ -1664,8 +1986,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1719,86 +2041,100 @@
           <t>2XrRecc3</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
         <v>23.12890442890443</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AE9" t="n">
         <v>182.9763791763791</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AF9" t="n">
         <v>1.716317016317016</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AG9" t="n">
         <v>78.11002331002331</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AH9" t="n">
         <v>21573115.77311577</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AI9" t="n">
         <v>83.49937839937841</v>
       </c>
-      <c r="V9" t="n">
-        <v>25.44628099173554</v>
-      </c>
-      <c r="W9" t="n">
-        <v>183.6074380165289</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.293388429752067</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>76.60826446280991</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>14240247.9338843</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>80.17933884297521</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AJ9" t="n">
+        <v>25.3682277318641</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>183.4219467401286</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.298898071625345</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>76.65785123966943</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>14512791.55188246</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>80.25371900826445</v>
+      </c>
+      <c r="AP9" t="n">
         <v>23.14204781860059</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AQ9" t="n">
         <v>182.7126129663354</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AR9" t="n">
         <v>1.610052463011113</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AS9" t="n">
         <v>74.29806764026351</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AT9" t="n">
         <v>16792835.1544793</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AU9" t="n">
         <v>81.57543799889027</v>
       </c>
-      <c r="AH9" t="n">
-        <v>26.6607384320485</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>183.7907961603614</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.162749594671792</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>73.40569349922896</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>7800636.632548102</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>76.58099402821944</v>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AV9" t="n">
+        <v>26.67299919759873</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>183.73218372017</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.156170647303371</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>73.82614804468351</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8222519.108624658</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>76.80677154018116</v>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
         </is>
       </c>
     </row>
@@ -1813,7 +2149,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
@@ -1869,83 +2205,125 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26.19338842975207</v>
+        <v>27.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>185.4355371900827</v>
+        <v>188</v>
       </c>
       <c r="R10" t="n">
-        <v>1.520661157024793</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="S10" t="n">
-        <v>77.96280991735537</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>19746115.70247934</v>
+        <v>471</v>
       </c>
       <c r="U10" t="n">
-        <v>80.9198347107438</v>
+        <v>106000000</v>
       </c>
       <c r="V10" t="n">
-        <v>24.82626262626263</v>
+        <v>490</v>
       </c>
       <c r="W10" t="n">
-        <v>184.8020202020202</v>
+        <v>25.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.071717171717172</v>
+        <v>187</v>
       </c>
       <c r="Y10" t="n">
-        <v>81.6141414141414</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>39430808.08080809</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>85.05050505050507</v>
+        <v>159</v>
       </c>
       <c r="AB10" t="n">
-        <v>26.17070232399179</v>
+        <v>53000000</v>
       </c>
       <c r="AC10" t="n">
-        <v>181.7850535429483</v>
+        <v>164</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.392953975848713</v>
+        <v>26.23140495867769</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.92584016860333</v>
+        <v>185.4363636363636</v>
       </c>
       <c r="AF10" t="n">
-        <v>12409765.17999544</v>
+        <v>1.552892561983471</v>
       </c>
       <c r="AG10" t="n">
-        <v>78.29967247664617</v>
+        <v>78.18347107438017</v>
       </c>
       <c r="AH10" t="n">
-        <v>24.12789437944237</v>
+        <v>20749917.3553719</v>
       </c>
       <c r="AI10" t="n">
-        <v>182.0491326913541</v>
+        <v>81.06942148760331</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.744406973315642</v>
+        <v>24.75333333333334</v>
       </c>
       <c r="AK10" t="n">
-        <v>78.17257493108886</v>
+        <v>184.86</v>
       </c>
       <c r="AL10" t="n">
-        <v>26236417.71401543</v>
+        <v>2.056666666666667</v>
       </c>
       <c r="AM10" t="n">
-        <v>82.17322886092235</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
+        <v>81.57555555555555</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>39335000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>85.06666666666668</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>26.24077808156756</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>181.7168717247664</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.425150945545682</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>75.04326441102756</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>14816280.33151059</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>78.94929368876737</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24.06449334119613</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>181.9445221509657</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.723609575409111</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>78.01840385276918</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>25973511.86636936</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>82.15245650891936</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
@@ -1962,7 +2340,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
@@ -2018,85 +2396,1397 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>24.86794612794613</v>
+        <v>24.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>184.6364983164983</v>
+        <v>181.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.315353535353536</v>
+        <v>1.8</v>
       </c>
       <c r="S11" t="n">
-        <v>80.206734006734</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>31470771.04377104</v>
+        <v>396</v>
       </c>
       <c r="U11" t="n">
-        <v>84.54276094276095</v>
+        <v>120500000</v>
       </c>
       <c r="V11" t="n">
-        <v>25.76893939393939</v>
-      </c>
-      <c r="W11" t="n">
-        <v>183.4962121212121</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.676515151515152</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>83.09469696969697</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>48600075.75757575</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>85.81212121212121</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>24.34011764000894</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>184.149615344398</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>1.875685976664238</v>
+        <v>24.89098124098124</v>
       </c>
       <c r="AE11" t="n">
-        <v>75.43328358437053</v>
+        <v>184.5326118326118</v>
       </c>
       <c r="AF11" t="n">
-        <v>18796187.63060611</v>
+        <v>2.324891774891775</v>
       </c>
       <c r="AG11" t="n">
-        <v>81.49840960167049</v>
+        <v>80.2215007215007</v>
       </c>
       <c r="AH11" t="n">
-        <v>23.38391816871676</v>
+        <v>31611540.4040404</v>
       </c>
       <c r="AI11" t="n">
-        <v>183.4199988328665</v>
+        <v>84.56854256854258</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.804351124507774</v>
+        <v>25.82231404958677</v>
       </c>
       <c r="AK11" t="n">
-        <v>79.53377303820078</v>
+        <v>183.4669421487603</v>
       </c>
       <c r="AL11" t="n">
-        <v>33828659.09044778</v>
+        <v>2.704958677685951</v>
       </c>
       <c r="AM11" t="n">
-        <v>84.44536724109935</v>
-      </c>
-      <c r="AN11" t="inlineStr">
+        <v>83.27685950413223</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>49561239.66942148</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>85.9190082644628</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>24.20568159842228</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>184.1880799324899</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.839028625791048</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>75.13089907849225</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>18049546.2708875</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>81.36734362083742</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>23.52577169207604</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>183.4635281385281</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.834693205345379</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>79.75342085450781</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>34153724.35535479</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>84.47515998494261</v>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>25.45749805749806</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>179.9722610722611</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>72.92198912198911</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4562758.352758354</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>76.19805749805749</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>24.89098124098124</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>184.5326118326118</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.324891774891775</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>80.2215007215007</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>31611540.4040404</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>84.56854256854258</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>24.43228620727708</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>179.0104778873138</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.016483516483516</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>70.40079929103494</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3159666.086917183</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>75.93805733908036</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>24.20568159842228</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>184.1880799324899</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.839028625791048</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>75.13089907849225</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18049546.2708875</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>81.36734362083742</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linington j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>25.74997704315886</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>181.7815656565657</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.40307621671258</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>75.09777318640955</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>9015494.719926538</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>79.93790174471992</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>25.88383838383838</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>182.6994949494949</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.013888888888889</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>71.05353535353535</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3033055.555555556</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>74.90479797979798</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>23.16136150034177</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>177.7503519689375</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.335655901116428</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>72.52437367091972</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8162298.620604542</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>80.09489609440267</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>25.20981816090512</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>182.967882761361</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01034151034151</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>69.25006273919318</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2378825.260890478</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>73.49106227910576</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>25.3682277318641</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>183.4219467401286</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.298898071625345</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>76.65785123966943</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>14512791.55188246</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>80.25371900826445</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>26.28888888888889</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>182.2711111111111</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.402222222222222</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75.60333333333334</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9166305.555555556</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>78.11777777777777</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>26.67299919759873</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>183.73218372017</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.156170647303371</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>73.82614804468351</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8222519.108624658</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>76.80677154018116</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>25.63833132295981</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>180.4193066389235</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.380135231125943</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>73.30408692185009</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6002031.673016096</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>76.64333073660086</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>184.1472727272727</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.488181818181818</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>76.5590909090909</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>11867818.18181818</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>78.75363636363636</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>27.70795454545455</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>182.8796717171717</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.123131313131313</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>79.07330808080808</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>19049530.3030303</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>80.58550505050505</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>27.49224657056499</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>181.7858682089437</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.282867356428738</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>74.67113306982871</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7114676.3543362</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>76.46118112066961</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>27.14383106272812</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>180.67535236822</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.79237479840421</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>75.05661096256685</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12050860.45327222</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>78.45969612087261</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>25.82231404958677</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>183.4669421487603</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.704958677685951</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>83.27685950413223</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>49561239.66942148</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>85.9190082644628</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>25.07777777777778</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>184.8666666666667</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75.03333333333333</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9026666.666666666</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>78.91111111111111</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>23.52577169207604</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>183.4635281385281</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.834693205345379</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>79.75342085450781</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>34153724.35535479</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>84.47515998494261</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>24.69311662307944</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>185.3841589026915</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.38368543641713</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>75.34458060913153</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10655320.22992263</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>79.61028236351748</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">howard p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>25.98311688311688</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>181.9097402597403</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.074675324675325</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>84.73116883116883</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>70366396.10389611</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>87.44220779220778</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>25.90090909090909</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>184.5872727272727</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>76.49818181818182</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>11559636.36363636</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>79.13272727272728</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>24.98150711466891</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>179.1066358084042</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.271020204420441</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>80.39890341338672</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>45332406.99712379</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>84.95100877498216</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>24.42081026988147</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>180.2584685867968</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.127291490758983</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>73.73430903461862</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>7935098.039215687</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>78.15122588110204</v>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>26.06363636363636</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.109090909090909</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>79.62727272727273</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>25281818.18181818</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>81.65454545454546</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>27.2147842056933</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>183.6492194674013</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.582552800734619</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>76.39632690541782</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10702883.37924702</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>78.87658402203856</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>23.50952847805789</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>182.7762523342671</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.655166900093371</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>74.04481442577031</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>14170772.55485528</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>79.59278011204484</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>25.33056567260531</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>185.5897276955781</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.348724751378204</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>73.07795393012785</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7191586.839471269</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>76.81826153386255</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="n">
+        <v>24.13535353535353</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>180.9333333333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.168686868686869</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>74.8959595959596</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8575858.585858585</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>79.17676767676768</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>23.12890442890443</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>182.9763791763791</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.716317016317016</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>78.11002331002331</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>21573115.77311577</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>83.49937839937841</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>23.56738563742535</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>182.3428433022256</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.234093310591126</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>74.12362130667147</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10299459.92056826</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>79.33317247387384</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>23.14204781860059</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>182.7126129663354</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.610052463011113</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>74.29806764026351</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>16792835.1544793</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>81.57543799889027</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC4"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">taylor a 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>40341</v>
+        <v>32384</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,145 +690,127 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>25.25925925925926</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>181.2592592592592</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.037037037037037</v>
+      </c>
+      <c r="S2" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6159259.25925926</v>
+      </c>
+      <c r="U2" t="n">
+        <v>77.1111111111111</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.36458333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>183.3506944444445</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>81.68055555555556</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>38175347.22222222</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>85.09027777777777</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>23.19426162073221</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>178.5965709127474</v>
+      </c>
       <c r="AD2" t="n">
-        <v>23.12890442890443</v>
+        <v>1.101809954751131</v>
       </c>
       <c r="AE2" t="n">
-        <v>182.9763791763791</v>
+        <v>68.45614516202751</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.716317016317016</v>
+        <v>3166165.901092372</v>
       </c>
       <c r="AG2" t="n">
-        <v>78.11002331002331</v>
+        <v>77.01542575071987</v>
       </c>
       <c r="AH2" t="n">
-        <v>21573115.77311577</v>
+        <v>24.98149038461538</v>
       </c>
       <c r="AI2" t="n">
-        <v>83.49937839937841</v>
+        <v>183.9794871794872</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25.3682277318641</v>
+        <v>1.947516025641026</v>
       </c>
       <c r="AK2" t="n">
-        <v>183.4219467401286</v>
+        <v>74.97435897435898</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.298898071625345</v>
+        <v>16337822.11538462</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.65785123966943</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14512791.55188246</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>80.25371900826445</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.14204781860059</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>182.7126129663354</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.610052463011113</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>74.29806764026351</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16792835.1544793</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>81.57543799889027</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>26.67299919759873</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>183.73218372017</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.156170647303371</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>73.82614804468351</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>8222519.108624658</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>76.80677154018116</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>thRJMAq0</t>
+        <v>80.27323717948718</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">smith l 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52305</v>
+        <v>31876</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -925,171 +837,129 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>27.5</v>
+        <v>26.05208333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>188</v>
+        <v>181.59375</v>
       </c>
       <c r="R3" t="n">
-        <v>1.833333333333333</v>
+        <v>1.520833333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>74.47569444444446</v>
       </c>
       <c r="T3" t="n">
-        <v>471</v>
+        <v>8721701.388888888</v>
       </c>
       <c r="U3" t="n">
-        <v>106000000</v>
+        <v>79.62847222222223</v>
       </c>
       <c r="V3" t="n">
-        <v>490</v>
+        <v>24.96590909090909</v>
       </c>
       <c r="W3" t="n">
-        <v>25.5</v>
+        <v>182.8238636363636</v>
       </c>
       <c r="X3" t="n">
-        <v>185.5</v>
+        <v>1.053977272727273</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>71.89318181818182</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>3983465.909090909</v>
       </c>
       <c r="AA3" t="n">
-        <v>158</v>
+        <v>76.35397727272726</v>
       </c>
       <c r="AB3" t="n">
-        <v>46000000</v>
+        <v>22.69502164502165</v>
       </c>
       <c r="AC3" t="n">
-        <v>162</v>
+        <v>177.2491341991342</v>
       </c>
       <c r="AD3" t="n">
-        <v>26.23140495867769</v>
+        <v>1.149891774891775</v>
       </c>
       <c r="AE3" t="n">
-        <v>185.4363636363636</v>
+        <v>71.71720779220779</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.552892561983471</v>
+        <v>8758425.324675325</v>
       </c>
       <c r="AG3" t="n">
-        <v>78.18347107438017</v>
+        <v>80.01883116883117</v>
       </c>
       <c r="AH3" t="n">
-        <v>20749917.3553719</v>
+        <v>24.9140551477508</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.06942148760331</v>
+        <v>181.3949981178242</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24.75333333333334</v>
+        <v>1.041125541125541</v>
       </c>
       <c r="AK3" t="n">
-        <v>184.86</v>
+        <v>69.71442687747036</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.056666666666667</v>
+        <v>2950868.741765481</v>
       </c>
       <c r="AM3" t="n">
-        <v>81.57555555555555</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>39335000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>85.06666666666668</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>26.24077808156756</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>181.7168717247664</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.425150945545682</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>75.04326441102756</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>14816280.33151059</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>78.94929368876737</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24.06449334119613</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>181.9445221509657</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.723609575409111</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>78.01840385276918</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>25973511.86636936</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>82.15245650891936</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
+        <v>73.89506869941653</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>75635</v>
+        <v>25486</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1116,122 +986,1117 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>24.96944444444444</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.9694444444444</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.283333333333333</v>
+      </c>
+      <c r="S4" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13922222.22222222</v>
+      </c>
+      <c r="U4" t="n">
+        <v>80.42500000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="W4" t="n">
+        <v>181.0055555555555</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.361111111111111</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>75.06944444444444</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8206041.666666666</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>78.19444444444444</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>26.75996810207337</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>183.3672248803828</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.120614035087719</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>74.50588118022328</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8398833.732057417</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>77.10127591706539</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>24.77283834586466</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>179.4229558270677</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.238345864661654</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>73.00493421052632</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>6444487.194548872</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>77.54767387218044</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10137500</v>
+      </c>
+      <c r="U5" t="n">
+        <v>78.325</v>
+      </c>
+      <c r="V5" t="n">
+        <v>26.93402777777778</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182.78125</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>79.30902777777779</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20634027.77777778</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>81.10416666666666</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>26.85074110671937</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>182.7040513833992</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.292638339920949</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>74.31768774703556</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7107435.770750988</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>76.59115612648222</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>27.29156454248366</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>180.766441993464</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.921772875816993</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>78.10610702614379</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>17066278.59477124</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80.46609477124183</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>396</v>
-      </c>
-      <c r="U4" t="n">
-        <v>120500000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>416</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>24.89098124098124</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>184.5326118326118</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.324891774891775</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>80.2215007215007</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>31611540.4040404</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>84.56854256854258</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>25.82231404958677</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>183.4669421487603</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.704958677685951</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>83.27685950413223</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>49561239.66942148</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>85.9190082644628</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>24.20568159842228</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>184.1880799324899</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.839028625791048</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>75.13089907849225</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>18049546.2708875</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>81.36734362083742</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>23.52577169207604</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>183.4635281385281</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.834693205345379</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>79.75342085450781</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>34153724.35535479</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>84.47515998494261</v>
-      </c>
-      <c r="BB4" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>26.06666666666667</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>184.3666666666667</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.966666666666667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>84.73333333333333</v>
+      </c>
+      <c r="T6" t="n">
+        <v>58093333.33333334</v>
+      </c>
+      <c r="U6" t="n">
+        <v>86.93333333333332</v>
+      </c>
+      <c r="V6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>75.10000000000001</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10156666.66666667</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.90434782608696</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>182.9152173913043</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.773188405797101</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>79.42173913043477</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>30832463.76811594</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>83.87463768115941</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24.57132675438597</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>185.515625</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.255098684210526</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>75.47615131578948</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>10463673.24561404</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>79.75290570175439</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>24.69545454545455</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>181.7272727272727</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.00909090909091</v>
+      </c>
+      <c r="S7" t="n">
+        <v>83.23636363636363</v>
+      </c>
+      <c r="T7" t="n">
+        <v>64966477.27272727</v>
+      </c>
+      <c r="U7" t="n">
+        <v>87.17272727272727</v>
+      </c>
+      <c r="V7" t="n">
+        <v>25.60606060606061</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03030303030303</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>76.36363636363636</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11172727.27272727</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>79.39393939393939</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25.7703216374269</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>181.7406432748538</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.230409356725146</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>80.25219298245614</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>42853523.39181287</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>84.50453216374268</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23.1577485380117</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>179.4644736842105</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.192836257309942</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>73.20014619883041</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>7812905.701754386</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>79.40233918128655</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>25.45454545454546</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.9393939393939</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.060606060606061</v>
+      </c>
+      <c r="S8" t="n">
+        <v>79.27272727272727</v>
+      </c>
+      <c r="T8" t="n">
+        <v>24518181.81818182</v>
+      </c>
+      <c r="U8" t="n">
+        <v>81.87878787878788</v>
+      </c>
+      <c r="V8" t="n">
+        <v>27.01111111111111</v>
+      </c>
+      <c r="W8" t="n">
+        <v>183.3376262626263</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.57020202020202</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>75.889898989899</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9621452.02020202</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>78.23333333333333</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23.37761069340017</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>180.7986633249791</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.408521303258146</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>74.95655806182121</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13185797.82790309</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>80.52380952380953</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>26.61760635198135</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>184.7941797785548</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.355222902097902</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>74.1416083916084</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>8217973.302738929</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>76.31439393939394</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>23.90972222222222</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>179.8229166666666</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.170138888888889</v>
+      </c>
+      <c r="S9" t="n">
+        <v>74.63888888888889</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8107986.111111111</v>
+      </c>
+      <c r="U9" t="n">
+        <v>79.36111111111111</v>
+      </c>
+      <c r="V9" t="n">
+        <v>21.93636363636364</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183.0272727272727</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.448484848484848</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>78.25454545454545</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>25074242.42424242</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>84.31212121212121</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>22.69975490196078</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>179.8102124183006</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>73.46609477124183</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>8212001.633986928</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>79.75931372549019</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23.18536324786325</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>180.0042735042735</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.484508547008547</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>78.60897435897436</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>27783279.91452992</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>83.44658119658119</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>24.37962962962963</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>184.4768518518518</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.00462962962963</v>
+      </c>
+      <c r="S10" t="n">
+        <v>80.91666666666667</v>
+      </c>
+      <c r="T10" t="n">
+        <v>38875462.96296296</v>
+      </c>
+      <c r="U10" t="n">
+        <v>84.96296296296296</v>
+      </c>
+      <c r="V10" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182.9166666666667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.458333333333333</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>65500000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>87.33333333333333</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.39838157485216</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>183.5846560846561</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.774976657329598</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>77.31543728602553</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>22319798.47494553</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>82.92888266417678</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24.0746336996337</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>177.1673534798535</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.946428571428571</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>79.2985347985348</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>35009157.50915751</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>84.32600732600731</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>26.58333333333333</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>182</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11279166.66666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>79.20833333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>26.225</v>
+      </c>
+      <c r="W11" t="n">
+        <v>186.725</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>24662500</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>27.55972652218782</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>179.2880546955624</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.444078947368421</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>76.02005933952529</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9835165.11867905</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>77.93008255933952</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25.82434210526316</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>181.5996710526316</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.471546052631579</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>77.16332236842106</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>20086266.44736842</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>80.3358552631579</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AO21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,22 +715,22 @@
         <v>77.1111111111111</v>
       </c>
       <c r="V2" t="n">
-        <v>25.36458333333333</v>
+        <v>24.84318181818182</v>
       </c>
       <c r="W2" t="n">
-        <v>183.3506944444445</v>
+        <v>182.9113636363636</v>
       </c>
       <c r="X2" t="n">
-        <v>2.666666666666667</v>
+        <v>2.465909090909091</v>
       </c>
       <c r="Y2" t="n">
-        <v>81.68055555555556</v>
+        <v>81.03863636363636</v>
       </c>
       <c r="Z2" t="n">
-        <v>38175347.22222222</v>
+        <v>35795454.54545455</v>
       </c>
       <c r="AA2" t="n">
-        <v>85.09027777777777</v>
+        <v>84.87727272727273</v>
       </c>
       <c r="AB2" t="n">
         <v>23.19426162073221</v>
@@ -751,22 +751,22 @@
         <v>77.01542575071987</v>
       </c>
       <c r="AH2" t="n">
-        <v>24.98149038461538</v>
+        <v>23.8953842940685</v>
       </c>
       <c r="AI2" t="n">
-        <v>183.9794871794872</v>
+        <v>184.3436507936508</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.947516025641026</v>
+        <v>1.860714285714286</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.97435897435898</v>
+        <v>76.19329573934837</v>
       </c>
       <c r="AL2" t="n">
-        <v>16337822.11538462</v>
+        <v>22326568.08688387</v>
       </c>
       <c r="AM2" t="n">
-        <v>80.27323717948718</v>
+        <v>82.12343358395989</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -864,22 +864,22 @@
         <v>79.62847222222223</v>
       </c>
       <c r="V3" t="n">
-        <v>24.96590909090909</v>
+        <v>24.88257575757576</v>
       </c>
       <c r="W3" t="n">
-        <v>182.8238636363636</v>
+        <v>182.9280303030303</v>
       </c>
       <c r="X3" t="n">
-        <v>1.053977272727273</v>
+        <v>1.05050505050505</v>
       </c>
       <c r="Y3" t="n">
-        <v>71.89318181818182</v>
+        <v>71.94873737373737</v>
       </c>
       <c r="Z3" t="n">
-        <v>3983465.909090909</v>
+        <v>4007424.242424242</v>
       </c>
       <c r="AA3" t="n">
-        <v>76.35397727272726</v>
+        <v>76.50328282828282</v>
       </c>
       <c r="AB3" t="n">
         <v>22.69502164502165</v>
@@ -891,31 +891,31 @@
         <v>1.149891774891775</v>
       </c>
       <c r="AE3" t="n">
-        <v>71.71720779220779</v>
+        <v>71.69339826839827</v>
       </c>
       <c r="AF3" t="n">
-        <v>8758425.324675325</v>
+        <v>8725091.991341993</v>
       </c>
       <c r="AG3" t="n">
-        <v>80.01883116883117</v>
+        <v>80.0069264069264</v>
       </c>
       <c r="AH3" t="n">
-        <v>24.9140551477508</v>
+        <v>24.78641456582633</v>
       </c>
       <c r="AI3" t="n">
-        <v>181.3949981178242</v>
+        <v>181.8721570149799</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.041125541125541</v>
+        <v>1.037480209475095</v>
       </c>
       <c r="AK3" t="n">
-        <v>69.71442687747036</v>
+        <v>69.88712930824504</v>
       </c>
       <c r="AL3" t="n">
-        <v>2950868.741765481</v>
+        <v>3021320.484715625</v>
       </c>
       <c r="AM3" t="n">
-        <v>73.89506869941653</v>
+        <v>74.20295563877724</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -995,76 +995,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>24.96944444444444</v>
+        <v>24.79545454545454</v>
       </c>
       <c r="Q4" t="n">
-        <v>182.9694444444444</v>
+        <v>183.2045454545455</v>
       </c>
       <c r="R4" t="n">
-        <v>1.283333333333333</v>
+        <v>1.318181818181818</v>
       </c>
       <c r="S4" t="n">
-        <v>76.7</v>
+        <v>76.63636363636364</v>
       </c>
       <c r="T4" t="n">
-        <v>13922222.22222222</v>
+        <v>14538636.36363637</v>
       </c>
       <c r="U4" t="n">
-        <v>80.42500000000001</v>
+        <v>80.56818181818181</v>
       </c>
       <c r="V4" t="n">
-        <v>25.95</v>
+        <v>25.71136363636364</v>
       </c>
       <c r="W4" t="n">
-        <v>181.0055555555555</v>
+        <v>181.5136363636364</v>
       </c>
       <c r="X4" t="n">
-        <v>1.361111111111111</v>
+        <v>1.340909090909091</v>
       </c>
       <c r="Y4" t="n">
-        <v>75.06944444444444</v>
+        <v>74.91818181818182</v>
       </c>
       <c r="Z4" t="n">
-        <v>8206041.666666666</v>
+        <v>8018068.181818182</v>
       </c>
       <c r="AA4" t="n">
-        <v>78.19444444444444</v>
+        <v>78.38863636363637</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.75996810207337</v>
+        <v>26.26111111111111</v>
       </c>
       <c r="AC4" t="n">
-        <v>183.3672248803828</v>
+        <v>183.7354166666667</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.120614035087719</v>
+        <v>1.169444444444445</v>
       </c>
       <c r="AE4" t="n">
-        <v>74.50588118022328</v>
+        <v>75.16180555555556</v>
       </c>
       <c r="AF4" t="n">
-        <v>8398833.732057417</v>
+        <v>10176041.66666667</v>
       </c>
       <c r="AG4" t="n">
-        <v>77.10127591706539</v>
+        <v>77.60138888888889</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.77283834586466</v>
+        <v>24.61379551820728</v>
       </c>
       <c r="AI4" t="n">
-        <v>179.4229558270677</v>
+        <v>179.8825280112045</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.238345864661654</v>
+        <v>1.227871148459384</v>
       </c>
       <c r="AK4" t="n">
-        <v>73.00493421052632</v>
+        <v>72.94754901960785</v>
       </c>
       <c r="AL4" t="n">
-        <v>6444487.194548872</v>
+        <v>6376066.176470588</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.54767387218044</v>
+        <v>77.71372549019608</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1140,76 +1140,76 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>25.875</v>
+        <v>25.72272727272727</v>
       </c>
       <c r="Q5" t="n">
-        <v>184.3</v>
+        <v>184.4090909090909</v>
       </c>
       <c r="R5" t="n">
-        <v>1.375</v>
+        <v>1.368181818181818</v>
       </c>
       <c r="S5" t="n">
-        <v>75.55</v>
+        <v>75.85909090909091</v>
       </c>
       <c r="T5" t="n">
-        <v>10137500</v>
+        <v>10437727.27272727</v>
       </c>
       <c r="U5" t="n">
-        <v>78.325</v>
+        <v>78.70227272727273</v>
       </c>
       <c r="V5" t="n">
-        <v>26.93402777777778</v>
+        <v>27.21111111111111</v>
       </c>
       <c r="W5" t="n">
-        <v>182.78125</v>
+        <v>183.5083333333334</v>
       </c>
       <c r="X5" t="n">
         <v>2.111111111111111</v>
       </c>
       <c r="Y5" t="n">
-        <v>79.30902777777779</v>
+        <v>79.87777777777778</v>
       </c>
       <c r="Z5" t="n">
-        <v>20634027.77777778</v>
+        <v>22700277.77777778</v>
       </c>
       <c r="AA5" t="n">
-        <v>81.10416666666666</v>
+        <v>81.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.85074110671937</v>
+        <v>26.650983436853</v>
       </c>
       <c r="AC5" t="n">
-        <v>182.7040513833992</v>
+        <v>182.9506858178054</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.292638339920949</v>
+        <v>1.282479296066252</v>
       </c>
       <c r="AE5" t="n">
-        <v>74.31768774703556</v>
+        <v>74.55512422360249</v>
       </c>
       <c r="AF5" t="n">
-        <v>7107435.770750988</v>
+        <v>7344196.428571428</v>
       </c>
       <c r="AG5" t="n">
-        <v>76.59115612648222</v>
+        <v>76.95736283643893</v>
       </c>
       <c r="AH5" t="n">
-        <v>27.29156454248366</v>
+        <v>27.39500926228615</v>
       </c>
       <c r="AI5" t="n">
-        <v>180.766441993464</v>
+        <v>182.7843521848098</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.921772875816993</v>
+        <v>1.947123242889833</v>
       </c>
       <c r="AK5" t="n">
-        <v>78.10610702614379</v>
+        <v>78.928135556282</v>
       </c>
       <c r="AL5" t="n">
-        <v>17066278.59477124</v>
+        <v>20268132.28723984</v>
       </c>
       <c r="AM5" t="n">
-        <v>80.46609477124183</v>
+        <v>81.20357960117686</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1285,76 +1285,76 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>26.06666666666667</v>
+        <v>26.06060606060606</v>
       </c>
       <c r="Q6" t="n">
-        <v>184.3666666666667</v>
+        <v>183.7878787878788</v>
       </c>
       <c r="R6" t="n">
-        <v>2.966666666666667</v>
+        <v>2.878787878787879</v>
       </c>
       <c r="S6" t="n">
-        <v>84.73333333333333</v>
+        <v>84.75757575757576</v>
       </c>
       <c r="T6" t="n">
-        <v>58093333.33333334</v>
+        <v>58675757.57575759</v>
       </c>
       <c r="U6" t="n">
-        <v>86.93333333333332</v>
+        <v>86.84848484848486</v>
       </c>
       <c r="V6" t="n">
-        <v>24.5</v>
+        <v>24.57670454545455</v>
       </c>
       <c r="W6" t="n">
-        <v>184.3333333333333</v>
+        <v>184.7897727272727</v>
       </c>
       <c r="X6" t="n">
-        <v>1.4</v>
+        <v>1.340909090909091</v>
       </c>
       <c r="Y6" t="n">
-        <v>75.10000000000001</v>
+        <v>74.98011363636364</v>
       </c>
       <c r="Z6" t="n">
-        <v>10156666.66666667</v>
+        <v>10449857.95454545</v>
       </c>
       <c r="AA6" t="n">
-        <v>79.5</v>
+        <v>79.71022727272728</v>
       </c>
       <c r="AB6" t="n">
-        <v>23.90434782608696</v>
+        <v>24</v>
       </c>
       <c r="AC6" t="n">
-        <v>182.9152173913043</v>
+        <v>182.6884920634921</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.773188405797101</v>
+        <v>1.783730158730159</v>
       </c>
       <c r="AE6" t="n">
-        <v>79.42173913043477</v>
+        <v>79.6765873015873</v>
       </c>
       <c r="AF6" t="n">
-        <v>30832463.76811594</v>
+        <v>32370833.33333333</v>
       </c>
       <c r="AG6" t="n">
-        <v>83.87463768115941</v>
+        <v>83.97222222222221</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.57132675438597</v>
+        <v>24.31830595874713</v>
       </c>
       <c r="AI6" t="n">
-        <v>185.515625</v>
+        <v>185.3001846193023</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.255098684210526</v>
+        <v>1.247202062643239</v>
       </c>
       <c r="AK6" t="n">
-        <v>75.47615131578948</v>
+        <v>74.84695696460403</v>
       </c>
       <c r="AL6" t="n">
-        <v>10463673.24561404</v>
+        <v>10330978.64145659</v>
       </c>
       <c r="AM6" t="n">
-        <v>79.75290570175439</v>
+        <v>79.76860516934046</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1430,76 +1430,76 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>24.69545454545455</v>
+        <v>24.40909090909091</v>
       </c>
       <c r="Q7" t="n">
-        <v>181.7272727272727</v>
+        <v>181.4772727272727</v>
       </c>
       <c r="R7" t="n">
-        <v>3.00909090909091</v>
+        <v>2.909090909090909</v>
       </c>
       <c r="S7" t="n">
-        <v>83.23636363636363</v>
+        <v>83.02272727272727</v>
       </c>
       <c r="T7" t="n">
-        <v>64966477.27272727</v>
+        <v>63800568.18181818</v>
       </c>
       <c r="U7" t="n">
-        <v>87.17272727272727</v>
+        <v>87.18181818181819</v>
       </c>
       <c r="V7" t="n">
-        <v>25.60606060606061</v>
+        <v>24.95454545454546</v>
       </c>
       <c r="W7" t="n">
-        <v>185.3333333333333</v>
+        <v>184.1875</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03030303030303</v>
+        <v>1.085227272727273</v>
       </c>
       <c r="Y7" t="n">
-        <v>76.36363636363636</v>
+        <v>75.42897727272727</v>
       </c>
       <c r="Z7" t="n">
-        <v>11172727.27272727</v>
+        <v>10106889.20454546</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.39393939393939</v>
+        <v>79.60795454545453</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.7703216374269</v>
+        <v>25.7551842871536</v>
       </c>
       <c r="AC7" t="n">
-        <v>181.7406432748538</v>
+        <v>181.0629477087278</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.230409356725146</v>
+        <v>2.177262209231518</v>
       </c>
       <c r="AE7" t="n">
-        <v>80.25219298245614</v>
+        <v>80.52884711196731</v>
       </c>
       <c r="AF7" t="n">
-        <v>42853523.39181287</v>
+        <v>42603616.83606249</v>
       </c>
       <c r="AG7" t="n">
-        <v>84.50453216374268</v>
+        <v>84.7572602163395</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.1577485380117</v>
+        <v>23.04906798245614</v>
       </c>
       <c r="AI7" t="n">
-        <v>179.4644736842105</v>
+        <v>180.3450292397661</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.192836257309942</v>
+        <v>1.18311403508772</v>
       </c>
       <c r="AK7" t="n">
-        <v>73.20014619883041</v>
+        <v>73.19910453216374</v>
       </c>
       <c r="AL7" t="n">
-        <v>7812905.701754386</v>
+        <v>7783417.854532164</v>
       </c>
       <c r="AM7" t="n">
-        <v>79.40233918128655</v>
+        <v>79.52247807017544</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1593,22 +1593,22 @@
         <v>81.87878787878788</v>
       </c>
       <c r="V8" t="n">
-        <v>27.01111111111111</v>
+        <v>26.79772727272727</v>
       </c>
       <c r="W8" t="n">
-        <v>183.3376262626263</v>
+        <v>183.0681818181818</v>
       </c>
       <c r="X8" t="n">
-        <v>1.57020202020202</v>
+        <v>1.559090909090909</v>
       </c>
       <c r="Y8" t="n">
-        <v>75.889898989899</v>
+        <v>75.91818181818182</v>
       </c>
       <c r="Z8" t="n">
-        <v>9621452.02020202</v>
+        <v>9742840.90909091</v>
       </c>
       <c r="AA8" t="n">
-        <v>78.23333333333333</v>
+        <v>78.41818181818181</v>
       </c>
       <c r="AB8" t="n">
         <v>23.37761069340017</v>
@@ -1629,22 +1629,22 @@
         <v>80.52380952380953</v>
       </c>
       <c r="AH8" t="n">
-        <v>26.61760635198135</v>
+        <v>25.98089492207139</v>
       </c>
       <c r="AI8" t="n">
-        <v>184.7941797785548</v>
+        <v>183.8242835595777</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.355222902097902</v>
+        <v>1.381724484665661</v>
       </c>
       <c r="AK8" t="n">
-        <v>74.1416083916084</v>
+        <v>74.5475113122172</v>
       </c>
       <c r="AL8" t="n">
-        <v>8217973.302738929</v>
+        <v>8914170.123177476</v>
       </c>
       <c r="AM8" t="n">
-        <v>76.31439393939394</v>
+        <v>77.36060834590246</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1724,28 +1724,28 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23.90972222222222</v>
+        <v>22.66666666666666</v>
       </c>
       <c r="Q9" t="n">
-        <v>179.8229166666666</v>
+        <v>179.5833333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>1.170138888888889</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S9" t="n">
-        <v>74.63888888888889</v>
+        <v>73.94444444444446</v>
       </c>
       <c r="T9" t="n">
-        <v>8107986.111111111</v>
+        <v>8144444.444444444</v>
       </c>
       <c r="U9" t="n">
-        <v>79.36111111111111</v>
+        <v>79.94444444444444</v>
       </c>
       <c r="V9" t="n">
         <v>21.93636363636364</v>
       </c>
       <c r="W9" t="n">
-        <v>183.0272727272727</v>
+        <v>183.2212121212121</v>
       </c>
       <c r="X9" t="n">
         <v>1.448484848484848</v>
@@ -1760,40 +1760,40 @@
         <v>84.31212121212121</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.69975490196078</v>
+        <v>22.29256292906179</v>
       </c>
       <c r="AC9" t="n">
-        <v>179.8102124183006</v>
+        <v>180.1728260869565</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.016666666666667</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="AE9" t="n">
-        <v>73.46609477124183</v>
+        <v>73.21661899313501</v>
       </c>
       <c r="AF9" t="n">
-        <v>8212001.633986928</v>
+        <v>8000214.530892448</v>
       </c>
       <c r="AG9" t="n">
-        <v>79.75931372549019</v>
+        <v>80.23655606407323</v>
       </c>
       <c r="AH9" t="n">
-        <v>23.18536324786325</v>
+        <v>22.57983193277311</v>
       </c>
       <c r="AI9" t="n">
-        <v>180.0042735042735</v>
+        <v>181.1422735760971</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.484508547008547</v>
+        <v>1.587359943977591</v>
       </c>
       <c r="AK9" t="n">
-        <v>78.60897435897436</v>
+        <v>77.390406162465</v>
       </c>
       <c r="AL9" t="n">
-        <v>27783279.91452992</v>
+        <v>25981051.58730159</v>
       </c>
       <c r="AM9" t="n">
-        <v>83.44658119658119</v>
+        <v>83.45868347338934</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>24.37962962962963</v>
+        <v>24.575</v>
       </c>
       <c r="Q10" t="n">
-        <v>184.4768518518518</v>
+        <v>183.1592592592593</v>
       </c>
       <c r="R10" t="n">
-        <v>2.00462962962963</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="S10" t="n">
-        <v>80.91666666666667</v>
+        <v>81.35462962962963</v>
       </c>
       <c r="T10" t="n">
-        <v>38875462.96296296</v>
+        <v>40602129.62962963</v>
       </c>
       <c r="U10" t="n">
-        <v>84.96296296296296</v>
+        <v>85.11666666666666</v>
       </c>
       <c r="V10" t="n">
         <v>23.66666666666667</v>
@@ -1909,40 +1909,40 @@
         <v>87.33333333333333</v>
       </c>
       <c r="AB10" t="n">
-        <v>23.39838157485216</v>
+        <v>23.71329365079365</v>
       </c>
       <c r="AC10" t="n">
-        <v>183.5846560846561</v>
+        <v>183.250992063492</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.774976657329598</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="n">
-        <v>77.31543728602553</v>
+        <v>77.37996031746032</v>
       </c>
       <c r="AF10" t="n">
-        <v>22319798.47494553</v>
+        <v>22958268.84920635</v>
       </c>
       <c r="AG10" t="n">
-        <v>82.92888266417678</v>
+        <v>82.95575396825397</v>
       </c>
       <c r="AH10" t="n">
-        <v>24.0746336996337</v>
+        <v>23.66544117647058</v>
       </c>
       <c r="AI10" t="n">
-        <v>177.1673534798535</v>
+        <v>178.6899509803922</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.946428571428571</v>
+        <v>1.81985294117647</v>
       </c>
       <c r="AK10" t="n">
-        <v>79.2985347985348</v>
+        <v>78.88357843137256</v>
       </c>
       <c r="AL10" t="n">
-        <v>35009157.50915751</v>
+        <v>32374540.44117647</v>
       </c>
       <c r="AM10" t="n">
-        <v>84.32600732600731</v>
+        <v>84.42647058823529</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -2018,28 +2018,28 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>26.58333333333333</v>
+        <v>25.98472222222222</v>
       </c>
       <c r="Q11" t="n">
-        <v>182</v>
+        <v>183.1881944444444</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.395833333333333</v>
       </c>
       <c r="S11" t="n">
-        <v>76.33333333333333</v>
+        <v>75.74097222222221</v>
       </c>
       <c r="T11" t="n">
-        <v>11279166.66666667</v>
+        <v>10505347.22222222</v>
       </c>
       <c r="U11" t="n">
-        <v>79.20833333333333</v>
+        <v>79.33611111111111</v>
       </c>
       <c r="V11" t="n">
         <v>26.225</v>
       </c>
       <c r="W11" t="n">
-        <v>186.725</v>
+        <v>186.8</v>
       </c>
       <c r="X11" t="n">
         <v>1.65</v>
@@ -2054,28 +2054,28 @@
         <v>81.59999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>27.55972652218782</v>
+        <v>27.35402840623429</v>
       </c>
       <c r="AC11" t="n">
-        <v>179.2880546955624</v>
+        <v>179.9018979386626</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.444078947368421</v>
+        <v>1.426156359979889</v>
       </c>
       <c r="AE11" t="n">
-        <v>76.02005933952529</v>
+        <v>75.97630718954248</v>
       </c>
       <c r="AF11" t="n">
-        <v>9835165.11867905</v>
+        <v>9908183.132227249</v>
       </c>
       <c r="AG11" t="n">
-        <v>77.93008255933952</v>
+        <v>78.12029914529916</v>
       </c>
       <c r="AH11" t="n">
         <v>25.82434210526316</v>
       </c>
       <c r="AI11" t="n">
-        <v>181.5996710526316</v>
+        <v>181.9243421052632</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.471546052631579</v>
@@ -2097,6 +2097,1472 @@
       <c r="AO11" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>27.21111111111111</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>183.5083333333334</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.111111111111111</v>
+      </c>
+      <c r="S12" t="n">
+        <v>79.87777777777778</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22700277.77777778</v>
+      </c>
+      <c r="U12" t="n">
+        <v>81.55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>21.93636363636364</v>
+      </c>
+      <c r="W12" t="n">
+        <v>183.2212121212121</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.448484848484848</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>78.25454545454545</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>25074242.42424242</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>84.31212121212121</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>27.39500926228615</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>182.7843521848098</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.947123242889833</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>78.928135556282</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20268132.28723984</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>81.20357960117686</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22.57983193277311</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>181.1422735760971</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.587359943977591</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>77.390406162465</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>25981051.58730159</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>83.45868347338934</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>25.45454545454546</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>183.9393939393939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.060606060606061</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79.27272727272727</v>
+      </c>
+      <c r="T13" t="n">
+        <v>24518181.81818182</v>
+      </c>
+      <c r="U13" t="n">
+        <v>81.87878787878788</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25.98472222222222</v>
+      </c>
+      <c r="W13" t="n">
+        <v>183.1881944444444</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.395833333333333</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>75.74097222222221</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10505347.22222222</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>79.33611111111111</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>23.37761069340017</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>180.7986633249791</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.408521303258146</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>74.95655806182121</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13185797.82790309</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>80.52380952380953</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>27.35402840623429</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>179.9018979386626</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.426156359979889</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>75.97630718954248</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>9908183.132227249</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>78.12029914529916</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>25.72272727272727</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>184.4090909090909</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.368181818181818</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.85909090909091</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10437727.27272727</v>
+      </c>
+      <c r="U14" t="n">
+        <v>78.70227272727273</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.225</v>
+      </c>
+      <c r="W14" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>24662500</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>26.650983436853</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>182.9506858178054</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.282479296066252</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>74.55512422360249</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7344196.428571428</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>76.95736283643893</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25.82434210526316</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>181.9243421052632</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.471546052631579</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>77.16332236842106</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>20086266.44736842</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>80.3358552631579</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>25.71136363636364</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>181.5136363636364</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.340909090909091</v>
+      </c>
+      <c r="S15" t="n">
+        <v>74.91818181818182</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8018068.181818182</v>
+      </c>
+      <c r="U15" t="n">
+        <v>78.38863636363637</v>
+      </c>
+      <c r="V15" t="n">
+        <v>26.79772727272727</v>
+      </c>
+      <c r="W15" t="n">
+        <v>183.0681818181818</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.559090909090909</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>75.91818181818182</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9742840.90909091</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>78.41818181818181</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24.61379551820728</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>179.8825280112045</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.227871148459384</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>72.94754901960785</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>6376066.176470588</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>77.71372549019608</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25.98089492207139</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>183.8242835595777</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.381724484665661</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>74.5475113122172</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>8914170.123177476</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>77.36060834590246</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>26.06060606060606</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>183.7878787878788</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.878787878787879</v>
+      </c>
+      <c r="S16" t="n">
+        <v>84.75757575757576</v>
+      </c>
+      <c r="T16" t="n">
+        <v>58675757.57575759</v>
+      </c>
+      <c r="U16" t="n">
+        <v>86.84848484848486</v>
+      </c>
+      <c r="V16" t="n">
+        <v>22.66666666666666</v>
+      </c>
+      <c r="W16" t="n">
+        <v>179.5833333333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>73.94444444444446</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8144444.444444444</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>79.94444444444444</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>182.6884920634921</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.783730158730159</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>79.6765873015873</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>32370833.33333333</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>83.97222222222221</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22.29256292906179</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180.1728260869565</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.013157894736842</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>73.21661899313501</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>8000214.530892448</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80.23655606407323</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>25.25925925925926</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>181.2592592592592</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.037037037037037</v>
+      </c>
+      <c r="S17" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6159259.25925926</v>
+      </c>
+      <c r="U17" t="n">
+        <v>77.1111111111111</v>
+      </c>
+      <c r="V17" t="n">
+        <v>24.88257575757576</v>
+      </c>
+      <c r="W17" t="n">
+        <v>182.9280303030303</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05050505050505</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>71.94873737373737</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4007424.242424242</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>76.50328282828282</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.19426162073221</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>178.5965709127474</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.101809954751131</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>68.45614516202751</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3166165.901092372</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>77.01542575071987</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24.78641456582633</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>181.8721570149799</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.037480209475095</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>69.88712930824504</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3021320.484715625</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>74.20295563877724</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>24.575</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>183.1592592592593</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.083333333333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>81.35462962962963</v>
+      </c>
+      <c r="T18" t="n">
+        <v>40602129.62962963</v>
+      </c>
+      <c r="U18" t="n">
+        <v>85.11666666666666</v>
+      </c>
+      <c r="V18" t="n">
+        <v>24.95454545454546</v>
+      </c>
+      <c r="W18" t="n">
+        <v>184.1875</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.085227272727273</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>75.42897727272727</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10106889.20454546</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>79.60795454545453</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23.71329365079365</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.250992063492</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>77.37996031746032</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>22958268.84920635</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>82.95575396825397</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23.04906798245614</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>180.3450292397661</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.18311403508772</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>73.19910453216374</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>7783417.854532164</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>79.52247807017544</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>24.79545454545454</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>183.2045454545455</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="S19" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="T19" t="n">
+        <v>14538636.36363637</v>
+      </c>
+      <c r="U19" t="n">
+        <v>80.56818181818181</v>
+      </c>
+      <c r="V19" t="n">
+        <v>24.84318181818182</v>
+      </c>
+      <c r="W19" t="n">
+        <v>182.9113636363636</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.465909090909091</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>81.03863636363636</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>35795454.54545455</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>84.87727272727273</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>26.26111111111111</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>183.7354166666667</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.169444444444445</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>75.16180555555556</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10176041.66666667</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>77.60138888888889</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23.8953842940685</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>184.3436507936508</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.860714285714286</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>76.19329573934837</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>22326568.08688387</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>82.12343358395989</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>26.05208333333333</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>181.59375</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.520833333333333</v>
+      </c>
+      <c r="S20" t="n">
+        <v>74.47569444444446</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8721701.388888888</v>
+      </c>
+      <c r="U20" t="n">
+        <v>79.62847222222223</v>
+      </c>
+      <c r="V20" t="n">
+        <v>24.57670454545455</v>
+      </c>
+      <c r="W20" t="n">
+        <v>184.7897727272727</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.340909090909091</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>74.98011363636364</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10449857.95454545</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>79.71022727272728</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22.69502164502165</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>177.2491341991342</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.149891774891775</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>71.69339826839827</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8725091.991341993</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>80.0069264069264</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>24.31830595874713</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>185.3001846193023</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.247202062643239</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>74.84695696460403</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>10330978.64145659</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>79.76860516934046</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>24.40909090909091</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>181.4772727272727</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.909090909090909</v>
+      </c>
+      <c r="S21" t="n">
+        <v>83.02272727272727</v>
+      </c>
+      <c r="T21" t="n">
+        <v>63800568.18181818</v>
+      </c>
+      <c r="U21" t="n">
+        <v>87.18181818181819</v>
+      </c>
+      <c r="V21" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="W21" t="n">
+        <v>182.9166666666667</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.458333333333333</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>65500000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>87.33333333333333</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>25.7551842871536</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>181.0629477087278</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.177262209231518</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>80.52884711196731</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>42603616.83606249</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>84.7572602163395</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23.66544117647058</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>178.6899509803922</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.81985294117647</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>78.88357843137256</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>32374540.44117647</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>84.42647058823529</v>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:AO21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45556.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">barrott s 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
+          <t xml:space="preserve">london stadium
   london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62850</v>
+        <v>62500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -762,147 +692,105 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>27.14666666666667</v>
       </c>
       <c r="Q2" t="n">
-        <v>184</v>
+        <v>183.8733333333333</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>79.90222222222222</v>
       </c>
       <c r="T2" t="n">
-        <v>81</v>
+        <v>22726888.88888889</v>
       </c>
       <c r="U2" t="n">
-        <v>32500000</v>
+        <v>81.57333333333334</v>
       </c>
       <c r="V2" t="n">
-        <v>83</v>
+        <v>22.09116161616161</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>183.554797979798</v>
       </c>
       <c r="X2" t="n">
-        <v>183</v>
+        <v>1.419696969696969</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>78.21868686868686</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>24236237.37373737</v>
       </c>
       <c r="AA2" t="n">
-        <v>416</v>
+        <v>84.06742424242424</v>
       </c>
       <c r="AB2" t="n">
-        <v>289500000</v>
+        <v>27.40691650073801</v>
       </c>
       <c r="AC2" t="n">
-        <v>428</v>
+        <v>182.2274817478479</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.575</v>
+        <v>1.912244048857321</v>
       </c>
       <c r="AE2" t="n">
-        <v>183.1592592592593</v>
+        <v>78.83341753593469</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.083333333333333</v>
+        <v>19876324.01161005</v>
       </c>
       <c r="AG2" t="n">
-        <v>81.35462962962963</v>
+        <v>81.05377277185057</v>
       </c>
       <c r="AH2" t="n">
-        <v>40602129.62962963</v>
+        <v>22.68487394957983</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.11666666666666</v>
+        <v>181.8942051820728</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23.66666666666667</v>
+        <v>1.690519957983193</v>
       </c>
       <c r="AK2" t="n">
-        <v>182.9166666666667</v>
+        <v>77.59280462184874</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.458333333333333</v>
+        <v>26974538.69047619</v>
       </c>
       <c r="AM2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>65500000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>87.33333333333333</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.71329365079365</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183.250992063492</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>77.37996031746032</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>22958268.84920635</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>82.95575396825397</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>23.66544117647058</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>178.6899509803922</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.81985294117647</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>78.88357843137256</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>32374540.44117647</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>84.42647058823529</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
+        <v>83.59401260504202</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,173 +800,2769 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I3" t="n">
+        <v>481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>25.29545454545455</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>183.9545454545454</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>78.95454545454547</v>
+      </c>
+      <c r="T3" t="n">
+        <v>23909090.90909091</v>
+      </c>
+      <c r="U3" t="n">
+        <v>81.86363636363636</v>
+      </c>
+      <c r="V3" t="n">
+        <v>26.05444444444445</v>
+      </c>
+      <c r="W3" t="n">
+        <v>183.3727777777778</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>75.90388888888887</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10833166.66666667</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>79.44666666666666</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>23.44625149831099</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>180.5989974937344</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.415086629617522</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>74.69567941593112</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12625761.41440558</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>80.22981366459628</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>27.39091503267974</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>180.1522875816993</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.402463549522373</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>76.08873805932629</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>10077315.73655103</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>78.14239316239316</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25.91818181818181</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>184.3472727272727</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.414545454545455</v>
+      </c>
+      <c r="S4" t="n">
+        <v>76.12727272727273</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10862181.81818182</v>
+      </c>
+      <c r="U4" t="n">
+        <v>78.76181818181819</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="W4" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24506000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>26.5457867494824</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>183.0938819875776</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.259316770186335</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>74.56909937888199</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7314523.809523809</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>77.06589026915114</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25.94368421052632</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>182.15</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.556184210526316</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>77.84644736842105</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>22692171.05263158</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80.72131578947366</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>181.6472727272727</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.345454545454545</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75.02545454545455</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8143545.454545455</v>
+      </c>
+      <c r="U5" t="n">
+        <v>78.5109090909091</v>
+      </c>
+      <c r="V5" t="n">
+        <v>26.91090909090909</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182.8363636363636</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.556363636363636</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>75.93454545454546</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9649272.727272728</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>78.38909090909091</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>24.9637636872931</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>179.6878405907817</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25502419149478</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>73.08531194295901</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>6447671.122994652</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>77.35279857397504</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25.60289775583893</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>184.0321541203894</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.378106860459801</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>74.4834635952283</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>9044972.462178344</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>77.58848667672198</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.886363636363636</v>
+      </c>
+      <c r="S6" t="n">
+        <v>84.84090909090909</v>
+      </c>
+      <c r="T6" t="n">
+        <v>58995454.54545455</v>
+      </c>
+      <c r="U6" t="n">
+        <v>86.88636363636364</v>
+      </c>
+      <c r="V6" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="W6" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.088888888888889</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>74.11111111111111</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8137777.777777778</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>79.71111111111111</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.01041666666667</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>182.9851190476191</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.775297619047619</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>79.69494047619048</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>32088541.66666667</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>83.89583333333334</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22.51024081943991</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>180.50016563147</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.039097744360902</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>73.65900948022229</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>9047790.672333006</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80.37972104173477</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>25.25925925925926</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>181.2592592592592</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.037037037037037</v>
+      </c>
+      <c r="S7" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6159259.25925926</v>
+      </c>
+      <c r="U7" t="n">
+        <v>77.1111111111111</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.81515151515152</v>
+      </c>
+      <c r="W7" t="n">
+        <v>182.7242424242424</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.058585858585859</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>72.08626262626262</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4167757.575757576</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>76.76626262626262</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>23.8917729329494</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>178.9045294574706</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.13599341834636</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>69.37400703871292</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3463159.99360117</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>76.78506787330318</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25.05913165266107</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>181.4577256119839</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.029984167580076</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>70.25970344659603</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3038056.3877725</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>74.2523645110218</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>24.63125</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.3694444444445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.0625</v>
+      </c>
+      <c r="S8" t="n">
+        <v>81.49097222222221</v>
+      </c>
+      <c r="T8" t="n">
+        <v>40739097.22222222</v>
+      </c>
+      <c r="U8" t="n">
+        <v>85.1125</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24.96363636363636</v>
+      </c>
+      <c r="W8" t="n">
+        <v>184.4409090909091</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.086363636363636</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>75.57954545454545</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>10340056.81818182</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>79.70454545454545</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23.68080357142857</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.1674107142857</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>76.9516369047619</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>21611930.80357143</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>82.63348214285715</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22.97675438596491</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>180.4135233918128</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.171491228070176</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>72.95928362573099</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>7531421.783625731</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>79.49298245614035</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>24.75636363636364</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>183.0236363636364</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.334545454545455</v>
+      </c>
+      <c r="S9" t="n">
+        <v>76.66909090909091</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14712909.09090909</v>
+      </c>
+      <c r="U9" t="n">
+        <v>80.75454545454545</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24.74727272727273</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183.0563636363636</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.427272727272727</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>80.97636363636363</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>35809090.90909091</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>84.90181818181819</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>26.45888888888889</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>183.5083333333333</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.175555555555556</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>75.33944444444444</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10365833.33333333</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>77.5211111111111</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>24.32741854636591</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>184.1749206349206</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.910793650793651</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>76.78796992481203</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>23444587.80284043</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>82.33208020050125</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>25.64166666666666</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181.855</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.516666666666667</v>
+      </c>
+      <c r="S10" t="n">
+        <v>74.30055555555555</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9024361.11111111</v>
+      </c>
+      <c r="U10" t="n">
+        <v>79.86277777777778</v>
+      </c>
+      <c r="V10" t="n">
+        <v>24.825</v>
+      </c>
+      <c r="W10" t="n">
+        <v>184.5590909090909</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.327272727272728</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>75.18409090909091</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10598068.18181818</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>79.62272727272727</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>22.58101731601732</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>178.0243073593074</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.13241341991342</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>72.11721861471861</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>8768823.593073593</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>80.34304112554112</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24.12523300229183</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>184.6754418130889</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.23305576776165</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>74.84227145403615</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>10129488.79551821</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>79.83841354723708</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>24.92727272727273</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>181.6181818181818</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.890909090909091</v>
+      </c>
+      <c r="S11" t="n">
+        <v>83.3090909090909</v>
+      </c>
+      <c r="T11" t="n">
+        <v>62995000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>87.09090909090909</v>
+      </c>
+      <c r="V11" t="n">
+        <v>23.90625</v>
+      </c>
+      <c r="W11" t="n">
+        <v>182.59375</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>83.71875</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>61468750</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>87.03125</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>25.48986171543716</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>180.8789295955536</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.227524053099501</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>80.94688721338339</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>45059083.94504046</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>85.07247483973826</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23.46336659663865</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>177.8031775210084</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.882746848739496</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>78.16268382352942</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>31979566.04516806</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>84.39128151260505</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S12" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="T12" t="n">
+        <v>24506000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="V12" t="n">
+        <v>24.92727272727273</v>
+      </c>
+      <c r="W12" t="n">
+        <v>181.6181818181818</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.890909090909091</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>83.3090909090909</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>62995000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>87.09090909090909</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>25.94368421052632</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>182.15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.556184210526316</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>77.84644736842105</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>22692171.05263158</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>80.72131578947366</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25.48986171543716</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>180.8789295955536</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.227524053099501</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>80.94688721338339</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>45059083.94504046</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85.07247483973826</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>23.90625</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>182.59375</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="S13" t="n">
+        <v>83.71875</v>
+      </c>
+      <c r="T13" t="n">
+        <v>61468750</v>
+      </c>
+      <c r="U13" t="n">
+        <v>87.03125</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="W13" t="n">
+        <v>181.6472727272727</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.345454545454545</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>75.02545454545455</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8143545.454545455</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>78.5109090909091</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>23.46336659663865</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>177.8031775210084</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.882746848739496</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>78.16268382352942</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>31979566.04516806</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>84.39128151260505</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24.9637636872931</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>179.6878405907817</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25502419149478</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>73.08531194295901</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>6447671.122994652</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>77.35279857397504</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>24.96363636363636</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>184.4409090909091</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.086363636363636</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.57954545454545</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10340056.81818182</v>
+      </c>
+      <c r="U14" t="n">
+        <v>79.70454545454545</v>
+      </c>
+      <c r="V14" t="n">
+        <v>27.14666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>183.8733333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.133333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>79.90222222222222</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>22726888.88888889</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>81.57333333333334</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>22.97675438596491</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>180.4135233918128</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.171491228070176</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>72.95928362573099</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>7531421.783625731</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>79.49298245614035</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>27.40691650073801</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>182.2274817478479</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.912244048857321</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>78.83341753593469</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>19876324.01161005</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>81.05377277185057</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>22.09116161616161</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>183.554797979798</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.419696969696969</v>
+      </c>
+      <c r="S15" t="n">
+        <v>78.21868686868686</v>
+      </c>
+      <c r="T15" t="n">
+        <v>24236237.37373737</v>
+      </c>
+      <c r="U15" t="n">
+        <v>84.06742424242424</v>
+      </c>
+      <c r="V15" t="n">
+        <v>25.64166666666666</v>
+      </c>
+      <c r="W15" t="n">
+        <v>181.855</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.516666666666667</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>74.30055555555555</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9024361.11111111</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>79.86277777777778</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22.68487394957983</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>181.8942051820728</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.690519957983193</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>77.59280462184874</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>26974538.69047619</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>83.59401260504202</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22.58101731601732</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>178.0243073593074</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.13241341991342</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>72.11721861471861</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>8768823.593073593</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80.34304112554112</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>26.91090909090909</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>182.8363636363636</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.556363636363636</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75.93454545454546</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9649272.727272728</v>
+      </c>
+      <c r="U16" t="n">
+        <v>78.38909090909091</v>
+      </c>
+      <c r="V16" t="n">
+        <v>24.75636363636364</v>
+      </c>
+      <c r="W16" t="n">
+        <v>183.0236363636364</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.334545454545455</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>76.66909090909091</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14712909.09090909</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>80.75454545454545</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.60289775583893</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>184.0321541203894</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.378106860459801</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>74.4834635952283</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9044972.462178344</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>77.58848667672198</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26.45888888888889</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>183.5083333333333</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.175555555555556</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>75.33944444444444</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10365833.33333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>77.5211111111111</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>24.825</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>184.5590909090909</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.327272727272728</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75.18409090909091</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10598068.18181818</v>
+      </c>
+      <c r="U17" t="n">
+        <v>79.62272727272727</v>
+      </c>
+      <c r="V17" t="n">
+        <v>25.91818181818181</v>
+      </c>
+      <c r="W17" t="n">
+        <v>184.3472727272727</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.414545454545455</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>76.12727272727273</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10862181.81818182</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>78.76181818181819</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>24.12523300229183</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>184.6754418130889</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.23305576776165</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>74.84227145403615</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>10129488.79551821</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>79.83841354723708</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>26.5457867494824</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>183.0938819875776</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.259316770186335</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>74.56909937888199</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>7314523.809523809</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>77.06589026915114</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t xml:space="preserve">molineux stadium
   wolverhampton </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E18" t="n">
         <v>31750</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>j3Azpf5d</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>48</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I18" t="n">
         <v>481</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K18" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>200</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>26.05444444444445</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>183.3727777777778</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>75.90388888888887</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10833166.66666667</v>
+      </c>
+      <c r="U18" t="n">
+        <v>79.44666666666666</v>
+      </c>
+      <c r="V18" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="W18" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.886363636363636</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>84.84090909090909</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>58995454.54545455</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>86.88636363636364</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>27.39091503267974</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>180.1522875816993</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.402463549522373</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>76.08873805932629</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10077315.73655103</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>78.14239316239316</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24.01041666666667</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>182.9851190476191</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.775297619047619</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>79.69494047619048</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32088541.66666667</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>83.89583333333334</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>24.81515151515152</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>182.7242424242424</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.058585858585859</v>
+      </c>
+      <c r="S19" t="n">
+        <v>72.08626262626262</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4167757.575757576</v>
+      </c>
+      <c r="U19" t="n">
+        <v>76.76626262626262</v>
+      </c>
+      <c r="V19" t="n">
+        <v>25.29545454545455</v>
+      </c>
+      <c r="W19" t="n">
+        <v>183.9545454545454</v>
+      </c>
+      <c r="X19" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>79</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>82600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>330</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>25.98472222222222</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>183.1881944444444</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.395833333333333</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>75.74097222222221</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>10505347.22222222</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>79.33611111111111</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>26.225</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>186.8</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24662500</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>27.35402840623429</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>179.9018979386626</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.426156359979889</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>75.97630718954248</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9908183.132227249</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>78.12029914529916</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>25.82434210526316</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>181.9243421052632</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.471546052631579</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>77.16332236842106</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20086266.44736842</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>80.3358552631579</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
+      <c r="Y19" t="n">
+        <v>78.95454545454547</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>23909090.90909091</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>81.86363636363636</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.05913165266107</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>181.4577256119839</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.029984167580076</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70.25970344659603</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3038056.3877725</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>74.2523645110218</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23.44625149831099</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>180.5989974937344</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.415086629617522</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>74.69567941593112</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>12625761.41440558</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>80.22981366459628</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>24.74727272727273</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>183.0563636363636</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.427272727272727</v>
+      </c>
+      <c r="S20" t="n">
+        <v>80.97636363636363</v>
+      </c>
+      <c r="T20" t="n">
+        <v>35809090.90909091</v>
+      </c>
+      <c r="U20" t="n">
+        <v>84.90181818181819</v>
+      </c>
+      <c r="V20" t="n">
+        <v>24.63125</v>
+      </c>
+      <c r="W20" t="n">
+        <v>183.3694444444445</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.0625</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>81.49097222222221</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40739097.22222222</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>85.1125</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>24.32741854636591</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>184.1749206349206</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.910793650793651</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>76.78796992481203</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>23444587.80284043</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>82.33208020050125</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23.68080357142857</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>183.1674107142857</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>76.9516369047619</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>21611930.80357143</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>82.63348214285715</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.088888888888889</v>
+      </c>
+      <c r="S21" t="n">
+        <v>74.11111111111111</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8137777.777777778</v>
+      </c>
+      <c r="U21" t="n">
+        <v>79.71111111111111</v>
+      </c>
+      <c r="V21" t="n">
+        <v>25.25925925925926</v>
+      </c>
+      <c r="W21" t="n">
+        <v>181.2592592592592</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.037037037037037</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>73.55555555555556</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6159259.25925926</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>77.1111111111111</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>22.51024081943991</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>180.50016563147</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.039097744360902</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>73.65900948022229</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9047790.672333006</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>80.37972104173477</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23.8917729329494</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>178.9045294574706</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.13599341834636</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>69.37400703871292</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3463159.99360117</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>76.78506787330318</v>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,90 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +597,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>8MkyzwoT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45563.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">oliver m 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62850</v>
+        <v>52305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -762,323 +652,2397 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>26.31666666666666</v>
       </c>
       <c r="Q2" t="n">
-        <v>184</v>
+        <v>186.9</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>79.51666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>100333.3333333333</v>
       </c>
       <c r="T2" t="n">
-        <v>81</v>
+        <v>25.07272727272727</v>
       </c>
       <c r="U2" t="n">
-        <v>32500000</v>
+        <v>181.7984848484848</v>
       </c>
       <c r="V2" t="n">
-        <v>83</v>
+        <v>83.57424242424243</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>170109.0909090909</v>
       </c>
       <c r="X2" t="n">
-        <v>183</v>
+        <v>25.80601135190919</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>181.9877450980392</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>77.76419633642932</v>
       </c>
       <c r="AA2" t="n">
-        <v>416</v>
+        <v>89365.00902992777</v>
       </c>
       <c r="AB2" t="n">
-        <v>289500000</v>
+        <v>25.6248847628643</v>
       </c>
       <c r="AC2" t="n">
-        <v>428</v>
+        <v>180.607441329628</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.575</v>
+        <v>80.99740601115282</v>
       </c>
       <c r="AE2" t="n">
-        <v>183.1592592592593</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.083333333333333</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>81.35462962962963</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>40602129.62962963</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>85.11666666666666</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>182.9166666666667</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.458333333333333</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>65500000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>87.33333333333333</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.71329365079365</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183.250992063492</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>77.37996031746032</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>22958268.84920635</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>82.95575396825397</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>23.66544117647058</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>178.6899509803922</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.81985294117647</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>78.88357843137256</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>32374540.44117647</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>84.42647058823529</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
+        <v>138278.048017626</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45563.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I3" t="n">
+        <v>481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>23.81388888888889</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>182.6972222222222</v>
+      </c>
+      <c r="R3" t="n">
+        <v>83.48611111111111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>120025</v>
+      </c>
+      <c r="T3" t="n">
+        <v>25.68333333333333</v>
+      </c>
+      <c r="U3" t="n">
+        <v>181.8560606060606</v>
+      </c>
+      <c r="V3" t="n">
+        <v>75.07121212121211</v>
+      </c>
+      <c r="W3" t="n">
+        <v>34592.42424242424</v>
+      </c>
+      <c r="X3" t="n">
+        <v>23.22069327731092</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>177.9675420168067</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>77.55514705882354</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>92270.69327731093</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25.00826461120579</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>179.5090979282156</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>73.12237533708122</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32209.84260837202</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>24.54545454545454</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>184.1292207792208</v>
+      </c>
+      <c r="R4" t="n">
+        <v>74.92348484848485</v>
+      </c>
+      <c r="S4" t="n">
+        <v>44039.01515151516</v>
+      </c>
+      <c r="T4" t="n">
+        <v>26.82592592592593</v>
+      </c>
+      <c r="U4" t="n">
+        <v>183.7833333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>79.93703703703704</v>
+      </c>
+      <c r="W4" t="n">
+        <v>65753.70370370371</v>
+      </c>
+      <c r="X4" t="n">
+        <v>22.70608506560519</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>181.0057379969532</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>72.13058074106836</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>38889.43713450292</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>27.67243041728167</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>182.1895681232065</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>78.76118127994557</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>58303.85829527706</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>22.17292929292929</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>183.9438383838384</v>
+      </c>
+      <c r="R5" t="n">
+        <v>78.27494949494948</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75618.78787878787</v>
+      </c>
+      <c r="T5" t="n">
+        <v>25.02110389610389</v>
+      </c>
+      <c r="U5" t="n">
+        <v>181.9296176046176</v>
+      </c>
+      <c r="V5" t="n">
+        <v>74.34310966810968</v>
+      </c>
+      <c r="W5" t="n">
+        <v>48349.38672438672</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22.80007307270735</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>181.9066684934843</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>77.98728717573987</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>74545.05084642553</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>22.67803757866783</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>178.7955136600095</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>72.54759312816036</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>39433.00956746335</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26.64776334776335</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.4487734487735</v>
+      </c>
+      <c r="R6" t="n">
+        <v>75.82193362193361</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34588.16738816739</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24.66883116883117</v>
+      </c>
+      <c r="U6" t="n">
+        <v>183.2597402597403</v>
+      </c>
+      <c r="V6" t="n">
+        <v>76.8922077922078</v>
+      </c>
+      <c r="W6" t="n">
+        <v>36323.37662337662</v>
+      </c>
+      <c r="X6" t="n">
+        <v>25.79511011863953</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>183.8013555072378</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>74.20980000391765</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>31470.48702931056</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>26.78650793650794</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>183.3948412698413</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>75.2186507936508</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34371.03174603174</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>24.87083333333333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>183.9674242424242</v>
+      </c>
+      <c r="R7" t="n">
+        <v>75.0003787878788</v>
+      </c>
+      <c r="S7" t="n">
+        <v>48160</v>
+      </c>
+      <c r="T7" t="n">
+        <v>25.95064935064935</v>
+      </c>
+      <c r="U7" t="n">
+        <v>184.3272727272727</v>
+      </c>
+      <c r="V7" t="n">
+        <v>75.98961038961038</v>
+      </c>
+      <c r="W7" t="n">
+        <v>60589.61038961039</v>
+      </c>
+      <c r="X7" t="n">
+        <v>24.04539786408982</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>184.0889558641107</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>74.49594858544162</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>46235.29411764706</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>26.40864467068292</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>183.2832239760893</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>74.80405594732171</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>59344.6072479335</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
   wolverhampton </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E8" t="n">
         <v>31750</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>j3Azpf5d</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>26.10092592592592</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.4958333333333</v>
+      </c>
+      <c r="R8" t="n">
+        <v>76.01249999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>47188.8888888889</v>
+      </c>
+      <c r="T8" t="n">
+        <v>25.96363636363636</v>
+      </c>
+      <c r="U8" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="V8" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>153272.7272727272</v>
+      </c>
+      <c r="X8" t="n">
+        <v>27.10601073762839</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>181.1373482726424</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>76.21874147094734</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>52129.27440206852</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23.91944444444444</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.1214285714286</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>79.6781746031746</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>100026.5873015873</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>24.70959595959596</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>182.739898989899</v>
+      </c>
+      <c r="R9" t="n">
+        <v>72.11734006734007</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22952.69360269361</v>
+      </c>
+      <c r="T9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>184.0181818181818</v>
+      </c>
+      <c r="V9" t="n">
+        <v>79.07272727272728</v>
+      </c>
+      <c r="W9" t="n">
+        <v>76054.54545454546</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25.1511282290694</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>181.5203268988754</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>70.45716027957077</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>18751.76220246552</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>23.4961316334314</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>180.427024081944</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>74.73045657622316</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>52209.56739675275</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>24.75779220779221</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>183.088961038961</v>
+      </c>
+      <c r="R10" t="n">
+        <v>80.37110389610389</v>
+      </c>
+      <c r="S10" t="n">
+        <v>103041.8831168831</v>
+      </c>
+      <c r="T10" t="n">
+        <v>24.665</v>
+      </c>
+      <c r="U10" t="n">
+        <v>183.4955555555556</v>
+      </c>
+      <c r="V10" t="n">
+        <v>81.57277777777779</v>
+      </c>
+      <c r="W10" t="n">
+        <v>94067.22222222222</v>
+      </c>
+      <c r="X10" t="n">
+        <v>24.31544388922617</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>184.2313615301193</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>77.69327044318872</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>78638.27477596684</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.8546626984127</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>182.9250992063492</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>77.59871031746032</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>65042.75793650794</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>179.6481481481481</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74.0925925925926</v>
+      </c>
+      <c r="S11" t="n">
+        <v>32611.11111111111</v>
+      </c>
+      <c r="T11" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="U11" t="n">
+        <v>180.7555555555555</v>
+      </c>
+      <c r="V11" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="W11" t="n">
+        <v>38533.33333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22.60853401619992</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>180.3334713595583</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>73.87417456685192</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>32644.93752497185</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.18585284684356</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>179.210002244058</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>69.83105765923104</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>27324.17032571831</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>24.66883116883117</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>183.2597402597403</v>
+      </c>
+      <c r="R12" t="n">
+        <v>76.8922077922078</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36323.37662337662</v>
+      </c>
+      <c r="T12" t="n">
+        <v>25.96363636363636</v>
+      </c>
+      <c r="U12" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="V12" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>153272.7272727272</v>
+      </c>
+      <c r="X12" t="n">
+        <v>26.78650793650794</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>183.3948412698413</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>75.2186507936508</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>34371.03174603174</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>23.91944444444444</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>183.1214285714286</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>79.6781746031746</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>100026.5873015873</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>23.81388888888889</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>182.6972222222222</v>
+      </c>
+      <c r="R13" t="n">
+        <v>83.48611111111111</v>
+      </c>
+      <c r="S13" t="n">
+        <v>120025</v>
+      </c>
+      <c r="T13" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="U13" t="n">
+        <v>180.7555555555555</v>
+      </c>
+      <c r="V13" t="n">
+        <v>73.33333333333334</v>
+      </c>
+      <c r="W13" t="n">
+        <v>38533.33333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>23.22069327731092</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>177.9675420168067</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77.55514705882354</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>92270.69327731093</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>24.18585284684356</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>179.210002244058</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>69.83105765923104</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27324.17032571831</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>24.54545454545454</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>184.1292207792208</v>
+      </c>
+      <c r="R14" t="n">
+        <v>74.92348484848485</v>
+      </c>
+      <c r="S14" t="n">
+        <v>44039.01515151516</v>
+      </c>
+      <c r="T14" t="n">
+        <v>26.10092592592592</v>
+      </c>
+      <c r="U14" t="n">
+        <v>183.4958333333333</v>
+      </c>
+      <c r="V14" t="n">
+        <v>76.01249999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>47188.8888888889</v>
+      </c>
+      <c r="X14" t="n">
+        <v>22.70608506560519</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>181.0057379969532</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>72.13058074106836</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>38889.43713450292</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>27.10601073762839</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.1373482726424</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>76.21874147094734</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>52129.27440206852</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>25.68333333333333</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>181.8560606060606</v>
+      </c>
+      <c r="R15" t="n">
+        <v>75.07121212121211</v>
+      </c>
+      <c r="S15" t="n">
+        <v>34592.42424242424</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>179.6481481481481</v>
+      </c>
+      <c r="V15" t="n">
+        <v>74.0925925925926</v>
+      </c>
+      <c r="W15" t="n">
+        <v>32611.11111111111</v>
+      </c>
+      <c r="X15" t="n">
+        <v>25.00826461120579</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>179.5090979282156</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>73.12237533708122</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>32209.84260837202</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22.60853401619992</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>180.3334713595583</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>73.87417456685192</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>32644.93752497185</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>25.07272727272727</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>181.7984848484848</v>
+      </c>
+      <c r="R16" t="n">
+        <v>83.57424242424243</v>
+      </c>
+      <c r="S16" t="n">
+        <v>170109.0909090909</v>
+      </c>
+      <c r="T16" t="n">
+        <v>25.95064935064935</v>
+      </c>
+      <c r="U16" t="n">
+        <v>184.3272727272727</v>
+      </c>
+      <c r="V16" t="n">
+        <v>75.98961038961038</v>
+      </c>
+      <c r="W16" t="n">
+        <v>60589.61038961039</v>
+      </c>
+      <c r="X16" t="n">
+        <v>25.6248847628643</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>180.607441329628</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80.99740601115282</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>138278.048017626</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>26.40864467068292</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>183.2832239760893</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>74.80405594732171</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>59344.6072479335</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>26.82592592592593</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>183.7833333333333</v>
+      </c>
+      <c r="R17" t="n">
+        <v>79.93703703703704</v>
+      </c>
+      <c r="S17" t="n">
+        <v>65753.70370370371</v>
+      </c>
+      <c r="T17" t="n">
+        <v>24.70959595959596</v>
+      </c>
+      <c r="U17" t="n">
+        <v>182.739898989899</v>
+      </c>
+      <c r="V17" t="n">
+        <v>72.11734006734007</v>
+      </c>
+      <c r="W17" t="n">
+        <v>22952.69360269361</v>
+      </c>
+      <c r="X17" t="n">
+        <v>27.67243041728167</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>182.1895681232065</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>78.76118127994557</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>58303.85829527706</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.1511282290694</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>181.5203268988754</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>70.45716027957077</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>18751.76220246552</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>p6ahwuwJ</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H18" t="n">
         <v>48</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I18" t="n">
         <v>481</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K18" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>200</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>79</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>82600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>330</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>25.98472222222222</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>183.1881944444444</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.395833333333333</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>75.74097222222221</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>10505347.22222222</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>79.33611111111111</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>26.225</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>186.8</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24662500</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>27.35402840623429</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>179.9018979386626</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.426156359979889</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>75.97630718954248</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9908183.132227249</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>78.12029914529916</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>25.82434210526316</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>181.9243421052632</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.471546052631579</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>77.16332236842106</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20086266.44736842</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>80.3358552631579</v>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="P18" t="n">
+        <v>26.64776334776335</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>183.4487734487735</v>
+      </c>
+      <c r="R18" t="n">
+        <v>75.82193362193361</v>
+      </c>
+      <c r="S18" t="n">
+        <v>34588.16738816739</v>
+      </c>
+      <c r="T18" t="n">
+        <v>26.31666666666666</v>
+      </c>
+      <c r="U18" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>79.51666666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>100333.3333333333</v>
+      </c>
+      <c r="X18" t="n">
+        <v>25.79511011863953</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>183.8013555072378</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>74.20980000391765</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>31470.48702931056</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25.80601135190919</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>181.9877450980392</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>77.76419633642932</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>89365.00902992777</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>184.0181818181818</v>
+      </c>
+      <c r="R19" t="n">
+        <v>79.07272727272728</v>
+      </c>
+      <c r="S19" t="n">
+        <v>76054.54545454546</v>
+      </c>
+      <c r="T19" t="n">
+        <v>24.75779220779221</v>
+      </c>
+      <c r="U19" t="n">
+        <v>183.088961038961</v>
+      </c>
+      <c r="V19" t="n">
+        <v>80.37110389610389</v>
+      </c>
+      <c r="W19" t="n">
+        <v>103041.8831168831</v>
+      </c>
+      <c r="X19" t="n">
+        <v>23.4961316334314</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>180.427024081944</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>74.73045657622316</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>52209.56739675275</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>24.31544388922617</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>184.2313615301193</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>77.69327044318872</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>78638.27477596684</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>22.17292929292929</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>183.9438383838384</v>
+      </c>
+      <c r="R20" t="n">
+        <v>78.27494949494948</v>
+      </c>
+      <c r="S20" t="n">
+        <v>75618.78787878787</v>
+      </c>
+      <c r="T20" t="n">
+        <v>24.87083333333333</v>
+      </c>
+      <c r="U20" t="n">
+        <v>183.9674242424242</v>
+      </c>
+      <c r="V20" t="n">
+        <v>75.0003787878788</v>
+      </c>
+      <c r="W20" t="n">
+        <v>48160</v>
+      </c>
+      <c r="X20" t="n">
+        <v>22.80007307270735</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>181.9066684934843</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>77.98728717573987</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>74545.05084642553</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>24.04539786408982</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>184.0889558641107</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>74.49594858544162</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>46235.29411764706</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>25.02110389610389</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>181.9296176046176</v>
+      </c>
+      <c r="R21" t="n">
+        <v>74.34310966810968</v>
+      </c>
+      <c r="S21" t="n">
+        <v>48349.38672438672</v>
+      </c>
+      <c r="T21" t="n">
+        <v>24.665</v>
+      </c>
+      <c r="U21" t="n">
+        <v>183.4955555555556</v>
+      </c>
+      <c r="V21" t="n">
+        <v>81.57277777777779</v>
+      </c>
+      <c r="W21" t="n">
+        <v>94067.22222222222</v>
+      </c>
+      <c r="X21" t="n">
+        <v>22.67803757866783</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>178.7955136600095</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>72.54759312816036</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>39433.00956746335</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>23.8546626984127</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>182.9250992063492</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>77.59871031746032</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>65042.75793650794</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS4"/>
+  <dimension ref="A1:BG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,110 +545,180 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -657,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29673</v>
+        <v>25486</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -710,139 +780,181 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>185.6666666666667</v>
+      </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="R2" t="n">
-        <v>68</v>
+        <v>178000</v>
       </c>
       <c r="S2" t="n">
-        <v>8000</v>
+        <v>36600000</v>
       </c>
       <c r="T2" t="n">
+        <v>237</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>21</v>
+      </c>
+      <c r="W2" t="n">
+        <v>168</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>68</v>
-      </c>
-      <c r="V2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>184.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>77.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>67250</v>
+        <v>78</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>61000</v>
       </c>
       <c r="AA2" t="n">
-        <v>310</v>
+        <v>31500000</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.70959595959596</v>
+        <v>86</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.739898989899</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>72.11734006734007</v>
+        <v>25.75381944444444</v>
       </c>
       <c r="AE2" t="n">
-        <v>22952.69360269361</v>
+        <v>182.6965277777778</v>
       </c>
       <c r="AF2" t="n">
-        <v>24.85185185185185</v>
+        <v>78.61423611111111</v>
       </c>
       <c r="AG2" t="n">
-        <v>183.6447811447811</v>
+        <v>71965.625</v>
       </c>
       <c r="AH2" t="n">
-        <v>77.83838383838385</v>
+        <v>19627222.22222222</v>
       </c>
       <c r="AI2" t="n">
-        <v>69730.63973063973</v>
+        <v>80.89027777777778</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25.1511282290694</v>
+        <v>1.461111111111111</v>
       </c>
       <c r="AK2" t="n">
-        <v>181.5203268988754</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="AL2" t="n">
-        <v>70.45716027957077</v>
+        <v>183.953823953824</v>
       </c>
       <c r="AM2" t="n">
-        <v>18751.76220246552</v>
+        <v>83.89177489177489</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.14955413897061</v>
+        <v>130431.4574314574</v>
       </c>
       <c r="AO2" t="n">
-        <v>180.2030756238422</v>
+        <v>50323232.32323233</v>
       </c>
       <c r="AP2" t="n">
-        <v>74.23371381351932</v>
+        <v>85.75180375180376</v>
       </c>
       <c r="AQ2" t="n">
-        <v>51063.52838618285</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
+        <v>3.152958152958153</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>27.63765284423179</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>183.1793859649123</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>74.73575890483787</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>60975.27246145667</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8595778.841041999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>76.67124534821903</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.049900318979266</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>25.3921768707483</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>183.0777210884354</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>80.40323129251701</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>100304.4217687075</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>33583265.30612245</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>83.53639455782313</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2.251700680272109</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
+        <v>45570.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75635</v>
+        <v>60704</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -867,143 +979,181 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
+      <c r="N3" t="n">
+        <v>26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>180.25</v>
       </c>
       <c r="P3" t="n">
-        <v>23.75</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.75</v>
+        <v>325</v>
       </c>
       <c r="R3" t="n">
-        <v>78.5</v>
+        <v>540000</v>
       </c>
       <c r="S3" t="n">
-        <v>74750</v>
+        <v>173500000</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
       <c r="U3" t="n">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>22</v>
       </c>
       <c r="W3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="X3" t="n">
-        <v>74.5</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>53000</v>
+        <v>73</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="AA3" t="n">
-        <v>149</v>
+        <v>6000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.75779220779221</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="n">
-        <v>183.088961038961</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>80.37110389610389</v>
+        <v>25.33531746031746</v>
       </c>
       <c r="AE3" t="n">
-        <v>103041.8831168831</v>
+        <v>182.1785714285714</v>
       </c>
       <c r="AF3" t="n">
-        <v>24.665</v>
+        <v>83.0515873015873</v>
       </c>
       <c r="AG3" t="n">
-        <v>183.4955555555556</v>
+        <v>146543.6507936508</v>
       </c>
       <c r="AH3" t="n">
-        <v>81.57277777777779</v>
+        <v>54386904.76190477</v>
       </c>
       <c r="AI3" t="n">
-        <v>94067.22222222222</v>
+        <v>85.46031746031746</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24.31544388922617</v>
+        <v>3.23015873015873</v>
       </c>
       <c r="AK3" t="n">
-        <v>184.2313615301193</v>
+        <v>26.40674603174603</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.69327044318872</v>
+        <v>182.1130952380952</v>
       </c>
       <c r="AM3" t="n">
-        <v>78638.27477596684</v>
+        <v>73.15277777777779</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.8546626984127</v>
+        <v>45869.04761904762</v>
       </c>
       <c r="AO3" t="n">
-        <v>182.9250992063492</v>
+        <v>5892013.888888889</v>
       </c>
       <c r="AP3" t="n">
-        <v>77.59871031746032</v>
+        <v>76.67460317460316</v>
       </c>
       <c r="AQ3" t="n">
-        <v>65042.75793650794</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
+        <v>1.259920634920635</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>24.79567634746206</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>178.1746991104134</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>78.24327577184719</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>112402.2828362114</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>30383464.15489272</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>83.333836996337</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.476713762428048</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>25.47593599640813</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>179.8102399492493</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>70.71053123003588</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>38853.40850455014</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4025374.507458486</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>76.33917740541193</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.167205781834265</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11307</v>
+        <v>17250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1028,104 +1178,2509 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>309</v>
+      </c>
+      <c r="R4" t="n">
+        <v>258000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>316</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>190.3333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>218</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>134000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>237</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>25.44318181818182</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>184.0744949494949</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>75.38484848484848</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>54902.08333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>10249472.85353535</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>79.72304292929293</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.168150252525253</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>26.68492063492064</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>182.397619047619</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>76.54801587301587</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>54272.22222222223</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>12557896.82539682</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>79.83809523809524</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.46984126984127</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>23.56556756474519</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>180.9617285401003</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>71.85814405806181</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>45641.54788011696</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6886870.724989558</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>79.00405049081036</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.068496762740184</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>28.00596033868093</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>180.4273804218657</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>76.07570558526442</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>56804.65686274509</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10740675.87641117</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>78.13409462269757</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.4125</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>286</v>
+      </c>
+      <c r="R5" t="n">
+        <v>146000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14200000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>298</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>175</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26.93333333333333</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>180.9798611111111</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75.44409722222221</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>43109.02777777778</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>7562387.152777778</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>77.74756944444445</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.360416666666667</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>25.44285714285714</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>181.0511904761904</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>76.13769841269841</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49315.07936507936</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>10966865.07936508</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>79.40793650793651</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.167063492063492</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>26.47716526303504</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>179.6526543841221</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>73.70876847449506</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>42954.93014091602</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6014938.193753378</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>76.79983383704359</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.252401223647354</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>24.7809305540398</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>179.9449416130089</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>74.77733517649484</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>47156.59597172202</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9298689.778941879</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>78.8115124837814</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.082930141753671</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>246</v>
+      </c>
+      <c r="R6" t="n">
+        <v>529000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>260</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>29</v>
+      </c>
+      <c r="W6" t="n">
+        <v>190</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26.04469696969697</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>181.2727272727273</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>83.20555555555556</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>177010.101010101</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>55797095.95959596</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>85.92853535353535</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.19040404040404</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>184.175</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>76.4375</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>66312.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10467500</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>78.2625</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>26.07475750674764</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>179.3288512748217</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>80.31076579670329</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>142673.3633964719</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>41148530.08422498</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>83.71727937632542</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.641327778581068</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>26.97010869565217</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>182.753759057971</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>74.3578804347826</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>61377.35507246377</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7008337.86231884</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>77.05534420289854</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.273460144927536</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>28.14756944444444</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>182.390625</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>79.49479166666666</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>85770.83333333334</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>20322916.66666667</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80.69270833333334</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.284722222222222</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>25.68701298701299</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>183.124025974026</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>73.84512987012987</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43035.3896103896</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>5780292.207792208</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>77.57207792207792</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.058116883116883</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>28.81985294117647</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>180.3890931372549</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>77.9077308006536</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>78874.84681372548</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15848703.02287582</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>79.49004289215686</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.008629493464052</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>26.55414727294427</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>180.5419739825755</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>71.7640947607113</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>41464.0947607113</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3772724.072084974</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>74.53668098818476</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.033178183554123</v>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>218</v>
+      </c>
+      <c r="R8" t="n">
+        <v>130000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>236</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W8" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>314</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>380000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>118100000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>28.05858585858586</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>182.8516594516595</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>76.38773448773449</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>46759.01875901876</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>10666139.97113997</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>78.61818181818182</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.498268398268398</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>27.52443181818182</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>186.7772727272727</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>79.98352272727273</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>106817.0454545454</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>25616413.35227273</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>81.55767045454546</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2.363920454545454</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>27.11946451220348</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>182.9012729305009</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>74.18372672058334</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>41318.20189614307</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6534525.32700143</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>76.77744519573564</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.2352469528021</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>26.89380775635613</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>182.9420432556994</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>77.84096787339337</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>92867.13839243831</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>19723577.06442326</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>80.43166660803078</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.973145933014354</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>186</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>399</v>
+      </c>
+      <c r="R9" t="n">
+        <v>493000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>411</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24</v>
+      </c>
+      <c r="W9" t="n">
+        <v>169</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>63000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>25.93506493506494</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>183.8932178932179</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>79.36940836940838</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>103298.7012987013</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>25453463.2034632</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>82.12409812409813</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.284271284271284</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>26.23084415584416</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>182.6840909090909</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>80.48636363636363</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>101362.6623376623</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>30662540.58441558</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>83.50714285714285</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.545779220779221</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>24.13308291904238</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>181.4488610713684</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>76.40209324836653</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>82789.53630547288</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>18099144.72445937</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>81.17515450115972</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.521969095522544</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>26.32937461843712</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>183.6718998015873</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>77.24677960927961</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>82713.63514957264</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>21095885.79822955</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>81.21642246642247</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.001869658119658</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>180</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>128</v>
+      </c>
+      <c r="R10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>146</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>191</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>23.21875901875902</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>183.4974025974026</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>80.01673881673881</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>99678.21067821069</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>32337445.88744589</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>84.46320346320347</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.850505050505051</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26.58703703703704</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>183.3685185185185</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>76.96666666666665</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>55833.33333333334</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>11843518.51851852</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>79.03148148148149</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.344444444444444</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>23.99510080562712</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>180.9560457086773</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>79.08522237995922</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>103841.9536603747</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>27486265.57652873</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>83.5558719058719</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.819314311419574</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>25.68565592903828</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>183.809126984127</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>75.87718253968254</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>53924.07796451914</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>9607820.961718019</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>78.30089869281046</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.225070028011205</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>182</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>151</v>
+      </c>
+      <c r="R11" t="n">
+        <v>111000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>156</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>183</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>241</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>363000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>253</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25.9354797979798</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>182.9472222222222</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>75.41275252525253</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>64851.64141414141</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>11516161.61616162</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>80.1094696969697</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.561489898989899</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>25.46851851851852</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>184.2777777777778</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>82.24814814814815</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>112359.2592592593</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>40063888.88888889</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>84.8351851851852</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.742592592592592</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>23.57733087514182</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>179.6616853835356</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>73.28050304790108</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>56944.89740976482</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9963628.600753803</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>80.43357594754148</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.305141049554833</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>24.40666765540715</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>184.0791940086058</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>77.98462890983899</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>77757.29611191795</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22756552.10335883</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>82.43920038878022</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.883233479872136</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>25.46851851851852</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>184.2777777777778</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>82.24814814814815</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>112359.2592592593</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>40063888.88888889</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>84.8351851851852</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.742592592592592</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>28.14756944444444</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>182.390625</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>79.49479166666666</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>85770.83333333334</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>20322916.66666667</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>80.69270833333334</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.284722222222222</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>24.40666765540715</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>184.0791940086058</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>77.98462890983899</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>77757.29611191795</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>22756552.10335883</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>82.43920038878022</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.883233479872136</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>28.81985294117647</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>180.3890931372549</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>77.9077308006536</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>78874.84681372548</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>15848703.02287582</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>79.49004289215686</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.008629493464052</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>184.175</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>76.4375</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>66312.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>10467500</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>78.2625</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>25.93506493506494</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>183.8932178932179</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>79.36940836940838</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>103298.7012987013</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>25453463.2034632</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>82.12409812409813</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.284271284271284</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>26.97010869565217</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>182.753759057971</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>74.3578804347826</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>61377.35507246377</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7008337.86231884</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>77.05534420289854</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.273460144927536</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>24.13308291904238</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>181.4488610713684</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>76.40209324836653</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>82789.53630547288</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18099144.72445937</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>81.17515450115972</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.521969095522544</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>25.68701298701299</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>183.124025974026</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>73.84512987012987</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>43035.3896103896</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5780292.207792208</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>77.57207792207792</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.058116883116883</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>28.05858585858586</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>182.8516594516595</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>76.38773448773449</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>46759.01875901876</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>10666139.97113997</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>78.61818181818182</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.498268398268398</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>26.55414727294427</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>180.5419739825755</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>71.7640947607113</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>41464.0947607113</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3772724.072084974</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>74.53668098818476</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.033178183554123</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>27.11946451220348</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>182.9012729305009</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>74.18372672058334</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>41318.20189614307</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6534525.32700143</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>76.77744519573564</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.2352469528021</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>26.23084415584416</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>182.6840909090909</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>80.48636363636363</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>101362.6623376623</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>30662540.58441558</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>83.50714285714285</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.545779220779221</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25.44318181818182</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>184.0744949494949</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75.38484848484848</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>54902.08333333333</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>10249472.85353535</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>79.72304292929293</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.168150252525253</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>26.32937461843712</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>183.6718998015873</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>77.24677960927961</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>82713.63514957264</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>21095885.79822955</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>81.21642246642247</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.001869658119658</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>23.56556756474519</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>180.9617285401003</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>71.85814405806181</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>45641.54788011696</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6886870.724989558</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>79.00405049081036</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.068496762740184</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>27.52443181818182</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>186.7772727272727</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>79.98352272727273</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>106817.0454545454</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>25616413.35227273</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>81.55767045454546</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.363920454545454</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25.9354797979798</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>182.9472222222222</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75.41275252525253</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>64851.64141414141</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>11516161.61616162</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>80.1094696969697</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.561489898989899</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>26.89380775635613</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>182.9420432556994</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>77.84096787339337</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>92867.13839243831</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>19723577.06442326</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>80.43166660803078</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.973145933014354</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>23.57733087514182</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>179.6616853835356</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>73.28050304790108</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>56944.89740976482</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>9963628.600753803</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>80.43357594754148</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.305141049554833</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>WdKOwxDM</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>175</v>
-      </c>
-      <c r="R4" t="n">
-        <v>77</v>
-      </c>
-      <c r="S4" t="n">
-        <v>37000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>21</v>
-      </c>
-      <c r="W4" t="n">
-        <v>189</v>
-      </c>
-      <c r="X4" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>22.83333333333333</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>179.6481481481481</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>74.0925925925926</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>32611.11111111111</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>25.77777777777778</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>180.7555555555555</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>73.33333333333334</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>38533.33333333333</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>22.60853401619992</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>180.3334713595583</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>73.87417456685192</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>32644.93752497185</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24.18585284684356</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>179.210002244058</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>69.83105765923104</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>27324.17032571831</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>26.40674603174603</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>182.1130952380952</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>73.15277777777779</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>45869.04761904762</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>5892013.888888889</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>76.67460317460316</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.259920634920635</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>26.93333333333333</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>180.9798611111111</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>75.44409722222221</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>43109.02777777778</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>7562387.152777778</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>77.74756944444445</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.360416666666667</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>25.47593599640813</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>179.8102399492493</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>70.71053123003588</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>38853.40850455014</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4025374.507458486</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>76.33917740541193</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.167205781834265</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>26.47716526303504</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>179.6526543841221</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>73.70876847449506</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>42954.93014091602</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6014938.193753378</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>76.79983383704359</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.252401223647354</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG17"/>
+  <dimension ref="A1:BG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45570.35416666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25486</v>
+        <v>42789</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>185.6666666666667</v>
+        <v>178</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="R2" t="n">
-        <v>178000</v>
+        <v>130000</v>
       </c>
       <c r="S2" t="n">
-        <v>36600000</v>
+        <v>29500000</v>
       </c>
       <c r="T2" t="n">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>26.5</v>
       </c>
       <c r="W2" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="Z2" t="n">
-        <v>61000</v>
+        <v>253000</v>
       </c>
       <c r="AA2" t="n">
-        <v>31500000</v>
+        <v>88000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.75381944444444</v>
+        <v>25.93506493506494</v>
       </c>
       <c r="AE2" t="n">
-        <v>182.6965277777778</v>
+        <v>183.8932178932179</v>
       </c>
       <c r="AF2" t="n">
-        <v>78.61423611111111</v>
+        <v>79.36940836940838</v>
       </c>
       <c r="AG2" t="n">
-        <v>71965.625</v>
+        <v>103298.7012987013</v>
       </c>
       <c r="AH2" t="n">
-        <v>19627222.22222222</v>
+        <v>25453463.2034632</v>
       </c>
       <c r="AI2" t="n">
-        <v>80.89027777777778</v>
+        <v>82.12409812409813</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.461111111111111</v>
+        <v>2.284271284271284</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.77777777777778</v>
+        <v>26.23084415584416</v>
       </c>
       <c r="AL2" t="n">
-        <v>183.953823953824</v>
+        <v>182.6840909090909</v>
       </c>
       <c r="AM2" t="n">
-        <v>83.89177489177489</v>
+        <v>80.48636363636363</v>
       </c>
       <c r="AN2" t="n">
-        <v>130431.4574314574</v>
+        <v>101362.6623376623</v>
       </c>
       <c r="AO2" t="n">
-        <v>50323232.32323233</v>
+        <v>30662540.58441558</v>
       </c>
       <c r="AP2" t="n">
-        <v>85.75180375180376</v>
+        <v>83.50714285714285</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.152958152958153</v>
+        <v>2.545779220779221</v>
       </c>
       <c r="AR2" t="n">
-        <v>27.63765284423179</v>
+        <v>24.13308291904238</v>
       </c>
       <c r="AS2" t="n">
-        <v>183.1793859649123</v>
+        <v>181.4488610713684</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.73575890483787</v>
+        <v>76.40209324836653</v>
       </c>
       <c r="AU2" t="n">
-        <v>60975.27246145667</v>
+        <v>82789.53630547288</v>
       </c>
       <c r="AV2" t="n">
-        <v>8595778.841041999</v>
+        <v>18099144.72445937</v>
       </c>
       <c r="AW2" t="n">
-        <v>76.67124534821903</v>
+        <v>81.17515450115972</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.049900318979266</v>
+        <v>1.521969095522544</v>
       </c>
       <c r="AY2" t="n">
-        <v>25.3921768707483</v>
+        <v>26.32937461843712</v>
       </c>
       <c r="AZ2" t="n">
-        <v>183.0777210884354</v>
+        <v>183.6718998015873</v>
       </c>
       <c r="BA2" t="n">
-        <v>80.40323129251701</v>
+        <v>77.24677960927961</v>
       </c>
       <c r="BB2" t="n">
-        <v>100304.4217687075</v>
+        <v>82713.63514957264</v>
       </c>
       <c r="BC2" t="n">
-        <v>33583265.30612245</v>
+        <v>21095885.79822955</v>
       </c>
       <c r="BD2" t="n">
-        <v>83.53639455782313</v>
+        <v>81.21642246642247</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.251700680272109</v>
+        <v>2.001869658119658</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60704</v>
+        <v>40341</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +980,180 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>180</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>128</v>
+      </c>
+      <c r="R3" t="n">
+        <v>41000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>146</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
         <v>26</v>
       </c>
-      <c r="O3" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325</v>
-      </c>
-      <c r="R3" t="n">
-        <v>540000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>173500000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>329</v>
-      </c>
-      <c r="U3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22</v>
-      </c>
       <c r="W3" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Z3" t="n">
-        <v>20000</v>
+        <v>56000</v>
       </c>
       <c r="AA3" t="n">
-        <v>6000000</v>
+        <v>11500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>25.33531746031746</v>
+        <v>23.21875901875902</v>
       </c>
       <c r="AE3" t="n">
-        <v>182.1785714285714</v>
+        <v>183.4974025974026</v>
       </c>
       <c r="AF3" t="n">
-        <v>83.0515873015873</v>
+        <v>80.01673881673881</v>
       </c>
       <c r="AG3" t="n">
-        <v>146543.6507936508</v>
+        <v>99678.21067821069</v>
       </c>
       <c r="AH3" t="n">
-        <v>54386904.76190477</v>
+        <v>32337445.88744589</v>
       </c>
       <c r="AI3" t="n">
-        <v>85.46031746031746</v>
+        <v>84.46320346320347</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.23015873015873</v>
+        <v>1.850505050505051</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.40674603174603</v>
+        <v>26.58703703703704</v>
       </c>
       <c r="AL3" t="n">
-        <v>182.1130952380952</v>
+        <v>183.3685185185185</v>
       </c>
       <c r="AM3" t="n">
-        <v>73.15277777777779</v>
+        <v>76.96666666666665</v>
       </c>
       <c r="AN3" t="n">
-        <v>45869.04761904762</v>
+        <v>55833.33333333334</v>
       </c>
       <c r="AO3" t="n">
-        <v>5892013.888888889</v>
+        <v>11843518.51851852</v>
       </c>
       <c r="AP3" t="n">
-        <v>76.67460317460316</v>
+        <v>79.03148148148149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.259920634920635</v>
+        <v>1.344444444444444</v>
       </c>
       <c r="AR3" t="n">
-        <v>24.79567634746206</v>
+        <v>23.99510080562712</v>
       </c>
       <c r="AS3" t="n">
-        <v>178.1746991104134</v>
+        <v>180.9560457086773</v>
       </c>
       <c r="AT3" t="n">
-        <v>78.24327577184719</v>
+        <v>79.08522237995922</v>
       </c>
       <c r="AU3" t="n">
-        <v>112402.2828362114</v>
+        <v>103841.9536603747</v>
       </c>
       <c r="AV3" t="n">
-        <v>30383464.15489272</v>
+        <v>27486265.57652873</v>
       </c>
       <c r="AW3" t="n">
-        <v>83.333836996337</v>
+        <v>83.5558719058719</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.476713762428048</v>
+        <v>1.819314311419574</v>
       </c>
       <c r="AY3" t="n">
-        <v>25.47593599640813</v>
+        <v>25.68565592903828</v>
       </c>
       <c r="AZ3" t="n">
-        <v>179.8102399492493</v>
+        <v>183.809126984127</v>
       </c>
       <c r="BA3" t="n">
-        <v>70.71053123003588</v>
+        <v>75.87718253968254</v>
       </c>
       <c r="BB3" t="n">
-        <v>38853.40850455014</v>
+        <v>53924.07796451914</v>
       </c>
       <c r="BC3" t="n">
-        <v>4025374.507458486</v>
+        <v>9607820.961718019</v>
       </c>
       <c r="BD3" t="n">
-        <v>76.33917740541193</v>
+        <v>78.30089869281046</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.167205781834265</v>
+        <v>1.225070028011205</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17250</v>
+        <v>31876</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,180 +1179,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="O4" t="n">
-        <v>177.75</v>
+        <v>185.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="R4" t="n">
-        <v>258000</v>
+        <v>253000</v>
       </c>
       <c r="S4" t="n">
-        <v>52000000</v>
+        <v>69500000</v>
       </c>
       <c r="T4" t="n">
-        <v>316</v>
+        <v>167</v>
       </c>
       <c r="U4" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>23.66666666666667</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>190.3333333333333</v>
+        <v>183</v>
       </c>
       <c r="X4" t="n">
         <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="Z4" t="n">
-        <v>134000</v>
+        <v>363000</v>
       </c>
       <c r="AA4" t="n">
-        <v>19800000</v>
+        <v>104000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AC4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.44318181818182</v>
+        <v>25.9354797979798</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.0744949494949</v>
+        <v>182.9472222222222</v>
       </c>
       <c r="AF4" t="n">
-        <v>75.38484848484848</v>
+        <v>75.41275252525253</v>
       </c>
       <c r="AG4" t="n">
-        <v>54902.08333333333</v>
+        <v>64851.64141414141</v>
       </c>
       <c r="AH4" t="n">
-        <v>10249472.85353535</v>
+        <v>11516161.61616162</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.72304292929293</v>
+        <v>80.1094696969697</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.168150252525253</v>
+        <v>1.561489898989899</v>
       </c>
       <c r="AK4" t="n">
-        <v>26.68492063492064</v>
+        <v>25.46851851851852</v>
       </c>
       <c r="AL4" t="n">
-        <v>182.397619047619</v>
+        <v>184.2777777777778</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.54801587301587</v>
+        <v>82.24814814814815</v>
       </c>
       <c r="AN4" t="n">
-        <v>54272.22222222223</v>
+        <v>112359.2592592593</v>
       </c>
       <c r="AO4" t="n">
-        <v>12557896.82539682</v>
+        <v>40063888.88888889</v>
       </c>
       <c r="AP4" t="n">
-        <v>79.83809523809524</v>
+        <v>84.8351851851852</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.46984126984127</v>
+        <v>2.742592592592592</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.56556756474519</v>
+        <v>23.57733087514182</v>
       </c>
       <c r="AS4" t="n">
-        <v>180.9617285401003</v>
+        <v>179.6616853835356</v>
       </c>
       <c r="AT4" t="n">
-        <v>71.85814405806181</v>
+        <v>73.28050304790108</v>
       </c>
       <c r="AU4" t="n">
-        <v>45641.54788011696</v>
+        <v>56944.89740976482</v>
       </c>
       <c r="AV4" t="n">
-        <v>6886870.724989558</v>
+        <v>9963628.600753803</v>
       </c>
       <c r="AW4" t="n">
-        <v>79.00405049081036</v>
+        <v>80.43357594754148</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.068496762740184</v>
+        <v>1.305141049554833</v>
       </c>
       <c r="AY4" t="n">
-        <v>28.00596033868093</v>
+        <v>24.40666765540715</v>
       </c>
       <c r="AZ4" t="n">
-        <v>180.4273804218657</v>
+        <v>184.0791940086058</v>
       </c>
       <c r="BA4" t="n">
-        <v>76.07570558526442</v>
+        <v>77.98462890983899</v>
       </c>
       <c r="BB4" t="n">
-        <v>56804.65686274509</v>
+        <v>77757.29611191795</v>
       </c>
       <c r="BC4" t="n">
-        <v>10740675.87641117</v>
+        <v>22756552.10335883</v>
       </c>
       <c r="BD4" t="n">
-        <v>78.13409462269757</v>
+        <v>82.43920038878022</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.4125</v>
+        <v>1.883233479872136</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45584.35416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32261</v>
+        <v>62850</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1377,181 +1377,149 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>286</v>
-      </c>
-      <c r="R5" t="n">
-        <v>146000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14200000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>298</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>175</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>53000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>79</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>26.93333333333333</v>
+        <v>25.46851851851852</v>
       </c>
       <c r="AE5" t="n">
-        <v>180.9798611111111</v>
+        <v>184.2777777777778</v>
       </c>
       <c r="AF5" t="n">
-        <v>75.44409722222221</v>
+        <v>82.24814814814815</v>
       </c>
       <c r="AG5" t="n">
-        <v>43109.02777777778</v>
+        <v>112359.2592592593</v>
       </c>
       <c r="AH5" t="n">
-        <v>7562387.152777778</v>
+        <v>40063888.88888889</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.74756944444445</v>
+        <v>84.8351851851852</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.360416666666667</v>
+        <v>2.742592592592592</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.44285714285714</v>
+        <v>28.14506172839506</v>
       </c>
       <c r="AL5" t="n">
-        <v>181.0511904761904</v>
+        <v>182.375</v>
       </c>
       <c r="AM5" t="n">
-        <v>76.13769841269841</v>
+        <v>79.56481481481481</v>
       </c>
       <c r="AN5" t="n">
-        <v>49315.07936507936</v>
+        <v>86324.07407407409</v>
       </c>
       <c r="AO5" t="n">
-        <v>10966865.07936508</v>
+        <v>20516203.70370371</v>
       </c>
       <c r="AP5" t="n">
-        <v>79.40793650793651</v>
+        <v>80.69907407407408</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.167063492063492</v>
+        <v>2.294753086419753</v>
       </c>
       <c r="AR5" t="n">
-        <v>26.47716526303504</v>
+        <v>24.40666765540715</v>
       </c>
       <c r="AS5" t="n">
-        <v>179.6526543841221</v>
+        <v>184.0791940086058</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.70876847449506</v>
+        <v>77.98462890983899</v>
       </c>
       <c r="AU5" t="n">
-        <v>42954.93014091602</v>
+        <v>77757.29611191795</v>
       </c>
       <c r="AV5" t="n">
-        <v>6014938.193753378</v>
+        <v>22756552.10335883</v>
       </c>
       <c r="AW5" t="n">
-        <v>76.79983383704359</v>
+        <v>82.43920038878022</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.252401223647354</v>
+        <v>1.883233479872136</v>
       </c>
       <c r="AY5" t="n">
-        <v>24.7809305540398</v>
+        <v>28.7875816993464</v>
       </c>
       <c r="AZ5" t="n">
-        <v>179.9449416130089</v>
+        <v>180.3327886710239</v>
       </c>
       <c r="BA5" t="n">
-        <v>74.77733517649484</v>
+        <v>77.8787672476398</v>
       </c>
       <c r="BB5" t="n">
-        <v>47156.59597172202</v>
+        <v>78483.52396514161</v>
       </c>
       <c r="BC5" t="n">
-        <v>9298689.778941879</v>
+        <v>15851134.71314452</v>
       </c>
       <c r="BD5" t="n">
-        <v>78.8115124837814</v>
+        <v>79.53363289760348</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.082930141753671</v>
+        <v>2.014206608569354</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55097</v>
+        <v>26600</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1576,181 +1544,149 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="O6" t="n">
-        <v>178.3333333333333</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>246</v>
-      </c>
-      <c r="R6" t="n">
-        <v>529000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>260</v>
-      </c>
-      <c r="U6" t="n">
-        <v>9</v>
-      </c>
-      <c r="V6" t="n">
-        <v>29</v>
-      </c>
-      <c r="W6" t="n">
-        <v>190</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>66000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>26.04469696969697</v>
+        <v>27.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>181.2727272727273</v>
+        <v>184.3111111111111</v>
       </c>
       <c r="AF6" t="n">
-        <v>83.20555555555556</v>
+        <v>76.52222222222223</v>
       </c>
       <c r="AG6" t="n">
-        <v>177010.101010101</v>
+        <v>66777.77777777778</v>
       </c>
       <c r="AH6" t="n">
-        <v>55797095.95959596</v>
+        <v>10556666.66666667</v>
       </c>
       <c r="AI6" t="n">
-        <v>85.92853535353535</v>
+        <v>78.24444444444445</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.19040404040404</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AK6" t="n">
-        <v>27.1</v>
+        <v>25.93506493506494</v>
       </c>
       <c r="AL6" t="n">
-        <v>184.175</v>
+        <v>183.8932178932179</v>
       </c>
       <c r="AM6" t="n">
-        <v>76.4375</v>
+        <v>79.36940836940838</v>
       </c>
       <c r="AN6" t="n">
-        <v>66312.5</v>
+        <v>103298.7012987013</v>
       </c>
       <c r="AO6" t="n">
-        <v>10467500</v>
+        <v>25453463.2034632</v>
       </c>
       <c r="AP6" t="n">
-        <v>78.2625</v>
+        <v>82.12409812409813</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.425</v>
+        <v>2.284271284271284</v>
       </c>
       <c r="AR6" t="n">
-        <v>26.07475750674764</v>
+        <v>26.94927536231884</v>
       </c>
       <c r="AS6" t="n">
-        <v>179.3288512748217</v>
+        <v>182.8294283413849</v>
       </c>
       <c r="AT6" t="n">
-        <v>80.31076579670329</v>
+        <v>74.48236714975845</v>
       </c>
       <c r="AU6" t="n">
-        <v>142673.3633964719</v>
+        <v>61881.32045088566</v>
       </c>
       <c r="AV6" t="n">
-        <v>41148530.08422498</v>
+        <v>7182773.752012882</v>
       </c>
       <c r="AW6" t="n">
-        <v>83.71727937632542</v>
+        <v>77.15547504025764</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.641327778581068</v>
+        <v>1.262399355877617</v>
       </c>
       <c r="AY6" t="n">
-        <v>26.97010869565217</v>
+        <v>24.13308291904238</v>
       </c>
       <c r="AZ6" t="n">
-        <v>182.753759057971</v>
+        <v>181.4488610713684</v>
       </c>
       <c r="BA6" t="n">
-        <v>74.3578804347826</v>
+        <v>76.40209324836653</v>
       </c>
       <c r="BB6" t="n">
-        <v>61377.35507246377</v>
+        <v>82789.53630547288</v>
       </c>
       <c r="BC6" t="n">
-        <v>7008337.86231884</v>
+        <v>18099144.72445937</v>
       </c>
       <c r="BD6" t="n">
-        <v>77.05534420289854</v>
+        <v>81.17515450115972</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.273460144927536</v>
+        <v>1.521969095522544</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
-  london </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62500</v>
+        <v>29673</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1792,132 +1728,132 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>28.14756944444444</v>
+        <v>25.62891414141414</v>
       </c>
       <c r="AE7" t="n">
-        <v>182.390625</v>
+        <v>183.1918560606061</v>
       </c>
       <c r="AF7" t="n">
-        <v>79.49479166666666</v>
+        <v>73.92004419191917</v>
       </c>
       <c r="AG7" t="n">
-        <v>85770.83333333334</v>
+        <v>43350.41035353535</v>
       </c>
       <c r="AH7" t="n">
-        <v>20322916.66666667</v>
+        <v>5904977.904040404</v>
       </c>
       <c r="AI7" t="n">
-        <v>80.69270833333334</v>
+        <v>77.7366792929293</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.284722222222222</v>
+        <v>1.064741161616162</v>
       </c>
       <c r="AK7" t="n">
-        <v>25.68701298701299</v>
+        <v>28.09671717171717</v>
       </c>
       <c r="AL7" t="n">
-        <v>183.124025974026</v>
+        <v>182.8133838383839</v>
       </c>
       <c r="AM7" t="n">
-        <v>73.84512987012987</v>
+        <v>76.40744949494949</v>
       </c>
       <c r="AN7" t="n">
-        <v>43035.3896103896</v>
+        <v>46834.59595959596</v>
       </c>
       <c r="AO7" t="n">
-        <v>5780292.207792208</v>
+        <v>10624633.83838384</v>
       </c>
       <c r="AP7" t="n">
-        <v>77.57207792207792</v>
+        <v>78.58636363636363</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.058116883116883</v>
+        <v>1.504166666666667</v>
       </c>
       <c r="AR7" t="n">
-        <v>28.81985294117647</v>
+        <v>26.54408939014202</v>
       </c>
       <c r="AS7" t="n">
-        <v>180.3890931372549</v>
+        <v>180.4215956558062</v>
       </c>
       <c r="AT7" t="n">
-        <v>77.9077308006536</v>
+        <v>71.94489870509608</v>
       </c>
       <c r="AU7" t="n">
-        <v>78874.84681372548</v>
+        <v>41971.8723893066</v>
       </c>
       <c r="AV7" t="n">
-        <v>15848703.02287582</v>
+        <v>3891265.142021721</v>
       </c>
       <c r="AW7" t="n">
-        <v>79.49004289215686</v>
+        <v>74.66696428571429</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.008629493464052</v>
+        <v>1.035609857978279</v>
       </c>
       <c r="AY7" t="n">
-        <v>26.55414727294427</v>
+        <v>27.18699875832229</v>
       </c>
       <c r="AZ7" t="n">
-        <v>180.5419739825755</v>
+        <v>182.8718385644856</v>
       </c>
       <c r="BA7" t="n">
-        <v>71.7640947607113</v>
+        <v>74.08250455971044</v>
       </c>
       <c r="BB7" t="n">
-        <v>41464.0947607113</v>
+        <v>40747.49259455142</v>
       </c>
       <c r="BC7" t="n">
-        <v>3772724.072084974</v>
+        <v>6296446.755314403</v>
       </c>
       <c r="BD7" t="n">
-        <v>74.53668098818476</v>
+        <v>76.77187047701754</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.033178183554123</v>
+        <v>1.249512442894796</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>39572</v>
+        <v>75635</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1942,181 +1878,149 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="O8" t="n">
-        <v>186.6666666666667</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>218</v>
-      </c>
-      <c r="R8" t="n">
-        <v>130000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>11400000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>236</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>24</v>
-      </c>
-      <c r="W8" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>314</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>380000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>118100000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>333</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>28.05858585858586</v>
+        <v>26.23084415584416</v>
       </c>
       <c r="AE8" t="n">
-        <v>182.8516594516595</v>
+        <v>182.6840909090909</v>
       </c>
       <c r="AF8" t="n">
-        <v>76.38773448773449</v>
+        <v>80.48636363636363</v>
       </c>
       <c r="AG8" t="n">
-        <v>46759.01875901876</v>
+        <v>101362.6623376623</v>
       </c>
       <c r="AH8" t="n">
-        <v>10666139.97113997</v>
+        <v>30662540.58441558</v>
       </c>
       <c r="AI8" t="n">
-        <v>78.61818181818182</v>
+        <v>83.50714285714285</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.498268398268398</v>
+        <v>2.545779220779221</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.52443181818182</v>
+        <v>25.45454545454546</v>
       </c>
       <c r="AL8" t="n">
-        <v>186.7772727272727</v>
+        <v>184.2985409652076</v>
       </c>
       <c r="AM8" t="n">
-        <v>79.98352272727273</v>
+        <v>75.46329966329967</v>
       </c>
       <c r="AN8" t="n">
-        <v>106817.0454545454</v>
+        <v>54973.56902356903</v>
       </c>
       <c r="AO8" t="n">
-        <v>25616413.35227273</v>
+        <v>10320743.54657688</v>
       </c>
       <c r="AP8" t="n">
-        <v>81.55767045454546</v>
+        <v>79.77401795735129</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.363920454545454</v>
+        <v>1.169668911335578</v>
       </c>
       <c r="AR8" t="n">
-        <v>27.11946451220348</v>
+        <v>26.32937461843712</v>
       </c>
       <c r="AS8" t="n">
-        <v>182.9012729305009</v>
+        <v>183.6718998015873</v>
       </c>
       <c r="AT8" t="n">
-        <v>74.18372672058334</v>
+        <v>77.24677960927961</v>
       </c>
       <c r="AU8" t="n">
-        <v>41318.20189614307</v>
+        <v>82713.63514957264</v>
       </c>
       <c r="AV8" t="n">
-        <v>6534525.32700143</v>
+        <v>21095885.79822955</v>
       </c>
       <c r="AW8" t="n">
-        <v>76.77744519573564</v>
+        <v>81.21642246642247</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.2352469528021</v>
+        <v>2.001869658119658</v>
       </c>
       <c r="AY8" t="n">
-        <v>26.89380775635613</v>
+        <v>23.57415529564652</v>
       </c>
       <c r="AZ8" t="n">
-        <v>182.9420432556994</v>
+        <v>181.0135999721526</v>
       </c>
       <c r="BA8" t="n">
-        <v>77.84096787339337</v>
+        <v>71.7866042420867</v>
       </c>
       <c r="BB8" t="n">
-        <v>92867.13839243831</v>
+        <v>45308.36002042142</v>
       </c>
       <c r="BC8" t="n">
-        <v>19723577.06442326</v>
+        <v>6713726.358720877</v>
       </c>
       <c r="BD8" t="n">
-        <v>80.43166660803078</v>
+        <v>78.96391789659333</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.973145933014354</v>
+        <v>1.068822519261116</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>zHJOSLsG</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42789</v>
+        <v>52305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2141,181 +2045,149 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>186</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>399</v>
-      </c>
-      <c r="R9" t="n">
-        <v>493000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>411</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10</v>
-      </c>
-      <c r="V9" t="n">
-        <v>24</v>
-      </c>
-      <c r="W9" t="n">
-        <v>169</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>63000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>25.93506493506494</v>
+        <v>27.52676767676768</v>
       </c>
       <c r="AE9" t="n">
-        <v>183.8932178932179</v>
+        <v>186.559595959596</v>
       </c>
       <c r="AF9" t="n">
-        <v>79.36940836940838</v>
+        <v>80.07626262626263</v>
       </c>
       <c r="AG9" t="n">
-        <v>103298.7012987013</v>
+        <v>107352.5252525253</v>
       </c>
       <c r="AH9" t="n">
-        <v>25453463.2034632</v>
+        <v>25805498.73737374</v>
       </c>
       <c r="AI9" t="n">
-        <v>82.12409812409813</v>
+        <v>81.67752525252526</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.284271284271284</v>
+        <v>2.394191919191919</v>
       </c>
       <c r="AK9" t="n">
-        <v>26.23084415584416</v>
+        <v>25.9354797979798</v>
       </c>
       <c r="AL9" t="n">
-        <v>182.6840909090909</v>
+        <v>182.9472222222222</v>
       </c>
       <c r="AM9" t="n">
-        <v>80.48636363636363</v>
+        <v>75.41275252525253</v>
       </c>
       <c r="AN9" t="n">
-        <v>101362.6623376623</v>
+        <v>64851.64141414141</v>
       </c>
       <c r="AO9" t="n">
-        <v>30662540.58441558</v>
+        <v>11516161.61616162</v>
       </c>
       <c r="AP9" t="n">
-        <v>83.50714285714285</v>
+        <v>80.1094696969697</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.545779220779221</v>
+        <v>1.561489898989899</v>
       </c>
       <c r="AR9" t="n">
-        <v>24.13308291904238</v>
+        <v>27.08814657707847</v>
       </c>
       <c r="AS9" t="n">
-        <v>181.4488610713684</v>
+        <v>182.916736862209</v>
       </c>
       <c r="AT9" t="n">
-        <v>76.40209324836653</v>
+        <v>77.75546350650841</v>
       </c>
       <c r="AU9" t="n">
-        <v>82789.53630547288</v>
+        <v>92405.71031708801</v>
       </c>
       <c r="AV9" t="n">
-        <v>18099144.72445937</v>
+        <v>19085322.46996353</v>
       </c>
       <c r="AW9" t="n">
-        <v>81.17515450115972</v>
+        <v>80.1773544452337</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.521969095522544</v>
+        <v>1.936447178552442</v>
       </c>
       <c r="AY9" t="n">
-        <v>26.32937461843712</v>
+        <v>23.57733087514182</v>
       </c>
       <c r="AZ9" t="n">
-        <v>183.6718998015873</v>
+        <v>179.6616853835356</v>
       </c>
       <c r="BA9" t="n">
-        <v>77.24677960927961</v>
+        <v>73.28050304790108</v>
       </c>
       <c r="BB9" t="n">
-        <v>82713.63514957264</v>
+        <v>56944.89740976482</v>
       </c>
       <c r="BC9" t="n">
-        <v>21095885.79822955</v>
+        <v>9963628.600753803</v>
       </c>
       <c r="BD9" t="n">
-        <v>81.21642246642247</v>
+        <v>80.43357594754148</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.001869658119658</v>
+        <v>1.305141049554833</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40341</v>
+        <v>32384</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2340,181 +2212,149 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>180</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>128</v>
-      </c>
-      <c r="R10" t="n">
-        <v>41000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>146</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26</v>
-      </c>
-      <c r="W10" t="n">
-        <v>191</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>56000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>79</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>23.21875901875902</v>
+        <v>26.36979166666666</v>
       </c>
       <c r="AE10" t="n">
-        <v>183.4974025974026</v>
+        <v>182.3211805555556</v>
       </c>
       <c r="AF10" t="n">
-        <v>80.01673881673881</v>
+        <v>73.25868055555556</v>
       </c>
       <c r="AG10" t="n">
-        <v>99678.21067821069</v>
+        <v>46982.63888888888</v>
       </c>
       <c r="AH10" t="n">
-        <v>32337445.88744589</v>
+        <v>6123914.930555556</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.46320346320347</v>
+        <v>76.78472222222223</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.850505050505051</v>
+        <v>1.282986111111111</v>
       </c>
       <c r="AK10" t="n">
-        <v>26.58703703703704</v>
+        <v>26.82962962962963</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.3685185185185</v>
+        <v>180.9932098765432</v>
       </c>
       <c r="AM10" t="n">
-        <v>76.96666666666665</v>
+        <v>75.48364197530864</v>
       </c>
       <c r="AN10" t="n">
-        <v>55833.33333333334</v>
+        <v>43096.91358024692</v>
       </c>
       <c r="AO10" t="n">
-        <v>11843518.51851852</v>
+        <v>7639899.691358025</v>
       </c>
       <c r="AP10" t="n">
-        <v>79.03148148148149</v>
+        <v>77.86450617283951</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.344444444444444</v>
+        <v>1.364814814814815</v>
       </c>
       <c r="AR10" t="n">
-        <v>23.99510080562712</v>
+        <v>25.75021471285661</v>
       </c>
       <c r="AS10" t="n">
-        <v>180.9560457086773</v>
+        <v>180.164657732666</v>
       </c>
       <c r="AT10" t="n">
-        <v>79.08522237995922</v>
+        <v>71.04516356250103</v>
       </c>
       <c r="AU10" t="n">
-        <v>103841.9536603747</v>
+        <v>39585.74583120507</v>
       </c>
       <c r="AV10" t="n">
-        <v>27486265.57652873</v>
+        <v>4159746.475765568</v>
       </c>
       <c r="AW10" t="n">
-        <v>83.5558719058719</v>
+        <v>76.20272559493407</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.819314311419574</v>
+        <v>1.154800201136631</v>
       </c>
       <c r="AY10" t="n">
-        <v>25.68565592903828</v>
+        <v>26.6790488612599</v>
       </c>
       <c r="AZ10" t="n">
-        <v>183.809126984127</v>
+        <v>179.7500718708536</v>
       </c>
       <c r="BA10" t="n">
-        <v>75.87718253968254</v>
+        <v>73.8130229577211</v>
       </c>
       <c r="BB10" t="n">
-        <v>53924.07796451914</v>
+        <v>43522.02940630443</v>
       </c>
       <c r="BC10" t="n">
-        <v>9607820.961718019</v>
+        <v>6014422.18529712</v>
       </c>
       <c r="BD10" t="n">
-        <v>78.30089869281046</v>
+        <v>76.75671504469234</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.225070028011205</v>
+        <v>1.257036381804184</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31876</v>
+        <v>11307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2539,181 +2379,149 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>31</v>
-      </c>
-      <c r="O11" t="n">
-        <v>182</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>151</v>
-      </c>
-      <c r="R11" t="n">
-        <v>111000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="T11" t="n">
-        <v>156</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="W11" t="n">
-        <v>183</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>241</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>363000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>104000000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>253</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>25.9354797979798</v>
+        <v>25.5125</v>
       </c>
       <c r="AE11" t="n">
-        <v>182.9472222222222</v>
+        <v>181.0447916666666</v>
       </c>
       <c r="AF11" t="n">
-        <v>75.41275252525253</v>
+        <v>76.19548611111111</v>
       </c>
       <c r="AG11" t="n">
-        <v>64851.64141414141</v>
+        <v>49713.19444444445</v>
       </c>
       <c r="AH11" t="n">
-        <v>11516161.61616162</v>
+        <v>11072256.94444444</v>
       </c>
       <c r="AI11" t="n">
-        <v>80.1094696969697</v>
+        <v>79.38194444444444</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.561489898989899</v>
+        <v>1.171180555555556</v>
       </c>
       <c r="AK11" t="n">
-        <v>25.46851851851852</v>
+        <v>25.52951388888889</v>
       </c>
       <c r="AL11" t="n">
-        <v>184.2777777777778</v>
+        <v>182.2118055555555</v>
       </c>
       <c r="AM11" t="n">
-        <v>82.24814814814815</v>
+        <v>83.14236111111111</v>
       </c>
       <c r="AN11" t="n">
-        <v>112359.2592592593</v>
+        <v>146975.6944444444</v>
       </c>
       <c r="AO11" t="n">
-        <v>40063888.88888889</v>
+        <v>53977430.55555556</v>
       </c>
       <c r="AP11" t="n">
-        <v>84.8351851851852</v>
+        <v>85.375</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.742592592592592</v>
+        <v>3.243055555555555</v>
       </c>
       <c r="AR11" t="n">
-        <v>23.57733087514182</v>
+        <v>24.74283804430863</v>
       </c>
       <c r="AS11" t="n">
-        <v>179.6616853835356</v>
+        <v>179.814919149478</v>
       </c>
       <c r="AT11" t="n">
-        <v>73.28050304790108</v>
+        <v>74.81112066038537</v>
       </c>
       <c r="AU11" t="n">
-        <v>56944.89740976482</v>
+        <v>47208.45004668534</v>
       </c>
       <c r="AV11" t="n">
-        <v>9963628.600753803</v>
+        <v>9351234.508955097</v>
       </c>
       <c r="AW11" t="n">
-        <v>80.43357594754148</v>
+        <v>78.83507342330873</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.305141049554833</v>
+        <v>1.090421016891605</v>
       </c>
       <c r="AY11" t="n">
-        <v>24.40666765540715</v>
+        <v>24.92447767359452</v>
       </c>
       <c r="AZ11" t="n">
-        <v>184.0791940086058</v>
+        <v>178.5713399824813</v>
       </c>
       <c r="BA11" t="n">
-        <v>77.98462890983899</v>
+        <v>78.25634456123586</v>
       </c>
       <c r="BB11" t="n">
-        <v>77757.29611191795</v>
+        <v>112444.3887860328</v>
       </c>
       <c r="BC11" t="n">
-        <v>22756552.10335883</v>
+        <v>29883900.70074853</v>
       </c>
       <c r="BD11" t="n">
-        <v>82.43920038878022</v>
+        <v>83.19971606744704</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.883233479872136</v>
+        <v>2.438863672559325</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.35416666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>62850</v>
+        <v>31750</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2755,132 +2563,132 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>25.46851851851852</v>
+        <v>26.68492063492064</v>
       </c>
       <c r="AE12" t="n">
-        <v>184.2777777777778</v>
+        <v>182.397619047619</v>
       </c>
       <c r="AF12" t="n">
-        <v>82.24814814814815</v>
+        <v>76.54801587301587</v>
       </c>
       <c r="AG12" t="n">
-        <v>112359.2592592593</v>
+        <v>54272.22222222223</v>
       </c>
       <c r="AH12" t="n">
-        <v>40063888.88888889</v>
+        <v>12557896.82539682</v>
       </c>
       <c r="AI12" t="n">
-        <v>84.8351851851852</v>
+        <v>79.83809523809524</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.742592592592592</v>
+        <v>1.46984126984127</v>
       </c>
       <c r="AK12" t="n">
-        <v>28.14756944444444</v>
+        <v>26.11043771043771</v>
       </c>
       <c r="AL12" t="n">
-        <v>182.390625</v>
+        <v>181.2525252525253</v>
       </c>
       <c r="AM12" t="n">
-        <v>79.49479166666666</v>
+        <v>83.45544332210999</v>
       </c>
       <c r="AN12" t="n">
-        <v>85770.83333333334</v>
+        <v>179817.0594837262</v>
       </c>
       <c r="AO12" t="n">
-        <v>20322916.66666667</v>
+        <v>57233782.26711561</v>
       </c>
       <c r="AP12" t="n">
-        <v>80.69270833333334</v>
+        <v>86.05768799102133</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.284722222222222</v>
+        <v>3.229854096520763</v>
       </c>
       <c r="AR12" t="n">
-        <v>24.40666765540715</v>
+        <v>27.97499504852446</v>
       </c>
       <c r="AS12" t="n">
-        <v>184.0791940086058</v>
+        <v>180.1576714861029</v>
       </c>
       <c r="AT12" t="n">
-        <v>77.98462890983899</v>
+        <v>76.13800092427543</v>
       </c>
       <c r="AU12" t="n">
-        <v>77757.29611191795</v>
+        <v>56937.47276688452</v>
       </c>
       <c r="AV12" t="n">
-        <v>22756552.10335883</v>
+        <v>10755348.25377963</v>
       </c>
       <c r="AW12" t="n">
-        <v>82.43920038878022</v>
+        <v>78.15959926057965</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.883233479872136</v>
+        <v>1.417171717171717</v>
       </c>
       <c r="AY12" t="n">
-        <v>28.81985294117647</v>
+        <v>26.12895111710901</v>
       </c>
       <c r="AZ12" t="n">
-        <v>180.3890931372549</v>
+        <v>179.2506455776193</v>
       </c>
       <c r="BA12" t="n">
-        <v>77.9077308006536</v>
+        <v>80.13040293040292</v>
       </c>
       <c r="BB12" t="n">
-        <v>78874.84681372548</v>
+        <v>139133.2674635306</v>
       </c>
       <c r="BC12" t="n">
-        <v>15848703.02287582</v>
+        <v>39650429.5193111</v>
       </c>
       <c r="BD12" t="n">
-        <v>79.49004289215686</v>
+        <v>83.4153594456226</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.008629493464052</v>
+        <v>2.583958025405394</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>26600</v>
+        <v>61276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2922,765 +2730,97 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>27.1</v>
+        <v>26.83055555555555</v>
       </c>
       <c r="AE13" t="n">
-        <v>184.175</v>
+        <v>184.0470959595959</v>
       </c>
       <c r="AF13" t="n">
-        <v>76.4375</v>
+        <v>83.96780303030303</v>
       </c>
       <c r="AG13" t="n">
-        <v>66312.5</v>
+        <v>131327.5252525253</v>
       </c>
       <c r="AH13" t="n">
-        <v>10467500</v>
+        <v>50801578.28282828</v>
       </c>
       <c r="AI13" t="n">
-        <v>78.2625</v>
+        <v>85.77032828282827</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.425</v>
+        <v>3.171338383838385</v>
       </c>
       <c r="AK13" t="n">
-        <v>25.93506493506494</v>
+        <v>23.21875901875902</v>
       </c>
       <c r="AL13" t="n">
-        <v>183.8932178932179</v>
+        <v>183.4974025974026</v>
       </c>
       <c r="AM13" t="n">
-        <v>79.36940836940838</v>
+        <v>80.01673881673881</v>
       </c>
       <c r="AN13" t="n">
-        <v>103298.7012987013</v>
+        <v>99678.21067821069</v>
       </c>
       <c r="AO13" t="n">
-        <v>25453463.2034632</v>
+        <v>32337445.88744589</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.12409812409813</v>
+        <v>84.46320346320347</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.284271284271284</v>
+        <v>1.850505050505051</v>
       </c>
       <c r="AR13" t="n">
-        <v>26.97010869565217</v>
+        <v>25.52250258799172</v>
       </c>
       <c r="AS13" t="n">
-        <v>182.753759057971</v>
+        <v>183.0462668219462</v>
       </c>
       <c r="AT13" t="n">
-        <v>74.3578804347826</v>
+        <v>80.39087085921325</v>
       </c>
       <c r="AU13" t="n">
-        <v>61377.35507246377</v>
+        <v>100462.0212215321</v>
       </c>
       <c r="AV13" t="n">
-        <v>7008337.86231884</v>
+        <v>33515248.44720497</v>
       </c>
       <c r="AW13" t="n">
-        <v>77.05534420289854</v>
+        <v>83.48564958592132</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.273460144927536</v>
+        <v>2.280020703933747</v>
       </c>
       <c r="AY13" t="n">
-        <v>24.13308291904238</v>
+        <v>23.99510080562712</v>
       </c>
       <c r="AZ13" t="n">
-        <v>181.4488610713684</v>
+        <v>180.9560457086773</v>
       </c>
       <c r="BA13" t="n">
-        <v>76.40209324836653</v>
+        <v>79.08522237995922</v>
       </c>
       <c r="BB13" t="n">
-        <v>82789.53630547288</v>
+        <v>103841.9536603747</v>
       </c>
       <c r="BC13" t="n">
-        <v>18099144.72445937</v>
+        <v>27486265.57652873</v>
       </c>
       <c r="BD13" t="n">
-        <v>81.17515450115972</v>
+        <v>83.5558719058719</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.521969095522544</v>
+        <v>1.819314311419574</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="n">
-        <v>25.68701298701299</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>183.124025974026</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>73.84512987012987</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>43035.3896103896</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5780292.207792208</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>77.57207792207792</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.058116883116883</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>28.05858585858586</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>182.8516594516595</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>76.38773448773449</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>46759.01875901876</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>10666139.97113997</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>78.61818181818182</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.498268398268398</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>26.55414727294427</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>180.5419739825755</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>71.7640947607113</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>41464.0947607113</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3772724.072084974</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>74.53668098818476</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.033178183554123</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>27.11946451220348</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>182.9012729305009</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>74.18372672058334</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>41318.20189614307</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>6534525.32700143</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>76.77744519573564</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.2352469528021</v>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="n">
-        <v>26.23084415584416</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>182.6840909090909</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>80.48636363636363</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>101362.6623376623</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>30662540.58441558</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>83.50714285714285</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.545779220779221</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>25.44318181818182</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>184.0744949494949</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75.38484848484848</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>54902.08333333333</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>10249472.85353535</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>79.72304292929293</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.168150252525253</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>26.32937461843712</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>183.6718998015873</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>77.24677960927961</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>82713.63514957264</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>21095885.79822955</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>81.21642246642247</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.001869658119658</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>23.56556756474519</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>180.9617285401003</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>71.85814405806181</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>45641.54788011696</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6886870.724989558</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>79.00405049081036</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.068496762740184</v>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>52305</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="n">
-        <v>27.52443181818182</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>186.7772727272727</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>79.98352272727273</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>106817.0454545454</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>25616413.35227273</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>81.55767045454546</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.363920454545454</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>25.9354797979798</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>182.9472222222222</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>75.41275252525253</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>64851.64141414141</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>11516161.61616162</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>80.1094696969697</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.561489898989899</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>26.89380775635613</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>182.9420432556994</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>77.84096787339337</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>92867.13839243831</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>19723577.06442326</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>80.43166660803078</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.973145933014354</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>23.57733087514182</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>179.6616853835356</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>73.28050304790108</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>56944.89740976482</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>9963628.600753803</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>80.43357594754148</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.305141049554833</v>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
           <t>QHesBmSQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>32384</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="n">
-        <v>26.40674603174603</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>182.1130952380952</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>73.15277777777779</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>45869.04761904762</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>5892013.888888889</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>76.67460317460316</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.259920634920635</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>26.93333333333333</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>180.9798611111111</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>75.44409722222221</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>43109.02777777778</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>7562387.152777778</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>77.74756944444445</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.360416666666667</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>25.47593599640813</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>179.8102399492493</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>70.71053123003588</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>38853.40850455014</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4025374.507458486</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>76.33917740541193</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.167205781834265</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>26.47716526303504</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>179.6526543841221</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>73.70876847449506</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>42954.93014091602</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>6014938.193753378</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>76.79983383704359</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.252401223647354</v>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG13"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,230 +495,150 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_home</t>
+          <t>mean_value_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_rep_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_value_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_away</t>
+          <t>mean_rep_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_value_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_home</t>
+          <t>mean_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_value_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_away</t>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -727,35 +647,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42789</v>
+        <v>62850</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +701,132 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>25.47301587301587</v>
       </c>
       <c r="O2" t="n">
-        <v>178</v>
+        <v>184.3238095238095</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>82.2126984126984</v>
       </c>
       <c r="Q2" t="n">
-        <v>82</v>
+        <v>111207.9365079365</v>
       </c>
       <c r="R2" t="n">
-        <v>130000</v>
+        <v>39690476.19047619</v>
       </c>
       <c r="S2" t="n">
-        <v>29500000</v>
+        <v>84.74444444444445</v>
       </c>
       <c r="T2" t="n">
-        <v>82</v>
+        <v>2.75079365079365</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>28.14506172839506</v>
       </c>
       <c r="V2" t="n">
-        <v>26.5</v>
+        <v>182.375</v>
       </c>
       <c r="W2" t="n">
-        <v>174</v>
+        <v>79.56481481481481</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>86324.07407407409</v>
       </c>
       <c r="Y2" t="n">
-        <v>163</v>
+        <v>20516203.70370371</v>
       </c>
       <c r="Z2" t="n">
-        <v>253000</v>
+        <v>80.69907407407408</v>
       </c>
       <c r="AA2" t="n">
-        <v>88000000</v>
+        <v>2.294753086419753</v>
       </c>
       <c r="AB2" t="n">
-        <v>167</v>
+        <v>24.51208419848125</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
+        <v>184.1109614241967</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.93506493506494</v>
+        <v>78.03863362944246</v>
       </c>
       <c r="AE2" t="n">
-        <v>183.8932178932179</v>
+        <v>77662.63409792821</v>
       </c>
       <c r="AF2" t="n">
-        <v>79.36940836940838</v>
+        <v>22629170.59043898</v>
       </c>
       <c r="AG2" t="n">
-        <v>103298.7012987013</v>
+        <v>82.37388367351602</v>
       </c>
       <c r="AH2" t="n">
-        <v>25453463.2034632</v>
+        <v>1.866579294888119</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.12409812409813</v>
+        <v>28.7875816993464</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.284271284271284</v>
+        <v>180.3327886710239</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.23084415584416</v>
+        <v>77.8787672476398</v>
       </c>
       <c r="AL2" t="n">
-        <v>182.6840909090909</v>
+        <v>78483.52396514161</v>
       </c>
       <c r="AM2" t="n">
-        <v>80.48636363636363</v>
+        <v>15851134.71314452</v>
       </c>
       <c r="AN2" t="n">
-        <v>101362.6623376623</v>
+        <v>79.53363289760348</v>
       </c>
       <c r="AO2" t="n">
-        <v>30662540.58441558</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>83.50714285714285</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.545779220779221</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>24.13308291904238</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>181.4488610713684</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>76.40209324836653</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>82789.53630547288</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>18099144.72445937</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>81.17515450115972</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.521969095522544</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>26.32937461843712</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>183.6718998015873</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>77.24677960927961</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>82713.63514957264</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>21095885.79822955</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>81.21642246642247</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.001869658119658</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+        <v>2.014206608569354</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
+          <t xml:space="preserve">craven cottage
   london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40341</v>
+        <v>26600</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +852,132 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.5</v>
+        <v>27.2</v>
       </c>
       <c r="O3" t="n">
-        <v>180</v>
+        <v>184.3111111111111</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>76.52222222222223</v>
       </c>
       <c r="Q3" t="n">
-        <v>128</v>
+        <v>66777.77777777778</v>
       </c>
       <c r="R3" t="n">
-        <v>41000</v>
+        <v>10556666.66666667</v>
       </c>
       <c r="S3" t="n">
-        <v>1750000</v>
+        <v>78.24444444444445</v>
       </c>
       <c r="T3" t="n">
-        <v>146</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>26.03409090909091</v>
       </c>
       <c r="V3" t="n">
-        <v>26</v>
+        <v>183.8497474747475</v>
       </c>
       <c r="W3" t="n">
-        <v>191</v>
+        <v>79.49368686868686</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>104011.3636363636</v>
       </c>
       <c r="Y3" t="n">
-        <v>77</v>
+        <v>25567234.84848485</v>
       </c>
       <c r="Z3" t="n">
-        <v>56000</v>
+        <v>82.13131313131312</v>
       </c>
       <c r="AA3" t="n">
-        <v>11500000</v>
+        <v>2.305555555555555</v>
       </c>
       <c r="AB3" t="n">
-        <v>79</v>
+        <v>26.94927536231884</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>182.8294283413849</v>
       </c>
       <c r="AD3" t="n">
-        <v>23.21875901875902</v>
+        <v>74.48236714975845</v>
       </c>
       <c r="AE3" t="n">
-        <v>183.4974025974026</v>
+        <v>61881.32045088566</v>
       </c>
       <c r="AF3" t="n">
-        <v>80.01673881673881</v>
+        <v>7182773.752012882</v>
       </c>
       <c r="AG3" t="n">
-        <v>99678.21067821069</v>
+        <v>77.15547504025764</v>
       </c>
       <c r="AH3" t="n">
-        <v>32337445.88744589</v>
+        <v>1.262399355877617</v>
       </c>
       <c r="AI3" t="n">
-        <v>84.46320346320347</v>
+        <v>24.14769755416209</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.850505050505051</v>
+        <v>181.5568159374474</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.58703703703704</v>
+        <v>76.31276909232072</v>
       </c>
       <c r="AL3" t="n">
-        <v>183.3685185185185</v>
+        <v>82354.90676728878</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.96666666666665</v>
+        <v>17835579.75890195</v>
       </c>
       <c r="AN3" t="n">
-        <v>55833.33333333334</v>
+        <v>81.13763518851476</v>
       </c>
       <c r="AO3" t="n">
-        <v>11843518.51851852</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>79.03148148148149</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.344444444444444</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>23.99510080562712</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>180.9560457086773</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>79.08522237995922</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>103841.9536603747</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>27486265.57652873</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>83.5558719058719</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.819314311419574</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>25.68565592903828</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>183.809126984127</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>75.87718253968254</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>53924.07796451914</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9607820.961718019</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>78.30089869281046</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.225070028011205</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
+        <v>1.527035458582226</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31876</v>
+        <v>29673</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,180 +1003,132 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>26.5</v>
+        <v>25.62891414141414</v>
       </c>
       <c r="O4" t="n">
-        <v>185.5</v>
+        <v>183.1918560606061</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>73.92004419191917</v>
       </c>
       <c r="Q4" t="n">
-        <v>162</v>
+        <v>43350.41035353535</v>
       </c>
       <c r="R4" t="n">
-        <v>253000</v>
+        <v>5904977.904040404</v>
       </c>
       <c r="S4" t="n">
-        <v>69500000</v>
+        <v>77.7366792929293</v>
       </c>
       <c r="T4" t="n">
-        <v>167</v>
+        <v>1.064741161616162</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>28.09671717171717</v>
       </c>
       <c r="V4" t="n">
-        <v>25.66666666666667</v>
+        <v>182.8133838383839</v>
       </c>
       <c r="W4" t="n">
-        <v>183</v>
+        <v>76.40744949494949</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>46834.59595959596</v>
       </c>
       <c r="Y4" t="n">
-        <v>241</v>
+        <v>10624633.83838384</v>
       </c>
       <c r="Z4" t="n">
-        <v>363000</v>
+        <v>78.58636363636363</v>
       </c>
       <c r="AA4" t="n">
-        <v>104000000</v>
+        <v>1.504166666666667</v>
       </c>
       <c r="AB4" t="n">
-        <v>253</v>
+        <v>26.54408939014202</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>180.4215956558062</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.9354797979798</v>
+        <v>71.94489870509608</v>
       </c>
       <c r="AE4" t="n">
-        <v>182.9472222222222</v>
+        <v>41971.8723893066</v>
       </c>
       <c r="AF4" t="n">
-        <v>75.41275252525253</v>
+        <v>3891265.142021721</v>
       </c>
       <c r="AG4" t="n">
-        <v>64851.64141414141</v>
+        <v>74.66696428571429</v>
       </c>
       <c r="AH4" t="n">
-        <v>11516161.61616162</v>
+        <v>1.035609857978279</v>
       </c>
       <c r="AI4" t="n">
-        <v>80.1094696969697</v>
+        <v>27.18699875832229</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.561489898989899</v>
+        <v>182.8718385644856</v>
       </c>
       <c r="AK4" t="n">
-        <v>25.46851851851852</v>
+        <v>74.08250455971044</v>
       </c>
       <c r="AL4" t="n">
-        <v>184.2777777777778</v>
+        <v>40747.49259455142</v>
       </c>
       <c r="AM4" t="n">
-        <v>82.24814814814815</v>
+        <v>6296446.755314403</v>
       </c>
       <c r="AN4" t="n">
-        <v>112359.2592592593</v>
+        <v>76.77187047701754</v>
       </c>
       <c r="AO4" t="n">
-        <v>40063888.88888889</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>84.8351851851852</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.742592592592592</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>23.57733087514182</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>179.6616853835356</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>73.28050304790108</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>56944.89740976482</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9963628.600753803</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>80.43357594754148</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.305141049554833</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>24.40666765540715</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>184.0791940086058</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>77.98462890983899</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>77757.29611191795</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>22756552.10335883</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>82.43920038878022</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.883233479872136</v>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
+        <v>1.249512442894796</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45584.35416666666</v>
+        <v>45584.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>62850</v>
+        <v>75635</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1377,121 +1153,105 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>26.175</v>
+      </c>
+      <c r="O5" t="n">
+        <v>182.9607142857143</v>
+      </c>
+      <c r="P5" t="n">
+        <v>80.40714285714286</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>100239.2857142857</v>
+      </c>
+      <c r="R5" t="n">
+        <v>30724553.57142857</v>
+      </c>
+      <c r="S5" t="n">
+        <v>83.47857142857143</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.510714285714286</v>
+      </c>
+      <c r="U5" t="n">
+        <v>25.45454545454546</v>
+      </c>
+      <c r="V5" t="n">
+        <v>184.2985409652076</v>
+      </c>
+      <c r="W5" t="n">
+        <v>75.46329966329967</v>
+      </c>
+      <c r="X5" t="n">
+        <v>54973.56902356903</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10320743.54657688</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>79.77401795735129</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.169668911335578</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>26.79118017399267</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>183.8941220238095</v>
+      </c>
       <c r="AD5" t="n">
-        <v>25.46851851851852</v>
+        <v>77.7919184981685</v>
       </c>
       <c r="AE5" t="n">
-        <v>184.2777777777778</v>
+        <v>85800.4407051282</v>
       </c>
       <c r="AF5" t="n">
-        <v>82.24814814814815</v>
+        <v>21138767.74267399</v>
       </c>
       <c r="AG5" t="n">
-        <v>112359.2592592593</v>
+        <v>81.35531135531136</v>
       </c>
       <c r="AH5" t="n">
-        <v>40063888.88888889</v>
+        <v>2.040064102564103</v>
       </c>
       <c r="AI5" t="n">
-        <v>84.8351851851852</v>
+        <v>23.57415529564652</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.742592592592592</v>
+        <v>181.0135999721526</v>
       </c>
       <c r="AK5" t="n">
-        <v>28.14506172839506</v>
+        <v>71.7866042420867</v>
       </c>
       <c r="AL5" t="n">
-        <v>182.375</v>
+        <v>45308.36002042142</v>
       </c>
       <c r="AM5" t="n">
-        <v>79.56481481481481</v>
+        <v>6713726.358720877</v>
       </c>
       <c r="AN5" t="n">
-        <v>86324.07407407409</v>
+        <v>78.96391789659333</v>
       </c>
       <c r="AO5" t="n">
-        <v>20516203.70370371</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>80.69907407407408</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.294753086419753</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>24.40666765540715</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>184.0791940086058</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>77.98462890983899</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>77757.29611191795</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>22756552.10335883</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>82.43920038878022</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.883233479872136</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>28.7875816993464</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>180.3327886710239</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>77.8787672476398</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>78483.52396514161</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>15851134.71314452</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>79.53363289760348</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.014206608569354</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
+        <v>1.068822519261116</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1499,27 +1259,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26600</v>
+        <v>52305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1544,121 +1304,105 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>27.52676767676768</v>
+      </c>
+      <c r="O6" t="n">
+        <v>186.559595959596</v>
+      </c>
+      <c r="P6" t="n">
+        <v>80.07626262626263</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>107352.5252525252</v>
+      </c>
+      <c r="R6" t="n">
+        <v>25805498.73737374</v>
+      </c>
+      <c r="S6" t="n">
+        <v>81.67752525252526</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.394191919191919</v>
+      </c>
+      <c r="U6" t="n">
+        <v>25.95499438832772</v>
+      </c>
+      <c r="V6" t="n">
+        <v>183.1753086419753</v>
+      </c>
+      <c r="W6" t="n">
+        <v>75.44096520763188</v>
+      </c>
+      <c r="X6" t="n">
+        <v>64645.90347923681</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11371156.00448934</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>80.0973063973064</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.560830527497194</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>27.08814657707847</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>182.916736862209</v>
+      </c>
       <c r="AD6" t="n">
-        <v>27.2</v>
+        <v>77.75546350650841</v>
       </c>
       <c r="AE6" t="n">
-        <v>184.3111111111111</v>
+        <v>92405.71031708801</v>
       </c>
       <c r="AF6" t="n">
-        <v>76.52222222222223</v>
+        <v>19085322.46996353</v>
       </c>
       <c r="AG6" t="n">
-        <v>66777.77777777778</v>
+        <v>80.1773544452337</v>
       </c>
       <c r="AH6" t="n">
-        <v>10556666.66666667</v>
+        <v>1.936447178552442</v>
       </c>
       <c r="AI6" t="n">
-        <v>78.24444444444445</v>
+        <v>23.54790522234828</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.444444444444444</v>
+        <v>179.6992758964761</v>
       </c>
       <c r="AK6" t="n">
-        <v>25.93506493506494</v>
+        <v>73.4785027092454</v>
       </c>
       <c r="AL6" t="n">
-        <v>183.8932178932179</v>
+        <v>57034.35325312429</v>
       </c>
       <c r="AM6" t="n">
-        <v>79.36940836940838</v>
+        <v>10071142.08955894</v>
       </c>
       <c r="AN6" t="n">
-        <v>103298.7012987013</v>
+        <v>80.5590119533702</v>
       </c>
       <c r="AO6" t="n">
-        <v>25453463.2034632</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>82.12409812409813</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.284271284271284</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>26.94927536231884</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>182.8294283413849</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>74.48236714975845</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>61881.32045088566</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>7182773.752012882</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>77.15547504025764</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.262399355877617</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>24.13308291904238</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>181.4488610713684</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>76.40209324836653</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>82789.53630547288</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18099144.72445937</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>81.17515450115972</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.521969095522544</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
+        <v>1.312903155159852</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1666,27 +1410,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29673</v>
+        <v>32384</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1711,149 +1455,133 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>26.36979166666666</v>
+      </c>
+      <c r="O7" t="n">
+        <v>182.3211805555556</v>
+      </c>
+      <c r="P7" t="n">
+        <v>73.25868055555556</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>46982.63888888888</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6123914.930555556</v>
+      </c>
+      <c r="S7" t="n">
+        <v>76.78472222222223</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.282986111111111</v>
+      </c>
+      <c r="U7" t="n">
+        <v>26.82962962962963</v>
+      </c>
+      <c r="V7" t="n">
+        <v>180.9932098765432</v>
+      </c>
+      <c r="W7" t="n">
+        <v>75.48364197530864</v>
+      </c>
+      <c r="X7" t="n">
+        <v>43096.91358024692</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7639899.691358025</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>77.86450617283951</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.364814814814815</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25.75021471285661</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>180.164657732666</v>
+      </c>
       <c r="AD7" t="n">
-        <v>25.62891414141414</v>
+        <v>71.04516356250103</v>
       </c>
       <c r="AE7" t="n">
-        <v>183.1918560606061</v>
+        <v>39585.74583120507</v>
       </c>
       <c r="AF7" t="n">
-        <v>73.92004419191917</v>
+        <v>4159746.475765568</v>
       </c>
       <c r="AG7" t="n">
-        <v>43350.41035353535</v>
+        <v>76.20272559493407</v>
       </c>
       <c r="AH7" t="n">
-        <v>5904977.904040404</v>
+        <v>1.154800201136631</v>
       </c>
       <c r="AI7" t="n">
-        <v>77.7366792929293</v>
+        <v>26.6790488612599</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.064741161616162</v>
+        <v>179.7500718708536</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.09671717171717</v>
+        <v>73.8130229577211</v>
       </c>
       <c r="AL7" t="n">
-        <v>182.8133838383839</v>
+        <v>43522.02940630443</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.40744949494949</v>
+        <v>6014422.18529712</v>
       </c>
       <c r="AN7" t="n">
-        <v>46834.59595959596</v>
+        <v>76.75671504469234</v>
       </c>
       <c r="AO7" t="n">
-        <v>10624633.83838384</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>78.58636363636363</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.504166666666667</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>26.54408939014202</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>180.4215956558062</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>71.94489870509608</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>41971.8723893066</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3891265.142021721</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>74.66696428571429</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.035609857978279</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>27.18699875832229</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>182.8718385644856</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>74.08250455971044</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>40747.49259455142</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6296446.755314403</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>76.77187047701754</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.249512442894796</v>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
+        <v>1.257036381804184</v>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75635</v>
+        <v>11307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1878,125 +1606,109 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>25.5125</v>
+      </c>
+      <c r="O8" t="n">
+        <v>181.0447916666666</v>
+      </c>
+      <c r="P8" t="n">
+        <v>76.19548611111111</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>49713.19444444445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11072256.94444444</v>
+      </c>
+      <c r="S8" t="n">
+        <v>79.38194444444444</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.171180555555556</v>
+      </c>
+      <c r="U8" t="n">
+        <v>25.52951388888889</v>
+      </c>
+      <c r="V8" t="n">
+        <v>182.2118055555555</v>
+      </c>
+      <c r="W8" t="n">
+        <v>83.14236111111111</v>
+      </c>
+      <c r="X8" t="n">
+        <v>146975.6944444444</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>53977430.55555556</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>85.375</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.243055555555555</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.74283804430863</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>179.814919149478</v>
+      </c>
       <c r="AD8" t="n">
-        <v>26.23084415584416</v>
+        <v>74.81112066038537</v>
       </c>
       <c r="AE8" t="n">
-        <v>182.6840909090909</v>
+        <v>47208.45004668534</v>
       </c>
       <c r="AF8" t="n">
-        <v>80.48636363636363</v>
+        <v>9351234.508955097</v>
       </c>
       <c r="AG8" t="n">
-        <v>101362.6623376623</v>
+        <v>78.83507342330873</v>
       </c>
       <c r="AH8" t="n">
-        <v>30662540.58441558</v>
+        <v>1.090421016891605</v>
       </c>
       <c r="AI8" t="n">
-        <v>83.50714285714285</v>
+        <v>24.92447767359452</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.545779220779221</v>
+        <v>178.5713399824813</v>
       </c>
       <c r="AK8" t="n">
-        <v>25.45454545454546</v>
+        <v>78.25634456123586</v>
       </c>
       <c r="AL8" t="n">
-        <v>184.2985409652076</v>
+        <v>112444.3887860328</v>
       </c>
       <c r="AM8" t="n">
-        <v>75.46329966329967</v>
+        <v>29883900.70074853</v>
       </c>
       <c r="AN8" t="n">
-        <v>54973.56902356903</v>
+        <v>83.19971606744704</v>
       </c>
       <c r="AO8" t="n">
-        <v>10320743.54657688</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>79.77401795735129</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.169668911335578</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>26.32937461843712</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>183.6718998015873</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>77.24677960927961</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>82713.63514957264</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>21095885.79822955</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>81.21642246642247</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>2.001869658119658</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>23.57415529564652</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>181.0135999721526</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>71.7866042420867</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>45308.36002042142</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6713726.358720877</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>78.96391789659333</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.068822519261116</v>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
+        <v>2.438863672559325</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2006,21 +1718,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>52305</v>
+        <v>31750</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2045,149 +1757,133 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>26.68492063492064</v>
+      </c>
+      <c r="O9" t="n">
+        <v>182.397619047619</v>
+      </c>
+      <c r="P9" t="n">
+        <v>76.54801587301587</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>54272.22222222223</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12557896.82539682</v>
+      </c>
+      <c r="S9" t="n">
+        <v>79.83809523809524</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.46984126984127</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26.40833333333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="W9" t="n">
+        <v>83.93282828282828</v>
+      </c>
+      <c r="X9" t="n">
+        <v>184214.6464646464</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>58695391.41414142</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>86.13308080808082</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.292676767676768</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>27.97499504852446</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>180.1576714861029</v>
+      </c>
       <c r="AD9" t="n">
-        <v>27.52676767676768</v>
+        <v>76.13800092427543</v>
       </c>
       <c r="AE9" t="n">
-        <v>186.559595959596</v>
+        <v>56937.47276688452</v>
       </c>
       <c r="AF9" t="n">
-        <v>80.07626262626263</v>
+        <v>10755348.25377963</v>
       </c>
       <c r="AG9" t="n">
-        <v>107352.5252525253</v>
+        <v>78.15959926057965</v>
       </c>
       <c r="AH9" t="n">
-        <v>25805498.73737374</v>
+        <v>1.417171717171717</v>
       </c>
       <c r="AI9" t="n">
-        <v>81.67752525252526</v>
+        <v>25.99626048293811</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.394191919191919</v>
+        <v>179.115309608155</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.9354797979798</v>
+        <v>80.14670329670329</v>
       </c>
       <c r="AL9" t="n">
-        <v>182.9472222222222</v>
+        <v>137935.6401821862</v>
       </c>
       <c r="AM9" t="n">
-        <v>75.41275252525253</v>
+        <v>39963876.06636784</v>
       </c>
       <c r="AN9" t="n">
-        <v>64851.64141414141</v>
+        <v>83.42561270965876</v>
       </c>
       <c r="AO9" t="n">
-        <v>11516161.61616162</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>80.1094696969697</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.561489898989899</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>27.08814657707847</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>182.916736862209</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>77.75546350650841</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>92405.71031708801</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>19085322.46996353</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>80.1773544452337</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.936447178552442</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>23.57733087514182</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>179.6616853835356</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>73.28050304790108</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>56944.89740976482</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>9963628.600753803</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>80.43357594754148</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.305141049554833</v>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
+        <v>2.579571826200116</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32384</v>
+        <v>61276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2212,149 +1908,133 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>26.83055555555555</v>
+      </c>
+      <c r="O10" t="n">
+        <v>184.0470959595959</v>
+      </c>
+      <c r="P10" t="n">
+        <v>83.96780303030303</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>131327.5252525253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>50801578.28282828</v>
+      </c>
+      <c r="S10" t="n">
+        <v>85.77032828282827</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.171338383838385</v>
+      </c>
+      <c r="U10" t="n">
+        <v>23.19141414141414</v>
+      </c>
+      <c r="V10" t="n">
+        <v>183.5227272727273</v>
+      </c>
+      <c r="W10" t="n">
+        <v>80.08964646464646</v>
+      </c>
+      <c r="X10" t="n">
+        <v>99655.93434343435</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>32757765.15151515</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>84.53030303030303</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.869191919191919</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>25.52250258799172</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>183.0462668219462</v>
+      </c>
       <c r="AD10" t="n">
-        <v>26.36979166666666</v>
+        <v>80.39087085921325</v>
       </c>
       <c r="AE10" t="n">
-        <v>182.3211805555556</v>
+        <v>100462.0212215321</v>
       </c>
       <c r="AF10" t="n">
-        <v>73.25868055555556</v>
+        <v>33515248.44720497</v>
       </c>
       <c r="AG10" t="n">
-        <v>46982.63888888888</v>
+        <v>83.48564958592132</v>
       </c>
       <c r="AH10" t="n">
-        <v>6123914.930555556</v>
+        <v>2.280020703933747</v>
       </c>
       <c r="AI10" t="n">
-        <v>76.78472222222223</v>
+        <v>24.00761796682849</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.282986111111111</v>
+        <v>180.9913018998545</v>
       </c>
       <c r="AK10" t="n">
-        <v>26.82962962962963</v>
+        <v>79.12814101103575</v>
       </c>
       <c r="AL10" t="n">
-        <v>180.9932098765432</v>
+        <v>104052.1856433041</v>
       </c>
       <c r="AM10" t="n">
-        <v>75.48364197530864</v>
+        <v>27565363.33184359</v>
       </c>
       <c r="AN10" t="n">
-        <v>43096.91358024692</v>
+        <v>83.60543553668553</v>
       </c>
       <c r="AO10" t="n">
-        <v>7639899.691358025</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>77.86450617283951</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.364814814814815</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>25.75021471285661</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>180.164657732666</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>71.04516356250103</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>39585.74583120507</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4159746.475765568</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>76.20272559493407</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.154800201136631</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>26.6790488612599</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>179.7500718708536</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>73.8130229577211</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>43522.02940630443</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6014422.18529712</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>76.75671504469234</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.257036381804184</v>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
+        <v>1.818090498682604</v>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11307</v>
+        <v>30404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2379,149 +2059,133 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>26.67777777777778</v>
+      </c>
+      <c r="O11" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>77.00317460317459</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>56571.42857142857</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11921428.57142857</v>
+      </c>
+      <c r="S11" t="n">
+        <v>78.99523809523809</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.342857142857143</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.69475308641975</v>
+      </c>
+      <c r="V11" t="n">
+        <v>182.6685185185185</v>
+      </c>
+      <c r="W11" t="n">
+        <v>78.6324074074074</v>
+      </c>
+      <c r="X11" t="n">
+        <v>72117.59259259258</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19674814.81481481</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>80.92716049382716</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.459259259259259</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>25.65828227124183</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>183.5746527777778</v>
+      </c>
       <c r="AD11" t="n">
-        <v>25.5125</v>
+        <v>75.98420138888889</v>
       </c>
       <c r="AE11" t="n">
-        <v>181.0447916666666</v>
+        <v>54133.56821895425</v>
       </c>
       <c r="AF11" t="n">
-        <v>76.19548611111111</v>
+        <v>9827676.674836602</v>
       </c>
       <c r="AG11" t="n">
-        <v>49713.19444444445</v>
+        <v>78.44661968954247</v>
       </c>
       <c r="AH11" t="n">
-        <v>11072256.94444444</v>
+        <v>1.205269607843138</v>
       </c>
       <c r="AI11" t="n">
-        <v>79.38194444444444</v>
+        <v>27.68444958702957</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.171180555555556</v>
+        <v>183.2248136681573</v>
       </c>
       <c r="AK11" t="n">
-        <v>25.52951388888889</v>
+        <v>74.77165497423496</v>
       </c>
       <c r="AL11" t="n">
-        <v>182.2118055555555</v>
+        <v>61226.38597881116</v>
       </c>
       <c r="AM11" t="n">
-        <v>83.14236111111111</v>
+        <v>8704417.793344522</v>
       </c>
       <c r="AN11" t="n">
-        <v>146975.6944444444</v>
+        <v>76.70123769514895</v>
       </c>
       <c r="AO11" t="n">
-        <v>53977430.55555556</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>85.375</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>3.243055555555555</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>24.74283804430863</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>179.814919149478</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>74.81112066038537</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>47208.45004668534</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9351234.508955097</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>78.83507342330873</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.090421016891605</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>24.92447767359452</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>178.5713399824813</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>78.25634456123586</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>112444.3887860328</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>29883900.70074853</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>83.19971606744704</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.438863672559325</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
+        <v>1.044355839092681</v>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31750</v>
+        <v>32261</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2546,281 +2210,1457 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>26.82962962962963</v>
+      </c>
+      <c r="O12" t="n">
+        <v>180.9932098765432</v>
+      </c>
+      <c r="P12" t="n">
+        <v>75.48364197530864</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>43096.91358024692</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7639899.691358025</v>
+      </c>
+      <c r="S12" t="n">
+        <v>77.86450617283951</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.364814814814815</v>
+      </c>
+      <c r="U12" t="n">
+        <v>26.67777777777778</v>
+      </c>
+      <c r="V12" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>77.00317460317459</v>
+      </c>
+      <c r="X12" t="n">
+        <v>56571.42857142857</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11921428.57142857</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>78.99523809523809</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.342857142857143</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>26.6790488612599</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>179.7500718708536</v>
+      </c>
       <c r="AD12" t="n">
-        <v>26.68492063492064</v>
+        <v>73.8130229577211</v>
       </c>
       <c r="AE12" t="n">
-        <v>182.397619047619</v>
+        <v>43522.02940630443</v>
       </c>
       <c r="AF12" t="n">
-        <v>76.54801587301587</v>
+        <v>6014422.18529712</v>
       </c>
       <c r="AG12" t="n">
-        <v>54272.22222222223</v>
+        <v>76.75671504469234</v>
       </c>
       <c r="AH12" t="n">
-        <v>12557896.82539682</v>
+        <v>1.257036381804184</v>
       </c>
       <c r="AI12" t="n">
-        <v>79.83809523809524</v>
+        <v>25.65828227124183</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.46984126984127</v>
+        <v>183.5746527777778</v>
       </c>
       <c r="AK12" t="n">
-        <v>26.11043771043771</v>
+        <v>75.98420138888889</v>
       </c>
       <c r="AL12" t="n">
-        <v>181.2525252525253</v>
+        <v>54133.56821895425</v>
       </c>
       <c r="AM12" t="n">
-        <v>83.45544332210999</v>
+        <v>9827676.674836602</v>
       </c>
       <c r="AN12" t="n">
-        <v>179817.0594837262</v>
+        <v>78.44661968954247</v>
       </c>
       <c r="AO12" t="n">
-        <v>57233782.26711561</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>86.05768799102133</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.229854096520763</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>27.97499504852446</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>180.1576714861029</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>76.13800092427543</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>56937.47276688452</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10755348.25377963</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>78.15959926057965</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.417171717171717</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>26.12895111710901</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>179.2506455776193</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>80.13040293040292</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>139133.2674635306</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>39650429.5193111</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>83.4153594456226</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2.583958025405394</v>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
+        <v>1.205269607843138</v>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>26.03409090909091</v>
+      </c>
+      <c r="O13" t="n">
+        <v>183.8497474747475</v>
+      </c>
+      <c r="P13" t="n">
+        <v>79.49368686868686</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>104011.3636363636</v>
+      </c>
+      <c r="R13" t="n">
+        <v>25567234.84848485</v>
+      </c>
+      <c r="S13" t="n">
+        <v>82.13131313131312</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.305555555555555</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.5125</v>
+      </c>
+      <c r="V13" t="n">
+        <v>181.0447916666666</v>
+      </c>
+      <c r="W13" t="n">
+        <v>76.19548611111111</v>
+      </c>
+      <c r="X13" t="n">
+        <v>49713.19444444445</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11072256.94444444</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>79.38194444444444</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.171180555555556</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>24.14769755416209</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>181.5568159374474</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>76.31276909232072</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>82354.90676728878</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17835579.75890195</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>81.13763518851476</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.527035458582226</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>24.74283804430863</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>179.814919149478</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>74.81112066038537</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>47208.45004668534</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>9351234.508955097</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>78.83507342330873</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.090421016891605</v>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>25.45454545454546</v>
+      </c>
+      <c r="O14" t="n">
+        <v>184.2985409652076</v>
+      </c>
+      <c r="P14" t="n">
+        <v>75.46329966329967</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>54973.56902356903</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10320743.54657688</v>
+      </c>
+      <c r="S14" t="n">
+        <v>79.77401795735129</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.169668911335578</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25.62891414141414</v>
+      </c>
+      <c r="V14" t="n">
+        <v>183.1918560606061</v>
+      </c>
+      <c r="W14" t="n">
+        <v>73.92004419191917</v>
+      </c>
+      <c r="X14" t="n">
+        <v>43350.41035353535</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5904977.904040404</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>77.7366792929293</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.064741161616162</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>23.57415529564652</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.0135999721526</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>71.7866042420867</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>45308.36002042142</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>6713726.358720877</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>78.96391789659333</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.068822519261116</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>26.54408939014202</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>180.4215956558062</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>71.94489870509608</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>41971.8723893066</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>3891265.142021721</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>74.66696428571429</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.035609857978279</v>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>25.95499438832772</v>
+      </c>
+      <c r="O15" t="n">
+        <v>183.1753086419753</v>
+      </c>
+      <c r="P15" t="n">
+        <v>75.44096520763188</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>64645.90347923681</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11371156.00448934</v>
+      </c>
+      <c r="S15" t="n">
+        <v>80.0973063973064</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.560830527497194</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.68492063492064</v>
+      </c>
+      <c r="V15" t="n">
+        <v>182.397619047619</v>
+      </c>
+      <c r="W15" t="n">
+        <v>76.54801587301587</v>
+      </c>
+      <c r="X15" t="n">
+        <v>54272.22222222223</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12557896.82539682</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>79.83809523809524</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.46984126984127</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>23.54790522234828</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>179.6992758964761</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>73.4785027092454</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>57034.35325312429</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10071142.08955894</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>80.5590119533702</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.312903155159852</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>27.97499504852446</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>180.1576714861029</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>76.13800092427543</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>56937.47276688452</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>10755348.25377963</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>78.15959926057965</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.417171717171717</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>26.40833333333333</v>
+      </c>
+      <c r="O16" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="P16" t="n">
+        <v>83.93282828282828</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>184214.6464646464</v>
+      </c>
+      <c r="R16" t="n">
+        <v>58695391.41414142</v>
+      </c>
+      <c r="S16" t="n">
+        <v>86.13308080808082</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.292676767676768</v>
+      </c>
+      <c r="U16" t="n">
+        <v>26.36979166666666</v>
+      </c>
+      <c r="V16" t="n">
+        <v>182.3211805555556</v>
+      </c>
+      <c r="W16" t="n">
+        <v>73.25868055555556</v>
+      </c>
+      <c r="X16" t="n">
+        <v>46982.63888888888</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6123914.930555556</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>76.78472222222223</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.282986111111111</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.99626048293811</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>179.115309608155</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>80.14670329670329</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>137935.6401821862</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>39963876.06636784</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>83.42561270965876</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.579571826200116</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>25.75021471285661</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>180.164657732666</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>71.04516356250103</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>39585.74583120507</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4159746.475765568</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>76.20272559493407</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.154800201136631</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
   liverpool </t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>61276</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E17" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>28.09671717171717</v>
+      </c>
+      <c r="O17" t="n">
+        <v>182.8133838383839</v>
+      </c>
+      <c r="P17" t="n">
+        <v>76.40744949494949</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>46834.59595959596</v>
+      </c>
+      <c r="R17" t="n">
+        <v>10624633.83838384</v>
+      </c>
+      <c r="S17" t="n">
+        <v>78.58636363636363</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.504166666666667</v>
+      </c>
+      <c r="U17" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>184.3111111111111</v>
+      </c>
+      <c r="W17" t="n">
+        <v>76.52222222222223</v>
+      </c>
+      <c r="X17" t="n">
+        <v>66777.77777777778</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10556666.66666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>78.24444444444445</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>27.18699875832229</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>182.8718385644856</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>74.08250455971044</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>40747.49259455142</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>6296446.755314403</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>76.77187047701754</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.249512442894796</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>26.94927536231884</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>182.8294283413849</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>74.48236714975845</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>61881.32045088566</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>7182773.752012882</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>77.15547504025764</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.262399355877617</v>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>23.19141414141414</v>
+      </c>
+      <c r="O18" t="n">
+        <v>183.5227272727273</v>
+      </c>
+      <c r="P18" t="n">
+        <v>80.08964646464646</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>99655.93434343435</v>
+      </c>
+      <c r="R18" t="n">
+        <v>32757765.15151515</v>
+      </c>
+      <c r="S18" t="n">
+        <v>84.53030303030303</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.869191919191919</v>
+      </c>
+      <c r="U18" t="n">
+        <v>27.52676767676768</v>
+      </c>
+      <c r="V18" t="n">
+        <v>186.559595959596</v>
+      </c>
+      <c r="W18" t="n">
+        <v>80.07626262626263</v>
+      </c>
+      <c r="X18" t="n">
+        <v>107352.5252525252</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25805498.73737374</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>81.67752525252526</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.394191919191919</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24.00761796682849</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>180.9913018998545</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>79.12814101103575</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>104052.1856433041</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>27565363.33184359</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>83.60543553668553</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.818090498682604</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>27.08814657707847</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>182.916736862209</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>77.75546350650841</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>92405.71031708801</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>19085322.46996353</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>80.1773544452337</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.936447178552442</v>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>25.69475308641975</v>
+      </c>
+      <c r="O19" t="n">
+        <v>182.6685185185185</v>
+      </c>
+      <c r="P19" t="n">
+        <v>78.6324074074074</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>72117.59259259258</v>
+      </c>
+      <c r="R19" t="n">
+        <v>19674814.81481481</v>
+      </c>
+      <c r="S19" t="n">
+        <v>80.92716049382716</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.459259259259259</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.47301587301587</v>
+      </c>
+      <c r="V19" t="n">
+        <v>184.3238095238095</v>
+      </c>
+      <c r="W19" t="n">
+        <v>82.2126984126984</v>
+      </c>
+      <c r="X19" t="n">
+        <v>111207.9365079365</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>39690476.19047619</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>84.74444444444445</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.75079365079365</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>27.68444958702957</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>183.2248136681573</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>74.77165497423496</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>61226.38597881116</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8704417.793344522</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>76.70123769514895</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.044355839092681</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>24.51208419848125</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>184.1109614241967</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>78.03863362944246</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>77662.63409792821</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>22629170.59043898</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>82.37388367351602</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.866579294888119</v>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>28.14506172839506</v>
+      </c>
+      <c r="O20" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="P20" t="n">
+        <v>79.56481481481481</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>86324.07407407409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>20516203.70370371</v>
+      </c>
+      <c r="S20" t="n">
+        <v>80.69907407407408</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.294753086419753</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.175</v>
+      </c>
+      <c r="V20" t="n">
+        <v>182.9607142857143</v>
+      </c>
+      <c r="W20" t="n">
+        <v>80.40714285714286</v>
+      </c>
+      <c r="X20" t="n">
+        <v>100239.2857142857</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>30724553.57142857</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>83.47857142857143</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.510714285714286</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>28.7875816993464</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>180.3327886710239</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>77.8787672476398</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>78483.52396514161</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15851134.71314452</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>79.53363289760348</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.014206608569354</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>26.79118017399267</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>183.8941220238095</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>77.7919184981685</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>85800.4407051282</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>21138767.74267399</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>81.35531135531136</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>2.040064102564103</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+      <c r="H21" t="n">
         <v>48</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I21" t="n">
         <v>481</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K21" t="n">
         <v>20242025</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="n">
+      <c r="N21" t="n">
+        <v>25.52951388888889</v>
+      </c>
+      <c r="O21" t="n">
+        <v>182.2118055555555</v>
+      </c>
+      <c r="P21" t="n">
+        <v>83.14236111111111</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>146975.6944444444</v>
+      </c>
+      <c r="R21" t="n">
+        <v>53977430.55555556</v>
+      </c>
+      <c r="S21" t="n">
+        <v>85.375</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.243055555555555</v>
+      </c>
+      <c r="U21" t="n">
         <v>26.83055555555555</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="V21" t="n">
         <v>184.0470959595959</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="W21" t="n">
         <v>83.96780303030303</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="X21" t="n">
         <v>131327.5252525253</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="Y21" t="n">
         <v>50801578.28282828</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="Z21" t="n">
         <v>85.77032828282827</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AA21" t="n">
         <v>3.171338383838385</v>
       </c>
-      <c r="AK13" t="n">
-        <v>23.21875901875902</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>183.4974025974026</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>80.01673881673881</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>99678.21067821069</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>32337445.88744589</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>84.46320346320347</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.850505050505051</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="AB21" t="n">
+        <v>24.92447767359452</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>178.5713399824813</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>78.25634456123586</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>112444.3887860328</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>29883900.70074853</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>83.19971606744704</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.438863672559325</v>
+      </c>
+      <c r="AI21" t="n">
         <v>25.52250258799172</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AJ21" t="n">
         <v>183.0462668219462</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AK21" t="n">
         <v>80.39087085921325</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AL21" t="n">
         <v>100462.0212215321</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AM21" t="n">
         <v>33515248.44720497</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AN21" t="n">
         <v>83.48564958592132</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AO21" t="n">
         <v>2.280020703933747</v>
       </c>
-      <c r="AY13" t="n">
-        <v>23.99510080562712</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>180.9560457086773</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>79.08522237995922</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>103841.9536603747</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>27486265.57652873</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>83.5558719058719</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.819314311419574</v>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ21"/>
+  <dimension ref="A1:BG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,150 +495,230 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -655,7 +735,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
@@ -701,95 +781,143 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="O2" t="n">
+        <v>183</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>241</v>
+      </c>
+      <c r="R2" t="n">
+        <v>363000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>253</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>30</v>
+      </c>
+      <c r="W2" t="n">
+        <v>181</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>78500</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD2" t="n">
         <v>25.47301587301587</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AE2" t="n">
         <v>184.3238095238095</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AF2" t="n">
         <v>82.2126984126984</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AG2" t="n">
         <v>111207.9365079365</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AH2" t="n">
         <v>39690476.19047619</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AI2" t="n">
         <v>84.74444444444445</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AJ2" t="n">
         <v>2.75079365079365</v>
       </c>
-      <c r="U2" t="n">
-        <v>28.14506172839506</v>
-      </c>
-      <c r="V2" t="n">
-        <v>182.375</v>
-      </c>
-      <c r="W2" t="n">
-        <v>79.56481481481481</v>
-      </c>
-      <c r="X2" t="n">
-        <v>86324.07407407409</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>20516203.70370371</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>80.69907407407408</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.294753086419753</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AK2" t="n">
+        <v>28.10763888888889</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>182.3385416666667</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>79.53819444444444</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>86017.36111111112</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>20511284.72222222</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>80.703125</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2.289930555555555</v>
+      </c>
+      <c r="AR2" t="n">
         <v>24.51208419848125</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AS2" t="n">
         <v>184.1109614241967</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AT2" t="n">
         <v>78.03863362944246</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AU2" t="n">
         <v>77662.63409792821</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AV2" t="n">
         <v>22629170.59043898</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AW2" t="n">
         <v>82.37388367351602</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AX2" t="n">
         <v>1.866579294888119</v>
       </c>
-      <c r="AI2" t="n">
-        <v>28.7875816993464</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>180.3327886710239</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>77.8787672476398</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>78483.52396514161</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>15851134.71314452</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>79.53363289760348</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2.014206608569354</v>
-      </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AY2" t="n">
+        <v>28.76884191176471</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>180.7415747549019</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>77.94955065359477</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>78614.27696078431</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16133307.80228758</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>79.61596200980392</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2.047232434640523</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
@@ -806,7 +934,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
@@ -852,95 +980,143 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="O3" t="n">
-        <v>184.3111111111111</v>
+        <v>190</v>
       </c>
       <c r="P3" t="n">
-        <v>76.52222222222223</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>66777.77777777778</v>
+        <v>74</v>
       </c>
       <c r="R3" t="n">
-        <v>10556666.66666667</v>
+        <v>66000</v>
       </c>
       <c r="S3" t="n">
-        <v>78.24444444444445</v>
+        <v>4200000</v>
       </c>
       <c r="T3" t="n">
-        <v>1.444444444444444</v>
+        <v>74</v>
       </c>
       <c r="U3" t="n">
-        <v>26.03409090909091</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>183.8497474747475</v>
+        <v>29</v>
       </c>
       <c r="W3" t="n">
-        <v>79.49368686868686</v>
+        <v>178</v>
       </c>
       <c r="X3" t="n">
-        <v>104011.3636363636</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>25567234.84848485</v>
+        <v>82</v>
       </c>
       <c r="Z3" t="n">
-        <v>82.13131313131312</v>
+        <v>130000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.305555555555555</v>
+        <v>29500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>26.94927536231884</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="n">
-        <v>182.8294283413849</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>74.48236714975845</v>
+        <v>27.275</v>
       </c>
       <c r="AE3" t="n">
-        <v>61881.32045088566</v>
+        <v>184.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>7182773.752012882</v>
+        <v>76.44999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>77.15547504025764</v>
+        <v>66687.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.262399355877617</v>
+        <v>10426250</v>
       </c>
       <c r="AI3" t="n">
-        <v>24.14769755416209</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>181.5568159374474</v>
+        <v>1.45</v>
       </c>
       <c r="AK3" t="n">
-        <v>76.31276909232072</v>
+        <v>25.94805194805195</v>
       </c>
       <c r="AL3" t="n">
-        <v>82354.90676728878</v>
+        <v>183.8282828282828</v>
       </c>
       <c r="AM3" t="n">
-        <v>17835579.75890195</v>
+        <v>79.27849927849927</v>
       </c>
       <c r="AN3" t="n">
-        <v>81.13763518851476</v>
+        <v>102714.2857142857</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.527035458582226</v>
-      </c>
-      <c r="AP3" t="inlineStr">
+        <v>25135281.38528138</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>82.05916305916305</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.271284271284272</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>26.92119565217391</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>182.9494112318841</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>74.70570652173913</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>62768.65942028986</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7449098.731884058</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>77.26730072463766</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.262590579710145</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>24.12117815713762</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>181.5819393026609</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>76.11255243204002</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>81487.24038710554</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>17583519.72445937</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>81.04165109979918</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.527496306406898</v>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -957,7 +1133,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
@@ -1003,95 +1179,143 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.62891414141414</v>
+        <v>27.5</v>
       </c>
       <c r="O4" t="n">
-        <v>183.1918560606061</v>
+        <v>184</v>
       </c>
       <c r="P4" t="n">
-        <v>73.92004419191917</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>43350.41035353535</v>
+        <v>141</v>
       </c>
       <c r="R4" t="n">
-        <v>5904977.904040404</v>
+        <v>48000</v>
       </c>
       <c r="S4" t="n">
-        <v>77.7366792929293</v>
+        <v>4400000</v>
       </c>
       <c r="T4" t="n">
-        <v>1.064741161616162</v>
+        <v>143</v>
       </c>
       <c r="U4" t="n">
-        <v>28.09671717171717</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>182.8133838383839</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>76.40744949494949</v>
+        <v>191.5</v>
       </c>
       <c r="X4" t="n">
-        <v>46834.59595959596</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>10624633.83838384</v>
+        <v>144</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.58636363636363</v>
+        <v>98000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.504166666666667</v>
+        <v>10100000</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.54408939014202</v>
+        <v>162</v>
       </c>
       <c r="AC4" t="n">
-        <v>180.4215956558062</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>71.94489870509608</v>
+        <v>25.57590187590188</v>
       </c>
       <c r="AE4" t="n">
-        <v>41971.8723893066</v>
+        <v>183.2971861471862</v>
       </c>
       <c r="AF4" t="n">
-        <v>3891265.142021721</v>
+        <v>74.01251803751802</v>
       </c>
       <c r="AG4" t="n">
-        <v>74.66696428571429</v>
+        <v>43945.92352092352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.035609857978279</v>
+        <v>6017377.344877345</v>
       </c>
       <c r="AI4" t="n">
-        <v>27.18699875832229</v>
+        <v>77.84191919191919</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182.8718385644856</v>
+        <v>1.073989898989899</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.08250455971044</v>
+        <v>27.96767676767677</v>
       </c>
       <c r="AL4" t="n">
-        <v>40747.49259455142</v>
+        <v>182.8906204906205</v>
       </c>
       <c r="AM4" t="n">
-        <v>6296446.755314403</v>
+        <v>76.43968253968254</v>
       </c>
       <c r="AN4" t="n">
-        <v>76.77187047701754</v>
+        <v>46823.95382395382</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.249512442894796</v>
-      </c>
-      <c r="AP4" t="inlineStr">
+        <v>10775230.88023088</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>78.68311688311688</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.498268398268398</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>26.55832438238453</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>180.394522019334</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>72.1671858216971</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>42055.15574650913</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3994382.38453276</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>74.90510204081633</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.032760472610097</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>27.38537360311257</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>182.6641517183797</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>74.18448429634091</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>40640.92916887035</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6262252.599728703</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>76.87668761997806</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.264034831589979</v>
+      </c>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>joAFj9hO</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -1108,7 +1332,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
@@ -1154,95 +1378,143 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26.175</v>
+        <v>27.5</v>
       </c>
       <c r="O5" t="n">
-        <v>182.9607142857143</v>
+        <v>181</v>
       </c>
       <c r="P5" t="n">
-        <v>80.40714285714286</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>100239.2857142857</v>
+        <v>156</v>
       </c>
       <c r="R5" t="n">
-        <v>30724553.57142857</v>
+        <v>163000</v>
       </c>
       <c r="S5" t="n">
-        <v>83.47857142857143</v>
+        <v>24500000</v>
       </c>
       <c r="T5" t="n">
-        <v>2.510714285714286</v>
+        <v>160</v>
       </c>
       <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>177</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>232</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>191000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>239</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26.17083333333333</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>182.9708333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>80.29166666666667</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>99379.16666666667</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>30661979.16666667</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>83.40833333333335</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.479166666666667</v>
+      </c>
+      <c r="AK5" t="n">
         <v>25.45454545454546</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AL5" t="n">
         <v>184.2985409652076</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AM5" t="n">
         <v>75.46329966329967</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AN5" t="n">
         <v>54973.56902356903</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AO5" t="n">
         <v>10320743.54657688</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AP5" t="n">
         <v>79.77401795735129</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AQ5" t="n">
         <v>1.169668911335578</v>
       </c>
-      <c r="AB5" t="n">
-        <v>26.79118017399267</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>183.8941220238095</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>77.7919184981685</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>85800.4407051282</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>21138767.74267399</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>81.35531135531136</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.040064102564103</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AR5" t="n">
+        <v>26.86611067503924</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>183.7551870748299</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>78.04790685504972</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>88124.31318681317</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>21860734.56305599</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>81.52035583464155</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2.102930402930403</v>
+      </c>
+      <c r="AY5" t="n">
         <v>23.57415529564652</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AZ5" t="n">
         <v>181.0135999721526</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="BA5" t="n">
         <v>71.7866042420867</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="BB5" t="n">
         <v>45308.36002042142</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BC5" t="n">
         <v>6713726.358720877</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BD5" t="n">
         <v>78.96391789659333</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="BE5" t="n">
         <v>1.068822519261116</v>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -1259,7 +1531,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
@@ -1305,95 +1577,143 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.52676767676768</v>
+        <v>25.8</v>
       </c>
       <c r="O6" t="n">
-        <v>186.559595959596</v>
+        <v>187</v>
       </c>
       <c r="P6" t="n">
-        <v>80.07626262626263</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>107352.5252525252</v>
+        <v>397</v>
       </c>
       <c r="R6" t="n">
-        <v>25805498.73737374</v>
+        <v>515000</v>
       </c>
       <c r="S6" t="n">
-        <v>81.67752525252526</v>
+        <v>137100000</v>
       </c>
       <c r="T6" t="n">
-        <v>2.394191919191919</v>
+        <v>416</v>
       </c>
       <c r="U6" t="n">
-        <v>25.95499438832772</v>
+        <v>12</v>
       </c>
       <c r="V6" t="n">
-        <v>183.1753086419753</v>
+        <v>26.5</v>
       </c>
       <c r="W6" t="n">
-        <v>75.44096520763188</v>
+        <v>185.5</v>
       </c>
       <c r="X6" t="n">
-        <v>64645.90347923681</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="n">
-        <v>11371156.00448934</v>
+        <v>162</v>
       </c>
       <c r="Z6" t="n">
-        <v>80.0973063973064</v>
+        <v>253000</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.560830527497194</v>
+        <v>69500000</v>
       </c>
       <c r="AB6" t="n">
-        <v>27.08814657707847</v>
+        <v>167</v>
       </c>
       <c r="AC6" t="n">
-        <v>182.916736862209</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>77.75546350650841</v>
+        <v>27.59261363636364</v>
       </c>
       <c r="AE6" t="n">
-        <v>92405.71031708801</v>
+        <v>186.4670454545455</v>
       </c>
       <c r="AF6" t="n">
-        <v>19085322.46996353</v>
+        <v>80.06079545454546</v>
       </c>
       <c r="AG6" t="n">
-        <v>80.1773544452337</v>
+        <v>107284.0909090909</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.936447178552442</v>
+        <v>25606186.07954545</v>
       </c>
       <c r="AI6" t="n">
-        <v>23.54790522234828</v>
+        <v>81.58721590909092</v>
       </c>
       <c r="AJ6" t="n">
-        <v>179.6992758964761</v>
+        <v>2.393465909090909</v>
       </c>
       <c r="AK6" t="n">
-        <v>73.4785027092454</v>
+        <v>25.49103535353535</v>
       </c>
       <c r="AL6" t="n">
-        <v>57034.35325312429</v>
+        <v>183.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>10071142.08955894</v>
+        <v>75.24608585858586</v>
       </c>
       <c r="AN6" t="n">
-        <v>80.5590119533702</v>
+        <v>62712.75252525252</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.312903155159852</v>
-      </c>
-      <c r="AP6" t="inlineStr">
+        <v>11056439.39393939</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>80.2344696969697</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.519823232323232</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>27.06010239921327</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>182.8282039699851</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>77.89677144482195</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>93386.11160672402</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>19926261.21620897</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>80.40264875088792</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.983190575871497</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>23.50226294035921</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>179.8573375574486</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>73.54375033050978</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>57163.64740976482</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>10161964.19857989</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>80.67780149101975</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.319407353902659</v>
+      </c>
+      <c r="BF6" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
         </is>
@@ -1410,7 +1730,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
@@ -1456,95 +1776,143 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>26.36979166666666</v>
+        <v>23</v>
       </c>
       <c r="O7" t="n">
-        <v>182.3211805555556</v>
+        <v>186</v>
       </c>
       <c r="P7" t="n">
-        <v>73.25868055555556</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>46982.63888888888</v>
+        <v>146</v>
       </c>
       <c r="R7" t="n">
-        <v>6123914.930555556</v>
+        <v>56000</v>
       </c>
       <c r="S7" t="n">
-        <v>76.78472222222223</v>
+        <v>10800000</v>
       </c>
       <c r="T7" t="n">
-        <v>1.282986111111111</v>
+        <v>161</v>
       </c>
       <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>210</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>97000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>26.23214285714285</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>182.0178571428571</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>73.04166666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>45805.55555555555</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>6134871.031746032</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>76.76984126984128</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.291666666666666</v>
+      </c>
+      <c r="AK7" t="n">
         <v>26.82962962962963</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AL7" t="n">
         <v>180.9932098765432</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AM7" t="n">
         <v>75.48364197530864</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AN7" t="n">
         <v>43096.91358024692</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AO7" t="n">
         <v>7639899.691358025</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AP7" t="n">
         <v>77.86450617283951</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AQ7" t="n">
         <v>1.364814814814815</v>
       </c>
-      <c r="AB7" t="n">
-        <v>25.75021471285661</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>180.164657732666</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>71.04516356250103</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>39585.74583120507</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>4159746.475765568</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>76.20272559493407</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.154800201136631</v>
-      </c>
-      <c r="AI7" t="n">
+      <c r="AR7" t="n">
+        <v>26.18490064287278</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>180.2306944947038</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>71.28376355326819</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>40198.73678737842</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4128862.512508991</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>75.88715720339172</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.162786589915073</v>
+      </c>
+      <c r="AY7" t="n">
         <v>26.6790488612599</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AZ7" t="n">
         <v>179.7500718708536</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="BA7" t="n">
         <v>73.8130229577211</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="BB7" t="n">
         <v>43522.02940630443</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BC7" t="n">
         <v>6014422.18529712</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="BD7" t="n">
         <v>76.75671504469234</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="BE7" t="n">
         <v>1.257036381804184</v>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -1561,7 +1929,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
@@ -1607,95 +1975,143 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>25.5125</v>
+        <v>25.38888888888889</v>
       </c>
       <c r="O8" t="n">
-        <v>181.0447916666666</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="P8" t="n">
-        <v>76.19548611111111</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="Q8" t="n">
-        <v>49713.19444444445</v>
+        <v>140.8333333333333</v>
       </c>
       <c r="R8" t="n">
-        <v>11072256.94444444</v>
+        <v>102166.6666666667</v>
       </c>
       <c r="S8" t="n">
-        <v>79.38194444444444</v>
+        <v>21933333.33333333</v>
       </c>
       <c r="T8" t="n">
-        <v>1.171180555555556</v>
+        <v>144.5</v>
       </c>
       <c r="U8" t="n">
-        <v>25.52951388888889</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="V8" t="n">
-        <v>182.2118055555555</v>
+        <v>25.25</v>
       </c>
       <c r="W8" t="n">
-        <v>83.14236111111111</v>
+        <v>177.75</v>
       </c>
       <c r="X8" t="n">
-        <v>146975.6944444444</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>53977430.55555556</v>
+        <v>334</v>
       </c>
       <c r="Z8" t="n">
-        <v>85.375</v>
+        <v>645000</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.243055555555555</v>
+        <v>262000000</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.74283804430863</v>
+        <v>337</v>
       </c>
       <c r="AC8" t="n">
-        <v>179.814919149478</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>74.81112066038537</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="AE8" t="n">
-        <v>47208.45004668534</v>
+        <v>181.1369047619048</v>
       </c>
       <c r="AF8" t="n">
-        <v>9351234.508955097</v>
+        <v>76.23769841269841</v>
       </c>
       <c r="AG8" t="n">
-        <v>78.83507342330873</v>
+        <v>50315.07936507936</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.090421016891605</v>
+        <v>11196865.07936508</v>
       </c>
       <c r="AI8" t="n">
-        <v>24.92447767359452</v>
+        <v>79.3079365079365</v>
       </c>
       <c r="AJ8" t="n">
-        <v>178.5713399824813</v>
+        <v>1.181349206349207</v>
       </c>
       <c r="AK8" t="n">
-        <v>78.25634456123586</v>
+        <v>25.54166666666666</v>
       </c>
       <c r="AL8" t="n">
-        <v>112444.3887860328</v>
+        <v>182.0833333333333</v>
       </c>
       <c r="AM8" t="n">
-        <v>29883900.70074853</v>
+        <v>82.9563492063492</v>
       </c>
       <c r="AN8" t="n">
-        <v>83.19971606744704</v>
+        <v>145432.5396825397</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.438863672559325</v>
-      </c>
-      <c r="AP8" t="inlineStr">
+        <v>52640873.01587302</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>85.3015873015873</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.23015873015873</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>24.69249517989013</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>179.4823565789952</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>74.95420592479415</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>47333.46672002134</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9568077.534043919</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>79.00879139534602</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.103338305018978</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>24.8244030555366</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>178.7868885514072</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>77.94475092712671</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>110865.0157554661</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>29369100.80085546</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>83.19253264851091</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.385487054353514</v>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>GlJdeJqp</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>Aotm1TVI</t>
         </is>
@@ -1712,7 +2128,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
@@ -1758,95 +2174,143 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>26.68492063492064</v>
+        <v>24.27777777777778</v>
       </c>
       <c r="O9" t="n">
-        <v>182.397619047619</v>
+        <v>192.2777777777777</v>
       </c>
       <c r="P9" t="n">
-        <v>76.54801587301587</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="Q9" t="n">
-        <v>54272.22222222223</v>
+        <v>172.1666666666667</v>
       </c>
       <c r="R9" t="n">
-        <v>12557896.82539682</v>
+        <v>114500</v>
       </c>
       <c r="S9" t="n">
-        <v>79.83809523809524</v>
+        <v>18600000</v>
       </c>
       <c r="T9" t="n">
-        <v>1.46984126984127</v>
+        <v>184.5</v>
       </c>
       <c r="U9" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24.07142857142857</v>
+      </c>
+      <c r="W9" t="n">
+        <v>176.0714285714285</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>171.1428571428571</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>317571.4285714286</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>76214285.71428572</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>185</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26.66944444444444</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>182.4453703703704</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>76.5837962962963</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>54391.66666666666</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>12671250</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>79.9037037037037</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.492592592592593</v>
+      </c>
+      <c r="AK9" t="n">
         <v>26.40833333333333</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AL9" t="n">
         <v>181.0909090909091</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AM9" t="n">
         <v>83.93282828282828</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AN9" t="n">
         <v>184214.6464646464</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AO9" t="n">
         <v>58695391.41414142</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AP9" t="n">
         <v>86.13308080808082</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AQ9" t="n">
         <v>3.292676767676768</v>
       </c>
-      <c r="AB9" t="n">
-        <v>27.97499504852446</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>180.1576714861029</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>76.13800092427543</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>56937.47276688452</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>10755348.25377963</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>78.15959926057965</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.417171717171717</v>
-      </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
+        <v>28.03436942959002</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>180.3586304218657</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>76.18650103980985</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>57310.90686274509</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10799141.78550208</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>78.13579916815212</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.406818181818182</v>
+      </c>
+      <c r="AY9" t="n">
         <v>25.99626048293811</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AZ9" t="n">
         <v>179.115309608155</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="BA9" t="n">
         <v>80.14670329670329</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="BB9" t="n">
         <v>137935.6401821862</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="BC9" t="n">
         <v>39963876.06636784</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="BD9" t="n">
         <v>83.42561270965876</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="BE9" t="n">
         <v>2.579571826200116</v>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -1863,7 +2327,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
@@ -1909,95 +2373,143 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>26.83055555555555</v>
+        <v>22.75</v>
       </c>
       <c r="O10" t="n">
-        <v>184.0470959595959</v>
+        <v>173.5</v>
       </c>
       <c r="P10" t="n">
-        <v>83.96780303030303</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>131327.5252525253</v>
+        <v>120.75</v>
       </c>
       <c r="R10" t="n">
-        <v>50801578.28282828</v>
+        <v>122250</v>
       </c>
       <c r="S10" t="n">
-        <v>85.77032828282827</v>
+        <v>55375000</v>
       </c>
       <c r="T10" t="n">
-        <v>3.171338383838385</v>
+        <v>129.5</v>
       </c>
       <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>21.91666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>173</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>104000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>21750000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>195.6666666666667</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>26.83232323232323</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>184.118759018759</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>83.92424242424242</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>130854.8340548341</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>50455050.5050505</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>85.698556998557</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.156854256854257</v>
+      </c>
+      <c r="AK10" t="n">
         <v>23.19141414141414</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AL10" t="n">
         <v>183.5227272727273</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AM10" t="n">
         <v>80.08964646464646</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AN10" t="n">
         <v>99655.93434343435</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AO10" t="n">
         <v>32757765.15151515</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AP10" t="n">
         <v>84.53030303030303</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AQ10" t="n">
         <v>1.869191919191919</v>
       </c>
-      <c r="AB10" t="n">
-        <v>25.52250258799172</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>183.0462668219462</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>80.39087085921325</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>100462.0212215321</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>33515248.44720497</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>83.48564958592132</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.280020703933747</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
+        <v>25.60428867199053</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>182.9385906536528</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>80.43242383910085</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>101456.595681751</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>33863855.36823425</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>83.49788524105294</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.305737947352854</v>
+      </c>
+      <c r="AY10" t="n">
         <v>24.00761796682849</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AZ10" t="n">
         <v>180.9913018998545</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="BA10" t="n">
         <v>79.12814101103575</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="BB10" t="n">
         <v>104052.1856433041</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="BC10" t="n">
         <v>27565363.33184359</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="BD10" t="n">
         <v>83.60543553668553</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="BE10" t="n">
         <v>1.818090498682604</v>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>CznGurCt</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
@@ -2014,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
@@ -2060,95 +2572,143 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26.67777777777778</v>
+        <v>27.5</v>
       </c>
       <c r="O11" t="n">
-        <v>183.3</v>
+        <v>190.5</v>
       </c>
       <c r="P11" t="n">
-        <v>77.00317460317459</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>56571.42857142857</v>
+        <v>135.25</v>
       </c>
       <c r="R11" t="n">
-        <v>11921428.57142857</v>
+        <v>100250</v>
       </c>
       <c r="S11" t="n">
-        <v>78.99523809523809</v>
+        <v>20000000</v>
       </c>
       <c r="T11" t="n">
-        <v>1.342857142857143</v>
+        <v>138</v>
       </c>
       <c r="U11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>186.7666666666667</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>151000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>26.74074074074074</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>183</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>77.03703703703702</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>57500</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>78.94444444444444</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AK11" t="n">
         <v>25.69475308641975</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AL11" t="n">
         <v>182.6685185185185</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AM11" t="n">
         <v>78.6324074074074</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AN11" t="n">
         <v>72117.59259259258</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AO11" t="n">
         <v>19674814.81481481</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AP11" t="n">
         <v>80.92716049382716</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AQ11" t="n">
         <v>1.459259259259259</v>
       </c>
-      <c r="AB11" t="n">
-        <v>25.65828227124183</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>183.5746527777778</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>75.98420138888889</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>54133.56821895425</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>9827676.674836602</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>78.44661968954247</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.205269607843138</v>
-      </c>
-      <c r="AI11" t="n">
+      <c r="AR11" t="n">
+        <v>25.59265873015873</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>183.5138888888889</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>76.12480158730159</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>54572.81746031746</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10166924.6031746</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>78.71210317460317</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.226190476190476</v>
+      </c>
+      <c r="AY11" t="n">
         <v>27.68444958702957</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AZ11" t="n">
         <v>183.2248136681573</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="BA11" t="n">
         <v>74.77165497423496</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="BB11" t="n">
         <v>61226.38597881116</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="BC11" t="n">
         <v>8704417.793344522</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="BD11" t="n">
         <v>76.70123769514895</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="BE11" t="n">
         <v>1.044355839092681</v>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
         </is>
@@ -2211,95 +2771,143 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>25.6547619047619</v>
+      </c>
+      <c r="O12" t="n">
+        <v>188.2380952380952</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>192.7142857142857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>99285.71428571429</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10071428.57142857</v>
+      </c>
+      <c r="T12" t="n">
+        <v>202.4285714285714</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="V12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>100250</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>138</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD12" t="n">
         <v>26.82962962962963</v>
       </c>
-      <c r="O12" t="n">
+      <c r="AE12" t="n">
         <v>180.9932098765432</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AF12" t="n">
         <v>75.48364197530864</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AG12" t="n">
         <v>43096.91358024692</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AH12" t="n">
         <v>7639899.691358025</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AI12" t="n">
         <v>77.86450617283951</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AJ12" t="n">
         <v>1.364814814814815</v>
       </c>
-      <c r="U12" t="n">
-        <v>26.67777777777778</v>
-      </c>
-      <c r="V12" t="n">
-        <v>183.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>77.00317460317459</v>
-      </c>
-      <c r="X12" t="n">
-        <v>56571.42857142857</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>11921428.57142857</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>78.99523809523809</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.342857142857143</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
+        <v>26.74074074074074</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>183</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>77.03703703703702</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>57500</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>78.94444444444444</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AR12" t="n">
         <v>26.6790488612599</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AS12" t="n">
         <v>179.7500718708536</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AT12" t="n">
         <v>73.8130229577211</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AU12" t="n">
         <v>43522.02940630443</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AV12" t="n">
         <v>6014422.18529712</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AW12" t="n">
         <v>76.75671504469234</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AX12" t="n">
         <v>1.257036381804184</v>
       </c>
-      <c r="AI12" t="n">
-        <v>25.65828227124183</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>183.5746527777778</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>75.98420138888889</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>54133.56821895425</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>9827676.674836602</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>78.44661968954247</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.205269607843138</v>
-      </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AY12" t="n">
+        <v>25.59265873015873</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>183.5138888888889</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>76.12480158730159</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>54572.81746031746</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>10166924.6031746</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>78.71210317460317</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.226190476190476</v>
+      </c>
+      <c r="BF12" t="inlineStr">
         <is>
           <t>GlJdeJqp</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
@@ -2362,95 +2970,143 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26.03409090909091</v>
+        <v>26.69444444444445</v>
       </c>
       <c r="O13" t="n">
-        <v>183.8497474747475</v>
+        <v>186.4305555555555</v>
       </c>
       <c r="P13" t="n">
-        <v>79.49368686868686</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>104011.3636363636</v>
+        <v>279.6666666666667</v>
       </c>
       <c r="R13" t="n">
-        <v>25567234.84848485</v>
+        <v>357500</v>
       </c>
       <c r="S13" t="n">
-        <v>82.13131313131312</v>
+        <v>79000000</v>
       </c>
       <c r="T13" t="n">
-        <v>2.305555555555555</v>
+        <v>285</v>
       </c>
       <c r="U13" t="n">
-        <v>25.5125</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="V13" t="n">
-        <v>181.0447916666666</v>
+        <v>25.38888888888889</v>
       </c>
       <c r="W13" t="n">
-        <v>76.19548611111111</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="X13" t="n">
-        <v>49713.19444444445</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="Y13" t="n">
-        <v>11072256.94444444</v>
+        <v>140.8333333333333</v>
       </c>
       <c r="Z13" t="n">
-        <v>79.38194444444444</v>
+        <v>102166.6666666667</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.171180555555556</v>
+        <v>21933333.33333333</v>
       </c>
       <c r="AB13" t="n">
-        <v>24.14769755416209</v>
+        <v>144.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>181.5568159374474</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AD13" t="n">
-        <v>76.31276909232072</v>
+        <v>25.94805194805195</v>
       </c>
       <c r="AE13" t="n">
-        <v>82354.90676728878</v>
+        <v>183.8282828282828</v>
       </c>
       <c r="AF13" t="n">
-        <v>17835579.75890195</v>
+        <v>79.27849927849927</v>
       </c>
       <c r="AG13" t="n">
-        <v>81.13763518851476</v>
+        <v>102714.2857142857</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.527035458582226</v>
+        <v>25135281.38528138</v>
       </c>
       <c r="AI13" t="n">
-        <v>24.74283804430863</v>
+        <v>82.05916305916305</v>
       </c>
       <c r="AJ13" t="n">
-        <v>179.814919149478</v>
+        <v>2.271284271284272</v>
       </c>
       <c r="AK13" t="n">
-        <v>74.81112066038537</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="AL13" t="n">
-        <v>47208.45004668534</v>
+        <v>181.1369047619048</v>
       </c>
       <c r="AM13" t="n">
-        <v>9351234.508955097</v>
+        <v>76.23769841269841</v>
       </c>
       <c r="AN13" t="n">
-        <v>78.83507342330873</v>
+        <v>50315.07936507936</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.090421016891605</v>
-      </c>
-      <c r="AP13" t="inlineStr">
+        <v>11196865.07936508</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>79.3079365079365</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.181349206349207</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>24.12117815713762</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>181.5819393026609</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>76.11255243204002</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>81487.24038710554</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>17583519.72445937</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>81.04165109979918</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.527496306406898</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>24.69249517989013</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>179.4823565789952</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>74.95420592479415</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>47333.46672002134</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>9568077.534043919</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>79.00879139534602</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.103338305018978</v>
+      </c>
+      <c r="BF13" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -2513,95 +3169,143 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>25.20476190476191</v>
+      </c>
+      <c r="O14" t="n">
+        <v>178.4428571428571</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>253.2857142857143</v>
+      </c>
+      <c r="R14" t="n">
+        <v>202142.8571428571</v>
+      </c>
+      <c r="S14" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>260.2857142857143</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="V14" t="n">
+        <v>27.69166666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>181.5083333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>85666.66666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6716666.666666667</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>191</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="AD14" t="n">
         <v>25.45454545454546</v>
       </c>
-      <c r="O14" t="n">
+      <c r="AE14" t="n">
         <v>184.2985409652076</v>
       </c>
-      <c r="P14" t="n">
+      <c r="AF14" t="n">
         <v>75.46329966329967</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="AG14" t="n">
         <v>54973.56902356903</v>
       </c>
-      <c r="R14" t="n">
+      <c r="AH14" t="n">
         <v>10320743.54657688</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AI14" t="n">
         <v>79.77401795735129</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AJ14" t="n">
         <v>1.169668911335578</v>
       </c>
-      <c r="U14" t="n">
-        <v>25.62891414141414</v>
-      </c>
-      <c r="V14" t="n">
-        <v>183.1918560606061</v>
-      </c>
-      <c r="W14" t="n">
-        <v>73.92004419191917</v>
-      </c>
-      <c r="X14" t="n">
-        <v>43350.41035353535</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>5904977.904040404</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>77.7366792929293</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.064741161616162</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AK14" t="n">
+        <v>25.57590187590188</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>183.2971861471862</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>74.01251803751802</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>43945.92352092352</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>6017377.344877345</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>77.84191919191919</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.073989898989899</v>
+      </c>
+      <c r="AR14" t="n">
         <v>23.57415529564652</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AS14" t="n">
         <v>181.0135999721526</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AT14" t="n">
         <v>71.7866042420867</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AU14" t="n">
         <v>45308.36002042142</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AV14" t="n">
         <v>6713726.358720877</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AW14" t="n">
         <v>78.96391789659333</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AX14" t="n">
         <v>1.068822519261116</v>
       </c>
-      <c r="AI14" t="n">
-        <v>26.54408939014202</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>180.4215956558062</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>71.94489870509608</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>41971.8723893066</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>3891265.142021721</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>74.66696428571429</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.035609857978279</v>
-      </c>
-      <c r="AP14" t="inlineStr">
+      <c r="AY14" t="n">
+        <v>26.55832438238453</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>180.394522019334</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>72.1671858216971</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>42055.15574650913</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3994382.38453276</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>74.90510204081633</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.032760472610097</v>
+      </c>
+      <c r="BF14" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
@@ -2664,95 +3368,143 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>25.95499438832772</v>
+        <v>31.95</v>
       </c>
       <c r="O15" t="n">
-        <v>183.1753086419753</v>
+        <v>178.8166666666667</v>
       </c>
       <c r="P15" t="n">
-        <v>75.44096520763188</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>64645.90347923681</v>
+        <v>170.8</v>
       </c>
       <c r="R15" t="n">
-        <v>11371156.00448934</v>
+        <v>177000</v>
       </c>
       <c r="S15" t="n">
-        <v>80.0973063973064</v>
+        <v>39940000</v>
       </c>
       <c r="T15" t="n">
-        <v>1.560830527497194</v>
+        <v>177.6</v>
       </c>
       <c r="U15" t="n">
-        <v>26.68492063492064</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="n">
-        <v>182.397619047619</v>
+        <v>24.27777777777778</v>
       </c>
       <c r="W15" t="n">
-        <v>76.54801587301587</v>
+        <v>192.2777777777777</v>
       </c>
       <c r="X15" t="n">
-        <v>54272.22222222223</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="Y15" t="n">
-        <v>12557896.82539682</v>
+        <v>172.1666666666667</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.83809523809524</v>
+        <v>114500</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.46984126984127</v>
+        <v>18600000</v>
       </c>
       <c r="AB15" t="n">
-        <v>23.54790522234828</v>
+        <v>184.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>179.6992758964761</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="AD15" t="n">
-        <v>73.4785027092454</v>
+        <v>25.49103535353535</v>
       </c>
       <c r="AE15" t="n">
-        <v>57034.35325312429</v>
+        <v>183.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>10071142.08955894</v>
+        <v>75.24608585858586</v>
       </c>
       <c r="AG15" t="n">
-        <v>80.5590119533702</v>
+        <v>62712.75252525252</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.312903155159852</v>
+        <v>11056439.39393939</v>
       </c>
       <c r="AI15" t="n">
-        <v>27.97499504852446</v>
+        <v>80.2344696969697</v>
       </c>
       <c r="AJ15" t="n">
-        <v>180.1576714861029</v>
+        <v>1.519823232323232</v>
       </c>
       <c r="AK15" t="n">
-        <v>76.13800092427543</v>
+        <v>26.66944444444444</v>
       </c>
       <c r="AL15" t="n">
-        <v>56937.47276688452</v>
+        <v>182.4453703703704</v>
       </c>
       <c r="AM15" t="n">
-        <v>10755348.25377963</v>
+        <v>76.5837962962963</v>
       </c>
       <c r="AN15" t="n">
-        <v>78.15959926057965</v>
+        <v>54391.66666666666</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.417171717171717</v>
-      </c>
-      <c r="AP15" t="inlineStr">
+        <v>12671250</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>79.9037037037037</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.492592592592593</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>23.50226294035921</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>179.8573375574486</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>73.54375033050978</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>57163.64740976482</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10161964.19857989</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>80.67780149101975</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.319407353902659</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>28.03436942959002</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>180.3586304218657</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>76.18650103980985</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>57310.90686274509</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>10799141.78550208</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>78.13579916815212</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.406818181818182</v>
+      </c>
+      <c r="BF15" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>4rSZHs2M</t>
         </is>
@@ -2815,95 +3567,143 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>24.07142857142857</v>
+      </c>
+      <c r="O16" t="n">
+        <v>176.0714285714285</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>171.1428571428571</v>
+      </c>
+      <c r="R16" t="n">
+        <v>317571.4285714286</v>
+      </c>
+      <c r="S16" t="n">
+        <v>76214285.71428572</v>
+      </c>
+      <c r="T16" t="n">
+        <v>185</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="V16" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="W16" t="n">
+        <v>185.875</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>61666.66666666666</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9395833.333333334</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AD16" t="n">
         <v>26.40833333333333</v>
       </c>
-      <c r="O16" t="n">
+      <c r="AE16" t="n">
         <v>181.0909090909091</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AF16" t="n">
         <v>83.93282828282828</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AG16" t="n">
         <v>184214.6464646464</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AH16" t="n">
         <v>58695391.41414142</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AI16" t="n">
         <v>86.13308080808082</v>
       </c>
-      <c r="T16" t="n">
+      <c r="AJ16" t="n">
         <v>3.292676767676768</v>
       </c>
-      <c r="U16" t="n">
-        <v>26.36979166666666</v>
-      </c>
-      <c r="V16" t="n">
-        <v>182.3211805555556</v>
-      </c>
-      <c r="W16" t="n">
-        <v>73.25868055555556</v>
-      </c>
-      <c r="X16" t="n">
-        <v>46982.63888888888</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6123914.930555556</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>76.78472222222223</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.282986111111111</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
+        <v>26.23214285714285</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>182.0178571428571</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>73.04166666666667</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>45805.55555555555</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>6134871.031746032</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>76.76984126984128</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.291666666666666</v>
+      </c>
+      <c r="AR16" t="n">
         <v>25.99626048293811</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AS16" t="n">
         <v>179.115309608155</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AT16" t="n">
         <v>80.14670329670329</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AU16" t="n">
         <v>137935.6401821862</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AV16" t="n">
         <v>39963876.06636784</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AW16" t="n">
         <v>83.42561270965876</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AX16" t="n">
         <v>2.579571826200116</v>
       </c>
-      <c r="AI16" t="n">
-        <v>25.75021471285661</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>180.164657732666</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>71.04516356250103</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>39585.74583120507</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>4159746.475765568</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>76.20272559493407</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1.154800201136631</v>
-      </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AY16" t="n">
+        <v>26.18490064287278</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>180.2306944947038</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>71.28376355326819</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>40198.73678737842</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4128862.512508991</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>75.88715720339172</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.162786589915073</v>
+      </c>
+      <c r="BF16" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>Aotm1TVI</t>
         </is>
@@ -2966,95 +3766,143 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>28.09671717171717</v>
+        <v>24.58888888888889</v>
       </c>
       <c r="O17" t="n">
-        <v>182.8133838383839</v>
+        <v>186.4055555555556</v>
       </c>
       <c r="P17" t="n">
-        <v>76.40744949494949</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="Q17" t="n">
-        <v>46834.59595959596</v>
+        <v>342.3333333333333</v>
       </c>
       <c r="R17" t="n">
-        <v>10624633.83838384</v>
+        <v>187000</v>
       </c>
       <c r="S17" t="n">
-        <v>78.58636363636363</v>
+        <v>36029166.66666666</v>
       </c>
       <c r="T17" t="n">
-        <v>1.504166666666667</v>
+        <v>369.6666666666667</v>
       </c>
       <c r="U17" t="n">
-        <v>27.2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="V17" t="n">
-        <v>184.3111111111111</v>
+        <v>29</v>
       </c>
       <c r="W17" t="n">
-        <v>76.52222222222223</v>
+        <v>190</v>
       </c>
       <c r="X17" t="n">
-        <v>66777.77777777778</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>10556666.66666667</v>
+        <v>74</v>
       </c>
       <c r="Z17" t="n">
-        <v>78.24444444444445</v>
+        <v>66000</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.444444444444444</v>
+        <v>4200000</v>
       </c>
       <c r="AB17" t="n">
-        <v>27.18699875832229</v>
+        <v>74</v>
       </c>
       <c r="AC17" t="n">
-        <v>182.8718385644856</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>74.08250455971044</v>
+        <v>27.96767676767677</v>
       </c>
       <c r="AE17" t="n">
-        <v>40747.49259455142</v>
+        <v>182.8906204906205</v>
       </c>
       <c r="AF17" t="n">
-        <v>6296446.755314403</v>
+        <v>76.43968253968254</v>
       </c>
       <c r="AG17" t="n">
-        <v>76.77187047701754</v>
+        <v>46823.95382395382</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.249512442894796</v>
+        <v>10775230.88023088</v>
       </c>
       <c r="AI17" t="n">
-        <v>26.94927536231884</v>
+        <v>78.68311688311688</v>
       </c>
       <c r="AJ17" t="n">
-        <v>182.8294283413849</v>
+        <v>1.498268398268398</v>
       </c>
       <c r="AK17" t="n">
-        <v>74.48236714975845</v>
+        <v>27.275</v>
       </c>
       <c r="AL17" t="n">
-        <v>61881.32045088566</v>
+        <v>184.35</v>
       </c>
       <c r="AM17" t="n">
-        <v>7182773.752012882</v>
+        <v>76.44999999999999</v>
       </c>
       <c r="AN17" t="n">
-        <v>77.15547504025764</v>
+        <v>66687.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.262399355877617</v>
-      </c>
-      <c r="AP17" t="inlineStr">
+        <v>10426250</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>27.38537360311257</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>182.6641517183797</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>74.18448429634091</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>40640.92916887035</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6262252.599728703</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>76.87668761997806</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.264034831589979</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>26.92119565217391</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>182.9494112318841</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>74.70570652173913</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>62768.65942028986</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>7449098.731884058</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>77.26730072463766</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.262590579710145</v>
+      </c>
+      <c r="BF17" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -3117,95 +3965,143 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>21.91666666666667</v>
+      </c>
+      <c r="O18" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>173</v>
+      </c>
+      <c r="R18" t="n">
+        <v>104000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21750000</v>
+      </c>
+      <c r="T18" t="n">
+        <v>195.6666666666667</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="V18" t="n">
+        <v>24.86666666666666</v>
+      </c>
+      <c r="W18" t="n">
+        <v>189.2166666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>364833.3333333333</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>89200000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" t="n">
         <v>23.19141414141414</v>
       </c>
-      <c r="O18" t="n">
+      <c r="AE18" t="n">
         <v>183.5227272727273</v>
       </c>
-      <c r="P18" t="n">
+      <c r="AF18" t="n">
         <v>80.08964646464646</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AG18" t="n">
         <v>99655.93434343435</v>
       </c>
-      <c r="R18" t="n">
+      <c r="AH18" t="n">
         <v>32757765.15151515</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AI18" t="n">
         <v>84.53030303030303</v>
       </c>
-      <c r="T18" t="n">
+      <c r="AJ18" t="n">
         <v>1.869191919191919</v>
       </c>
-      <c r="U18" t="n">
-        <v>27.52676767676768</v>
-      </c>
-      <c r="V18" t="n">
-        <v>186.559595959596</v>
-      </c>
-      <c r="W18" t="n">
-        <v>80.07626262626263</v>
-      </c>
-      <c r="X18" t="n">
-        <v>107352.5252525252</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>25805498.73737374</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>81.67752525252526</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.394191919191919</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AK18" t="n">
+        <v>27.59261363636364</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>186.4670454545455</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>80.06079545454546</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>107284.0909090909</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25606186.07954545</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>81.58721590909092</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.393465909090909</v>
+      </c>
+      <c r="AR18" t="n">
         <v>24.00761796682849</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AS18" t="n">
         <v>180.9913018998545</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AT18" t="n">
         <v>79.12814101103575</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AU18" t="n">
         <v>104052.1856433041</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AV18" t="n">
         <v>27565363.33184359</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AW18" t="n">
         <v>83.60543553668553</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AX18" t="n">
         <v>1.818090498682604</v>
       </c>
-      <c r="AI18" t="n">
-        <v>27.08814657707847</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>182.916736862209</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>77.75546350650841</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>92405.71031708801</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>19085322.46996353</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>80.1773544452337</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1.936447178552442</v>
-      </c>
-      <c r="AP18" t="inlineStr">
+      <c r="AY18" t="n">
+        <v>27.06010239921327</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>182.8282039699851</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>77.89677144482195</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>93386.11160672402</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19926261.21620897</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>80.40264875088792</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.983190575871497</v>
+      </c>
+      <c r="BF18" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -3268,95 +4164,143 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>186.7666666666667</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>151000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="T19" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>26.54761904761905</v>
+      </c>
+      <c r="W19" t="n">
+        <v>185.1428571428571</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>182</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>241857.1428571429</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>62764285.71428572</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>188.1428571428571</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="AD19" t="n">
         <v>25.69475308641975</v>
       </c>
-      <c r="O19" t="n">
+      <c r="AE19" t="n">
         <v>182.6685185185185</v>
       </c>
-      <c r="P19" t="n">
+      <c r="AF19" t="n">
         <v>78.6324074074074</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="AG19" t="n">
         <v>72117.59259259258</v>
       </c>
-      <c r="R19" t="n">
+      <c r="AH19" t="n">
         <v>19674814.81481481</v>
       </c>
-      <c r="S19" t="n">
+      <c r="AI19" t="n">
         <v>80.92716049382716</v>
       </c>
-      <c r="T19" t="n">
+      <c r="AJ19" t="n">
         <v>1.459259259259259</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AK19" t="n">
         <v>25.47301587301587</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AL19" t="n">
         <v>184.3238095238095</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AM19" t="n">
         <v>82.2126984126984</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AN19" t="n">
         <v>111207.9365079365</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AO19" t="n">
         <v>39690476.19047619</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AP19" t="n">
         <v>84.74444444444445</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AQ19" t="n">
         <v>2.75079365079365</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AR19" t="n">
         <v>27.68444958702957</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AS19" t="n">
         <v>183.2248136681573</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AT19" t="n">
         <v>74.77165497423496</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AU19" t="n">
         <v>61226.38597881116</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AV19" t="n">
         <v>8704417.793344522</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AW19" t="n">
         <v>76.70123769514895</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AX19" t="n">
         <v>1.044355839092681</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AY19" t="n">
         <v>24.51208419848125</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AZ19" t="n">
         <v>184.1109614241967</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="BA19" t="n">
         <v>78.03863362944246</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="BB19" t="n">
         <v>77662.63409792821</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="BC19" t="n">
         <v>22629170.59043898</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="BD19" t="n">
         <v>82.37388367351602</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="BE19" t="n">
         <v>1.866579294888119</v>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="BF19" t="inlineStr">
         <is>
           <t>CznGurCt</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
         </is>
@@ -3419,95 +4363,143 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>28.14506172839506</v>
+        <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>182.375</v>
+        <v>181</v>
       </c>
       <c r="P20" t="n">
-        <v>79.56481481481481</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>86324.07407407409</v>
+        <v>77.5</v>
       </c>
       <c r="R20" t="n">
-        <v>20516203.70370371</v>
+        <v>78500</v>
       </c>
       <c r="S20" t="n">
-        <v>80.69907407407408</v>
+        <v>15000000</v>
       </c>
       <c r="T20" t="n">
-        <v>2.294753086419753</v>
+        <v>78.5</v>
       </c>
       <c r="U20" t="n">
-        <v>26.175</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>182.9607142857143</v>
+        <v>25.44444444444445</v>
       </c>
       <c r="W20" t="n">
-        <v>80.40714285714286</v>
+        <v>180.0555555555555</v>
       </c>
       <c r="X20" t="n">
-        <v>100239.2857142857</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="Y20" t="n">
-        <v>30724553.57142857</v>
+        <v>219.3333333333333</v>
       </c>
       <c r="Z20" t="n">
-        <v>83.47857142857143</v>
+        <v>215166.6666666667</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.510714285714286</v>
+        <v>44166666.66666666</v>
       </c>
       <c r="AB20" t="n">
-        <v>28.7875816993464</v>
+        <v>228.3333333333333</v>
       </c>
       <c r="AC20" t="n">
-        <v>180.3327886710239</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="AD20" t="n">
-        <v>77.8787672476398</v>
+        <v>28.10763888888889</v>
       </c>
       <c r="AE20" t="n">
-        <v>78483.52396514161</v>
+        <v>182.3385416666667</v>
       </c>
       <c r="AF20" t="n">
-        <v>15851134.71314452</v>
+        <v>79.53819444444444</v>
       </c>
       <c r="AG20" t="n">
-        <v>79.53363289760348</v>
+        <v>86017.36111111112</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.014206608569354</v>
+        <v>20511284.72222222</v>
       </c>
       <c r="AI20" t="n">
-        <v>26.79118017399267</v>
+        <v>80.703125</v>
       </c>
       <c r="AJ20" t="n">
-        <v>183.8941220238095</v>
+        <v>2.289930555555555</v>
       </c>
       <c r="AK20" t="n">
-        <v>77.7919184981685</v>
+        <v>26.17083333333333</v>
       </c>
       <c r="AL20" t="n">
-        <v>85800.4407051282</v>
+        <v>182.9708333333333</v>
       </c>
       <c r="AM20" t="n">
-        <v>21138767.74267399</v>
+        <v>80.29166666666667</v>
       </c>
       <c r="AN20" t="n">
-        <v>81.35531135531136</v>
+        <v>99379.16666666667</v>
       </c>
       <c r="AO20" t="n">
-        <v>2.040064102564103</v>
-      </c>
-      <c r="AP20" t="inlineStr">
+        <v>30661979.16666667</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>83.40833333333335</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>2.479166666666667</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>28.76884191176471</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>180.7415747549019</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>77.94955065359477</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>78614.27696078431</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>16133307.80228758</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>79.61596200980392</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.047232434640523</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>26.86611067503924</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>183.7551870748299</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>78.04790685504972</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>88124.31318681317</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>21860734.56305599</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>81.52035583464155</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.102930402930403</v>
+      </c>
+      <c r="BF20" t="inlineStr">
         <is>
           <t>joAFj9hO</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -3570,95 +4562,143 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>25.52951388888889</v>
+        <v>26.25833333333334</v>
       </c>
       <c r="O21" t="n">
-        <v>182.2118055555555</v>
+        <v>181.4166666666667</v>
       </c>
       <c r="P21" t="n">
-        <v>83.14236111111111</v>
+        <v>4.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>146975.6944444444</v>
+        <v>367.6666666666667</v>
       </c>
       <c r="R21" t="n">
-        <v>53977430.55555556</v>
+        <v>628333.3333333334</v>
       </c>
       <c r="S21" t="n">
-        <v>85.375</v>
+        <v>189083333.3333333</v>
       </c>
       <c r="T21" t="n">
-        <v>3.243055555555555</v>
+        <v>371.6666666666667</v>
       </c>
       <c r="U21" t="n">
-        <v>26.83055555555555</v>
+        <v>11</v>
       </c>
       <c r="V21" t="n">
-        <v>184.0470959595959</v>
+        <v>22.75</v>
       </c>
       <c r="W21" t="n">
-        <v>83.96780303030303</v>
+        <v>173.5</v>
       </c>
       <c r="X21" t="n">
-        <v>131327.5252525253</v>
+        <v>1.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>50801578.28282828</v>
+        <v>120.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>85.77032828282827</v>
+        <v>122250</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.171338383838385</v>
+        <v>55375000</v>
       </c>
       <c r="AB21" t="n">
-        <v>24.92447767359452</v>
+        <v>129.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>178.5713399824813</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>78.25634456123586</v>
+        <v>25.54166666666666</v>
       </c>
       <c r="AE21" t="n">
-        <v>112444.3887860328</v>
+        <v>182.0833333333333</v>
       </c>
       <c r="AF21" t="n">
-        <v>29883900.70074853</v>
+        <v>82.9563492063492</v>
       </c>
       <c r="AG21" t="n">
-        <v>83.19971606744704</v>
+        <v>145432.5396825397</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.438863672559325</v>
+        <v>52640873.01587302</v>
       </c>
       <c r="AI21" t="n">
-        <v>25.52250258799172</v>
+        <v>85.3015873015873</v>
       </c>
       <c r="AJ21" t="n">
-        <v>183.0462668219462</v>
+        <v>3.23015873015873</v>
       </c>
       <c r="AK21" t="n">
-        <v>80.39087085921325</v>
+        <v>26.83232323232323</v>
       </c>
       <c r="AL21" t="n">
-        <v>100462.0212215321</v>
+        <v>184.118759018759</v>
       </c>
       <c r="AM21" t="n">
-        <v>33515248.44720497</v>
+        <v>83.92424242424242</v>
       </c>
       <c r="AN21" t="n">
-        <v>83.48564958592132</v>
+        <v>130854.8340548341</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.280020703933747</v>
-      </c>
-      <c r="AP21" t="inlineStr">
+        <v>50455050.5050505</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>85.698556998557</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.156854256854257</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>24.8244030555366</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>178.7868885514072</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>77.94475092712671</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>110865.0157554661</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>29369100.80085546</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>83.19253264851091</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2.385487054353514</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>25.60428867199053</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>182.9385906536528</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>80.43242383910085</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>101456.595681751</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>33863855.36823425</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>83.49788524105294</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.305737947352854</v>
+      </c>
+      <c r="BF21" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -980,52 +980,52 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
-        <v>190</v>
+        <v>186.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="R3" t="n">
-        <v>66000</v>
+        <v>129000</v>
       </c>
       <c r="S3" t="n">
-        <v>4200000</v>
+        <v>10200000</v>
       </c>
       <c r="T3" t="n">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="W3" t="n">
-        <v>178</v>
+        <v>180.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Z3" t="n">
-        <v>130000</v>
+        <v>240000</v>
       </c>
       <c r="AA3" t="n">
-        <v>29500000</v>
+        <v>57500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD3" t="n">
         <v>27.275</v>
@@ -1179,28 +1179,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
-        <v>184</v>
+        <v>182.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>48000</v>
+        <v>120000</v>
       </c>
       <c r="S4" t="n">
-        <v>4400000</v>
+        <v>8300000</v>
       </c>
       <c r="T4" t="n">
-        <v>143</v>
+        <v>289</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
         <v>21</v>
@@ -1447,25 +1447,25 @@
         <v>2.479166666666667</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.45454545454546</v>
+        <v>25.30681818181818</v>
       </c>
       <c r="AL5" t="n">
-        <v>184.2985409652076</v>
+        <v>184.0972222222222</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.46329966329967</v>
+        <v>75.31666666666666</v>
       </c>
       <c r="AN5" t="n">
-        <v>54973.56902356903</v>
+        <v>54311.17424242424</v>
       </c>
       <c r="AO5" t="n">
-        <v>10320743.54657688</v>
+        <v>10176745.58080808</v>
       </c>
       <c r="AP5" t="n">
-        <v>79.77401795735129</v>
+        <v>79.83667929292929</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.169668911335578</v>
+        <v>1.168150252525253</v>
       </c>
       <c r="AR5" t="n">
         <v>26.86611067503924</v>
@@ -1489,25 +1489,25 @@
         <v>2.102930402930403</v>
       </c>
       <c r="AY5" t="n">
-        <v>23.57415529564652</v>
+        <v>23.4156615497076</v>
       </c>
       <c r="AZ5" t="n">
-        <v>181.0135999721526</v>
+        <v>181.4955631265664</v>
       </c>
       <c r="BA5" t="n">
-        <v>71.7866042420867</v>
+        <v>71.52966661445279</v>
       </c>
       <c r="BB5" t="n">
-        <v>45308.36002042142</v>
+        <v>44623.22081244779</v>
       </c>
       <c r="BC5" t="n">
-        <v>6713726.358720877</v>
+        <v>6570705.311455723</v>
       </c>
       <c r="BD5" t="n">
-        <v>78.96391789659333</v>
+        <v>78.9265128968254</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.068822519261116</v>
+        <v>1.057688492063492</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1577,34 +1577,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.8</v>
+        <v>26.25</v>
       </c>
       <c r="O6" t="n">
-        <v>187</v>
+        <v>185.75</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>397</v>
+        <v>312</v>
       </c>
       <c r="R6" t="n">
-        <v>515000</v>
+        <v>360000</v>
       </c>
       <c r="S6" t="n">
-        <v>137100000</v>
+        <v>66100000</v>
       </c>
       <c r="T6" t="n">
-        <v>416</v>
+        <v>329</v>
       </c>
       <c r="U6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="W6" t="n">
-        <v>185.5</v>
+        <v>186.5</v>
       </c>
       <c r="X6" t="n">
         <v>2</v>
@@ -1613,13 +1613,13 @@
         <v>162</v>
       </c>
       <c r="Z6" t="n">
-        <v>253000</v>
+        <v>266000</v>
       </c>
       <c r="AA6" t="n">
-        <v>69500000</v>
+        <v>66000000</v>
       </c>
       <c r="AB6" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="O7" t="n">
-        <v>186</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="R7" t="n">
-        <v>56000</v>
+        <v>99000</v>
       </c>
       <c r="S7" t="n">
-        <v>10800000</v>
+        <v>12800000</v>
       </c>
       <c r="T7" t="n">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>24.66666666666667</v>
@@ -1999,28 +1999,28 @@
         <v>4.333333333333333</v>
       </c>
       <c r="V8" t="n">
-        <v>25.25</v>
+        <v>28.25</v>
       </c>
       <c r="W8" t="n">
-        <v>177.75</v>
+        <v>180.75</v>
       </c>
       <c r="X8" t="n">
         <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="Z8" t="n">
-        <v>645000</v>
+        <v>491000</v>
       </c>
       <c r="AA8" t="n">
-        <v>262000000</v>
+        <v>158900000</v>
       </c>
       <c r="AB8" t="n">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>25.57142857142857</v>
@@ -2174,52 +2174,52 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24.27777777777778</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="O9" t="n">
-        <v>192.2777777777777</v>
+        <v>190.3333333333333</v>
       </c>
       <c r="P9" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>172.1666666666667</v>
+        <v>218</v>
       </c>
       <c r="R9" t="n">
-        <v>114500</v>
+        <v>134000</v>
       </c>
       <c r="S9" t="n">
-        <v>18600000</v>
+        <v>19800000</v>
       </c>
       <c r="T9" t="n">
-        <v>184.5</v>
+        <v>237</v>
       </c>
       <c r="U9" t="n">
-        <v>3.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>24.07142857142857</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="W9" t="n">
-        <v>176.0714285714285</v>
+        <v>178.3333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>2.142857142857143</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>171.1428571428571</v>
+        <v>246</v>
       </c>
       <c r="Z9" t="n">
-        <v>317571.4285714286</v>
+        <v>529000</v>
       </c>
       <c r="AA9" t="n">
-        <v>76214285.71428572</v>
+        <v>118000000</v>
       </c>
       <c r="AB9" t="n">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.428571428571429</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>26.66944444444444</v>
@@ -2641,25 +2641,25 @@
         <v>1.333333333333333</v>
       </c>
       <c r="AK11" t="n">
-        <v>25.69475308641975</v>
+        <v>25.70659722222222</v>
       </c>
       <c r="AL11" t="n">
-        <v>182.6685185185185</v>
+        <v>182.4645833333333</v>
       </c>
       <c r="AM11" t="n">
-        <v>78.6324074074074</v>
+        <v>78.64895833333334</v>
       </c>
       <c r="AN11" t="n">
-        <v>72117.59259259258</v>
+        <v>72194.79166666666</v>
       </c>
       <c r="AO11" t="n">
-        <v>19674814.81481481</v>
+        <v>19732916.66666666</v>
       </c>
       <c r="AP11" t="n">
-        <v>80.92716049382716</v>
+        <v>80.94305555555556</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.459259259259259</v>
+        <v>1.454166666666666</v>
       </c>
       <c r="AR11" t="n">
         <v>25.59265873015873</v>
@@ -2683,25 +2683,25 @@
         <v>1.226190476190476</v>
       </c>
       <c r="AY11" t="n">
-        <v>27.68444958702957</v>
+        <v>27.70182396722645</v>
       </c>
       <c r="AZ11" t="n">
-        <v>183.2248136681573</v>
+        <v>183.2188244675861</v>
       </c>
       <c r="BA11" t="n">
-        <v>74.77165497423496</v>
+        <v>74.54993002783252</v>
       </c>
       <c r="BB11" t="n">
-        <v>61226.38597881116</v>
+        <v>60652.41149888982</v>
       </c>
       <c r="BC11" t="n">
-        <v>8704417.793344522</v>
+        <v>8353265.472058043</v>
       </c>
       <c r="BD11" t="n">
-        <v>76.70123769514895</v>
+        <v>76.49911967976983</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.044355839092681</v>
+        <v>1.027173046251994</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -3169,28 +3169,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>25.20476190476191</v>
+        <v>25.23888888888889</v>
       </c>
       <c r="O14" t="n">
-        <v>178.4428571428571</v>
+        <v>178.0722222222222</v>
       </c>
       <c r="P14" t="n">
-        <v>3.285714285714286</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="Q14" t="n">
-        <v>253.2857142857143</v>
+        <v>256.6666666666667</v>
       </c>
       <c r="R14" t="n">
-        <v>202142.8571428571</v>
+        <v>205833.3333333333</v>
       </c>
       <c r="S14" t="n">
-        <v>41500000</v>
+        <v>40750000</v>
       </c>
       <c r="T14" t="n">
-        <v>260.2857142857143</v>
+        <v>263.6666666666667</v>
       </c>
       <c r="U14" t="n">
-        <v>3.285714285714286</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="V14" t="n">
         <v>27.69166666666667</v>
@@ -3217,25 +3217,25 @@
         <v>2.833333333333333</v>
       </c>
       <c r="AD14" t="n">
-        <v>25.45454545454546</v>
+        <v>25.30681818181818</v>
       </c>
       <c r="AE14" t="n">
-        <v>184.2985409652076</v>
+        <v>184.0972222222222</v>
       </c>
       <c r="AF14" t="n">
-        <v>75.46329966329967</v>
+        <v>75.31666666666666</v>
       </c>
       <c r="AG14" t="n">
-        <v>54973.56902356903</v>
+        <v>54311.17424242424</v>
       </c>
       <c r="AH14" t="n">
-        <v>10320743.54657688</v>
+        <v>10176745.58080808</v>
       </c>
       <c r="AI14" t="n">
-        <v>79.77401795735129</v>
+        <v>79.83667929292929</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.169668911335578</v>
+        <v>1.168150252525253</v>
       </c>
       <c r="AK14" t="n">
         <v>25.57590187590188</v>
@@ -3259,25 +3259,25 @@
         <v>1.073989898989899</v>
       </c>
       <c r="AR14" t="n">
-        <v>23.57415529564652</v>
+        <v>23.4156615497076</v>
       </c>
       <c r="AS14" t="n">
-        <v>181.0135999721526</v>
+        <v>181.4955631265664</v>
       </c>
       <c r="AT14" t="n">
-        <v>71.7866042420867</v>
+        <v>71.52966661445279</v>
       </c>
       <c r="AU14" t="n">
-        <v>45308.36002042142</v>
+        <v>44623.22081244779</v>
       </c>
       <c r="AV14" t="n">
-        <v>6713726.358720877</v>
+        <v>6570705.311455723</v>
       </c>
       <c r="AW14" t="n">
-        <v>78.96391789659333</v>
+        <v>78.9265128968254</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.068822519261116</v>
+        <v>1.057688492063492</v>
       </c>
       <c r="AY14" t="n">
         <v>26.55832438238453</v>
@@ -4212,25 +4212,25 @@
         <v>5.714285714285714</v>
       </c>
       <c r="AD19" t="n">
-        <v>25.69475308641975</v>
+        <v>25.70659722222222</v>
       </c>
       <c r="AE19" t="n">
-        <v>182.6685185185185</v>
+        <v>182.4645833333333</v>
       </c>
       <c r="AF19" t="n">
-        <v>78.6324074074074</v>
+        <v>78.64895833333334</v>
       </c>
       <c r="AG19" t="n">
-        <v>72117.59259259258</v>
+        <v>72194.79166666666</v>
       </c>
       <c r="AH19" t="n">
-        <v>19674814.81481481</v>
+        <v>19732916.66666666</v>
       </c>
       <c r="AI19" t="n">
-        <v>80.92716049382716</v>
+        <v>80.94305555555556</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.459259259259259</v>
+        <v>1.454166666666666</v>
       </c>
       <c r="AK19" t="n">
         <v>25.47301587301587</v>
@@ -4254,25 +4254,25 @@
         <v>2.75079365079365</v>
       </c>
       <c r="AR19" t="n">
-        <v>27.68444958702957</v>
+        <v>27.70182396722645</v>
       </c>
       <c r="AS19" t="n">
-        <v>183.2248136681573</v>
+        <v>183.2188244675861</v>
       </c>
       <c r="AT19" t="n">
-        <v>74.77165497423496</v>
+        <v>74.54993002783252</v>
       </c>
       <c r="AU19" t="n">
-        <v>61226.38597881116</v>
+        <v>60652.41149888982</v>
       </c>
       <c r="AV19" t="n">
-        <v>8704417.793344522</v>
+        <v>8353265.472058043</v>
       </c>
       <c r="AW19" t="n">
-        <v>76.70123769514895</v>
+        <v>76.49911967976983</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.044355839092681</v>
+        <v>1.027173046251994</v>
       </c>
       <c r="AY19" t="n">
         <v>24.51208419848125</v>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG4"/>
+  <dimension ref="A1:BG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,11 +727,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -741,21 +741,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31750</v>
+        <v>32261</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24.75</v>
+        <v>26.65555555555556</v>
       </c>
       <c r="O2" t="n">
-        <v>187</v>
+        <v>180.9154320987655</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>75.50462962962963</v>
       </c>
       <c r="Q2" t="n">
-        <v>296</v>
+        <v>42996.91358024692</v>
       </c>
       <c r="R2" t="n">
-        <v>206000</v>
+        <v>7806319.444444444</v>
       </c>
       <c r="S2" t="n">
-        <v>34300000</v>
+        <v>77.96697530864198</v>
       </c>
       <c r="T2" t="n">
-        <v>315</v>
+        <v>1.368518518518518</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>26.74074074074074</v>
       </c>
       <c r="V2" t="n">
-        <v>27.33333333333333</v>
+        <v>183</v>
       </c>
       <c r="W2" t="n">
-        <v>178.3333333333333</v>
+        <v>77.03703703703702</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>57500</v>
       </c>
       <c r="Y2" t="n">
-        <v>246</v>
+        <v>12000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>529000</v>
+        <v>78.94444444444444</v>
       </c>
       <c r="AA2" t="n">
-        <v>118000000</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AB2" t="n">
-        <v>260</v>
+        <v>26.98011095276317</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>179.6271143545137</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.66944444444444</v>
+        <v>73.97356217340737</v>
       </c>
       <c r="AE2" t="n">
-        <v>182.4453703703704</v>
+        <v>44200.54247819985</v>
       </c>
       <c r="AF2" t="n">
-        <v>76.5837962962963</v>
+        <v>6097438.933663134</v>
       </c>
       <c r="AG2" t="n">
-        <v>54391.66666666666</v>
+        <v>76.67991765907144</v>
       </c>
       <c r="AH2" t="n">
-        <v>12671250</v>
+        <v>1.261938342588498</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.9037037037037</v>
+        <v>25.59265873015873</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.492592592592593</v>
+        <v>183.5138888888889</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.42380952380953</v>
+        <v>76.12480158730159</v>
       </c>
       <c r="AL2" t="n">
-        <v>181.0324675324675</v>
+        <v>54572.81746031746</v>
       </c>
       <c r="AM2" t="n">
-        <v>83.76608946608947</v>
+        <v>10166924.6031746</v>
       </c>
       <c r="AN2" t="n">
-        <v>182102.4531024531</v>
+        <v>78.71210317460317</v>
       </c>
       <c r="AO2" t="n">
-        <v>57744733.04473305</v>
+        <v>1.226190476190476</v>
       </c>
       <c r="AP2" t="n">
-        <v>85.96637806637807</v>
+        <v>25.17857142857143</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.248773448773449</v>
+        <v>188.3095238095238</v>
       </c>
       <c r="AR2" t="n">
-        <v>28.03436942959002</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="AS2" t="n">
-        <v>180.3586304218657</v>
+        <v>201.5714285714286</v>
       </c>
       <c r="AT2" t="n">
-        <v>76.18650103980985</v>
+        <v>100571.4285714286</v>
       </c>
       <c r="AU2" t="n">
-        <v>57310.90686274509</v>
+        <v>10185714.28571429</v>
       </c>
       <c r="AV2" t="n">
-        <v>10799141.78550208</v>
+        <v>212.5714285714286</v>
       </c>
       <c r="AW2" t="n">
-        <v>78.13579916815212</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.406818181818182</v>
+        <v>27.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>26.1100119805007</v>
+        <v>190.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>179.1746395521771</v>
+        <v>1.75</v>
       </c>
       <c r="BA2" t="n">
-        <v>80.19623233908949</v>
+        <v>135.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>137969.3030653557</v>
+        <v>100250</v>
       </c>
       <c r="BC2" t="n">
-        <v>38823715.50442039</v>
+        <v>20000000</v>
       </c>
       <c r="BD2" t="n">
-        <v>83.40070023961002</v>
+        <v>138</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.59093922994299</v>
+        <v>3.75</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>61276</v>
+        <v>42789</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,344 +980,3727 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>27.66666666666667</v>
+        <v>26.02272727272727</v>
       </c>
       <c r="O3" t="n">
-        <v>179.6666666666667</v>
+        <v>183.9065656565656</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>79.43686868686869</v>
       </c>
       <c r="Q3" t="n">
-        <v>247</v>
+        <v>103454.5454545455</v>
       </c>
       <c r="R3" t="n">
-        <v>286000</v>
+        <v>25305871.21212121</v>
       </c>
       <c r="S3" t="n">
-        <v>101000000</v>
+        <v>82.09722222222221</v>
       </c>
       <c r="T3" t="n">
-        <v>255</v>
+        <v>2.271464646464647</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>25.36111111111111</v>
       </c>
       <c r="V3" t="n">
-        <v>22</v>
+        <v>181.2170138888889</v>
       </c>
       <c r="W3" t="n">
-        <v>184.6666666666667</v>
+        <v>76.26354166666667</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>50192.36111111111</v>
       </c>
       <c r="Y3" t="n">
-        <v>222</v>
+        <v>11359756.94444444</v>
       </c>
       <c r="Z3" t="n">
-        <v>237000</v>
+        <v>79.50555555555556</v>
       </c>
       <c r="AA3" t="n">
-        <v>54500000</v>
+        <v>1.186458333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>247</v>
+        <v>24.22582255416209</v>
       </c>
       <c r="AC3" t="n">
-        <v>5</v>
+        <v>181.6081552231617</v>
       </c>
       <c r="AD3" t="n">
-        <v>26.83232323232323</v>
+        <v>76.34848337803501</v>
       </c>
       <c r="AE3" t="n">
-        <v>184.118759018759</v>
+        <v>82780.50200538401</v>
       </c>
       <c r="AF3" t="n">
-        <v>83.92424242424242</v>
+        <v>17896517.25890195</v>
       </c>
       <c r="AG3" t="n">
-        <v>130854.8340548341</v>
+        <v>81.08852804565763</v>
       </c>
       <c r="AH3" t="n">
-        <v>50455050.5050505</v>
+        <v>1.565725934772702</v>
       </c>
       <c r="AI3" t="n">
-        <v>85.698556998557</v>
+        <v>24.9392666157372</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.156854256854257</v>
+        <v>179.3089667685256</v>
       </c>
       <c r="AK3" t="n">
-        <v>23.23174603174603</v>
+        <v>75.05516827943299</v>
       </c>
       <c r="AL3" t="n">
-        <v>183.5714285714286</v>
+        <v>47952.49766573296</v>
       </c>
       <c r="AM3" t="n">
-        <v>80.06349206349206</v>
+        <v>9593496.413717002</v>
       </c>
       <c r="AN3" t="n">
-        <v>99373.01587301587</v>
+        <v>78.86483532807063</v>
       </c>
       <c r="AO3" t="n">
-        <v>32573809.52380953</v>
+        <v>1.12018292165351</v>
       </c>
       <c r="AP3" t="n">
-        <v>84.47619047619047</v>
+        <v>27.52380952380953</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.863492063492064</v>
+        <v>187.9404761904762</v>
       </c>
       <c r="AR3" t="n">
-        <v>25.60428867199053</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="AS3" t="n">
-        <v>182.9385906536528</v>
+        <v>261.5714285714286</v>
       </c>
       <c r="AT3" t="n">
-        <v>80.43242383910085</v>
+        <v>327428.5714285714</v>
       </c>
       <c r="AU3" t="n">
-        <v>101456.595681751</v>
+        <v>69532142.85714285</v>
       </c>
       <c r="AV3" t="n">
-        <v>33863855.36823425</v>
+        <v>266.1428571428572</v>
       </c>
       <c r="AW3" t="n">
-        <v>83.49788524105294</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.305737947352854</v>
+        <v>25.38888888888889</v>
       </c>
       <c r="AY3" t="n">
-        <v>23.99771723681497</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="AZ3" t="n">
-        <v>181.2098395338997</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="BA3" t="n">
-        <v>79.17941390272219</v>
+        <v>140.8333333333333</v>
       </c>
       <c r="BB3" t="n">
-        <v>104565.1352406992</v>
+        <v>102166.6666666667</v>
       </c>
       <c r="BC3" t="n">
-        <v>28151624.02760147</v>
+        <v>21933333.33333333</v>
       </c>
       <c r="BD3" t="n">
-        <v>83.71390434961863</v>
+        <v>144.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.880015514977921</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>184.3187429854096</v>
+      </c>
+      <c r="P4" t="n">
+        <v>75.40269360269362</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>54448.3164983165</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10256097.08193042</v>
+      </c>
+      <c r="S4" t="n">
+        <v>79.87502805836139</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.169668911335578</v>
+      </c>
+      <c r="U4" t="n">
+        <v>25.59141414141414</v>
+      </c>
+      <c r="V4" t="n">
+        <v>183.4600378787879</v>
+      </c>
+      <c r="W4" t="n">
+        <v>74.01095328282827</v>
+      </c>
+      <c r="X4" t="n">
+        <v>44052.68308080808</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6005205.176767677</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>77.8616792929293</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.077241161616162</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>23.48753248862898</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>181.1835561125035</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>71.72081476840248</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>45303.97405550915</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>6791494.999071754</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>78.9555114638448</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.058223104056437</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>26.58412206988059</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>180.2643244139761</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>72.27864053516143</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>42570.32010172489</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4051702.233524989</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>74.94637605042017</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.036018354710305</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>25.25238095238095</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>178.1095238095238</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>252.8571428571429</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>201714.2857142857</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>39714285.71428572</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>259.8571428571428</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>27.59285714285715</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>181.6857142857143</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>201.5714285714286</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>90571.42857142857</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6942857.142857143</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>205</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>25.33647586980921</v>
+      </c>
+      <c r="O5" t="n">
+        <v>183.2777777777778</v>
+      </c>
+      <c r="P5" t="n">
+        <v>75.10763187429853</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>61700.22446689113</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10739057.23905724</v>
+      </c>
+      <c r="S5" t="n">
+        <v>80.30841750841751</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.495398428731762</v>
+      </c>
+      <c r="U5" t="n">
+        <v>26.71666666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>182.8103174603175</v>
+      </c>
+      <c r="W5" t="n">
+        <v>76.78611111111111</v>
+      </c>
+      <c r="X5" t="n">
+        <v>54978.57142857143</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13011071.42857143</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>80.06031746031746</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.493650793650794</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>23.59090039143041</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>179.8176333843988</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>73.80000029378647</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>57984.35325312429</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>10444523.73207101</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>80.73026799201756</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.356139870135697</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>27.97499504852446</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>179.9854492638806</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>76.11022314649765</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>56831.91721132898</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>10678403.80933518</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.07904370502411</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.431060606060606</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>31.95833333333333</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>179.4583333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>200666.6666666667</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>44583333.33333334</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>24.52380952380953</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>191.6952380952381</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>201</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>133571.4285714286</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>21914285.71428571</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>214.2857142857143</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>26.38472222222222</v>
+      </c>
+      <c r="O6" t="n">
+        <v>181.0006313131313</v>
+      </c>
+      <c r="P6" t="n">
+        <v>83.90643939393939</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183645.202020202</v>
+      </c>
+      <c r="R6" t="n">
+        <v>58707196.96969697</v>
+      </c>
+      <c r="S6" t="n">
+        <v>86.1233585858586</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.287121212121212</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26.14756944444444</v>
+      </c>
+      <c r="V6" t="n">
+        <v>182.0711805555556</v>
+      </c>
+      <c r="W6" t="n">
+        <v>73.21701388888889</v>
+      </c>
+      <c r="X6" t="n">
+        <v>46968.75</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6468359.375</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>77.02083333333333</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.310763888888889</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>26.14773107117341</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>179.3145743140373</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>80.14229153199742</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>138186.3754763039</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>39125162.83107372</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>83.30649506259994</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.57589535561188</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>26.40509686773877</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>180.3285185631935</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>71.43124661525074</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>40448.25986038576</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4123495.072847499</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>75.80092985980498</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.150872030541793</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>25.02380952380952</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>176.3571428571428</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>194.8571428571429</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>367428.5714285714</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>87714285.71428572</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>208.7142857142857</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.285714285714286</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>153.8571428571429</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>61857.14285714286</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9196428.571428571</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>167.5714285714286</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>28.13080808080808</v>
+      </c>
+      <c r="O7" t="n">
+        <v>182.7792929292929</v>
+      </c>
+      <c r="P7" t="n">
+        <v>76.47563131313132</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>47073.23232323233</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10687133.83838384</v>
+      </c>
+      <c r="S7" t="n">
+        <v>78.59772727272727</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.504166666666666</v>
+      </c>
+      <c r="U7" t="n">
+        <v>27.31111111111111</v>
+      </c>
+      <c r="V7" t="n">
+        <v>184.4555555555555</v>
+      </c>
+      <c r="W7" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="X7" t="n">
+        <v>67100</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10620000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>78.21111111111112</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>27.37959135091488</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>182.8496163422634</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>74.17633172020426</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>40075.88765627981</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>6246817.125684773</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>76.8780433165237</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.271734665117018</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>26.8717506326202</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>182.8333390844261</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>74.66962272831837</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>62752.03588681849</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7435177.708764666</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77.31696572348746</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.249286864504256</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.16190476190476</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>186.7190476190476</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>345.8571428571428</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>190571.4285714286</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>38753571.42857143</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>375.1428571428572</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>92800</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>23.25277777777778</v>
+      </c>
+      <c r="O8" t="n">
+        <v>183.65</v>
+      </c>
+      <c r="P8" t="n">
+        <v>79.84305555555555</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>97413.88888888889</v>
+      </c>
+      <c r="R8" t="n">
+        <v>32123958.33333334</v>
+      </c>
+      <c r="S8" t="n">
+        <v>84.29166666666666</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.830555555555556</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.50454545454546</v>
+      </c>
+      <c r="V8" t="n">
+        <v>186.4929292929293</v>
+      </c>
+      <c r="W8" t="n">
+        <v>80.17626262626261</v>
+      </c>
+      <c r="X8" t="n">
+        <v>107952.5252525252</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>26399943.18181818</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>81.76641414141415</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.427525252525252</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.08550258221311</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>181.2523595921622</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>79.1382371648819</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>104063.2433356118</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>28107983.52415129</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>83.5496663059163</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.895013575605681</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>26.94848608325131</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182.8534652572707</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>77.86503140774296</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>93330.86463807567</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>19804824.78477834</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>80.38877419832014</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.960366931638861</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>22.16666666666667</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>180.8611111111111</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>122833.3333333333</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>209.6666666666667</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>25.45714285714286</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>188.5666666666667</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>311.5714285714286</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>358142.8571428572</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>85114285.71428572</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>327.4285714285714</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.857142857142858</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>25.70659722222222</v>
+      </c>
+      <c r="O9" t="n">
+        <v>182.4645833333333</v>
+      </c>
+      <c r="P9" t="n">
+        <v>78.64895833333334</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>72194.79166666666</v>
+      </c>
+      <c r="R9" t="n">
+        <v>19732916.66666666</v>
+      </c>
+      <c r="S9" t="n">
+        <v>80.94305555555556</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.454166666666666</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.51587301587302</v>
+      </c>
+      <c r="V9" t="n">
+        <v>184.2809523809524</v>
+      </c>
+      <c r="W9" t="n">
+        <v>82.24126984126984</v>
+      </c>
+      <c r="X9" t="n">
+        <v>111465.0793650794</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>39797619.04761905</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>84.73015873015872</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.765079365079365</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>27.70182396722645</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>183.2188244675861</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>74.54993002783252</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>60652.41149888982</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>8353265.472058043</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>76.49911967976983</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.027173046251994</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24.64276601666307</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>184.2495977878331</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>78.18522453853336</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>78305.81591611003</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>22702380.8177117</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>82.42842912806148</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.875670203979028</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>186.7666666666667</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>151000</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>183.7857142857143</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>170.5714285714286</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>231000</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>60571428.57142857</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>28.10956790123457</v>
+      </c>
+      <c r="O10" t="n">
+        <v>182.3287037037037</v>
+      </c>
+      <c r="P10" t="n">
+        <v>79.60339506172839</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>86543.20987654322</v>
+      </c>
+      <c r="R10" t="n">
+        <v>20683641.97530864</v>
+      </c>
+      <c r="S10" t="n">
+        <v>80.70833333333333</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.299382716049382</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26.36071428571429</v>
+      </c>
+      <c r="V10" t="n">
+        <v>183.1464285714286</v>
+      </c>
+      <c r="W10" t="n">
+        <v>80.39285714285714</v>
+      </c>
+      <c r="X10" t="n">
+        <v>100139.2857142857</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>30899553.57142857</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>83.35000000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.482142857142857</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>28.66952614379085</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>181.0411220043573</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>77.94821169208424</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>78379.35729847493</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16151829.15758896</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>79.72113289760348</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.041984386347131</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>26.89847184065934</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>183.8795386904762</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>78.0419184981685</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>87233.77403846153</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>21389861.49267399</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>81.47093635531135</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.043189102564103</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>181</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>78500</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>25.3452380952381</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>180.1904761904762</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>232.4285714285714</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>227142.8571428571</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>47071428.57142857</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>242.5714285714286</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>25.75520833333333</v>
+      </c>
+      <c r="O11" t="n">
+        <v>182.3072916666667</v>
+      </c>
+      <c r="P11" t="n">
+        <v>83.07118055555556</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>146394.0972222222</v>
+      </c>
+      <c r="R11" t="n">
+        <v>52162326.3888889</v>
+      </c>
+      <c r="S11" t="n">
+        <v>85.23263888888889</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.232638888888889</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.80328282828283</v>
+      </c>
+      <c r="V11" t="n">
+        <v>184.2414141414141</v>
+      </c>
+      <c r="W11" t="n">
+        <v>83.88371212121211</v>
+      </c>
+      <c r="X11" t="n">
+        <v>130647.9797979798</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>50273169.19191919</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>85.69873737373737</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.137247474747475</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.74108951569978</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>178.8135274824813</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>77.8069202191306</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>109908.2045755065</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>28659147.41127484</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>83.20136080428915</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.350459067296167</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>25.60375258799171</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>182.9150168219462</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>80.51587085921324</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>102430.7712215321</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>34626498.44720497</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>83.49814958592133</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.342520703933747</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>26.22142857142857</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>181.5238095238095</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>385.1428571428572</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>647285.7142857143</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>203057142.8571429</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>390</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11.71428571428571</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>130</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>136000</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>61500000</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>27.50454545454546</v>
+      </c>
+      <c r="O12" t="n">
+        <v>186.4929292929293</v>
+      </c>
+      <c r="P12" t="n">
+        <v>80.17626262626261</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>107952.5252525252</v>
+      </c>
+      <c r="R12" t="n">
+        <v>26399943.18181818</v>
+      </c>
+      <c r="S12" t="n">
+        <v>81.76641414141415</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.427525252525252</v>
+      </c>
+      <c r="U12" t="n">
+        <v>25.75520833333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>182.3072916666667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>83.07118055555556</v>
+      </c>
+      <c r="X12" t="n">
+        <v>146394.0972222222</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>52162326.3888889</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>85.23263888888889</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.232638888888889</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>26.94848608325131</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>182.8534652572707</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>77.86503140774296</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>93330.86463807567</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>19804824.78477834</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>80.38877419832014</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.960366931638861</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>24.74108951569978</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>178.8135274824813</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>77.8069202191306</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>109908.2045755065</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>28659147.41127484</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>83.20136080428915</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.350459067296167</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>25.45714285714286</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>188.5666666666667</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>311.5714285714286</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>358142.8571428572</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>85114285.71428572</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>327.4285714285714</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.857142857142858</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>26.22142857142857</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>181.5238095238095</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>385.1428571428572</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>647285.7142857143</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>203057142.8571429</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>390</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>11.71428571428571</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>25.36111111111111</v>
+      </c>
+      <c r="O13" t="n">
+        <v>181.2170138888889</v>
+      </c>
+      <c r="P13" t="n">
+        <v>76.26354166666667</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>50192.36111111111</v>
+      </c>
+      <c r="R13" t="n">
+        <v>11359756.94444444</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79.50555555555556</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.186458333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.38472222222222</v>
+      </c>
+      <c r="V13" t="n">
+        <v>181.0006313131313</v>
+      </c>
+      <c r="W13" t="n">
+        <v>83.90643939393939</v>
+      </c>
+      <c r="X13" t="n">
+        <v>183645.202020202</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>58707196.96969697</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>86.1233585858586</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.287121212121212</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>24.9392666157372</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>179.3089667685256</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>75.05516827943299</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>47952.49766573296</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9593496.413717002</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>78.86483532807063</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.12018292165351</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26.14773107117341</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>179.3145743140373</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>80.14229153199742</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>138186.3754763039</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>39125162.83107372</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>83.30649506259994</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.57589535561188</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>25.38888888888889</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>140.8333333333333</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>102166.6666666667</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>21933333.33333333</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>25.02380952380952</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>176.3571428571428</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>194.8571428571429</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>367428.5714285714</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>87714285.71428572</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>208.7142857142857</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.285714285714286</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>25.59141414141414</v>
+      </c>
+      <c r="O14" t="n">
+        <v>183.4600378787879</v>
+      </c>
+      <c r="P14" t="n">
+        <v>74.01095328282827</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>44052.68308080808</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6005205.176767677</v>
+      </c>
+      <c r="S14" t="n">
+        <v>77.8616792929293</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.077241161616162</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26.65555555555556</v>
+      </c>
+      <c r="V14" t="n">
+        <v>180.9154320987655</v>
+      </c>
+      <c r="W14" t="n">
+        <v>75.50462962962963</v>
+      </c>
+      <c r="X14" t="n">
+        <v>42996.91358024692</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7806319.444444444</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>77.96697530864198</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.368518518518518</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>26.58412206988059</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>180.2643244139761</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>72.27864053516143</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>42570.32010172489</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4051702.233524989</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>74.94637605042017</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.036018354710305</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>26.98011095276317</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>179.6271143545137</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>73.97356217340737</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>44200.54247819985</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>6097438.933663134</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>76.67991765907144</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.261938342588498</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>27.59285714285715</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>181.6857142857143</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>201.5714285714286</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>90571.42857142857</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6942857.142857143</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>205</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>25.17857142857143</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>188.3095238095238</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>201.5714285714286</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>100571.4285714286</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>10185714.28571429</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>212.5714285714286</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>26.80328282828283</v>
+      </c>
+      <c r="O15" t="n">
+        <v>184.2414141414141</v>
+      </c>
+      <c r="P15" t="n">
+        <v>83.88371212121211</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>130647.9797979798</v>
+      </c>
+      <c r="R15" t="n">
+        <v>50273169.19191919</v>
+      </c>
+      <c r="S15" t="n">
+        <v>85.69873737373737</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.137247474747475</v>
+      </c>
+      <c r="U15" t="n">
+        <v>25.33647586980921</v>
+      </c>
+      <c r="V15" t="n">
+        <v>183.2777777777778</v>
+      </c>
+      <c r="W15" t="n">
+        <v>75.10763187429853</v>
+      </c>
+      <c r="X15" t="n">
+        <v>61700.22446689113</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10739057.23905724</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>80.30841750841751</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.495398428731762</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>25.60375258799171</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>182.9150168219462</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>80.51587085921324</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>102430.7712215321</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>34626498.44720497</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>83.49814958592133</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.342520703933747</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>23.59090039143041</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>179.8176333843988</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>73.80000029378647</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>57984.35325312429</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>10444523.73207101</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>80.73026799201756</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.356139870135697</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>136000</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>61500000</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>31.95833333333333</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>179.4583333333333</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>200666.6666666667</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>44583333.33333334</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">city ground
   nottingham </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E16" t="n">
         <v>30404</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>UsushcZr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>26.74074074074074</v>
+      </c>
+      <c r="O16" t="n">
+        <v>183</v>
+      </c>
+      <c r="P16" t="n">
+        <v>77.03703703703702</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>57500</v>
+      </c>
+      <c r="R16" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>78.94444444444444</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>28.10956790123457</v>
+      </c>
+      <c r="V16" t="n">
+        <v>182.3287037037037</v>
+      </c>
+      <c r="W16" t="n">
+        <v>79.60339506172839</v>
+      </c>
+      <c r="X16" t="n">
+        <v>86543.20987654322</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>20683641.97530864</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>80.70833333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.299382716049382</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.59265873015873</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>183.5138888888889</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>76.12480158730159</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>54572.81746031746</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>10166924.6031746</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>78.71210317460317</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.226190476190476</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>28.66952614379085</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>181.0411220043573</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>77.94821169208424</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>78379.35729847493</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>16151829.15758896</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>79.72113289760348</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.041984386347131</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>100250</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>138</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>181</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>78500</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>26.14756944444444</v>
+      </c>
+      <c r="O17" t="n">
+        <v>182.0711805555556</v>
+      </c>
+      <c r="P17" t="n">
+        <v>73.21701388888889</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>46968.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6468359.375</v>
+      </c>
+      <c r="S17" t="n">
+        <v>77.02083333333333</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.310763888888889</v>
+      </c>
+      <c r="U17" t="n">
+        <v>28.13080808080808</v>
+      </c>
+      <c r="V17" t="n">
+        <v>182.7792929292929</v>
+      </c>
+      <c r="W17" t="n">
+        <v>76.47563131313132</v>
+      </c>
+      <c r="X17" t="n">
+        <v>47073.23232323233</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10687133.83838384</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>78.59772727272727</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.504166666666666</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>26.40509686773877</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>180.3285185631935</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>71.43124661525074</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>40448.25986038576</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4123495.072847499</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>75.80092985980498</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.150872030541793</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>27.37959135091488</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>182.8496163422634</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>74.17633172020426</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>40075.88765627981</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>6246817.125684773</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>76.8780433165237</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.271734665117018</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>153.8571428571429</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>61857.14285714286</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9196428.571428571</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>167.5714285714286</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>24.16190476190476</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>186.7190476190476</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>345.8571428571428</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>190571.4285714286</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>38753571.42857143</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>375.1428571428572</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>AovF1Mia</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H18" t="n">
         <v>48</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I18" t="n">
         <v>481</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K18" t="n">
         <v>20242025</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>182.75</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>312</v>
-      </c>
-      <c r="R4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>57500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>317</v>
-      </c>
-      <c r="U4" t="n">
-        <v>8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>187</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>302</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>209000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>39400000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26.74074074074074</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>183</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>77.03703703703702</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>57500</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>78.94444444444444</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="N18" t="n">
+        <v>26.71666666666667</v>
+      </c>
+      <c r="O18" t="n">
+        <v>182.8103174603175</v>
+      </c>
+      <c r="P18" t="n">
+        <v>76.78611111111111</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>54978.57142857143</v>
+      </c>
+      <c r="R18" t="n">
+        <v>13011071.42857143</v>
+      </c>
+      <c r="S18" t="n">
+        <v>80.06031746031746</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.493650793650794</v>
+      </c>
+      <c r="U18" t="n">
         <v>25.70659722222222</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="V18" t="n">
         <v>182.4645833333333</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="W18" t="n">
         <v>78.64895833333334</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="X18" t="n">
         <v>72194.79166666666</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="Y18" t="n">
         <v>19732916.66666666</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="Z18" t="n">
         <v>80.94305555555556</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AA18" t="n">
         <v>1.454166666666666</v>
       </c>
-      <c r="AR4" t="n">
-        <v>25.59265873015873</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>183.5138888888889</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>76.12480158730159</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>54572.81746031746</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10166924.6031746</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>78.71210317460317</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.226190476190476</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="AB18" t="n">
+        <v>27.97499504852446</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>179.9854492638806</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>76.11022314649765</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>56831.91721132898</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10678403.80933518</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>78.07904370502411</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.431060606060606</v>
+      </c>
+      <c r="AI18" t="n">
         <v>27.70182396722645</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AJ18" t="n">
         <v>183.2188244675861</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="AK18" t="n">
         <v>74.54993002783252</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="AL18" t="n">
         <v>60652.41149888982</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="AM18" t="n">
         <v>8353265.472058043</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="AN18" t="n">
         <v>76.49911967976983</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="AO18" t="n">
         <v>1.027173046251994</v>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="AP18" t="n">
+        <v>24.52380952380953</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>191.6952380952381</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>201</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>133571.4285714286</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>21914285.71428571</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>214.2857142857143</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>186.7666666666667</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>151000</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>25.51587301587302</v>
+      </c>
+      <c r="O19" t="n">
+        <v>184.2809523809524</v>
+      </c>
+      <c r="P19" t="n">
+        <v>82.24126984126984</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>111465.0793650794</v>
+      </c>
+      <c r="R19" t="n">
+        <v>39797619.04761905</v>
+      </c>
+      <c r="S19" t="n">
+        <v>84.73015873015872</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.765079365079365</v>
+      </c>
+      <c r="U19" t="n">
+        <v>26.02272727272727</v>
+      </c>
+      <c r="V19" t="n">
+        <v>183.9065656565656</v>
+      </c>
+      <c r="W19" t="n">
+        <v>79.43686868686869</v>
+      </c>
+      <c r="X19" t="n">
+        <v>103454.5454545455</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>25305871.21212121</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>82.09722222222221</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.271464646464647</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>24.64276601666307</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>184.2495977878331</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>78.18522453853336</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>78305.81591611003</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>22702380.8177117</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>82.42842912806148</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.875670203979028</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>24.22582255416209</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>181.6081552231617</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>76.34848337803501</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>82780.50200538401</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>17896517.25890195</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>81.08852804565763</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.565725934772702</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>183.7857142857143</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>170.5714285714286</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>231000</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>60571428.57142857</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>178.1428571428571</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>27.52380952380953</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>187.9404761904762</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>261.5714285714286</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>327428.5714285714</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>69532142.85714285</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>266.1428571428572</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>26.36071428571429</v>
+      </c>
+      <c r="O20" t="n">
+        <v>183.1464285714286</v>
+      </c>
+      <c r="P20" t="n">
+        <v>80.39285714285714</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>100139.2857142857</v>
+      </c>
+      <c r="R20" t="n">
+        <v>30899553.57142857</v>
+      </c>
+      <c r="S20" t="n">
+        <v>83.35000000000001</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.482142857142857</v>
+      </c>
+      <c r="U20" t="n">
+        <v>23.25277777777778</v>
+      </c>
+      <c r="V20" t="n">
+        <v>183.65</v>
+      </c>
+      <c r="W20" t="n">
+        <v>79.84305555555555</v>
+      </c>
+      <c r="X20" t="n">
+        <v>97413.88888888889</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>32123958.33333334</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>84.29166666666666</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.830555555555556</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>26.89847184065934</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>183.8795386904762</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>78.0419184981685</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>87233.77403846153</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>21389861.49267399</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>81.47093635531135</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.043189102564103</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>24.08550258221311</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>181.2523595921622</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>79.1382371648819</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>104063.2433356118</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>28107983.52415129</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>83.5496663059163</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.895013575605681</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>25.3452380952381</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>180.1904761904762</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>232.4285714285714</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>227142.8571428571</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>47071428.57142857</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>242.5714285714286</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>22.16666666666667</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>180.8611111111111</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>122833.3333333333</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>209.6666666666667</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>27.31111111111111</v>
+      </c>
+      <c r="O21" t="n">
+        <v>184.4555555555555</v>
+      </c>
+      <c r="P21" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>67100</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10620000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>78.21111111111112</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="U21" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="V21" t="n">
+        <v>184.3187429854096</v>
+      </c>
+      <c r="W21" t="n">
+        <v>75.40269360269362</v>
+      </c>
+      <c r="X21" t="n">
+        <v>54448.3164983165</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10256097.08193042</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>79.87502805836139</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.169668911335578</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>26.8717506326202</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>182.8333390844261</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>74.66962272831837</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>62752.03588681849</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>7435177.708764666</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>77.31696572348746</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.249286864504256</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>23.48753248862898</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>181.1835561125035</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>71.72081476840248</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>45303.97405550915</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>6791494.999071754</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>78.9555114638448</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.058223104056437</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>92800</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>25.25238095238095</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>178.1095238095238</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>252.8571428571429</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>201714.2857142857</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>39714285.71428572</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>259.8571428571428</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>WIs9mjGL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.66666666666</v>
+        <v>45598.39583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32261</v>
+        <v>52305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>26.25</v>
+        <v>27.48011363636364</v>
       </c>
       <c r="O2" t="n">
-        <v>188.5</v>
+        <v>186.4670454545455</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>80.39829545454546</v>
       </c>
       <c r="Q2" t="n">
-        <v>286</v>
+        <v>109334.0909090909</v>
       </c>
       <c r="R2" t="n">
-        <v>146000</v>
+        <v>27182436.07954545</v>
       </c>
       <c r="S2" t="n">
-        <v>14200000</v>
+        <v>82.03721590909092</v>
       </c>
       <c r="T2" t="n">
-        <v>298</v>
+        <v>2.493465909090909</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>25.88020833333333</v>
       </c>
       <c r="V2" t="n">
-        <v>25</v>
+        <v>182.1545138888889</v>
       </c>
       <c r="W2" t="n">
-        <v>185</v>
+        <v>82.96006944444444</v>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>145560.7638888889</v>
       </c>
       <c r="Y2" t="n">
-        <v>156</v>
+        <v>50426215.27777778</v>
       </c>
       <c r="Z2" t="n">
-        <v>117000</v>
+        <v>85.07986111111111</v>
       </c>
       <c r="AA2" t="n">
-        <v>35500000</v>
+        <v>3.204861111111111</v>
       </c>
       <c r="AB2" t="n">
-        <v>161</v>
+        <v>26.91477162435947</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>183.3401283120904</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.625</v>
+        <v>77.57015412026055</v>
       </c>
       <c r="AE2" t="n">
-        <v>180.8173611111111</v>
+        <v>90526.50817105152</v>
       </c>
       <c r="AF2" t="n">
-        <v>75.48020833333334</v>
+        <v>18620941.86313879</v>
       </c>
       <c r="AG2" t="n">
-        <v>43009.02777777778</v>
+        <v>80.07498062223294</v>
       </c>
       <c r="AH2" t="n">
-        <v>7884609.375</v>
+        <v>1.872856146046936</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.92534722222221</v>
+        <v>24.51693538036144</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.377083333333333</v>
+        <v>178.948865828346</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.92592592592592</v>
+        <v>77.23032247476971</v>
       </c>
       <c r="AL2" t="n">
-        <v>182.9074074074074</v>
+        <v>107047.3023198674</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.01851851851852</v>
+        <v>27734758.31353048</v>
       </c>
       <c r="AN2" t="n">
-        <v>58314.81481481481</v>
+        <v>83.18162396218389</v>
       </c>
       <c r="AO2" t="n">
-        <v>11703703.7037037</v>
+        <v>2.314744781581881</v>
       </c>
       <c r="AP2" t="n">
-        <v>78.79629629629629</v>
+        <v>26.15714285714285</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.296296296296296</v>
+        <v>188.3095238095238</v>
       </c>
       <c r="AR2" t="n">
-        <v>27.04012482185857</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="AS2" t="n">
-        <v>179.7492536488279</v>
+        <v>300.1428571428572</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.9265074450833</v>
+        <v>338857.1428571428</v>
       </c>
       <c r="AU2" t="n">
-        <v>44419.36028797484</v>
+        <v>75303571.42857143</v>
       </c>
       <c r="AV2" t="n">
-        <v>5991025.050371025</v>
+        <v>313.7142857142857</v>
       </c>
       <c r="AW2" t="n">
-        <v>76.61490736645536</v>
+        <v>8.428571428571429</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.25093063541206</v>
+        <v>26.03095238095238</v>
       </c>
       <c r="AY2" t="n">
-        <v>25.43392857142857</v>
+        <v>182.0595238095238</v>
       </c>
       <c r="AZ2" t="n">
-        <v>183.1945970695971</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="BA2" t="n">
-        <v>76.08878205128205</v>
+        <v>398.5714285714286</v>
       </c>
       <c r="BB2" t="n">
-        <v>54596.01648351648</v>
+        <v>685142.8571428572</v>
       </c>
       <c r="BC2" t="n">
-        <v>10180050.36630036</v>
+        <v>228985714.2857143</v>
       </c>
       <c r="BD2" t="n">
-        <v>78.8323717948718</v>
+        <v>403.8571428571428</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.213369963369964</v>
+        <v>12.42857142857143</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>MqhPmaA4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42789</v>
+        <v>11307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +980,180 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>25.15873015873016</v>
       </c>
       <c r="O3" t="n">
-        <v>179</v>
+        <v>181.3019841269841</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>76.50277777777777</v>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>50875.39682539682</v>
       </c>
       <c r="R3" t="n">
-        <v>67000</v>
+        <v>12035277.77777778</v>
       </c>
       <c r="S3" t="n">
-        <v>12500000</v>
+        <v>79.69682539682539</v>
       </c>
       <c r="T3" t="n">
-        <v>83</v>
+        <v>1.181349206349206</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>26.30972222222222</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>181.0006313131313</v>
       </c>
       <c r="W3" t="n">
-        <v>175</v>
+        <v>83.85643939393938</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>182582.702020202</v>
       </c>
       <c r="Y3" t="n">
-        <v>77</v>
+        <v>59063446.96969697</v>
       </c>
       <c r="Z3" t="n">
-        <v>53000</v>
+        <v>86.04835858585859</v>
       </c>
       <c r="AA3" t="n">
-        <v>12000000</v>
+        <v>3.249621212121212</v>
       </c>
       <c r="AB3" t="n">
-        <v>79</v>
+        <v>25.40237913347157</v>
       </c>
       <c r="AC3" t="n">
+        <v>179.0861981156099</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>75.30514630094463</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>49227.02414299053</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9631943.080262406</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>78.59142444856731</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.196175439872919</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>26.29773107117341</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>179.4583243140373</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>79.72354153199741</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>134198.8754763039</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>37598287.83107372</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>83.06274506259993</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.54464535561188</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>24.80555555555555</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>176.8888888888889</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>127.8333333333333</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>89333.33333333333</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>20083333.33333333</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>133</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>25.88095238095238</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>176.6714285714285</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>3</v>
       </c>
-      <c r="AD3" t="n">
-        <v>25.93506493506494</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>183.8932178932179</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>79.21356421356423</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>102077.9220779221</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>24836580.08658009</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>82.02020202020201</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.232323232323233</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25.30158730158731</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>181.2162698412698</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>76.17420634920634</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>50203.96825396825</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>11309563.49206349</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>79.48253968253968</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.181349206349207</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>24.12883121836211</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>181.4501365815725</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>76.13976331639375</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>81919.21317622119</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17724591.15303079</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>81.03995041952707</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.571713993481728</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>25.03263123431191</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>179.2374586198116</v>
-      </c>
       <c r="BA3" t="n">
-        <v>75.35556646901185</v>
+        <v>242</v>
       </c>
       <c r="BB3" t="n">
-        <v>48857.27624383086</v>
+        <v>460857.1428571428</v>
       </c>
       <c r="BC3" t="n">
-        <v>9996648.96261535</v>
+        <v>110142857.1428571</v>
       </c>
       <c r="BD3" t="n">
-        <v>78.96117234772699</v>
+        <v>256.7142857142857</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.137351910461154</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>lb85TUOk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith l 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17250</v>
+        <v>29673</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,180 +1179,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.75</v>
+        <v>25.50923520923521</v>
       </c>
       <c r="O4" t="n">
-        <v>177.75</v>
+        <v>183.3471861471862</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>74.31370851370851</v>
       </c>
       <c r="Q4" t="n">
-        <v>309</v>
+        <v>45057.43145743146</v>
       </c>
       <c r="R4" t="n">
-        <v>258000</v>
+        <v>6297258.297258297</v>
       </c>
       <c r="S4" t="n">
-        <v>52000000</v>
+        <v>78.16017316017314</v>
       </c>
       <c r="T4" t="n">
-        <v>316</v>
+        <v>1.086291486291486</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>26.56944444444444</v>
       </c>
       <c r="V4" t="n">
-        <v>26.6</v>
+        <v>180.9145833333333</v>
       </c>
       <c r="W4" t="n">
-        <v>183.8</v>
+        <v>75.66076388888889</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>43272.91666666667</v>
       </c>
       <c r="Y4" t="n">
-        <v>354</v>
+        <v>7922456.597222222</v>
       </c>
       <c r="Z4" t="n">
-        <v>161000</v>
+        <v>78.18923611111111</v>
       </c>
       <c r="AA4" t="n">
-        <v>13800000</v>
+        <v>1.390972222222222</v>
       </c>
       <c r="AB4" t="n">
-        <v>367</v>
+        <v>26.82546281670563</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>180.3547166234915</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.15909090909091</v>
+        <v>72.50265685221459</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.290404040404</v>
+        <v>43119.46357490363</v>
       </c>
       <c r="AF4" t="n">
-        <v>75.23712121212122</v>
+        <v>3980986.763126303</v>
       </c>
       <c r="AG4" t="n">
-        <v>53708.90151515151</v>
+        <v>74.97555759145764</v>
       </c>
       <c r="AH4" t="n">
-        <v>10098336.48989899</v>
+        <v>1.033645036962153</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.97304292929293</v>
+        <v>27.34212062017789</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.168150252525253</v>
+        <v>179.859547766475</v>
       </c>
       <c r="AK4" t="n">
-        <v>25.60447330447331</v>
+        <v>74.27629736104969</v>
       </c>
       <c r="AL4" t="n">
-        <v>183.5257575757576</v>
+        <v>45456.65020394123</v>
       </c>
       <c r="AM4" t="n">
-        <v>73.99823232323232</v>
+        <v>6293900.575581109</v>
       </c>
       <c r="AN4" t="n">
-        <v>44674.49494949495</v>
+        <v>76.60177711435452</v>
       </c>
       <c r="AO4" t="n">
-        <v>6028805.916305916</v>
+        <v>1.289796181630547</v>
       </c>
       <c r="AP4" t="n">
-        <v>77.79906204906204</v>
+        <v>27.57142857142857</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.088275613275613</v>
+        <v>182.0714285714286</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.4625365497076</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="AS4" t="n">
-        <v>181.4096256265664</v>
+        <v>191.4285714285714</v>
       </c>
       <c r="AT4" t="n">
-        <v>71.48279161445279</v>
+        <v>76000</v>
       </c>
       <c r="AU4" t="n">
-        <v>44888.84581244779</v>
+        <v>6371428.571428572</v>
       </c>
       <c r="AV4" t="n">
-        <v>6669338.123955723</v>
+        <v>195.1428571428571</v>
       </c>
       <c r="AW4" t="n">
-        <v>78.8093253968254</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.057688492063492</v>
+        <v>25.01666666666667</v>
       </c>
       <c r="AY4" t="n">
-        <v>26.65328236557781</v>
+        <v>188.2142857142857</v>
       </c>
       <c r="AZ4" t="n">
-        <v>180.0020850445441</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="BA4" t="n">
-        <v>72.52558918304165</v>
+        <v>222.8571428571429</v>
       </c>
       <c r="BB4" t="n">
-        <v>43301.79440197131</v>
+        <v>111285.7142857143</v>
       </c>
       <c r="BC4" t="n">
-        <v>4181945.409742844</v>
+        <v>12085714.28571429</v>
       </c>
       <c r="BD4" t="n">
-        <v>75.14585834333732</v>
+        <v>235</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.041163833954634</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>rc1ER8g2</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31876</v>
+        <v>61276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1378,180 +1378,180 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>26.75555555555556</v>
       </c>
       <c r="O5" t="n">
-        <v>182.6666666666667</v>
+        <v>184.2652777777778</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>83.74621212121212</v>
       </c>
       <c r="Q5" t="n">
-        <v>237</v>
+        <v>129702.5252525253</v>
       </c>
       <c r="R5" t="n">
-        <v>319000</v>
+        <v>49727146.46464646</v>
       </c>
       <c r="S5" t="n">
-        <v>67800000</v>
+        <v>85.60441919191919</v>
       </c>
       <c r="T5" t="n">
-        <v>237</v>
+        <v>3.092929292929293</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>25.22853535353535</v>
       </c>
       <c r="V5" t="n">
-        <v>26</v>
+        <v>183.7125</v>
       </c>
       <c r="W5" t="n">
-        <v>188.2</v>
+        <v>75.40858585858587</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>61800.25252525252</v>
       </c>
       <c r="Y5" t="n">
-        <v>374</v>
+        <v>10998939.39393939</v>
       </c>
       <c r="Z5" t="n">
-        <v>248000</v>
+        <v>80.57196969696969</v>
       </c>
       <c r="AA5" t="n">
-        <v>41800000</v>
+        <v>1.532323232323232</v>
       </c>
       <c r="AB5" t="n">
-        <v>393</v>
+        <v>25.69125258799171</v>
       </c>
       <c r="AC5" t="n">
-        <v>7</v>
+        <v>183.1223084886128</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.89103535353535</v>
+        <v>80.32732919254659</v>
       </c>
       <c r="AE5" t="n">
-        <v>183.3875</v>
+        <v>101643.2712215321</v>
       </c>
       <c r="AF5" t="n">
-        <v>74.90858585858587</v>
+        <v>34020248.44720497</v>
       </c>
       <c r="AG5" t="n">
-        <v>59825.25252525252</v>
+        <v>83.25231625258799</v>
       </c>
       <c r="AH5" t="n">
-        <v>10443939.39393939</v>
+        <v>2.350854037267081</v>
       </c>
       <c r="AI5" t="n">
-        <v>80.45946969696969</v>
+        <v>23.78976294035921</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.457323232323232</v>
+        <v>180.0453202519566</v>
       </c>
       <c r="AK5" t="n">
-        <v>26.73611111111111</v>
+        <v>74.81888977558987</v>
       </c>
       <c r="AL5" t="n">
-        <v>182.912037037037</v>
+        <v>60864.90599100052</v>
       </c>
       <c r="AM5" t="n">
-        <v>76.81712962962963</v>
+        <v>11079258.24892314</v>
       </c>
       <c r="AN5" t="n">
-        <v>54875</v>
+        <v>81.27837714891449</v>
       </c>
       <c r="AO5" t="n">
-        <v>13006250</v>
+        <v>1.36288203925735</v>
       </c>
       <c r="AP5" t="n">
-        <v>80.12037037037037</v>
+        <v>23.625</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.50925925925926</v>
+        <v>175.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>23.66476294035921</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>180.0991853835356</v>
+        <v>162.8333333333333</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.81847859137935</v>
+        <v>178833.3333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>58688.91914889526</v>
+        <v>77333333.33333333</v>
       </c>
       <c r="AV5" t="n">
-        <v>10668567.45944946</v>
+        <v>172.8333333333333</v>
       </c>
       <c r="AW5" t="n">
-        <v>80.69655149101975</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.378918223467877</v>
+        <v>33.625</v>
       </c>
       <c r="AY5" t="n">
-        <v>27.88363413547237</v>
+        <v>179.0138888888889</v>
       </c>
       <c r="AZ5" t="n">
-        <v>180.160101010101</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>76.0651775103981</v>
+        <v>183</v>
       </c>
       <c r="BB5" t="n">
-        <v>56671.20098039215</v>
+        <v>226500</v>
       </c>
       <c r="BC5" t="n">
-        <v>10797763.10903149</v>
+        <v>47800000</v>
       </c>
       <c r="BD5" t="n">
-        <v>78.08892416815212</v>
+        <v>185</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.418766711229947</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>21YvrUwq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45598.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55097</v>
+        <v>30404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1577,180 +1577,180 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="O6" t="n">
-        <v>176.2</v>
+        <v>182.984126984127</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>76.96825396825398</v>
       </c>
       <c r="Q6" t="n">
-        <v>402</v>
+        <v>57857.14285714286</v>
       </c>
       <c r="R6" t="n">
-        <v>713000</v>
+        <v>11515873.01587302</v>
       </c>
       <c r="S6" t="n">
-        <v>162500000</v>
+        <v>78.77777777777779</v>
       </c>
       <c r="T6" t="n">
-        <v>421</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>28.13020833333334</v>
       </c>
       <c r="V6" t="n">
-        <v>26.33333333333333</v>
+        <v>182.5364583333333</v>
       </c>
       <c r="W6" t="n">
-        <v>180</v>
+        <v>79.64409722222223</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>86763.88888888889</v>
       </c>
       <c r="Y6" t="n">
-        <v>216</v>
+        <v>20879340.27777778</v>
       </c>
       <c r="Z6" t="n">
-        <v>108000</v>
+        <v>80.71354166666666</v>
       </c>
       <c r="AA6" t="n">
-        <v>10300000</v>
+        <v>2.326388888888889</v>
       </c>
       <c r="AB6" t="n">
-        <v>225</v>
+        <v>25.7429945054945</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>183.0249542124542</v>
       </c>
       <c r="AD6" t="n">
-        <v>26.3968253968254</v>
+        <v>76.27559523809524</v>
       </c>
       <c r="AE6" t="n">
-        <v>180.9292929292929</v>
+        <v>56319.23076923077</v>
       </c>
       <c r="AF6" t="n">
-        <v>83.73593073593074</v>
+        <v>10169473.44322344</v>
       </c>
       <c r="AG6" t="n">
-        <v>181451.6594516594</v>
+        <v>78.7135531135531</v>
       </c>
       <c r="AH6" t="n">
-        <v>57758225.10822511</v>
+        <v>1.154990842490843</v>
       </c>
       <c r="AI6" t="n">
-        <v>85.95526695526696</v>
+        <v>28.90150122549019</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.242424242424242</v>
+        <v>181.109170751634</v>
       </c>
       <c r="AK6" t="n">
-        <v>25.9781746031746</v>
+        <v>77.64721200980392</v>
       </c>
       <c r="AL6" t="n">
-        <v>181.7321428571429</v>
+        <v>76929.63643790848</v>
       </c>
       <c r="AM6" t="n">
-        <v>72.99404761904762</v>
+        <v>14808389.50163399</v>
       </c>
       <c r="AN6" t="n">
-        <v>45789.68253968254</v>
+        <v>79.45179738562092</v>
       </c>
       <c r="AO6" t="n">
-        <v>6528521.825396826</v>
+        <v>1.959814133986928</v>
       </c>
       <c r="AP6" t="n">
-        <v>77.03968253968253</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.323412698412698</v>
+        <v>188</v>
       </c>
       <c r="AR6" t="n">
-        <v>26.04026408134104</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>179.1237992160427</v>
+        <v>155.3333333333333</v>
       </c>
       <c r="AT6" t="n">
-        <v>80.05547603656848</v>
+        <v>121666.6666666667</v>
       </c>
       <c r="AU6" t="n">
-        <v>135941.5719729187</v>
+        <v>28000000</v>
       </c>
       <c r="AV6" t="n">
-        <v>39583757.52122711</v>
+        <v>158.8333333333333</v>
       </c>
       <c r="AW6" t="n">
-        <v>83.28599435725707</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.579594692127864</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="AY6" t="n">
-        <v>26.78906730953944</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="AZ6" t="n">
-        <v>180.3626389391482</v>
+        <v>1</v>
       </c>
       <c r="BA6" t="n">
-        <v>71.74209688660153</v>
+        <v>79</v>
       </c>
       <c r="BB6" t="n">
-        <v>41587.62567626731</v>
+        <v>84000</v>
       </c>
       <c r="BC6" t="n">
-        <v>4170181.956953436</v>
+        <v>24500000</v>
       </c>
       <c r="BD6" t="n">
-        <v>75.65104609228061</v>
+        <v>81</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.169731034359518</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>OGMmt88e</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45598.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39572</v>
+        <v>32384</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1776,180 +1776,180 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22.14285714285714</v>
+        <v>26.50396825396825</v>
       </c>
       <c r="O7" t="n">
-        <v>186.5714285714286</v>
+        <v>181.8531746031746</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>73.96626984126985</v>
       </c>
       <c r="Q7" t="n">
-        <v>515</v>
+        <v>49654.7619047619</v>
       </c>
       <c r="R7" t="n">
-        <v>291000</v>
+        <v>7345882.936507936</v>
       </c>
       <c r="S7" t="n">
-        <v>70900000</v>
+        <v>77.36309523809526</v>
       </c>
       <c r="T7" t="n">
-        <v>565</v>
+        <v>1.402777777777777</v>
       </c>
       <c r="U7" t="n">
-        <v>7</v>
+        <v>28.52337662337662</v>
       </c>
       <c r="V7" t="n">
-        <v>28</v>
+        <v>182.4779220779221</v>
       </c>
       <c r="W7" t="n">
-        <v>187.5</v>
+        <v>76.6077922077922</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>47640.25974025975</v>
       </c>
       <c r="Y7" t="n">
-        <v>306</v>
+        <v>10688376.62337662</v>
       </c>
       <c r="Z7" t="n">
-        <v>288000</v>
+        <v>78.48311688311688</v>
       </c>
       <c r="AA7" t="n">
-        <v>39700000</v>
+        <v>1.520779220779221</v>
       </c>
       <c r="AB7" t="n">
-        <v>307</v>
+        <v>27.06726279826125</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>180.8184660068174</v>
       </c>
       <c r="AD7" t="n">
-        <v>28.13520923520923</v>
+        <v>72.30929613472183</v>
       </c>
       <c r="AE7" t="n">
-        <v>182.7477633477633</v>
+        <v>43465.91514995153</v>
       </c>
       <c r="AF7" t="n">
-        <v>76.47215007215007</v>
+        <v>4362945.114848172</v>
       </c>
       <c r="AG7" t="n">
-        <v>46840.83694083694</v>
+        <v>75.3728506035588</v>
       </c>
       <c r="AH7" t="n">
-        <v>10719581.52958153</v>
+        <v>1.156103214810645</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.625974025974</v>
+        <v>27.02814321095571</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.490476190476191</v>
+        <v>183.6602564102564</v>
       </c>
       <c r="AK7" t="n">
-        <v>27.4</v>
+        <v>74.45355963480964</v>
       </c>
       <c r="AL7" t="n">
-        <v>184.5125</v>
+        <v>40378.30953768454</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.4875</v>
+        <v>7221800.043706294</v>
       </c>
       <c r="AN7" t="n">
-        <v>67050</v>
+        <v>77.30719211344211</v>
       </c>
       <c r="AO7" t="n">
-        <v>10497500</v>
+        <v>1.281213578088578</v>
       </c>
       <c r="AP7" t="n">
-        <v>78.11250000000001</v>
+        <v>23.67857142857143</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.475</v>
+        <v>186.3928571428571</v>
       </c>
       <c r="AR7" t="n">
-        <v>27.55204026977924</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AS7" t="n">
-        <v>182.7236755279035</v>
+        <v>155.4285714285714</v>
       </c>
       <c r="AT7" t="n">
-        <v>74.22515889951552</v>
+        <v>65428.57142857143</v>
       </c>
       <c r="AU7" t="n">
-        <v>39719.30218474336</v>
+        <v>9928571.428571429</v>
       </c>
       <c r="AV7" t="n">
-        <v>6158472.83782394</v>
+        <v>167.8571428571429</v>
       </c>
       <c r="AW7" t="n">
-        <v>76.92529873108917</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.278915783970931</v>
+        <v>23.42380952380952</v>
       </c>
       <c r="AY7" t="n">
-        <v>26.69946946169772</v>
+        <v>187.147619047619</v>
       </c>
       <c r="AZ7" t="n">
-        <v>182.9937564699793</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="BA7" t="n">
-        <v>74.72832556935818</v>
+        <v>323.7142857142857</v>
       </c>
       <c r="BB7" t="n">
-        <v>63102.29037267081</v>
+        <v>183000</v>
       </c>
       <c r="BC7" t="n">
-        <v>7660199.922360249</v>
+        <v>34642857.14285714</v>
       </c>
       <c r="BD7" t="n">
-        <v>77.48783643892338</v>
+        <v>353.5714285714286</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.242947722567288</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>EJ4unbdE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45598.60416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40341</v>
+        <v>31750</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1975,180 +1975,180 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>26.73611111111111</v>
       </c>
       <c r="O8" t="n">
-        <v>191</v>
+        <v>183.599537037037</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>77.35879629629629</v>
       </c>
       <c r="Q8" t="n">
-        <v>62</v>
+        <v>56687.5</v>
       </c>
       <c r="R8" t="n">
-        <v>35000</v>
+        <v>14085416.66666667</v>
       </c>
       <c r="S8" t="n">
-        <v>1000000</v>
+        <v>80.57870370370371</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>1.550925925925926</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>25.640625</v>
       </c>
       <c r="V8" t="n">
-        <v>26.25</v>
+        <v>182.5798611111111</v>
       </c>
       <c r="W8" t="n">
-        <v>185.75</v>
+        <v>78.73680555555555</v>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>72866.31944444444</v>
       </c>
       <c r="Y8" t="n">
-        <v>312</v>
+        <v>19919548.61111111</v>
       </c>
       <c r="Z8" t="n">
-        <v>360000</v>
+        <v>81.00243055555556</v>
       </c>
       <c r="AA8" t="n">
-        <v>66100000</v>
+        <v>1.461111111111111</v>
       </c>
       <c r="AB8" t="n">
-        <v>329</v>
+        <v>27.96369949494949</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>180.0489898989899</v>
       </c>
       <c r="AD8" t="n">
-        <v>23.3031746031746</v>
+        <v>76.0431186868687</v>
       </c>
       <c r="AE8" t="n">
-        <v>183.7142857142857</v>
+        <v>56238.19444444444</v>
       </c>
       <c r="AF8" t="n">
-        <v>79.8063492063492</v>
+        <v>10685508.20707071</v>
       </c>
       <c r="AG8" t="n">
-        <v>97387.30158730158</v>
+        <v>78.0341856060606</v>
       </c>
       <c r="AH8" t="n">
-        <v>31998809.52380953</v>
+        <v>1.429387626262626</v>
       </c>
       <c r="AI8" t="n">
-        <v>84.23333333333333</v>
+        <v>27.98856639146887</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.834920634920635</v>
+        <v>183.1945820433436</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.53011363636364</v>
+        <v>74.40106639146887</v>
       </c>
       <c r="AL8" t="n">
-        <v>186.3045454545455</v>
+        <v>60974.00240798073</v>
       </c>
       <c r="AM8" t="n">
-        <v>80.26079545454544</v>
+        <v>8100898.047815617</v>
       </c>
       <c r="AN8" t="n">
-        <v>108346.5909090909</v>
+        <v>76.11048331613347</v>
       </c>
       <c r="AO8" t="n">
-        <v>26497436.07954545</v>
+        <v>1.013157894736842</v>
       </c>
       <c r="AP8" t="n">
-        <v>81.88721590909091</v>
+        <v>24.3452380952381</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.455965909090909</v>
+        <v>189.8380952380952</v>
       </c>
       <c r="AR8" t="n">
-        <v>24.06012325185257</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="AS8" t="n">
-        <v>181.4613432932982</v>
+        <v>232.2857142857143</v>
       </c>
       <c r="AT8" t="n">
-        <v>78.98505300046654</v>
+        <v>153714.2857142857</v>
       </c>
       <c r="AU8" t="n">
-        <v>102628.6690752856</v>
+        <v>25028571.42857143</v>
       </c>
       <c r="AV8" t="n">
-        <v>27503108.99000749</v>
+        <v>248.1428571428571</v>
       </c>
       <c r="AW8" t="n">
-        <v>83.4853329210472</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.880015514977921</v>
+        <v>25.63888888888889</v>
       </c>
       <c r="AY8" t="n">
-        <v>26.94862579102614</v>
+        <v>186.9166666666667</v>
       </c>
       <c r="AZ8" t="n">
-        <v>183.1048852565348</v>
+        <v>3</v>
       </c>
       <c r="BA8" t="n">
-        <v>77.9928971758161</v>
+        <v>227.8333333333333</v>
       </c>
       <c r="BB8" t="n">
-        <v>93891.9595599404</v>
+        <v>180666.6666666667</v>
       </c>
       <c r="BC8" t="n">
-        <v>20531019.98813879</v>
+        <v>35816666.66666666</v>
       </c>
       <c r="BD8" t="n">
-        <v>80.39789728889961</v>
+        <v>236</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.988307534935825</v>
+        <v>3</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45599.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
+          <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25486</v>
+        <v>62850</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2174,180 +2174,180 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>25.33333333333333</v>
+        <v>25.53333333333333</v>
       </c>
       <c r="O9" t="n">
-        <v>185.6666666666667</v>
+        <v>184.3746031746032</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>82.28571428571429</v>
       </c>
       <c r="Q9" t="n">
-        <v>228</v>
+        <v>111242.8571428571</v>
       </c>
       <c r="R9" t="n">
-        <v>178000</v>
+        <v>39731746.03174603</v>
       </c>
       <c r="S9" t="n">
-        <v>36600000</v>
+        <v>84.66666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>237</v>
+        <v>2.774603174603175</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>25.98863636363636</v>
       </c>
       <c r="V9" t="n">
-        <v>27</v>
+        <v>183.9292929292929</v>
       </c>
       <c r="W9" t="n">
-        <v>183.5</v>
+        <v>79.39141414141415</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>102954.5454545455</v>
       </c>
       <c r="Y9" t="n">
-        <v>159</v>
+        <v>25152462.12121212</v>
       </c>
       <c r="Z9" t="n">
-        <v>250000</v>
+        <v>82.09722222222221</v>
       </c>
       <c r="AA9" t="n">
-        <v>71000000</v>
+        <v>2.248737373737374</v>
       </c>
       <c r="AB9" t="n">
-        <v>165</v>
+        <v>24.91319085326438</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>184.232032428356</v>
       </c>
       <c r="AD9" t="n">
-        <v>25.81284722222222</v>
+        <v>78.51692388493859</v>
       </c>
       <c r="AE9" t="n">
-        <v>182.3770833333334</v>
+        <v>80183.67539323423</v>
       </c>
       <c r="AF9" t="n">
-        <v>78.66458333333333</v>
+        <v>23582834.24908425</v>
       </c>
       <c r="AG9" t="n">
-        <v>72463.54166666666</v>
+        <v>82.40228533721179</v>
       </c>
       <c r="AH9" t="n">
-        <v>19675104.16666666</v>
+        <v>1.954510073260074</v>
       </c>
       <c r="AI9" t="n">
-        <v>80.86493055555556</v>
+        <v>24.33668564940018</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.466666666666666</v>
+        <v>181.721994508876</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.58518518518519</v>
+        <v>76.50770956851119</v>
       </c>
       <c r="AL9" t="n">
-        <v>184.3444444444444</v>
+        <v>83778.26986252688</v>
       </c>
       <c r="AM9" t="n">
-        <v>82.31481481481482</v>
+        <v>18314876.63390195</v>
       </c>
       <c r="AN9" t="n">
-        <v>111875.9259259259</v>
+        <v>81.11308161708619</v>
       </c>
       <c r="AO9" t="n">
-        <v>39955555.55555556</v>
+        <v>1.620041410963179</v>
       </c>
       <c r="AP9" t="n">
-        <v>84.68518518518518</v>
+        <v>24.83333333333334</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.792592592592592</v>
+        <v>183.2857142857143</v>
       </c>
       <c r="AR9" t="n">
-        <v>27.71015730055977</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AS9" t="n">
-        <v>183.3104911342527</v>
+        <v>170.1428571428571</v>
       </c>
       <c r="AT9" t="n">
-        <v>74.5499300278325</v>
+        <v>233857.1428571429</v>
       </c>
       <c r="AU9" t="n">
-        <v>61327.41149888983</v>
+        <v>62071428.57142857</v>
       </c>
       <c r="AV9" t="n">
-        <v>8649307.138724709</v>
+        <v>178.2857142857143</v>
       </c>
       <c r="AW9" t="n">
-        <v>76.44911967976984</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01883971291866</v>
+        <v>26.73809523809524</v>
       </c>
       <c r="AY9" t="n">
-        <v>24.76633576507526</v>
+        <v>186.3690476190476</v>
       </c>
       <c r="AZ9" t="n">
-        <v>184.1979530273648</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="BA9" t="n">
-        <v>78.33866931387941</v>
+        <v>249.2857142857143</v>
       </c>
       <c r="BB9" t="n">
-        <v>79151.09120571306</v>
+        <v>307714.2857142857</v>
       </c>
       <c r="BC9" t="n">
-        <v>23196768.55357528</v>
+        <v>64532142.85714286</v>
       </c>
       <c r="BD9" t="n">
-        <v>82.42614122572104</v>
+        <v>254.7142857142857</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.89759134423</v>
+        <v>6.571428571428571</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>MeAQUqrN</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45599.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
-  london </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>62500</v>
+        <v>75635</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2373,344 +2373,2334 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>23</v>
+        <v>26.41150793650794</v>
       </c>
       <c r="O10" t="n">
-        <v>177</v>
+        <v>183.2718253968254</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>80.48968253968255</v>
       </c>
       <c r="Q10" t="n">
-        <v>82</v>
+        <v>100907.5396825397</v>
       </c>
       <c r="R10" t="n">
-        <v>95000</v>
+        <v>31575744.04761905</v>
       </c>
       <c r="S10" t="n">
-        <v>43500000</v>
+        <v>83.36428571428571</v>
       </c>
       <c r="T10" t="n">
-        <v>86</v>
+        <v>2.477380952380952</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>23.27777777777778</v>
       </c>
       <c r="V10" t="n">
-        <v>26.2</v>
+        <v>183.6</v>
       </c>
       <c r="W10" t="n">
-        <v>181.8</v>
+        <v>79.58055555555555</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>95576.38888888889</v>
       </c>
       <c r="Y10" t="n">
-        <v>395</v>
+        <v>31420833.33333334</v>
       </c>
       <c r="Z10" t="n">
-        <v>439000</v>
+        <v>84.06666666666666</v>
       </c>
       <c r="AA10" t="n">
-        <v>92500000</v>
+        <v>1.780555555555556</v>
       </c>
       <c r="AB10" t="n">
-        <v>412</v>
+        <v>26.96454326923077</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>183.5098958333333</v>
       </c>
       <c r="AD10" t="n">
-        <v>28.06770833333334</v>
+        <v>77.77227564102564</v>
       </c>
       <c r="AE10" t="n">
-        <v>182.2864583333333</v>
+        <v>85283.77403846153</v>
       </c>
       <c r="AF10" t="n">
-        <v>79.58159722222223</v>
+        <v>19928477.56410257</v>
       </c>
       <c r="AG10" t="n">
-        <v>86263.88888888889</v>
+        <v>81.41915064102565</v>
       </c>
       <c r="AH10" t="n">
-        <v>20699652.77777778</v>
+        <v>2.005689102564102</v>
       </c>
       <c r="AI10" t="n">
-        <v>80.71354166666666</v>
+        <v>24.03177451203767</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.295138888888889</v>
+        <v>181.0842309371915</v>
       </c>
       <c r="AK10" t="n">
-        <v>26.3875</v>
+        <v>79.17442137540822</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.1875</v>
+        <v>103633.4187742083</v>
       </c>
       <c r="AM10" t="n">
-        <v>80.27499999999999</v>
+        <v>28186748.14403433</v>
       </c>
       <c r="AN10" t="n">
-        <v>99262.5</v>
+        <v>83.60522186147186</v>
       </c>
       <c r="AO10" t="n">
-        <v>30866145.83333333</v>
+        <v>1.922791353383458</v>
       </c>
       <c r="AP10" t="n">
-        <v>83.25833333333334</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.445833333333333</v>
+        <v>180</v>
       </c>
       <c r="AR10" t="n">
-        <v>28.60738357843137</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="AS10" t="n">
-        <v>181.1018178104575</v>
+        <v>243.7142857142857</v>
       </c>
       <c r="AT10" t="n">
-        <v>77.94868259803921</v>
+        <v>238142.8571428571</v>
       </c>
       <c r="AU10" t="n">
-        <v>78378.16584967321</v>
+        <v>49000000</v>
       </c>
       <c r="AV10" t="n">
-        <v>16269418.91339869</v>
+        <v>254.7142857142857</v>
       </c>
       <c r="AW10" t="n">
-        <v>79.79738562091504</v>
+        <v>5.857142857142857</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.033343545751634</v>
+        <v>21.57142857142857</v>
       </c>
       <c r="AY10" t="n">
-        <v>27.08804945054945</v>
+        <v>182.3095238095238</v>
       </c>
       <c r="AZ10" t="n">
-        <v>183.8113095238095</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="BA10" t="n">
-        <v>78.13974358974359</v>
+        <v>168.7142857142857</v>
       </c>
       <c r="BB10" t="n">
-        <v>87552.88461538461</v>
+        <v>110285.7142857143</v>
       </c>
       <c r="BC10" t="n">
-        <v>21111117.21611722</v>
+        <v>22857142.85714286</v>
       </c>
       <c r="BD10" t="n">
-        <v>81.50760073260074</v>
+        <v>191.1428571428571</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.049358974358974</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45592.5625</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>29589</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>27.425</v>
+      </c>
+      <c r="O11" t="n">
+        <v>184.55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>76.91250000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>68487.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11103750</v>
+      </c>
+      <c r="S11" t="n">
+        <v>78.375</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.39772727272727</v>
+      </c>
+      <c r="V11" t="n">
+        <v>184.7506313131313</v>
+      </c>
+      <c r="W11" t="n">
+        <v>75.6689393939394</v>
+      </c>
+      <c r="X11" t="n">
+        <v>55018.56060606059</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10676887.62626263</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>79.94747474747476</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.175252525252525</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>26.79289596273292</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>182.6919966356108</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>74.82175207039339</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>63725.73757763975</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7587736.154244306</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>77.42443064182194</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.233630952380953</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>23.49236111111111</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>180.8153273809524</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>71.47051091269842</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>44748.93353174604</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>6485675.843253968</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>78.99265873015872</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.066021825396826</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>188.9166666666667</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>138</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>125333.3333333333</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>138.1666666666667</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>25.25238095238095</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>178.1095238095238</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>252.8571428571429</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>201714.2857142857</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>39714285.71428572</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>259.8571428571428</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>25.39772727272727</v>
+      </c>
+      <c r="O12" t="n">
+        <v>184.7506313131313</v>
+      </c>
+      <c r="P12" t="n">
+        <v>75.6689393939394</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>55018.56060606059</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10676887.62626263</v>
+      </c>
+      <c r="S12" t="n">
+        <v>79.94747474747476</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.175252525252525</v>
+      </c>
+      <c r="U12" t="n">
+        <v>25.15873015873016</v>
+      </c>
+      <c r="V12" t="n">
+        <v>181.3019841269841</v>
+      </c>
+      <c r="W12" t="n">
+        <v>76.50277777777777</v>
+      </c>
+      <c r="X12" t="n">
+        <v>50875.39682539682</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12035277.77777778</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>79.69682539682539</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.181349206349206</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>23.49236111111111</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>180.8153273809524</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>71.47051091269842</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>44748.93353174604</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6485675.843253968</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>78.99265873015872</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.066021825396826</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.40237913347157</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>179.0861981156099</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>75.30514630094463</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>49227.02414299053</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>9631943.080262406</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>78.59142444856731</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.196175439872919</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>25.25238095238095</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>178.1095238095238</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>252.8571428571429</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>201714.2857142857</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>39714285.71428572</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>259.8571428571428</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>24.80555555555555</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>176.8888888888889</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>127.8333333333333</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>89333.33333333333</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>20083333.33333333</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>133</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>25.640625</v>
+      </c>
+      <c r="O13" t="n">
+        <v>182.5798611111111</v>
+      </c>
+      <c r="P13" t="n">
+        <v>78.73680555555555</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>72866.31944444444</v>
+      </c>
+      <c r="R13" t="n">
+        <v>19919548.61111111</v>
+      </c>
+      <c r="S13" t="n">
+        <v>81.00243055555556</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.461111111111111</v>
+      </c>
+      <c r="U13" t="n">
+        <v>27.425</v>
+      </c>
+      <c r="V13" t="n">
+        <v>184.55</v>
+      </c>
+      <c r="W13" t="n">
+        <v>76.91250000000001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>68487.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11103750</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>78.375</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>27.98856639146887</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>183.1945820433436</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>74.40106639146887</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60974.00240798073</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8100898.047815617</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>76.11048331613347</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.013157894736842</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26.79289596273292</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>182.6919966356108</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>74.82175207039339</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>63725.73757763975</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>7587736.154244306</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>77.42443064182194</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.233630952380953</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>25.63888888888889</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>186.9166666666667</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>227.8333333333333</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>180666.6666666667</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>35816666.66666666</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>236</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>188.9166666666667</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>138</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>125333.3333333333</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>138.1666666666667</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>28.13020833333334</v>
+      </c>
+      <c r="O14" t="n">
+        <v>182.5364583333333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>79.64409722222223</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>86763.88888888889</v>
+      </c>
+      <c r="R14" t="n">
+        <v>20879340.27777778</v>
+      </c>
+      <c r="S14" t="n">
+        <v>80.71354166666666</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.326388888888889</v>
+      </c>
+      <c r="U14" t="n">
+        <v>28.52337662337662</v>
+      </c>
+      <c r="V14" t="n">
+        <v>182.4779220779221</v>
+      </c>
+      <c r="W14" t="n">
+        <v>76.6077922077922</v>
+      </c>
+      <c r="X14" t="n">
+        <v>47640.25974025975</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10688376.62337662</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>78.48311688311688</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.520779220779221</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>28.90150122549019</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.109170751634</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>77.64721200980392</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>76929.63643790848</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>14808389.50163399</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>79.45179738562092</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.959814133986928</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>27.02814321095571</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>183.6602564102564</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>74.45355963480964</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40378.30953768454</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>7221800.043706294</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>77.30719211344211</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.281213578088578</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>79</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>84000</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>81</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>23.42380952380952</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>187.147619047619</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>323.7142857142857</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>183000</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>34642857.14285714</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>353.5714285714286</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0d4cBEPP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>26.73611111111111</v>
+      </c>
+      <c r="O15" t="n">
+        <v>183.599537037037</v>
+      </c>
+      <c r="P15" t="n">
+        <v>77.35879629629629</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>56687.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14085416.66666667</v>
+      </c>
+      <c r="S15" t="n">
+        <v>80.57870370370371</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.550925925925926</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.50396825396825</v>
+      </c>
+      <c r="V15" t="n">
+        <v>181.8531746031746</v>
+      </c>
+      <c r="W15" t="n">
+        <v>73.96626984126985</v>
+      </c>
+      <c r="X15" t="n">
+        <v>49654.7619047619</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7345882.936507936</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>77.36309523809526</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.402777777777777</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>27.96369949494949</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>180.0489898989899</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>76.0431186868687</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>56238.19444444444</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10685508.20707071</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>78.0341856060606</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.429387626262626</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>27.06726279826125</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>180.8184660068174</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>72.30929613472183</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>43465.91514995153</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>4362945.114848172</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>75.3728506035588</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.156103214810645</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>24.3452380952381</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>189.8380952380952</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>232.2857142857143</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>153714.2857142857</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>25028571.42857143</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>248.1428571428571</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>23.67857142857143</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>186.3928571428571</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>155.4285714285714</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>65428.57142857143</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>9928571.428571429</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>167.8571428571429</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>25.22853535353535</v>
+      </c>
+      <c r="O16" t="n">
+        <v>183.7125</v>
+      </c>
+      <c r="P16" t="n">
+        <v>75.40858585858587</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>61800.25252525252</v>
+      </c>
+      <c r="R16" t="n">
+        <v>10998939.39393939</v>
+      </c>
+      <c r="S16" t="n">
+        <v>80.57196969696969</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.532323232323232</v>
+      </c>
+      <c r="U16" t="n">
+        <v>26.30972222222222</v>
+      </c>
+      <c r="V16" t="n">
+        <v>181.0006313131313</v>
+      </c>
+      <c r="W16" t="n">
+        <v>83.85643939393938</v>
+      </c>
+      <c r="X16" t="n">
+        <v>182582.702020202</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>59063446.96969697</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>86.04835858585859</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.249621212121212</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>23.78976294035921</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>180.0453202519566</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>74.81888977558987</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>60864.90599100052</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11079258.24892314</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>81.27837714891449</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.36288203925735</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>26.29773107117341</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>179.4583243140373</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>79.72354153199741</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>134198.8754763039</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>37598287.83107372</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>83.06274506259993</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.54464535561188</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>33.625</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>179.0138888888889</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>183</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>226500</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>47800000</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>185</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>25.88095238095238</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>176.6714285714285</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>242</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>460857.1428571428</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>110142857.1428571</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>256.7142857142857</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>26.75555555555556</v>
+      </c>
+      <c r="O17" t="n">
+        <v>184.2652777777778</v>
+      </c>
+      <c r="P17" t="n">
+        <v>83.74621212121212</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>129702.5252525253</v>
+      </c>
+      <c r="R17" t="n">
+        <v>49727146.46464646</v>
+      </c>
+      <c r="S17" t="n">
+        <v>85.60441919191919</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.092929292929293</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25.98863636363636</v>
+      </c>
+      <c r="V17" t="n">
+        <v>183.9292929292929</v>
+      </c>
+      <c r="W17" t="n">
+        <v>79.39141414141415</v>
+      </c>
+      <c r="X17" t="n">
+        <v>102954.5454545455</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>25152462.12121212</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>82.09722222222221</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.248737373737374</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.69125258799171</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>183.1223084886128</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>80.32732919254659</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>101643.2712215321</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>34020248.44720497</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>83.25231625258799</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.350854037267081</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24.33668564940018</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>181.721994508876</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>76.50770956851119</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>83778.26986252688</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>18314876.63390195</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>81.11308161708619</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.620041410963179</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>162.8333333333333</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>178833.3333333333</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>77333333.33333333</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>172.8333333333333</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>26.73809523809524</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>186.3690476190476</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>249.2857142857143</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>307714.2857142857</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>64532142.85714286</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>254.7142857142857</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.571428571428571</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KK9ggF3s</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>26.41150793650794</v>
+      </c>
+      <c r="O18" t="n">
+        <v>183.2718253968254</v>
+      </c>
+      <c r="P18" t="n">
+        <v>80.48968253968255</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>100907.5396825397</v>
+      </c>
+      <c r="R18" t="n">
+        <v>31575744.04761905</v>
+      </c>
+      <c r="S18" t="n">
+        <v>83.36428571428571</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.477380952380952</v>
+      </c>
+      <c r="U18" t="n">
+        <v>26.56944444444444</v>
+      </c>
+      <c r="V18" t="n">
+        <v>180.9145833333333</v>
+      </c>
+      <c r="W18" t="n">
+        <v>75.66076388888889</v>
+      </c>
+      <c r="X18" t="n">
+        <v>43272.91666666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7922456.597222222</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>78.18923611111111</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.390972222222222</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>26.96454326923077</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.5098958333333</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>77.77227564102564</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>85283.77403846153</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>19928477.56410257</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>81.41915064102565</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.005689102564102</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>27.34212062017789</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>179.859547766475</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>74.27629736104969</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>45456.65020394123</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>6293900.575581109</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>76.60177711435452</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.289796181630547</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>243.7142857142857</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>238142.8571428571</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>254.7142857142857</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>25.01666666666667</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>188.2142857142857</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>222.8571428571429</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>111285.7142857143</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12085714.28571429</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>235</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hY71igYg</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="O19" t="n">
+        <v>182.984126984127</v>
+      </c>
+      <c r="P19" t="n">
+        <v>76.96825396825398</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>57857.14285714286</v>
+      </c>
+      <c r="R19" t="n">
+        <v>11515873.01587302</v>
+      </c>
+      <c r="S19" t="n">
+        <v>78.77777777777779</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.48011363636364</v>
+      </c>
+      <c r="V19" t="n">
+        <v>186.4670454545455</v>
+      </c>
+      <c r="W19" t="n">
+        <v>80.39829545454546</v>
+      </c>
+      <c r="X19" t="n">
+        <v>109334.0909090909</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>27182436.07954545</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>82.03721590909092</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.493465909090909</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.7429945054945</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>183.0249542124542</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>76.27559523809524</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>56319.23076923077</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10169473.44322344</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>78.7135531135531</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.154990842490843</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>26.91477162435947</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>183.3401283120904</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>77.57015412026055</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>90526.50817105152</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>18620941.86313879</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>80.07498062223294</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.872856146046936</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>188</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>155.3333333333333</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>121666.6666666667</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>158.8333333333333</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>26.15714285714285</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>188.3095238095238</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>300.1428571428572</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>338857.1428571428</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>75303571.42857143</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>313.7142857142857</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.428571428571429</v>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>25.53333333333333</v>
+      </c>
+      <c r="O20" t="n">
+        <v>184.3746031746032</v>
+      </c>
+      <c r="P20" t="n">
+        <v>82.28571428571429</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>111242.8571428571</v>
+      </c>
+      <c r="R20" t="n">
+        <v>39731746.03174603</v>
+      </c>
+      <c r="S20" t="n">
+        <v>84.66666666666667</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.774603174603175</v>
+      </c>
+      <c r="U20" t="n">
+        <v>25.50923520923521</v>
+      </c>
+      <c r="V20" t="n">
+        <v>183.3471861471862</v>
+      </c>
+      <c r="W20" t="n">
+        <v>74.31370851370851</v>
+      </c>
+      <c r="X20" t="n">
+        <v>45057.43145743146</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6297258.297258297</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>78.16017316017314</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.086291486291486</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>24.91319085326438</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>184.232032428356</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>78.51692388493859</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>80183.67539323423</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>23582834.24908425</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>82.40228533721179</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.954510073260074</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>26.82546281670563</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>180.3547166234915</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>72.50265685221459</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>43119.46357490363</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>3980986.763126303</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>74.97555759145764</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.033645036962153</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>24.83333333333334</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>183.2857142857143</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>170.1428571428571</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>233857.1428571429</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>62071428.57142857</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>178.2857142857143</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>27.57142857142857</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>182.0714285714286</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>191.4285714285714</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>76000</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>6371428.571428572</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>195.1428571428571</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CEnSxfJ0</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45606.5625</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">emirates stadium
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>60704</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E21" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+      <c r="H21" t="n">
         <v>48</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I21" t="n">
         <v>481</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K21" t="n">
         <v>20242025</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="O11" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>499</v>
-      </c>
-      <c r="R11" t="n">
-        <v>890000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>376500000</v>
-      </c>
-      <c r="T11" t="n">
-        <v>511</v>
-      </c>
-      <c r="U11" t="n">
-        <v>18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>180</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>327</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>393000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>156500000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>344</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25.86309523809524</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>182.1289682539683</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>82.875</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>145005.9523809524</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>50479166.66666667</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>85.07539682539682</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>3.202380952380952</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>26.74920634920635</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>184.2888888888889</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>83.72424242424242</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>129260.0288600289</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>49481024.53102452</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>85.59076479076478</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>3.091919191919192</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>24.67349005875894</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>179.0317865105908</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>77.64668433206762</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>109956.3154332319</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>28821678.67411003</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>83.23012663347332</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.359708321807864</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>25.69000295770482</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>183.1112097012718</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>80.55980479148181</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>103313.7385388938</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>34930283.93966282</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>83.43836143152915</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.379547471162378</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
+      <c r="N21" t="n">
+        <v>23.27777777777778</v>
+      </c>
+      <c r="O21" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>79.58055555555555</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>95576.38888888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v>31420833.33333334</v>
+      </c>
+      <c r="S21" t="n">
+        <v>84.06666666666666</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.780555555555556</v>
+      </c>
+      <c r="U21" t="n">
+        <v>25.88020833333333</v>
+      </c>
+      <c r="V21" t="n">
+        <v>182.1545138888889</v>
+      </c>
+      <c r="W21" t="n">
+        <v>82.96006944444444</v>
+      </c>
+      <c r="X21" t="n">
+        <v>145560.7638888889</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>50426215.27777778</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>85.07986111111111</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.204861111111111</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>24.03177451203767</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>181.0842309371915</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>79.17442137540822</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>103633.4187742083</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>28186748.14403433</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>83.60522186147186</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.922791353383458</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>24.51693538036144</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>178.948865828346</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>77.23032247476971</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>107047.3023198674</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>27734758.31353048</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>83.18162396218389</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.314744781581881</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>21.57142857142857</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>182.3095238095238</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>168.7142857142857</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>110285.7142857143</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>22857142.85714286</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>191.1428571428571</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>26.03095238095238</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>182.0595238095238</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>398.5714285714286</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>685142.8571428572</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>228985714.2857143</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>403.8571428571428</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>12.42857142857143</v>
+      </c>
+      <c r="BF21" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled.xlsx
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.39583333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52305</v>
+        <v>17250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>26.8</v>
+        <v>25.26262626262626</v>
       </c>
       <c r="O2" t="n">
-        <v>184.4</v>
+        <v>184.2227833894501</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>75.50370370370371</v>
       </c>
       <c r="Q2" t="n">
-        <v>388</v>
+        <v>54390.23569023568</v>
       </c>
       <c r="R2" t="n">
-        <v>450000</v>
+        <v>10603950.61728395</v>
       </c>
       <c r="S2" t="n">
-        <v>73600000</v>
+        <v>79.97351290684624</v>
       </c>
       <c r="T2" t="n">
-        <v>405</v>
+        <v>1.18608305274972</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>25.21269841269841</v>
       </c>
       <c r="V2" t="n">
-        <v>25.66666666666667</v>
+        <v>181.3146825396825</v>
       </c>
       <c r="W2" t="n">
-        <v>182</v>
+        <v>76.35992063492063</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>50083.33333333334</v>
       </c>
       <c r="Y2" t="n">
-        <v>246</v>
+        <v>11727500</v>
       </c>
       <c r="Z2" t="n">
-        <v>435000</v>
+        <v>79.55555555555556</v>
       </c>
       <c r="AA2" t="n">
-        <v>156500000</v>
+        <v>1.163888888888889</v>
       </c>
       <c r="AB2" t="n">
-        <v>250</v>
+        <v>23.77833008447043</v>
       </c>
       <c r="AC2" t="n">
-        <v>7</v>
+        <v>180.3862039357653</v>
       </c>
       <c r="AD2" t="n">
-        <v>27.36761363636364</v>
+        <v>71.64597721154739</v>
       </c>
       <c r="AE2" t="n">
-        <v>186.2545454545455</v>
+        <v>46168.05787617192</v>
       </c>
       <c r="AF2" t="n">
-        <v>80.36079545454545</v>
+        <v>6715149.157616262</v>
       </c>
       <c r="AG2" t="n">
-        <v>108559.0909090909</v>
+        <v>78.82726260094681</v>
       </c>
       <c r="AH2" t="n">
-        <v>27176186.07954545</v>
+        <v>1.07005708716235</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.14971590909092</v>
+        <v>25.54296870263257</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.493465909090909</v>
+        <v>179.3276947142494</v>
       </c>
       <c r="AK2" t="n">
-        <v>25.834375</v>
+        <v>75.49902385196502</v>
       </c>
       <c r="AL2" t="n">
-        <v>181.8572916666667</v>
+        <v>50716.82006135787</v>
       </c>
       <c r="AM2" t="n">
-        <v>82.37951388888888</v>
+        <v>9924006.572325898</v>
       </c>
       <c r="AN2" t="n">
-        <v>140580.2083333333</v>
+        <v>78.41115233972378</v>
       </c>
       <c r="AO2" t="n">
-        <v>46712604.16666667</v>
+        <v>1.280075666630289</v>
       </c>
       <c r="AP2" t="n">
-        <v>84.76736111111111</v>
+        <v>25.25238095238095</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.099305555555556</v>
+        <v>178.1095238095238</v>
       </c>
       <c r="AR2" t="n">
-        <v>26.80668338906536</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="AS2" t="n">
-        <v>184.1026283120904</v>
+        <v>252.8571428571429</v>
       </c>
       <c r="AT2" t="n">
-        <v>77.67236000261349</v>
+        <v>201714.2857142857</v>
       </c>
       <c r="AU2" t="n">
-        <v>91283.86111222798</v>
+        <v>39714285.71428572</v>
       </c>
       <c r="AV2" t="n">
-        <v>19452403.26019762</v>
+        <v>259.8571428571428</v>
       </c>
       <c r="AW2" t="n">
-        <v>80.34998062223295</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.922120851929288</v>
+        <v>24.47222222222222</v>
       </c>
       <c r="AY2" t="n">
-        <v>24.50010845728452</v>
+        <v>176.5555555555555</v>
       </c>
       <c r="AZ2" t="n">
-        <v>179.4483850591152</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>77.29186093630815</v>
+        <v>152.6666666666667</v>
       </c>
       <c r="BB2" t="n">
-        <v>108639.1292429443</v>
+        <v>103333.3333333333</v>
       </c>
       <c r="BC2" t="n">
-        <v>28862739.08276125</v>
+        <v>22666666.66666667</v>
       </c>
       <c r="BD2" t="n">
-        <v>83.32441242372235</v>
+        <v>160.6666666666667</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.360417858504958</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">salisbury m 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11307</v>
+        <v>25486</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +980,180 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25.4</v>
+        <v>25.63240740740741</v>
       </c>
       <c r="O3" t="n">
-        <v>182.2</v>
+        <v>183.029012345679</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>78.66604938271605</v>
       </c>
       <c r="Q3" t="n">
-        <v>384</v>
+        <v>73000</v>
       </c>
       <c r="R3" t="n">
-        <v>276000</v>
+        <v>19655555.55555556</v>
       </c>
       <c r="S3" t="n">
-        <v>58000000</v>
+        <v>80.87530864197531</v>
       </c>
       <c r="T3" t="n">
-        <v>399</v>
+        <v>1.430246913580247</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>27.5</v>
       </c>
       <c r="V3" t="n">
-        <v>25.71428571428572</v>
+        <v>184.675</v>
       </c>
       <c r="W3" t="n">
-        <v>179</v>
+        <v>76.95000000000002</v>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>69000</v>
       </c>
       <c r="Y3" t="n">
-        <v>569</v>
+        <v>11218750</v>
       </c>
       <c r="Z3" t="n">
-        <v>1013000</v>
+        <v>78.41249999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>252000000</v>
+        <v>1.5375</v>
       </c>
       <c r="AB3" t="n">
-        <v>593</v>
+        <v>28.18613308871307</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>182.5327501760938</v>
       </c>
       <c r="AD3" t="n">
-        <v>25.14814814814815</v>
+        <v>74.45861986119985</v>
       </c>
       <c r="AE3" t="n">
-        <v>181.3337962962963</v>
+        <v>60618.68997111516</v>
       </c>
       <c r="AF3" t="n">
-        <v>76.41990740740739</v>
+        <v>7973774.455201183</v>
       </c>
       <c r="AG3" t="n">
-        <v>50447.22222222223</v>
+        <v>76.11355130746256</v>
       </c>
       <c r="AH3" t="n">
-        <v>11883750</v>
+        <v>1.035505430242272</v>
       </c>
       <c r="AI3" t="n">
-        <v>79.66481481481482</v>
+        <v>26.66246118012423</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.174537037037037</v>
+        <v>182.420257505176</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.1695707070707</v>
+        <v>74.80544772256729</v>
       </c>
       <c r="AL3" t="n">
-        <v>180.9412878787879</v>
+        <v>63578.99844720497</v>
       </c>
       <c r="AM3" t="n">
-        <v>83.13421717171717</v>
+        <v>7593170.936853002</v>
       </c>
       <c r="AN3" t="n">
-        <v>174448.8636363636</v>
+        <v>77.52225672877847</v>
       </c>
       <c r="AO3" t="n">
-        <v>55896717.17171717</v>
+        <v>1.206457039337474</v>
       </c>
       <c r="AP3" t="n">
-        <v>85.67335858585859</v>
+        <v>25.77619047619048</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.125883838383838</v>
+        <v>186.3571428571429</v>
       </c>
       <c r="AR3" t="n">
-        <v>25.47870158164276</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="AS3" t="n">
-        <v>179.1561200237671</v>
+        <v>250.5714285714286</v>
       </c>
       <c r="AT3" t="n">
-        <v>75.43933735110205</v>
+        <v>203428.5714285714</v>
       </c>
       <c r="AU3" t="n">
-        <v>50098.19483348895</v>
+        <v>42857142.85714286</v>
       </c>
       <c r="AV3" t="n">
-        <v>9861341.001046883</v>
+        <v>259.5714285714286</v>
       </c>
       <c r="AW3" t="n">
-        <v>78.55110630110632</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.219612087259146</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AY3" t="n">
-        <v>26.12009949222604</v>
+        <v>188.5714285714286</v>
       </c>
       <c r="AZ3" t="n">
-        <v>179.3727979982479</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="BA3" t="n">
-        <v>79.94722574252373</v>
+        <v>139.5714285714286</v>
       </c>
       <c r="BB3" t="n">
-        <v>139244.9281078828</v>
+        <v>125857.1428571429</v>
       </c>
       <c r="BC3" t="n">
-        <v>41092037.83107372</v>
+        <v>12342857.14285714</v>
       </c>
       <c r="BD3" t="n">
-        <v>83.48379769417888</v>
+        <v>139.7142857142857</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.643329566138196</v>
+        <v>2</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29673</v>
+        <v>62500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,180 +1179,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>26.85714285714286</v>
+        <v>28.13888888888889</v>
       </c>
       <c r="O4" t="n">
-        <v>181.1428571428571</v>
+        <v>182.4583333333333</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>79.52083333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>513</v>
+        <v>85559.02777777778</v>
       </c>
       <c r="R4" t="n">
-        <v>258000</v>
+        <v>20523958.33333334</v>
       </c>
       <c r="S4" t="n">
-        <v>33500000</v>
+        <v>80.671875</v>
       </c>
       <c r="T4" t="n">
-        <v>530</v>
+        <v>2.302083333333333</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>28.65324675324675</v>
       </c>
       <c r="V4" t="n">
-        <v>23.75</v>
+        <v>182.4792207792208</v>
       </c>
       <c r="W4" t="n">
-        <v>184</v>
+        <v>76.6974025974026</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>47793.50649350649</v>
       </c>
       <c r="Y4" t="n">
-        <v>285</v>
+        <v>10800487.01298701</v>
       </c>
       <c r="Z4" t="n">
-        <v>129000</v>
+        <v>78.5038961038961</v>
       </c>
       <c r="AA4" t="n">
-        <v>17700000</v>
+        <v>1.541558441558441</v>
       </c>
       <c r="AB4" t="n">
-        <v>303</v>
+        <v>28.99039011437908</v>
       </c>
       <c r="AC4" t="n">
-        <v>4</v>
+        <v>180.6050040849674</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.53350168350168</v>
+        <v>77.31526756535948</v>
       </c>
       <c r="AE4" t="n">
-        <v>183.4050505050505</v>
+        <v>76987.96977124183</v>
       </c>
       <c r="AF4" t="n">
-        <v>74.29023569023569</v>
+        <v>14090333.94607843</v>
       </c>
       <c r="AG4" t="n">
-        <v>44976.09427609426</v>
+        <v>79.13929738562091</v>
       </c>
       <c r="AH4" t="n">
-        <v>6281649.831649832</v>
+        <v>1.923703022875817</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.14141414141413</v>
+        <v>26.82284018065268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.085521885521886</v>
+        <v>183.7814685314685</v>
       </c>
       <c r="AK4" t="n">
-        <v>26.66319444444444</v>
+        <v>74.5141656954157</v>
       </c>
       <c r="AL4" t="n">
-        <v>180.7774305555556</v>
+        <v>40244.9762043512</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.31874999999999</v>
+        <v>7837394.740675991</v>
       </c>
       <c r="AN4" t="n">
-        <v>42741.66666666667</v>
+        <v>77.49128302253303</v>
       </c>
       <c r="AO4" t="n">
-        <v>7564774.305555555</v>
+        <v>1.244092365967366</v>
       </c>
       <c r="AP4" t="n">
-        <v>77.80381944444444</v>
+        <v>25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.351041666666667</v>
+        <v>182.8333333333333</v>
       </c>
       <c r="AR4" t="n">
-        <v>26.93923042901371</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AS4" t="n">
-        <v>180.4138360607401</v>
+        <v>108</v>
       </c>
       <c r="AT4" t="n">
-        <v>72.61024251805986</v>
+        <v>124666.6666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>43020.32655167329</v>
+        <v>43500000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3945675.033171163</v>
+        <v>111.3333333333333</v>
       </c>
       <c r="AW4" t="n">
-        <v>74.99529338051011</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.02734778121775</v>
+        <v>23.44761904761905</v>
       </c>
       <c r="AY4" t="n">
-        <v>27.30773066802478</v>
+        <v>186.7190476190476</v>
       </c>
       <c r="AZ4" t="n">
-        <v>180.300038197097</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="BA4" t="n">
-        <v>74.13185956200662</v>
+        <v>333.2857142857143</v>
       </c>
       <c r="BB4" t="n">
-        <v>45643.55211781683</v>
+        <v>189857.1428571429</v>
       </c>
       <c r="BC4" t="n">
-        <v>6210168.518164841</v>
+        <v>32100000</v>
       </c>
       <c r="BD4" t="n">
-        <v>76.61104744928275</v>
+        <v>364.5714285714286</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.286207664884136</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">bramall t 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61276</v>
+        <v>31750</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1378,180 +1378,180 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26.33333333333333</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="O5" t="n">
-        <v>179.6666666666667</v>
+        <v>183.6875</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>77.52083333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>252</v>
+        <v>57125</v>
       </c>
       <c r="R5" t="n">
-        <v>346000</v>
+        <v>14335416.66666667</v>
       </c>
       <c r="S5" t="n">
-        <v>144500000</v>
+        <v>80.66666666666667</v>
       </c>
       <c r="T5" t="n">
-        <v>260</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>26.57986111111111</v>
       </c>
       <c r="V5" t="n">
-        <v>32</v>
+        <v>181.1631944444444</v>
       </c>
       <c r="W5" t="n">
-        <v>185</v>
+        <v>74.07291666666666</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>49012.15277777777</v>
       </c>
       <c r="Y5" t="n">
-        <v>316</v>
+        <v>7474175.347222222</v>
       </c>
       <c r="Z5" t="n">
-        <v>408000</v>
+        <v>77.28298611111111</v>
       </c>
       <c r="AA5" t="n">
-        <v>79300000</v>
+        <v>1.397569444444444</v>
       </c>
       <c r="AB5" t="n">
-        <v>316</v>
+        <v>27.90972222222222</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>180.0527777777778</v>
       </c>
       <c r="AD5" t="n">
-        <v>26.44532828282828</v>
+        <v>75.82626262626263</v>
       </c>
       <c r="AE5" t="n">
-        <v>184.2516414141414</v>
+        <v>55752.39898989898</v>
       </c>
       <c r="AF5" t="n">
-        <v>82.90871212121212</v>
+        <v>10369883.20707071</v>
       </c>
       <c r="AG5" t="n">
-        <v>122594.5707070707</v>
+        <v>77.96032196969696</v>
       </c>
       <c r="AH5" t="n">
-        <v>45828623.73737374</v>
+        <v>1.488099747474747</v>
       </c>
       <c r="AI5" t="n">
-        <v>85.13510101010101</v>
+        <v>26.97359634355248</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.911111111111111</v>
+        <v>181.7091883749779</v>
       </c>
       <c r="AK5" t="n">
-        <v>24.74416035353535</v>
+        <v>72.25032931655738</v>
       </c>
       <c r="AL5" t="n">
-        <v>183.471875</v>
+        <v>43950.09451237522</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.16483585858586</v>
+        <v>4318774.606444563</v>
       </c>
       <c r="AN5" t="n">
-        <v>59134.62752525252</v>
+        <v>75.28508107389686</v>
       </c>
       <c r="AO5" t="n">
-        <v>10254251.89393939</v>
+        <v>1.144613532990726</v>
       </c>
       <c r="AP5" t="n">
-        <v>80.6875946969697</v>
+        <v>24.45238095238096</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.432323232323232</v>
+        <v>189.1952380952381</v>
       </c>
       <c r="AR5" t="n">
-        <v>25.68969979296066</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="AS5" t="n">
-        <v>183.191149068323</v>
+        <v>253.4285714285714</v>
       </c>
       <c r="AT5" t="n">
-        <v>80.30507246376811</v>
+        <v>168714.2857142857</v>
       </c>
       <c r="AU5" t="n">
-        <v>103678.7267080745</v>
+        <v>27571428.57142857</v>
       </c>
       <c r="AV5" t="n">
-        <v>35350605.59006211</v>
+        <v>270.5714285714286</v>
       </c>
       <c r="AW5" t="n">
-        <v>83.47798913043478</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.425905797101449</v>
+        <v>23.85714285714286</v>
       </c>
       <c r="AY5" t="n">
-        <v>23.8959882368019</v>
+        <v>185.2857142857143</v>
       </c>
       <c r="AZ5" t="n">
-        <v>180.4808439673716</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="BA5" t="n">
-        <v>74.8290182340879</v>
+        <v>176.1428571428571</v>
       </c>
       <c r="BB5" t="n">
-        <v>61243.85856017048</v>
+        <v>77000</v>
       </c>
       <c r="BC5" t="n">
-        <v>11087608.05129468</v>
+        <v>10942857.14285714</v>
       </c>
       <c r="BD5" t="n">
-        <v>81.16251746512002</v>
+        <v>189.4285714285714</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.405372157834425</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30404</v>
+        <v>31876</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1577,180 +1577,180 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26.33333333333333</v>
+        <v>24.73925364758698</v>
       </c>
       <c r="O6" t="n">
-        <v>181</v>
+        <v>183.4194444444444</v>
       </c>
       <c r="P6" t="n">
+        <v>75.15763187429853</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>59297.44668911336</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10398223.90572391</v>
+      </c>
+      <c r="S6" t="n">
+        <v>80.67786195286196</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.450953984287318</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26.29214365881032</v>
+      </c>
+      <c r="V6" t="n">
+        <v>180.9579124579125</v>
+      </c>
+      <c r="W6" t="n">
+        <v>83.29102132435466</v>
+      </c>
+      <c r="X6" t="n">
+        <v>175914.1414141414</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>56529405.16273849</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>85.66924803591471</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.132098765432099</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.80296993598078</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>180.4993122847225</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>74.7303691492546</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>60412.84159596853</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10827547.02598743</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>81.15753186442041</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.379938650101189</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>25.84179783924366</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>179.0835127505793</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>79.63685023267067</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>136055.3207112805</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>39337794.31138177</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>83.59243555721883</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2.606036537421986</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>33.39285714285715</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>179.8690476190476</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.571428571428572</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>202</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>252428.5714285714</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>52300000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>203.7142857142857</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.142857142857143</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>26.16666666666666</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>177.3142857142857</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>235</v>
-      </c>
-      <c r="R6" t="n">
-        <v>212000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>240</v>
-      </c>
-      <c r="U6" t="n">
-        <v>6</v>
-      </c>
-      <c r="V6" t="n">
-        <v>23</v>
-      </c>
-      <c r="W6" t="n">
-        <v>177</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>95000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>43500000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>86</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>27.11111111111111</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>182.8148148148148</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>77</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>59129.62962962963</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>11407407.40740741</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>78.64814814814815</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.259259259259259</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>28.21230158730159</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>182.4702380952381</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>79.57738095238095</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>86317.46031746033</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>20568452.38095238</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>80.625</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.309523809523809</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>25.63071581196581</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>182.6541132478633</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>76.26597222222223</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>56052.99145299146</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10308830.12820513</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>78.84636752136753</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.139155982905983</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>28.83187441643324</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>180.8628618113912</v>
-      </c>
       <c r="BA6" t="n">
-        <v>77.73173436041084</v>
+        <v>241.4285714285714</v>
       </c>
       <c r="BB6" t="n">
-        <v>78157.67973856209</v>
+        <v>455142.8571428572</v>
       </c>
       <c r="BC6" t="n">
-        <v>15146095.93837535</v>
+        <v>99285714.28571428</v>
       </c>
       <c r="BD6" t="n">
-        <v>79.44491129785247</v>
+        <v>255.8571428571429</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.969946311858077</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32384</v>
+        <v>61276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1776,180 +1776,180 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24.5</v>
+        <v>26.40594837261504</v>
       </c>
       <c r="O7" t="n">
-        <v>185.25</v>
+        <v>184.3549943883277</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>82.89865319865319</v>
       </c>
       <c r="Q7" t="n">
-        <v>292</v>
+        <v>122488.1032547699</v>
       </c>
       <c r="R7" t="n">
-        <v>143000</v>
+        <v>45989079.68574635</v>
       </c>
       <c r="S7" t="n">
-        <v>19300000</v>
+        <v>85.14029180695849</v>
       </c>
       <c r="T7" t="n">
-        <v>310</v>
+        <v>2.910886644219977</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>25.96464646464646</v>
       </c>
       <c r="V7" t="n">
-        <v>22</v>
+        <v>183.8886644219978</v>
       </c>
       <c r="W7" t="n">
-        <v>186.2</v>
+        <v>79.34792368125702</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>101805.0505050505</v>
       </c>
       <c r="Y7" t="n">
-        <v>365</v>
+        <v>24551279.46127946</v>
       </c>
       <c r="Z7" t="n">
-        <v>206000</v>
+        <v>82.02682379349045</v>
       </c>
       <c r="AA7" t="n">
-        <v>37100000</v>
+        <v>2.199887766554434</v>
       </c>
       <c r="AB7" t="n">
-        <v>403</v>
+        <v>25.68714055670577</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>183.1275822406257</v>
       </c>
       <c r="AD7" t="n">
-        <v>26.44047619047619</v>
+        <v>80.26059351276743</v>
       </c>
       <c r="AE7" t="n">
-        <v>181.25</v>
+        <v>103000.138026225</v>
       </c>
       <c r="AF7" t="n">
-        <v>73.75</v>
+        <v>34765617.6673568</v>
       </c>
       <c r="AG7" t="n">
-        <v>47712.30158730159</v>
+        <v>83.44075224292617</v>
       </c>
       <c r="AH7" t="n">
-        <v>7227628.968253968</v>
+        <v>2.40503795721187</v>
       </c>
       <c r="AI7" t="n">
-        <v>77.11706349206349</v>
+        <v>24.19523129849217</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.375</v>
+        <v>181.4626793295272</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.59545454545454</v>
+        <v>75.78926035719513</v>
       </c>
       <c r="AL7" t="n">
-        <v>182.5424242424242</v>
+        <v>81336.28861074515</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.66363636363637</v>
+        <v>17545478.79153858</v>
       </c>
       <c r="AN7" t="n">
-        <v>47792.42424242425</v>
+        <v>80.85587761674719</v>
       </c>
       <c r="AO7" t="n">
-        <v>10807651.51515151</v>
+        <v>1.661771702532572</v>
       </c>
       <c r="AP7" t="n">
-        <v>78.48787878787878</v>
+        <v>24.01190476190476</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.531818181818182</v>
+        <v>176.3095238095238</v>
       </c>
       <c r="AR7" t="n">
-        <v>27.11873338649654</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="AS7" t="n">
-        <v>181.4540869218501</v>
+        <v>175.5714285714286</v>
       </c>
       <c r="AT7" t="n">
-        <v>72.51599548112706</v>
+        <v>202714.2857142857</v>
       </c>
       <c r="AU7" t="n">
-        <v>44693.85632642212</v>
+        <v>86928571.42857143</v>
       </c>
       <c r="AV7" t="n">
-        <v>4409207.369750133</v>
+        <v>185.2857142857143</v>
       </c>
       <c r="AW7" t="n">
-        <v>75.23477870813397</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.154877724614567</v>
+        <v>27.02380952380953</v>
       </c>
       <c r="AY7" t="n">
-        <v>26.90229353979354</v>
+        <v>186.1190476190476</v>
       </c>
       <c r="AZ7" t="n">
-        <v>183.2740592740593</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BA7" t="n">
-        <v>74.34952269952269</v>
+        <v>214.7142857142857</v>
       </c>
       <c r="BB7" t="n">
-        <v>39575.2109002109</v>
+        <v>262000</v>
       </c>
       <c r="BC7" t="n">
-        <v>7194070.17982018</v>
+        <v>54889285.71428572</v>
       </c>
       <c r="BD7" t="n">
-        <v>77.39003774003774</v>
+        <v>219.7142857142857</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.269438894438894</v>
+        <v>5.571428571428571</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31750</v>
+        <v>75635</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1975,180 +1975,180 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>26.66666666666667</v>
+        <v>26.44722222222222</v>
       </c>
       <c r="O8" t="n">
-        <v>187.5</v>
+        <v>183.4503968253968</v>
       </c>
       <c r="P8" t="n">
+        <v>80.50753968253969</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>101246.8253968254</v>
+      </c>
+      <c r="R8" t="n">
+        <v>31709672.61904762</v>
+      </c>
+      <c r="S8" t="n">
+        <v>83.32857142857142</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.477380952380952</v>
+      </c>
+      <c r="U8" t="n">
+        <v>26.67839506172839</v>
+      </c>
+      <c r="V8" t="n">
+        <v>180.9243827160494</v>
+      </c>
+      <c r="W8" t="n">
+        <v>75.40555555555557</v>
+      </c>
+      <c r="X8" t="n">
+        <v>42937.03703703704</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7636466.049382716</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>77.90339506172839</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.367592592592593</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>26.56967338217338</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.4280423280423</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>77.64420533170534</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>82684.98168498169</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>19843969.14428164</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>81.73368945868947</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.884025234025234</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>27.23432268530308</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>180.4366352601647</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>74.13681634269869</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>45232.17704590254</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>6241555.022682475</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>76.61504871308793</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.293622499504853</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>179.8571428571429</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>243.8571428571429</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>237285.7142857143</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>48285714.28571428</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>255.2857142857143</v>
+      </c>
+      <c r="AW8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>453</v>
-      </c>
-      <c r="R8" t="n">
-        <v>319000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>56300000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>472</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="W8" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>466</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>409000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>111100000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>485</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>183.675</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>77.47499999999999</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>57025</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>14342500</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>80.65000000000001</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>25.58645833333333</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>182.7826388888889</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>78.74930555555557</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>73109.375</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>20079687.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>81.03159722222222</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.452777777777778</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>27.92279942279942</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>180.0083694083694</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>76.06118326118326</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>56379.36507936507</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10701295.09379509</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>78.11049783549784</v>
-      </c>
       <c r="AX8" t="n">
-        <v>1.466919191919192</v>
+        <v>25.11190476190476</v>
       </c>
       <c r="AY8" t="n">
-        <v>28.15582829623077</v>
+        <v>187.7142857142857</v>
       </c>
       <c r="AZ8" t="n">
-        <v>182.7600582338198</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="BA8" t="n">
-        <v>74.59630448670697</v>
+        <v>233.1428571428571</v>
       </c>
       <c r="BB8" t="n">
-        <v>61258.52621750455</v>
+        <v>116571.4285714286</v>
       </c>
       <c r="BC8" t="n">
-        <v>8039469.476387046</v>
+        <v>12471428.57142857</v>
       </c>
       <c r="BD8" t="n">
-        <v>76.18131664946681</v>
+        <v>245.5714285714286</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.039943609022556</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>4fYy95jc</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>62850</v>
+        <v>30404</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2174,180 +2174,180 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24.8</v>
+        <v>27.00952380952381</v>
       </c>
       <c r="O9" t="n">
-        <v>184.4</v>
+        <v>182.8412698412698</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>76.98571428571428</v>
       </c>
       <c r="Q9" t="n">
-        <v>394</v>
+        <v>58639.68253968254</v>
       </c>
       <c r="R9" t="n">
-        <v>449000</v>
+        <v>11456349.20634921</v>
       </c>
       <c r="S9" t="n">
-        <v>138000000</v>
+        <v>78.6984126984127</v>
       </c>
       <c r="T9" t="n">
-        <v>415</v>
+        <v>1.250793650793651</v>
       </c>
       <c r="U9" t="n">
-        <v>12</v>
+        <v>27.30207631874299</v>
       </c>
       <c r="V9" t="n">
-        <v>26.52777777777778</v>
+        <v>186.4731762065095</v>
       </c>
       <c r="W9" t="n">
-        <v>186.1388888888889</v>
+        <v>80.39478114478113</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>108706.8462401796</v>
       </c>
       <c r="Y9" t="n">
-        <v>237.5</v>
+        <v>27446733.30527497</v>
       </c>
       <c r="Z9" t="n">
-        <v>289833.3333333333</v>
+        <v>82.25653759820426</v>
       </c>
       <c r="AA9" t="n">
-        <v>61787500</v>
+        <v>2.500364758698092</v>
       </c>
       <c r="AB9" t="n">
-        <v>243.3333333333333</v>
+        <v>25.73541874791874</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.166666666666667</v>
+        <v>182.8463827838828</v>
       </c>
       <c r="AD9" t="n">
-        <v>25.41746031746032</v>
+        <v>76.22797619047618</v>
       </c>
       <c r="AE9" t="n">
-        <v>184.9793650793651</v>
+        <v>55746.71994671995</v>
       </c>
       <c r="AF9" t="n">
-        <v>82.07301587301586</v>
+        <v>10220555.69430569</v>
       </c>
       <c r="AG9" t="n">
-        <v>108277.7777777778</v>
+        <v>78.69948384948384</v>
       </c>
       <c r="AH9" t="n">
-        <v>38448412.6984127</v>
+        <v>1.13226356976357</v>
       </c>
       <c r="AI9" t="n">
-        <v>84.55079365079366</v>
+        <v>26.64760745694698</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.752380952380952</v>
+        <v>184.1884473885248</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.91477272727273</v>
+        <v>77.72265333565643</v>
       </c>
       <c r="AL9" t="n">
-        <v>183.8520202020202</v>
+        <v>91682.87654420265</v>
       </c>
       <c r="AM9" t="n">
-        <v>79.18686868686869</v>
+        <v>20120365.39795344</v>
       </c>
       <c r="AN9" t="n">
-        <v>100894.3181818182</v>
+        <v>80.47776055309595</v>
       </c>
       <c r="AO9" t="n">
-        <v>24199734.84848485</v>
+        <v>1.951607423937145</v>
       </c>
       <c r="AP9" t="n">
-        <v>81.95063131313131</v>
+        <v>26.97619047619047</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.179419191919192</v>
+        <v>187.1428571428571</v>
       </c>
       <c r="AR9" t="n">
-        <v>25.10646816418875</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>184.1789862098686</v>
+        <v>155.4285714285714</v>
       </c>
       <c r="AT9" t="n">
-        <v>78.89560035552682</v>
+        <v>125857.1428571429</v>
       </c>
       <c r="AU9" t="n">
-        <v>83390.08295625943</v>
+        <v>28071428.57142857</v>
       </c>
       <c r="AV9" t="n">
-        <v>24773669.33311786</v>
+        <v>158.7142857142857</v>
       </c>
       <c r="AW9" t="n">
-        <v>82.4616340767076</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.013858812755871</v>
+        <v>26.58571428571429</v>
       </c>
       <c r="AY9" t="n">
-        <v>24.04776021080369</v>
+        <v>187.4166666666667</v>
       </c>
       <c r="AZ9" t="n">
-        <v>181.2653059123847</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="BA9" t="n">
-        <v>75.43479290184453</v>
+        <v>300.8571428571428</v>
       </c>
       <c r="BB9" t="n">
-        <v>79925.19968708827</v>
+        <v>347142.8571428572</v>
       </c>
       <c r="BC9" t="n">
-        <v>17190616.76548089</v>
+        <v>75446428.57142857</v>
       </c>
       <c r="BD9" t="n">
-        <v>80.75452898550725</v>
+        <v>312.4285714285714</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.62990983201581</v>
+        <v>8.428571428571429</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75635</v>
+        <v>62850</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2373,180 +2373,180 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>26.2</v>
+        <v>25.42083333333333</v>
       </c>
       <c r="O10" t="n">
-        <v>181.2</v>
+        <v>184.9819444444444</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>82.07777777777778</v>
       </c>
       <c r="Q10" t="n">
-        <v>389</v>
+        <v>108618.0555555555</v>
       </c>
       <c r="R10" t="n">
-        <v>389000</v>
+        <v>38503472.22222222</v>
       </c>
       <c r="S10" t="n">
-        <v>75500000</v>
+        <v>84.57916666666668</v>
       </c>
       <c r="T10" t="n">
-        <v>406</v>
+        <v>2.741666666666666</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>25.57157287157287</v>
       </c>
       <c r="V10" t="n">
-        <v>21</v>
+        <v>183.0614718614719</v>
       </c>
       <c r="W10" t="n">
-        <v>185.5</v>
+        <v>74.32020202020202</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>45236.65223665223</v>
       </c>
       <c r="Y10" t="n">
-        <v>144</v>
+        <v>6314271.284271285</v>
       </c>
       <c r="Z10" t="n">
-        <v>135000</v>
+        <v>78.14978354978355</v>
       </c>
       <c r="AA10" t="n">
-        <v>44500000</v>
+        <v>1.087590187590188</v>
       </c>
       <c r="AB10" t="n">
-        <v>166</v>
+        <v>25.23044083730358</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>184.1097161371671</v>
       </c>
       <c r="AD10" t="n">
-        <v>26.54259259259259</v>
+        <v>79.03682994565348</v>
       </c>
       <c r="AE10" t="n">
-        <v>183.3587962962963</v>
+        <v>85692.41941790962</v>
       </c>
       <c r="AF10" t="n">
-        <v>80.21712962962964</v>
+        <v>25359619.65412946</v>
       </c>
       <c r="AG10" t="n">
-        <v>99225.46296296296</v>
+        <v>82.52762535213515</v>
       </c>
       <c r="AH10" t="n">
-        <v>30505034.72222222</v>
+        <v>2.061701660721269</v>
       </c>
       <c r="AI10" t="n">
-        <v>83.09166666666667</v>
+        <v>26.89076893915461</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.452777777777778</v>
+        <v>180.6499547187296</v>
       </c>
       <c r="AK10" t="n">
-        <v>23.47222222222222</v>
+        <v>72.53258882500369</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.5430555555556</v>
+        <v>42541.23228238663</v>
       </c>
       <c r="AM10" t="n">
-        <v>79.51527777777778</v>
+        <v>3879150.028432426</v>
       </c>
       <c r="AN10" t="n">
-        <v>96520.83333333334</v>
+        <v>74.99596575472295</v>
       </c>
       <c r="AO10" t="n">
-        <v>30668750</v>
+        <v>1.0234409553295</v>
       </c>
       <c r="AP10" t="n">
-        <v>83.89583333333333</v>
+        <v>24.14285714285714</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.819444444444445</v>
+        <v>183.4047619047619</v>
       </c>
       <c r="AR10" t="n">
-        <v>26.76588255494505</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="AS10" t="n">
-        <v>183.5690476190476</v>
+        <v>179.4285714285714</v>
       </c>
       <c r="AT10" t="n">
-        <v>77.94973099816849</v>
+        <v>226428.5714285714</v>
       </c>
       <c r="AU10" t="n">
-        <v>84570.6043956044</v>
+        <v>60428571.42857143</v>
       </c>
       <c r="AV10" t="n">
-        <v>20643215.28731685</v>
+        <v>190.2857142857143</v>
       </c>
       <c r="AW10" t="n">
-        <v>81.76290064102565</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.932028388278388</v>
+        <v>27.42857142857143</v>
       </c>
       <c r="AY10" t="n">
-        <v>23.90796498822814</v>
+        <v>182.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>182.2532785562391</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BA10" t="n">
-        <v>78.48870708969393</v>
+        <v>192.4285714285714</v>
       </c>
       <c r="BB10" t="n">
-        <v>98736.99020277969</v>
+        <v>76285.71428571429</v>
       </c>
       <c r="BC10" t="n">
-        <v>27019456.47736766</v>
+        <v>7500000</v>
       </c>
       <c r="BD10" t="n">
-        <v>83.14807900432899</v>
+        <v>196.4285714285714</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.850172305764411</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4fYy95jc</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29589</v>
+        <v>40341</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2572,145 +2572,145 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>28.66666666666667</v>
+        <v>23.43086419753087</v>
       </c>
       <c r="O11" t="n">
-        <v>188.9166666666667</v>
+        <v>183.4604938271605</v>
       </c>
       <c r="